--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Picks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Video Queue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Published" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Research" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Video Queue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Published" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Research'!$A$1:$O$1</definedName>
@@ -63,9 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,8 +434,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -508,6 +528,2603 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Why Anthropic Invited A Hindu Monk To Discuss AI Ethics - NDTV</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYk1NOTlaYlNJY0ZwbTRPVE5TcnhlNlN1cVdXR2hLNmF6TnJmcFE2LU01TVV0X3hLWmJFRkFXWmNnXzUwOVEwbDB1bUw4Q2ZmNDI0WmJfWEgtUU81alB0X1RmMW5kNE9jQ2dleEs0WGdUWHVhR3hTbWZUS0s5REd0OUk2ZFlrUXZ4bFdkTFB1RnNkUlYtUGV5LVNKNDdoc2dUcnFDQVpBMTl1SzlVMFNVaExOQkxZbUNWN290VENsdlVjYnhDdmfSAc4BQVVfeXFMTW1WZldBRVVWM1cxYUxPaWJkQThHM0JZUU9ZcFhwMkNEczhQY3ZrenRidlA5NHI0TjA3U1FnMW12TnlBRFhDTjNVR05GcEVaZ2xPcUFuMldHdG5nV2RWOWZvZHRXUk04OFFDT0IxNFNGQjBzOVllU0RDVmUwVTF4bEUwemxPeWE1bnZpNzRlSUdiS2lVODVWUW5NN0EzS0o1Rm1IaEJwYlNjR21xbV9KSktyTmUtOGdOc1Z2TERBbVVQRk9RQXJha0tJWDczS2c?oc=5</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T02:46:13+00:00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>AI's race to transform the world before the money runs out - Reuters</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNV2NqbWtDbjVfc2dZYWtJWEp3ZnI5M1o5UWhkQndYZV83T3BxTE1VeDFNclNIeUZCMnV2a1NIVXc2enlzV3lFWktoWE11NUF0RlNjTGk1c1RTSEVsUEtGUU9HZlVuRVVhQ2ZFZTU2UHBoRVozX3pJeS1vRmtoM0w5dndmWnJ2YjQxYi03TDl4X3ZQNlhWdXBfQnRsRjByYllpaXF3VlEzWVdrS28?oc=5</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T05:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI’s Dot agent is enterprise software that can also order your dinner - The Verge</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>The Verge</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNVjFaRDdLNlhKLWVUZDRmQU5GeW5WdUpLWFVVMm5oREFlaXBEcEQyUHBqRTlBSXdiWk1hUWlPaDB5bWpZbWRSdy1Pd3NkRkxkRzM0V1VoaE1IbkdPZWZtU1RqS1B4TVRwVGhrTnczSmhtVmhKcURGc1BadS1wT1h6ZThsZlRKTmdrbjV1RDBQd0hiSHZwNkkyN2lR?oc=5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T18:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI fires workers for 'mishandling sensitive information' - BBC</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>BBC</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9mdmxTeGdPLUpjZUg2UXlsNWRXTTJ5MW10aXZEVEh6QXM2NXBhVDhCZk5tNWJlaUZ3REtNeEpHMFdxMWNwRGpqbE5MUkZ2NXRubndLYkRHSkM0NEk?oc=5</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T08:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI safety leader David Robinson resigns as the team's upheaval mounts - Business Insider</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Business Insider</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPN20tZjFiX1d5WEdVanJFQWoxNEdpalhTNzJPb3Rlc0tPOERjVW00cS01YkxudVI1LXNHQnBhVUJ2aDhSdFJKTm96eF9wZ2JVVDF0N2NibE9oRFdhQUg1ZEIxejNsUV9kalRvR1ZRaFg1UThCN1p2YVFxNjlxa0dZRWpTdGVONkYyZnNmTWJpc2c3UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T23:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI says three staffers fired for mishandling 'sensitive' info - The Hindu</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQMXF4dTVYbEpDZHJLSW9ObjZMM0J5ejRFV3loaFZvNnVzU09WOXBJTFNROE5yY1J3TlRrSFVWSS1qN1hSLWptUlRDUWlFRHNoZHgyeExzbllLN2k4RDA5c0VzS01uWWpZSWxKTU5GaDlhUXJWYnM4aGlYaTU3ZWVOT0hVVVVmTDZJREQ3d0hmcTlrWDJlTV96YTk0ZFpUaU5OTjEyeXRCbDV4cm9ETDJZTkxHeWpHVkVJTE9kVHV4N0FZaFQ1UFZF0gHOAUFVX3lxTE1DMXAxelFpLU9IMDl0eHVJWEI1eTRZNUthTndjSU1ScWFHWXBCWjVtRDhYVFJRbFZ1TDhoNW5xWmROVm1xazdRSG9uMkVrV09oWS1ldFdLdU1Gd0tIZE1wOXg2NERDbXZodzlvd1hBZExDMHRzWWE3dThpOVBBLVFXNUJEMC1ITnpSNFNRcEhrZUFGZGNRQnhWX2V2RURqY0NtcVlYRnZ5ajlEQlhLcW5YamkxV1BEbFlOTVZGeEZyY3FtX1JsVUIxdG16d1lR?oc=5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T03:59:22+00:00</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI alerts more than 100 groups about rogue AI agent activity - The Hindu</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNU1htcWZRWmM1M29LVmctdlFBMlBFSWhlNHRGZzdpRFZvaV9BUUdaMDVxNDhReEtVOVh2UlFwakZuX2Z5eVRwNGt1MEZOTlpLZ1BhWFpqeV9oWDQ0aWNVOVRoWGtLUTlJYzdwSmxlRW5yVWNwdld3UEY4SUV5aWNlZlVDVjB1MURMTG81Yl9lcGk1UHNkX0xJZ21iallpUW43VXktR1k4ZlRqRTNIUGRka0RZWGFmRVFwaElZRWw5am1tb19mbFlLR9IBzwFBVV95cUxNcTBFY2dyR3RKM0NTZUN0TUJxUDlzLW1zR3hvckF5ekhLM05hT2dFY2F2TVZlZXgzVWkyTG02LWNwQUEteHAtLUdsUEhpMnBVLTVCSXQzcDBQaFA5cTNxNW9RQ0pKS2RReDM0ellSNnQwRHpKUWVxaXBOcF9iSkw2YXlXM1QyWGwxZno4Rlp1Ti1fUjhqNFpSa3pnVTJhSnNzaWw1b3lmbzYwU21ELU9GMEdnN091YWRCdXlZWkl4SEVZOWFObnFybGltS2dlYm8?oc=5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T05:00:11+00:00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Can Google's new model really catch up to OpenAI and Anthropic at the frontier? - CNBC</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQY0EwdFVqRF81X3lORF9KSk9IWTYwSzJxclg4U1BMZmg1NkpzM1NyajBQWUV0ZWk0NXo5Y19SUl9wYWNycFJGYWs3bjA2d05lcmdMMU1yOVktbEQ1WDljNW4yRS1OS3RmdDczTzFPcTZDcHdWcjRFNndiNFR5UWNZZHE1b1QxRXVLenlRdU1ZcW8yRnPSAZgBQVVfeXFMTm12SHI4M2FuUlNia1hWdmZhc0pjMzhfajROeGEwU0V1RkZ3NWhPYURHQWg2YlFUUVVadkFVaDRYSzZFb1BtbnhBVjYtZS1FLVc2c2dRaVRkazRhbDFnV2FQSmZkLVhWQTVvWURobzNUNlhFZVB3VVNTOHJla3htM2JvR1ZJMnV2RVc0N2ZlX1R5aGNFTlVnU28?oc=5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T11:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Australian state reports second OpenAI website breach - news.cgtn.com</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>news.cgtn.com</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRmIwYlp6NFd0S3M0bVFEQVNmQ1habzBrdVVfTTV4Qjlhc0w3V1dieGRNelJjdENYbGM3SUtpVGY2SGtEb25BdnU5STZQWGVaUkFBWVRpNUlsWlFGcFM3THZHd3BJOEs3SjU0ZTAtQUZVWnZKOGlmSDI3MndNZzRmakJSbXlQOHhxY2FWeWc5MmoyRXZrb1dKd2dnSzEyYVJQQzg3aGs0TkxvN2RZTU5v?oc=5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T12:48:54+00:00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI partners with Sachin Tendulkar to expand AI use in India - Indian Television Dot Com</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Indian Television Dot Com</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONlNWOWxGalQxOE1JTUJLVFVBNWl1NC0xSHhfZGNCOVdRR0VkY2o1V0NodUlrNFhUSHN1TS1QdHpHaDhpaGo3ZmZqVmd5OERpdmtsZ2p2WmpqNDhXbXV0bzFtc3hFajZwRXlyZ1h3QUhLamlxNE00WUpabTFCNTNXejlRYXJ6b2xhSnNEcjJPZWNKZFFFLXZHZEJzbzd5QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T07:34:22+00:00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Founding Member: Make LLMs Write Like An Aircraft Manual - Search Engine Journal</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Search Engine Journal</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNZ2UwU2k0MXVUVklUQUVVTDZrSlBOd0xFclhuUzQxSHdITjJKQ1pQNUEtSndVcjNudlBheW1jcVoyYk9jdS12UnJHOW4tQ0JrVXNvb1dHVHpZVWpFbUJtQV9QdlNsMGYtc1pwSEFrMC1CRDJMY0xKSlhuMU9CYXZoQ2hJV09MVTA?oc=5</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T15:49:43+00:00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI DevDay 2026 Recap for Developers - infoq.com</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>infoq.com</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1aZXgzMEVJUk1NMDk2UGhUWlRVQWVfSzcxM3RySDdYRG92SWIwX3hxdEk3MW5ISVUzdUZOeWZVSi16aGFNRXAyWkJLYVgzeTdvVXFtVkItZ3FEcXdsWlFfZ3VNLUY?oc=5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T10:39:16+00:00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Vassilis Koutsoumpas joins OpenAI as Head of Strategy &amp; Operations - Exchange4Media</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Exchange4Media</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPTFVDSDhsblhrSm41eVpXeVZfeUJiMGVHVDBoYzJMbmpKVF9ib3dhcm9VTDhVcGpsbFBXa0w2Q09JeWVLb2paLXRlRmdyNVJGQW1yblQ5WW5TdkVaX0VaTUtMclN5Y1JPdC1aTklvejhKSm5NY2VCVE95NmRtVk5RNzNxQWZzeERUSlJFYlhNN2NGeXJaeXV3RjQ3UUR5NlkxX3ZCdy03eWFhbjBvQkozQTBDRzBseUFtWXFwVU5aRklwNFMtOWU0?oc=5</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T09:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>The latest AI news we announced in September 2026 - blog.google</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>blog.google</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNXzhIUnNPaFVfR0U3TGVCM1AwRnY0Rk15UnVkM1Y5ajNPYUtXWE1mOE5OMjNNM1ZsN2czZS1iOUY5VVRkTnc3ZWhVVUdPUFZHTngtTFl0VjZjREpFbGRWV2VhV19ucVZhN2hra21IcFZISHNZcF81bHQ1Ti1kbnhhcll5a3dzNTl2aGpuZDhB?oc=5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T15:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Google AI Plus and free users are losing access to Gemini models, and it's happening very soon - XDA</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>XDA</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPZGtoQmRIVE1HdnpDQm80dzhweGtha3dRVS1uWXZGNkFPbkYxYzRTRVhUSkdFbnc0ZTRlSWNDLXBxOUZZSHpqNzg4a2FTZklFS1FsdmdyMU9oR0Z2U25HbG5UZUZzcUU1R3lOTmRvSmM5TGdoV2RkM3NhcU9kQi1oWUd3bk45TUpjak9laWg2VmE2anpvVkF6S1RMaDRwQzRNTk02R2ZKLVphSFRucjU2bzZjZkJoR3FDNEMw?oc=5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T05:56:52+00:00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Google unveils Gemini 4 Argon, its most powerful AI model yet; CEO Sundar Pichai says: We're going to mak - The Times of India</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxQanZhR1p3YTZtcXRuN2hhNWF1SExMQ0VFcjVGX2RYMzlZOHNqclRNT1VkdEtyZnhHOUFOdVJKV2NJdUlDend2MllZTnFvUWczNlozT3J4UHRtNElFZGNreTgtcFNhM2FUenFTdDZGSWFkX2E1dl92akdqaHI1eGdBSXZQTmVpZzVfRGFtaUpjSDlzNGF5QzQ3MTluSV95WDBGY2k2VnQtaFFEem5BaXNyN3o1OEd0VVNFeFRkU19sUGJmUm9BWldoYUxxTmFxNDV2cDhQV0JjWnJIX3o1ZDc0aE5wZ3U1UTk3UjVhWjkyRzFERUJkc3FtUXloOG5oUXBRaUJGTklGWko2al94cEVDSFNFZndpWDl6SV9pZXlBWHp6dGdhcDZfbDlfSnQtZ25UQ1YxSXh3WkRwNUJ4ZVJqMkpSa0lTdTTSAcwCQVVfeXFMT3hROHZ0NnFlbVkwVjhaZFZ3WkptV05uWG5DRmZUckdPZnlEa3dMU0hCNmdBSWF2VDBBdkhCNkY3OGdRSWtWbWdUSTRYZHJlS21QU1djWjZ0TElIYXh4SDMtRnFtamhrbnVmeUR4MUZqdWNqTzA5aWlFOGdiamVDdVVVQUFGMVpsZ2ZTOFo2MkJNSmJDQXVwekg4eG5iSkFVWGYxWlRkb0FVLWRIbDdldC1QejViWjd6czBoMnV5MW81MENpX0ZTMTIzMTM1cXMtUkNpek9OYmJOd1FkSTNBV0hWS2owMHB2MTh3ZWpoeDFpdEtabjhRVFA3aTE4dmZya0dfUGV5WjNSNGxQeDhlZ2hrdUx4cDhadnFfOUg0djNQejdNdkdXVDMwQ3pQOEJ6cE91OGdxaGRLRWVsUXJQallfN1ZIeFRybF9SR28?oc=5</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T03:41:00+00:00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini 4 Argon Unveiled With 1 Million Token Output Window - IT Voice Media</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>IT Voice Media</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxORDI4ZUhXLU9UTi12bVBKSS1FWm5uY3FpdDk3R0xRYXJEYkdRd0xEOTlpbnREWHZWNEhCakp3cDg3Tk81OW9jZHF6ejl4anZBcGRpMmV3M1dhSGJ1NUFlMHlFZUZRS2Z4THRtT0tSM1NVcnVxNVRHNVNvX0dGb0NFUl8tRWhDOGJtOEVkTC1LYkJJblI0N1dIbVp0SVVrOFJRMzUtV2l6RXdTRTA?oc=5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T08:06:29+00:00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot Super App: Features, AI Agents, and Comparison with ChatGPT - Analytics Insight</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Analytics Insight</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNcTdfdHlKd1ZTTXV0cmQyVGx2dmN4dGt6Yno4cmw4OURPSms3ZDBJUGkxdHpEaXJBaFdwWXQ0SEhwQVpRcEZjMzJSQTJTZjBPZWVySTFlenVWNTZiZi1VOGctejRkS1BpYW9sSXQ5QnJuaUUwa1lmMDl6aFlFQ2pPMlFNMkNBZktFSmZJTzFGNzJfOUdVZFp4d2toMWRIcVhYMkJFYVl3N1hlUEpMNk5NWThpTjFqRHJpRmpIdXROMndYa1U2MlNxZGJPVdIB2AFBVV95cUxNTWp2WVp0b1ZlNldJSHFtaWZUQkg4RUN0eGE5Vk5DQzhLUzFGRC1aZlVBTzFQWGhibTl0eENtTlIteTd4U0JKS19WQ2tTY1U1U0R0NTF5ZFptMVRxNk5VTHZ4dUx0WUpzeUQ3SC03MXlBZmxNaEtJTUp3MDRXODRGdUN6SE8yTC1JYlFMNy1lR0ZqYlZ1R0x0bEhLa0FOTzktNlR1SzBEa3ZsemNBUHRaZE00QVBKLU9NX1ZwakhOMmRGaTJoMVZKMm1ZRTBaRzV1XzdISjRCS1A?oc=5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T07:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Delays Default Copilot Usage-Based Billing To Dec. 1, Adds Spending Cap Option - crn.com</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>crn.com</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQOWktc2NPUnVaZEcweEJVQ0FxMW93cnc1cmg5YTN2eDVKckRta3hiejdldjB1cFZ6ajJfMTdJT29zWW55aXJ0RnE2ZlMwS1hvUFN0bWowX2tCbmg2ckplbU5femJjVVZtcXlLQnYxdE04cE5iOFhkcEJ1aFEzNjNIMkI1RnJ3UDhGbFlQOXVvdmRvU0JKdlJ5eTBDWkMxX2xIamtaZGhnUVJ1eUtMZ0szRmtUWUItNzhwX0tv?oc=5</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T21:43:00+00:00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>California tech executive arrested for allegedly smuggling $300M in Nvidia AI chips to China - qz.com</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>qz.com</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9OdG03bTRxOTA0RWtNN1ZXMTJSYlREMlF0X0JXajF6MXRuMzlndGdadlBFQ0RMLWVTdGhnSFFwV29XcW5USVhyd0FPeDhja0hpOVFvT0tGMWlvemI4bXFFeGdhaHhqUFBiSG5zUFZBbktjclA4ZkFnV0tKOWg?oc=5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T13:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>California tech CEO arrested, faces up to 20 years in prison for smuggling $300 million in Nvidia AI servers to China — federal prosecutors say chips were routed through Malaysia and Singapore using false paperwork - Tom's Hardware</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Tom's Hardware</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgNBVV95cUxPTS1ZdWR6VWFvcURsdGFQNUZjODR2QkZVOFk4c3hBT3hBNnlyY0k1Q0oyRzNFNk4wY0Q3VTlKdEU0aVdUdGZHNW1YWkN2LUxpcUE4MmJBdVhSRkFyLTFRSEhocUloZTB1MnFNYnV6TmN0WENtUC01aGc5WkpLazJBZGZuNGYtVzZNYmoyX2pDQjNYS1VYSHd5MklwTk1aVWYwNktaUm1JWms0SGFEbWlTMDBXYzJZRUYtWURTQ2lZaVZxMmptaDdnWDctek81dWJQME4xTHh4a1FQT1NPWHMycWptS0hvUzYxVWhOZXBqVWd2VVgxWWlOWWJRWDg3SGY4OVFMY3lPbGVyU3pXa3QzZnlnTGxtWGRicDhjYjdvbndvTzJGNHlxS05Ja25FRGMyeF96Q1hjLU9JWmlrQ2RBUkw3Tm42dDEzU245ZmxFdVZlT0RtbTVaRUcwTk5TbDJEa3FPdXpyeVZ6OUFxMWY3Yzkwa3JIcERwM0NmX3ozUjJaLWcwY3FXN1FKNm1lMUF4UFE?oc=5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T14:53:41+00:00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Looks to Offload $8B of Nvidia AI Chips From Its Balance Sheet - Investopedia</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Investopedia</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQNHphc3o4Y0dGRnBTaE5jUTd0S1dJWFA1OUppaXBsY1hhb0pkRHZZbUUwSWZYQnYyRTl2WDF6d084bnpLSFNZV3ZRRW5jcllFQ1dQWjFIMmZMTkZsYWZrNkNVM3FJazNxTEFfMHJBbzJxeVM4TU9iS1FBWFppYXNhNHh6OV80Rjg0dy0wVkVNOTg4eVJ5cEZva3l6b0J3S1k0QmlnbXZhOHh5S1JYMDFRREhuZ19SOXJ0WTBWTGFkYzZIVE1qcTdZM29R?oc=5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T14:59:46+00:00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Launches DGX Spark 64 GB Desktop AI Systems - TechPowerUp</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>TechPowerUp</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNZkhnM1N1aU1NYlBVRTBjN0VPUFl5VUIwVkpSWFZXVGhfSWZQbVJaajZha2JRQ0gweGVUbVZPN09oZ19JVHlTMi15TlFsNW9BLV9NUUtncVQ4ajJseEJGUklJNEFVVHpLNWg1QWF1QWJyZHFmaUo0MDFlOUxJNXdIUFdBQjZxS2R0NGdIVnJ30gGTAUFVX3lxTE5xaVlFOS1scmpkdjd5dWdveWV1Ry11bnVvVFZIYmpXVmN1cVNKLTJwUlVpLTRfM3dUN1h6VTFyMzVHYmtRbVlKd0hqaW1JNWJIaXRHOU9iVVdmc19YbXZvMHFRVWdiaWJMbHM3b2ZrWS1nX1RuQUVMRjFFUjFXSFdSaGFJR2FOUU5vRDRjYXVrdGJlcw?oc=5</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T17:17:56+00:00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>The 7-year-old Nvidia Shield TV is now $100 more expensive due to AI - arstechnica.com</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>arstechnica.com</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPTTFxRWkwS2E4T1oyby10NHkyZW5Ec0FTWUJ4QThPMzlHR1UtZTJZWHh0RFgyRXlHY3dIeUJoemlzY2FiZ0VuMDR1c3cxSFVFTXVNeE1kdDA5aDBOVHdCNloxTUMyRE1IejBDRV9TVVd4UkZCbXpHTnJRYTc0OUhuZGNvaTN2RXVHNV8tM083Z0JIY0p3bEVBZjJGS3BDam5EMUhoa1cycXFBcjhYRzdlRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T14:52:16+00:00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia hits record high as AI optimism, buyback lift shares By Investing.com - in.investing.com</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>in.investing.com</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQZzh6Z0V1RGpnU013WG5Ba1lPbS1wWEdUOWZPRkgyNUI3V1dvTWRxOXByWU85b3cyR3Bkc1lZYmhRbWlhdDR6Sm01aVJyUFpqZkFkQ1draS00bW8tRUhoa2NVMGpnSEZkOWtoRVlPMi1DM2dHVmpYZHBvRXRYdjVadWZGLTRlczdCa3pIbklpWU9ETG9TeHBZeFBnbDJUSXlRbk4tQ3hPSDYxWE9rQVZ1RWlRZDU?oc=5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T14:14:46+00:00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Thieves steal Nvidia-labelled trailers in California expecting to find AI hardware, end up with 20 tons of... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxOVEpxT0RWdXJuMkZoZDZlT182N2xxUGtVTG5qNUhRT3R3d0c3Q2dGS25wQjRYdGtpOEdCejBLeXRKSkJwaDVrOEk4YTktbU0wVzZQblBuWEFXUUl6eEtqVmp4clplT01yUjNZclh2Vzhhd0t2cUtibnhIWjEyWlE2Qkh6c2JVSy1LcHVkckJZYnY2U056c2o3QVgwOGxKVXBaWVhnZ1BHV0tmMC1ER0ZqUUxrRUhlTS1laVJ6REh5c25OWjZxc0Mxa3k0R3RwLWQxQ29QbjhpV3cxN1pMWm9hZzZ4clpGbEFYeFNoZi1XdGVNZS1yX3F1UXBfbS02bktGYWfSAYcCQVVfeXFMTVl2TklFc0ZkNGNaWXBNT0FrQnhRa2xZWXpMVHlOUTA1TVdCS3AxWnlUM0RvY2VCeTJZQWJEazl4T2lpcTltZnRCaVBMVkkwanFrNEE1QUdKQm1GNFBMUXFzRnExV05YZ2ZBaEhGdWJkN19iSWtaYzRMclNYaEE5RDhZRXNLclV6c1owZjBCU0VXbzRlRy1ZeUU3MkQ2dVQzekNZRVlQRm0tSlJHMUNwWUh5OU52aHh2YjJvZ0R1c1FyNEZLaEF4WDBZSlAwVmxvRWZsY3lmeHVrQmVNcjFGdXJsc1pfc3J3c3Z3TUREbV9nVjJBdVBRS3hUNG8tRlVlOVRWS0JkYlU?oc=5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T06:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX stock rises 6% as Musk targets 250kW Nvidia AI system power - TradingView</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNbmNYejBTeTl3LVVMRXFEWmRsb0xEZTR6TzE0b0IzQXZ2RmwycUd0RmdaZjgxWkc0VW9iNzRMUVJaM2lnT0FpbGlBSm9KVlhjRThhRmdrcjJnS1Y1azlXOGdiZF9aTWtNakJGa0Q4aGo0bUJzR0FhUU1yRHFROFY2QmJUQTBaM3ZEV1B5TVJWRFNVRWI2eVUyUkxYajZXTGZhM2RGV3ZLX21pYnpraUNhZWdWbkg4TTZ4YTBwNkVwaw?oc=5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T17:32:08+00:00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Arm (NASDAQ:ARM) Stock Jumps 7% as Nvidia AI Safety Platform and US$2 Billion CPU Demand Fuel the Rally - stocksdownunder.com</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>stocksdownunder.com</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5DckttUzdvVHVZME56S3pfb0VLT0V5a01YTVVPNUhVSk5LMXFLcHJfNUYyTzhsTmlXZzNrZkFmLTM2dTFycUdkel9iMTQwSkVOM1dmSERtMEFQUXNKdTlpNVJsOHdEakU1cmdCOFY2S0t2MG4tMVktOEtyb0s?oc=5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T20:17:37+00:00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia wants AI chips to become fungible asset, but Wall Street isn’t convinced yet | Here's why - Livemint</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPOThfLUttWWJyUl8tSGtJVWtadGRXMVZhLVFnOWJBbjlVd2l6OUNQVnhqNXUwd19RN0EwNjI2S3RkbTZTQVp3RHNudHpVaV95Yy1CYmdfZ2szYU5yUTN2R2ZBR1VWQmtLSjNWT193eTJUaXRUb1FHMHNyU185d2ktOFZNbXZJdUdaZWV2TmlTM1ZJQjZUR0V6WTJDbnQ4R3BaRlBaQjFTeUwxeHhSSVNFem5meFkxcnJMV0dGczhVY2JmdUpaVmludjdlRHVpS0hoTjl3bmduVlpBb1Z2Z2FUSWpsWlFWNU3SAewBQVVfeXFMTzBra1RYOFBha1VTV1ltYjV6ZUZiLTlHZUtMeTJkUk0zR2wyNUR2b1RFbkNGZWtsSjBkNHNESWlBTnIzQXByMmFweVNDeGJsLW41eER1bUpTMmdaOHRHRndxWHJPdDR4RHZKZlpFN3l2UmtMNmZyLUtoNEdfMHRYbVIwQlpGVjVNVlVlcHVZaWlrVElPc2YwV0ZUa3NkbXVvYmJTbU5HVEhocTNHSUwwVFAweWhmQlczTXpIWjRHNVBnT3EzdDZlclRvbFpmS0FKMFowbWcxQVZZcjI2Y081Uk53M0wtSmItRzlDMUs?oc=5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T03:07:45+00:00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Apple will update Macs to protect users from AI agents with full disk access - mashable.com</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>mashable.com</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUDRRTmRHQURXblJFVlgwQ2JpNUFLRVVBcTNRVmxKRDgzX1pWbVUxZHJfeUNBTlVsT0pQV2Q5T2xOdzFjQ1FlQ09NajFXU2xfODhBNVNiOWJIbnphRTF2VDJzNWEtTHBpOFlGSmw5Tmtnc2FUcjBKTVExeDZ6MFNlSFh2ODlYWmh4OFZtb1FR?oc=5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T09:25:27+00:00</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>The ‘WarGames’ problem: Computer science has long understood what it takes to keep AI under control - The Hindu</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOamVQLS1ERnkzZ2JGYzV1NVZMYUtBRkpZdzlFX1VEWng1ZXlCX21CYW1QU21VbnVxNHhhcGlKTlFSUW9lREJENDNldVkyUWM5enFfZzAwMHkybC01UFBGTHUyMFZ0RXU5bzJqeTZ5dG9DT1E2MXRyU2wzT08xNTdlbEhOUWFTS1gzLW1Ua0RlU1lodnhRbFhwMUlOaDhBeXJMbi1kMGllYWdIanVnUXVUd0JMVmNRTkstejdfNFA4cXNOQTBHdHRVMHpvTElfVnNDWVZnWDBrcTNGUnNHTHdKY2VuTkh4NzVXcmwxZE95Z9IB9gFBVV95cUxNRWZlRXcwMUFyQm8zMFQtUTBzX3ZNeU1VMVRUWnNnU2hpclhOLTlnam5RcEdTTjBIVlMtRGs2TVdhWmV1aG9vR1hReWpPZklyZk8xZHRWOGJrWk5hUmVDLV84eTBZOHNiQVVRVnY0ckMwMzg5Qk9CRllpUDlCSTZhQU5sekVSb0V0T1pZN3lLclpibnBtcEVkZ0Q1T3NMbngtVkdicFIzdmhNTEZ0RGY3Qk0tc254dTlicGp3Z3k5VFJqSXNoQ3dLYTcxUmRCbjlEWVRjLU1uSXFlZnRkNm9CZWM5QTdZUExDcWtyRXloaDltRjhYc2c?oc=5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T06:17:13+00:00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>How AI is redefining Wall Street jobs — and boosting demand for this new 'hottest skill' by 1,721% - CNBC</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFA3S3Nrd2Z0Q3ZHVnpCc01VU2NDa2hpcVk0WS1EZHVMTGtZd0tSZGw5Q295alJjeG05YXVhUEpFTElDM2NEc3NPNVZZNDhWS3gwMURVc3ZrcXU3OFdST2NYQWZRYkNlZS1hbjA5TEIwRGVWRmhWWFHSAXtBVV95cUxPSnpUWW9lVzZfYUlaX2RqbGZhSkZiODFfQkUzUEhWc3RMYzhoR2JSQmtxXzlfbnkybHVZOE9CdzBXM1R1OWVaekdWUEc1N3BDam1KcmJKZjNPY1BvaXN6cTRqbl9wY1liMGsyUlFGWTF2TXp2SmZwQnB6cFE?oc=5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T10:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI investigating other potential AI hacking incidents after Hugging Face breach - Fox News</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Fox News</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQYkxQOVRxbnlsdHQ1RGM0TVNZLUF1bGVqQ2xlUnpGZHJFQ3dZR05tMjZOVGRmTm9XblhYdXg0U0pFTTF0UXNWb0pGTGdRY0hPd2tadk9vSmdRdkFCNWJjLXFhZDFJSzBOdTc2UkVXeTFTUl84cmVvVUdib0lWMS1uc3huRzdEdGdjeV8xbA?oc=5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T23:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>When agents enter your payments - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNLXVmZ1hhejFFLWVyTnhPQzhwajNTYWw3azZNRkk0MVpvVE1JX0JJRnpFWDlkdWRYeUxpUjBXOThERDU3TlhIa0VZQWE0a21kbFFUS09DcWh5TzY4R3M2X1VDNm1YUzFhTExJaHRXSGpiak5kNlpwQ2pnX0xBZ092S3AtS3RvMFhGZXJaVzlBZ1RuMDB6OTNjV1A0YW9fQ3hPT1ltTmZVbw?oc=5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T04:46:18+00:00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>I run an AI company with a workforce of 34 AI agents. My days are powered by Diet Coke, DoorDash, and 'Claude walks' — here's my routine. - Business Insider</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Business Insider</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQd1lZSnEtR19yYmExSWJXSlRYMDBuNXA2MzRXbFZBZEc0VkxFZTZkWlpydEhvZVAtMUFCeV9wNms5d09JRjZzWkdIaUJTUjFfMW04dTZQSUlVSnBTVkxsT3I4RWdrWUwtUTlPaU9xX1hDUGs1bFhNRi1KbW1CbG9udkdVckFodFJIaXRNTFU0SGF1WTdtQjhfbXV4WQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T09:05:00+00:00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Meta open sources code to let you make Muse AI gadgets - The Verge</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>The Verge</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9acTlqV1l5amVvNkRCLWJPa19NU29PWmN4T0hqMVgwQk11QXAxOTZjNEFnSWhsd010dDduejI0cmsyblNsWUxVUFpuSVhDN19UYjJrNmxseE9mVGpvY2xPaXRBWGd0NGhrSk5sTjNrYWJCcmZyVEU4?oc=5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T21:08:37+00:00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Consumer AI agents: What does it mean for Financial Services? - Investing.com</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPYnJ0dF9pVEhUalpLcS1oTWI0YTZmdERScUpueXJlcmRwOFZMdjRGVzJ2OTJ5ZkpRUUUxczVlRy1WUVlRT2k0bWtBMHNEbjNBUUUzWEdhYWt1UFVFNnk0WkFWWDFqbW80NDNsZVBZQUpydXdXWThKX3NGcDdjY2hnc1FMeC05ZG5PZ1JFUFFmU28wZlVUcS1jeVdBNEY3Ymx2X0g3Q3VwTF80UUgyb1FhSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T08:04:50+00:00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>AI industry is worried about rogue AI agents, but what does it mean for the common user? - Firstpost</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Firstpost</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPbVhpUml6dTY0ZmM3RUhhNi1LVnc3TzlzN0lRMnZhYmhEYjBmSUptQWpIZHZ3b0pRZjBwQzRYVC0zZXVGS2NicUxOa2k3NXQzUE5odkxEeVp6T29zZ3ZYenl2eFRlOHFKdjY4b25LV1RZWkZidzdPaVZWTFJEN3pGVmIwZHNqVDdyekdRSHZwQ1ZtOGpVX3NrVFZOcVRoSVJWczJfOWZyclhZMFNXdFNpaVU1V29tUUFuYU1yZGE4eG1IbUxBU3BDNW1hc9IB0AFBVV95cUxNMTloYlNfRmF1TXRpWDY3S1hVTzFpcE9EcVQ3WnliV2JUYmpMOFpfSi1RYlpVNlVFQmNOZUNkZjRwZHpDNkVGTHg5YWxDWHZjOFV5Ri1PUUFBemVyVGxNSVhrdTRnRFpzLUlLWm5aVjhzTzR3d0lHbmMzWkJNQlpkM0lSVndwajhrVFRfTTMyS09OcEp4bjZIc0xocEhwSHRyVzZrc2xlRTg2aWJkWDFFeXNDZUpRRlVUSTQ5ZXlobHBZRXdDNWNtdUNLdWVqOWY0?oc=5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T09:38:31+00:00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>AI is changing developer work. Here are three skills to strengthen. - The GitHub Blog</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>The GitHub Blog</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNQ3Q3MjNYV3NBZFhtb0hybGRjYWJKcWZYaUg3YmR0NmdRb3ZKMjIxd3g0NlVSci1IdW9TTV9jMU9BSE05d1Q0dmRPMFR1amg5NXZsNXVFNkZGWnA2YzFpMndobVFEdEVndTJIUGF6V19pbHVFcG9LRTFyYlY3MkNoVTljRXo0RVJHQmNCbGFXMy1aMVNQZ19XdEpaSXZFQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T18:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>AI Agents Are Disrupting Open Source Security Disclosure - infoq.com</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>infoq.com</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE5XQ3RIdVVXMF9KZnBYMzdsWERNU1FJQXFsRDN4WndCcThRTFlQN28xQlUyLWlpeDFmSTFiZFZfZmVNTHIwanRiZzBaRV8wRHc1MXlleXV5MldydGRwVkp1bG1rODVyOVlLOFhz?oc=5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T06:47:28+00:00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Apple puts new limits on how apps, including AI agents, gain full access to your Mac - The Times of India</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPSV84UnREbXBocFVOZk9hZHpDblV3ek90SzFDbXlMY1lERU9uMm85bC0yZmdsZy0zeDhLZkhnaGY5QUdIVGx0X3Rzek9rbGxsZXhmWVluX3ZPeW45dzZIM3JGUnVrNDN1eHZpbHdDcno1WHp5TUNDckdsZWxySFVDdFBHS1JfcThWZ0hTcnlTOTBLelRaYk8xWGZuT2YwTnVvY3psVW9MbkoyN09PRkl1d3J1MzR4Zy16WkdnNWZxbzk1QTU4VEdIQ1M3U3FOalNFS2Y4ZkdlZUpwUmZkbFNqZmRKNUdxT1FxYm9Dd2xpclY2aDNVVldVb9IB_gFBVV95cUxOX19MY09BWVhDNENGdWNINmVaUXpfS1BIYXNKLWpIaVBtZHZEemtDRUdoWkpkcUg5WVIydzRmNnctc0wtVmlOUjN1LUE1bjFJOTc1S1c5T1R2UXNBMmJybnRidWc3dVhqUTNPdnJRSTd0d0FqUjQwM1JSSy1HaDU5YkhoRFd2QzF4dUVVQmg5T0NNNEtyRnBDZ1JIZC1pamhBZXo3Nm9uazBXazlkMmFLVjBoVDhDN21MQ0JtYmJaMmc2S0tXbUVPajduUDZQb1VFZnJGeERJekU0T25JT2tyZlBsNmt0WkhNbll0c1dfZGFPMFRnd01qWTkwckFOUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T06:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>As AI writes more code, software quality takes a hit - Channel Dive</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Channel Dive</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQclBfTWZVYV81Z0NwTzRaWHM2Q1ZYY1dOSUJ3WElRT19zbFI1MmxKdmY2UWVLRXBmQlJIM2xFeW9NLUNDaDFSeE9uS01zdFktWWdDT3VJS2F6WU1tWTlwNVoycGpnMjdORDJTbzNsb0JHN0dvT2VZUW0xQVZxVUhkNGdRSDVsOVVWakxNckh5NkpqOVFobWhv?oc=5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T21:42:39+00:00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Why you cannot vibe code your way to a successful connected product - IOT Insider</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>IOT Insider</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPT1BYeG1fOE02VDNiWGhBcEEybVhrVHFCdDlpTlAwcGllYzN4WldDV3kydEx5VUtod0M5THIwVGhCV2llMnNqUUI0RGF2TlF6OHpaeE9CTGpvdksyb3Y4OVhrSG1WUzZrRzhXNEpWZ1lLSnpUWi1uVkxmUWtobFNHb1BKdDlscVgwenc4b1htQ2xiYWdyT0pCYU53UlJERm00bUFpMFE4cThWSDBV?oc=5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T08:00:39+00:00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>IBM Brings Its Bob AI Coding Agent Inside Firewalls For Regulated Companies - Forbes</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Forbes</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQdHpxNVoxdzYwV05TYnkyWmNlMEJZQjVKOW1yODR2eHpvdFBjZU1qczlHT3lpYUZjMGlqLVhBa1hsd2hNOFY3djJXUVhXUkJYX205Q1ZQVEFKN3Nnem91UkxCYkxJNzV2OG5BbnkweVJCUmgwZjAwOURYeGJOVjZVaV9GSnBkZVNHYnNzQWpvazNnY2R5N1ZVMDMzM2JXRHlJZlh1RUdNQmVxNnM4N2JjNTA2UnVxcnQ4anl3bHBIOTZ4RHFDenc?oc=5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T15:54:59+00:00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>What Does Open Source Mean for the Lucrative RL Environment Business? - analyticsindiamag.com</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>analyticsindiamag.com</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPQzZXYkFWblF1UnhlMFJBUi05bEIzTGxCdEdZa2NYRWhaTVc2ejVzd3RkLWR2U2Y5bGl5elJfeFpPTUV2Ty0zYXQtNVVzeFBETjZQSnczRjFKbU9DQ05DUkNrYU9vTFl3X2FuUzRweHF1b3VzejZYVXdRcnJkWW9zY2FKQWNXbEgyZ1A0UjFhTnVXME9ObEZ6eU1IWkJzNnN2Nl9USjNsM2pzMzJ1ZTU4?oc=5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T16:03:46+00:00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Robotics startup FieldAI is set to raise $700 million at a $10 billion valuation - Business Insider</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Business Insider</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPdlB3WE40MnpRb2RsaUFaV0tjekEyM2dMNFFWZTc0LWJEa3ZpUEFVVFZWTUtwR3lyY1JRRjFmTlVldHRWbHdZTks4TnR6aFJ3NXVwYXdRdFNKaFR0R241UUNQQVEtZ2hQb0F2WWZyUjNvWmpfNnBjUC1oUzhVdktrdXhFd2t3a2dRRzAtQS1TREZvM011MUlvVGVWaFBLYjlRdFpz?oc=5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T15:39:00+00:00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Robotics, AI to drive next phase of precision healthcare in India: Dr Jitendra Singh - The Hans India</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>The Hans India</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQWE1NZ0lZdVV5bVhTSUtjUjl3a3RscDV2UkdoSExBYmUxVWwzU01IXzM5UHEzbU9xME4wU3ZrS3FOV1BnYkJ6WGxERmpCUjY2S3hLcWZrclJCdElIU1g2c1NRMThNWVNSQ1pwdFdxYnRXTHhkd04xQWV4UTdCZ3Z6d25WcWw3VlpyNGJ1bm9zUGlpc0tZYlR5Zk9OZzU5RmtRMV9LWGhDNnhJdC1La3hzOG5GRk9xbVdERDhYQ21ESGNoQmhRVGEw?oc=5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T12:56:56+00:00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Robotics AI developer FieldAI reportedly raising $700M in funding - SiliconANGLE</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>SiliconANGLE</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNR2FNdU1RN2pQSV83Yzdwbmt2OGt4azBOTHlBclJ4ZkRsaWhFaE9WOHpwMEo2SXI2YThZM0dKdUtKcEtkYmp2dTFiY1cxYTAtbVFfZ1ZTdjA1Sml3UXBDZU5fbVNqdWp6eDRJVGtWOWVnempoSGVrT0JpbG9UeWRmNlU1MGZJZ0IzZUFMcllLZ1pESGdVSVhTcUpqTW41dGdGdDBR?oc=5</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Watch these defunct humanoid robots go full Terminator and dive into molten steel - mashable.com</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>mashable.com</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOSDhQbzhZRXR2QXp5TjR2NkFGS2h5dXhnWnJneldfS1ZYaDdGWV9aTDAtaHVOYzJUS2tDV19KMmgwUFE4ZHZZamw4Z0JiVVgxdDlXSGNoUkZwVHVZUEJkdlJDemlRdWdjdl9GZ0dDSEhha2haQUFLSmxFWFZPZnppQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T19:00:06+00:00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
         </is>
       </c>
     </row>
@@ -523,8 +3140,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -565,6 +3192,90 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Apple Tightens macOS Full Disk Access to Guard Against AI Agents</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Apple Is Locking Down macOS Against AI Agents</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>If you run AI agents on your Mac, Apple is about to change the rules.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNWWdpcHY3TXVWN1hVNlg2SVIzaVV6ME5tRnh6dS1LU0pUU0J6Z2k1UkNLSDktVzFvWTVIM0lwQ1FNRTR2VzViZ1dLWk5YdUlTWWQ4YWpSdWItN2pRR3R3dHlPbkpZVWZOMUlYZVNUaXI3XzI1bVpsUndMMTRPN1ZndndaT2FDenI0Wm8yRXhVYlhfdTBTVFM4YzZGcUpDWnZEZi11S3VmZHlLRGViOVpQczJaT05kRG0xSXExbV9SVFhpQQ?oc=5
+https://news.google.com/rss/articles/CBMijgFBVV95cUxPUDRRTmRHQURXblJFVlgwQ2JpNUFLRVVBcTNRVmxKRDgzX1pWbVUxZHJfeUNBTlVsT0pQV2Q5T2xOdzFjQ1FlQ09NajFXU2xfODhBNVNiOWJIbnphRTF2VDJzNWEtTHBpOFlGSmw5Tmtnc2FUcjBKTVExeDZ6MFNlSFh2ODlYWmh4OFZtb1FR?oc=5
+https://news.google.com/rss/articles/CBMi-AFBVV95cUxPSV84UnREbXBocFVOZk9hZHpDblV3ek90SzFDbXlMY1lERU9uMm85bC0yZmdsZy0zeDhLZkhnaGY5QUdIVGx0X3Rzek9rbGxsZXhmWVluX3ZPeW45dzZIM3JGUnVrNDN1eHZpbHdDcno1WHp5TUNDckdsZWxySFVDdFBHS1JfcThWZ0hTcnlTOTBLelRaYk8xWGZuT2YwTnVvY3psVW9MbkoyN09PRkl1d3J1MzR4Zy16WkdnNWZxbzk1QTU4VEdIQ1M3U3FOalNFS2Y4ZkdlZUpwUmZkbFNqZmRKNUdxT1FxYm9Dd2xpclY2aDNVVldVb9IB_gFBVV95cUxOX19MY09BWVhDNENGdWNINmVaUXpfS1BIYXNKLWpIaVBtZHZEemtDRUdoWkpkcUg5WVIydzRmNnctc0wtVmlOUjN1LUE1bjFJOTc1S1c5T1R2UXNBMmJybnRidWc3dVhqUTNPdnJRSTd0d0FqUjQwM1JSSy1HaDU5YkhoRFd2QzF4dUVVQmg5T0NNNEtyRnBDZ1JIZC1pamhBZXo3Nm9uazBXazlkMmFLVjBoVDhDN21MQ0JtYmJaMmc2S0tXbUVPajduUDZQb1VFZnJGeERJekU0T25JT2tyZlBsNmt0WkhNbll0c1dfZGFPMFRnd01qWTkwckFOUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Apple Tightens macOS Full Disk Access to Guard Against AI Agents</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Apple Is Locking Down macOS Against AI Agents</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>If you run AI agents on your Mac, Apple is about to change the rules.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNWWdpcHY3TXVWN1hVNlg2SVIzaVV6ME5tRnh6dS1LU0pUU0J6Z2k1UkNLSDktVzFvWTVIM0lwQ1FNRTR2VzViZ1dLWk5YdUlTWWQ4YWpSdWItN2pRR3R3dHlPbkpZVWZOMUlYZVNUaXI3XzI1bVpsUndMMTRPN1ZndndaT2FDenI0Wm8yRXhVYlhfdTBTVFM4YzZGcUpDWnZEZi11S3VmZHlLRGViOVpQczJaT05kRG0xSXExbV9SVFhpQQ?oc=5
+https://news.google.com/rss/articles/CBMijgFBVV95cUxPUDRRTmRHQURXblJFVlgwQ2JpNUFLRVVBcTNRVmxKRDgzX1pWbVUxZHJfeUNBTlVsT0pQV2Q5T2xOdzFjQ1FlQ09NajFXU2xfODhBNVNiOWJIbnphRTF2VDJzNWEtTHBpOFlGSmw5Tmtnc2FUcjBKTVExeDZ6MFNlSFh2ODlYWmh4OFZtb1FR?oc=5
+https://news.google.com/rss/articles/CBMi-AFBVV95cUxPSV84UnREbXBocFVOZk9hZHpDblV3ek90SzFDbXlMY1lERU9uMm85bC0yZmdsZy0zeDhLZkhnaGY5QUdIVGx0X3Rzek9rbGxsZXhmWVluX3ZPeW45dzZIM3JGUnVrNDN1eHZpbHdDcno1WHp5TUNDckdsZWxySFVDdFBHS1JfcThWZ0hTcnlTOTBLelRaYk8xWGZuT2YwTnVvY3psVW9MbkoyN09PRkl1d3J1MzR4Zy16WkdnNWZxbzk1QTU4VEdIQ1M3U3FOalNFS2Y4ZkdlZUpwUmZkbFNqZmRKNUdxT1FxYm9Dd2xpclY2aDNVVldVb9IB_gFBVV95cUxOX19MY09BWVhDNENGdWNINmVaUXpfS1BIYXNKLWpIaVBtZHZEemtDRUdoWkpkcUg5WVIydzRmNnctc0wtVmlOUjN1LUE1bjFJOTc1S1c5T1R2UXNBMmJybnRidWc3dVhqUTNPdnJRSTd0d0FqUjQwM1JSSy1HaDU5YkhoRFd2QzF4dUVVQmg5T0NNNEtyRnBDZ1JIZC1pamhBZXo3Nm9uazBXazlkMmFLVjBoVDhDN21MQ0JtYmJaMmc2S0tXbUVPajduUDZQb1VFZnJGeERJekU0T25JT2tyZlBsNmt0WkhNbll0c1dfZGFPMFRnd01qWTkwckFOUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
         </is>
       </c>
     </row>
@@ -580,8 +3291,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -617,6 +3337,80 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Apple Is Locking Down macOS Against AI Agents</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>If you run AI agents on your Mac, Apple is about to change the rules. macOS is rolling out stricter security updates targeting Full Disk Access, specifically aimed at new risks from autonomous AI agents. Right now, many background agents request broad drive permissions to browse files, automate workflows, and organize your system. The problem? Once an agent has the keys to your entire drive, any unexpected behavior or prompt hijacking could expose everything. Apple is clamping down by adding tighter controls over how apps request and maintain full system access. This shift means AI won't just get an all-access pass to your local machine anymore. Operating systems are being forced to adapt to autonomous software. Check your Mac's Privacy settings today, and inspect which AI tools already have unrestricted disk access.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>A modern 9:16 vertical tech video with smooth kinetic transitions and dark mode UI aesthetics. The visuals blend clean 3D isometric hardware renders of MacBooks with futuristic operating system overlays, glowing permission nodes, and dynamic system dialog boxes. Bold, high-contrast sans-serif typography appears on screen in sync with the narration, paired with burnt-in yellow and white subtitles. Camera motion feels deliberate and crisp, featuring slow pans and subtle macro push-ins. Background ambient electronic beats remain subtle under the voiceover. The short concludes with an on-screen citation badge citing TechCrunch and Mashable, transitioning to an actionable takeaway slide.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Apple is updating macOS to clamp down on Full Disk Access permissions as autonomous AI agents proliferate. Here is why the operating system is drawing the line and what it means for your files.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>#Apple #macOS #AIAgents #CyberSecurity #TechNews</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Apple Is Locking Down macOS Against AI Agents</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>If you run AI agents on your Mac, Apple is about to change the rules. macOS is rolling out stricter security updates targeting Full Disk Access, specifically aimed at new risks from autonomous AI agents. Right now, many background agents request broad drive permissions to browse files, automate workflows, and organize your system. The problem? Once an agent has the keys to your entire drive, any unexpected behavior or prompt hijacking could expose everything. Apple is clamping down by adding tighter controls over how apps request and maintain full system access. This shift means AI won't just get an all-access pass to your local machine anymore. Operating systems are being forced to adapt to autonomous software. Check your Mac's Privacy settings today, and inspect which AI tools already have unrestricted disk access.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>A modern 9:16 vertical tech video with smooth kinetic transitions and dark mode UI aesthetics. The visuals blend clean 3D isometric hardware renders of MacBooks with futuristic operating system overlays, glowing permission nodes, and dynamic system dialog boxes. Bold, high-contrast sans-serif typography appears on screen in sync with the narration, paired with burnt-in yellow and white subtitles. Camera motion feels deliberate and crisp, featuring slow pans and subtle macro push-ins. Background ambient electronic beats remain subtle under the voiceover. The short concludes with an on-screen citation badge citing TechCrunch and Mashable, transitioning to an actionable takeaway slide.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Apple is updating macOS to clamp down on Full Disk Access permissions as autonomous AI agents proliferate. Here is why the operating system is drawing the line and what it means for your files.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>#Apple #macOS #AIAgents #CyberSecurity #TechNews</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
         </is>
       </c>
     </row>
@@ -632,8 +3426,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -659,6 +3460,33 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Apple Is Locking Down macOS Against AI Agents</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>swp3L_WSkSE</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=swp3L_WSkSE</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>uploaded</t>
         </is>
       </c>
     </row>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3128,6 +3128,1066 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence for Automated Analysis and Interpretation of Intravascular Ultrasound in Coronary Artery Disease: A Systematic Review - Cureus</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxQRGU5cGhYWUY3NDNtaURrcmpqZTRDN3ZHQlk1ZHV2UUVvbEI5S2ZDM3BOaUR4N3Q0LXYwcjh3cTh6WnFkdnBhY2xtTjJ6OWdCeHVScHZOTXdPa0RjNkVzWkVtMTU0aFBGQWVMSmVRdVZva0UzVTU0SExaUGJicGFfQU00WjZEdG5FUWhMRnFHdnF5VHI2Smc0R0tvQjFTRFQtWDR0TUJuN20tYTJRbnFzRUNlTmNJT0FWc0xhX3FYaFUwRWM5STZGbktRcTlobkh1NTlOMlNMQl9xS1lwU0syZUpxeXMwdGNzd0VpSGlWNlpiX0h2RnVkUmtiVzVhVkVBQ19LdTc2QlhjcVJtVHY2bWpzdU9MRkZBZTBLQzFWTnc4VUJK?oc=5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T11:36:51+00:00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI safety employee quits, warns AI firms aren't doing enough on risks - Business Standard</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPTkJlQzBLV2d4RTdmSXlhT0lUV1hBYm53a2NxT2xJck9oaURZYjNsMWptM21YTGUzeHN5RkNFUlpzclNrUUh4Zjk0b0tWTGxmdWp0NHo4cWhVUWVmZVAzMVRLcGkwNG8yeGo3Ym5Sd05sdWQ2aVg3eG10MExxTmU5TVBsdlM2Z2ZaOVl2dUNVdlBxMENBYU9GQjNkVGc5b3ljdDV5cnBWZFdJYW5rS0dMSTNPV0R2YkZiRTdaUHlFeWdBS3Njcl94NnNyYjFxaHJZMFN2dXBDX05wcjJaSXAtVWpnbi16YlRvelo3bWt1YlprNGvSAfgBQVVfeXFMTkg2aGluakVaU1VWdXVkamtXaG53dVdLZEtOMHExWkVValNRZEJucVpSVnAzakJPeVFLdXJkU3R0MjhBSmk0c2FGVlBhdG9PVTgwSTFPeks3SWtTT3I3bjZDN1Z4MkNRN2w4dlA4MG9nRGotWF9YMjhHbkVtcWtvNzhPZ3RzQjJUOEY1NDZLWFlmUHVZYkJJMXZBSl95cEZqWWZkWWNnb3pTdEtHOTBFRjRPTjlmUkhiTkpyWTVLRHJ5bDJKY2lDRGpkQmpRUm83dVVnc1hMVlBOZkJ2b2dKNDVXUGdJR01zUlUxWnQ1QV9JbWhVOERPRGI?oc=5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T14:52:38+00:00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>I Quit OpenAI Because Its Culture Is Broken - The Atlantic</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>The Atlantic</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPX2NNSzBoT3NhRmFhWjdUZ1NtOTFVNUFRaFBvNUd2R1c2NlhCLVZNanZfdm5UR3BDZ2V0bC1Oa00zano0OWtDdUo3WFFzMXNqdUxDczJ2Ujl3Vng5N2VlRGZDeWx5OHBhbWFnTXZpNkVTbWNHOFMtTEcyLXFGckl4bDRtUE81ZnIyWU91S21n?oc=5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T11:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI discloses another Australian government hack - Mashable</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Mashable</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNQ1o1T2dBczJSZjhVTmlPcEljLWQzTTc0aVZLSUY4a1I3eF9ZSTBTYTZIb2g4bHpwU3pJSTBWUDZoc1RscUtYVWRfVkNFVS1VdnlZeG8yQ0tYbjZtVkxnOF9tT2EyWEFuNy0yVmZMM2NpekNzc0dWYmx4c1F2ZkVIbldlSFpTQUJG?oc=5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T09:06:05+00:00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Exclusive / How employees forced OpenAI’s president to back down - Semafor</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Semafor</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOQkNIaGItUndIa2RoYVZ4QVh1RE5XOUFkN2NrQUhqdjRfVS0yc2x4VzdaQWFraDVzeVFVcTF0amc4LTJfM2hyU0RwWkVKZERyS3lMLXo1V0pYSWVXUUFYc1RuX2h4aVp2UHZPMThNZkVzcG1ZbjROOXlxOHBDaDV6SGd1LVYyMm9JQkRuUmhnb0MwTVBSeV9mVWhR?oc=5</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>The eternal complement - OpenAI</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBVWmpWcUY1SVAtVWc2bnhmNHhSOWVFYnY4aGR3RG4xRHZwWlNNdFhwRS1aSUZhQk5kNUpGRnhBdU03T01rU0JXaWdnQ1hPck1RT0lCbE03V3Q5Ti05?oc=5</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T14:41:33+00:00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI says its review into hacks, including on Australian government sites, is costing $500,000 a day - The Guardian</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>The Guardian</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPQV9vbzIxazFuRjRrZVRqQnF1c2toZ1dMcnMxTUN4Uk5ISVNFQ1Q4aGdSd0t6aE16YjMzZ09nWGVHdUYzUE1jN0IyOThnYUNVTEdBNFlEWkJ1LVhBOU0yNGZwWnRvWGgwNTUyTTVNX1BnVkRvb2g1WFlmTDBTcGdfYUd2bGhHWFdycFY4WWFiSGxYOVR2QldpR3VnN0VsLW1JWDFBTUxlTFN6UTVwRjBVRGxjRlE3M3JSRnVV?oc=5</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T05:40:00+00:00</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Google Wants AI Content Fact-Checked, Gemini UTM Tags – SEO Pulse - Search Engine Journal</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Search Engine Journal</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOcTZBQURKU0RqM0g1LTY5ZFdBU25OQzY2UmtYSEFGdDFmNXpOYnhmTWc5TjUtRndWNW9aVGZMY2JYazdXMHZTanZGWnZSU1VKZEZQNGxqZXkwcEZnNUNIVkRFNVJBbGtiNldVSEE1NGFSYzlWTWdkaUFQMnZoWDU0dUxPTjZzZ3BIdkU2Y1BiNWVqbXh0Wkc0VThIOExRakk?oc=5</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T12:00:26+00:00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Google Pushed AI Into Schools—and Even Students Say It’s Gone Too Far - WSJ</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1GQ1g3MkhsR1VXWmJvLXU2UDYyMVR5ekl6aFJPc21nZW9GZUN6S2JwQkJNdHFFbHMtS2E3MlFTNnEtWFpsZHhRX2lhWVBsTEpZbm5ENGZha0hqb3hoT21aT0hLQ1FrSHdXVWJMUXB6R0pFeXphTnZqQ05VRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T16:31:56+00:00</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Just days after Gemini Argon launch, Google updates AI plans to limit free use significantly - Neowin</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Neowin</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQTnd0N3VMdHQ1aFJwUHZSVVdyaldycG5oXzZrRU1HTVZnWUpONUgtaEgyc2NyLTFPVERPRU5qZG4yYXZIcVRiMFJSOUdUd3RJRjc1Vk10NjhEZE1NMlg3bFE5aGZGUDloXzJuMXpnYngxR1RCSDVFNVoxQTJvZ2M2TXhWUGlqc1BfaHRIVmJwLWF3WmM5cTlHNGR0dVd4aHNlVDBfNW0zYkNrbHFxU2luQkxxQkZXSkxNUmN3UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T10:48:00+00:00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft adds agent governance and usage controls to Copilot - msspalert.com</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>msspalert.com</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOM2o1X2tTWFdQRzNlYS0zdjFkUjZrcXhEUVItUXExUkJUdFhpNnlVbkxtcWMxS1dMTTNFNnYzVjFyYm5QeVBZY2pqRmxrY2dBcHhqMFctbVVsWWRCd2tab3hqUFZrbDd4czZwVE94WC1iMGNZdGhQWm9oYWRDSTlpQTEtLWxUZ3IxeU9COWJjcWZPb3hHYmJta1k4eUV6YWVmVmRJ?oc=5</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T14:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>US arrests tech CEO accused of smuggling $300M in Nvidia chips into China - Ars Technica</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Ars Technica</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPVlhTZzZkSkdEUlZRM1lhSlFCbTJvU1BPOVRmX0RGeGlkWGU2RTBCZzdOQWJsTDlFY1g4Q1pRRFA2aVlaSDItaVpUaC1zNURkUFh1TlBzS3VqQU91Q0NqV254NXphOG1OTEpWUTVwVzA1SXVWbzVYRHVfWlBSTXV2MzlxV0dFLTZzZ2VEQ1QtMDFBa2ozWmw0ZEphUWl6bnB3OXNLU3JWNFU3MzJwcV96VFJhTWVfQWNr?oc=5</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T18:39:36+00:00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="n"/>
+      <c r="M62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia breaks to all-time high of $237.87, driven by buyback, analyst upgrade, and AI demand - Investing.com</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOUGt6RmJ4NjFGNHBKQUFnVXN4NVlIZzU3aEx1VkRwU3pSbVhUZWdEZEljX0JFR3ZhU3JvQUdma0ZsaS1LeW1TU0NPOUozazE2NHFxMjBhcmZPZnhYVHotVzM1VzRFWHBvWFR3LUV3YVRrOEpxSEJxSXdWVTZpQ3J6aUZwQjNJU2pjbVZwZWF4Z2c0SkdEM0N6WDE1S01LWjBpNWtvb3A4ZmFqRmlBTGRyQ3dxU0czelNZcEZ4U3RoRFdMSFZmT1d4Q2pvc3VUU2FLTElkUUNpaU91Vlp4Z0lBSDZB?oc=5</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T02:37:57+00:00</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Godfather of AI Yann LeCun does not believe that AI will kill humans; 'blames' humans for AI Agents hacki - The Times of India</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgNBVV95cUxOazNWRGJLVlVMbXpWeV9VRUp5bU83QnVuOTdlcG1ORFlKZXZ2NkdadW9fNTNZQkJLVDJpaDFsU1hGSDJtdlFrNVMzYVlFZ0ZTWXVyeEcwTnZwczJmRVlKSDBzZGNSN1hRV2gxUWFZYUp6UWNrU21LOUdWdVBvQ2tuVGZQXzdPeXQ3MDNEblEzd1Bab0hOb0VZWXNYWHdBVE1IdnBpVWN4UUtrMFBYZDZ5d1NOa3c3MEhGREN5MGJCY3U5STE0ZGt1LWlHdHVkZk1mM3VCSDFFZndlalpLcEFfY0RiT3lkM01hUUFjNmotcFE5aUpHNFgzbEV4OW9leGp1c2xULVFaY1p6QXIwdE9rUS1yYXdzRnRtMmMyVlBRcThFdWhTSkl5SVVNLUd5OXlvanJwLTVWR2FkRm10d2NXYTdIcVZRa19DY2NwLWpjRzhqN2h6LVRjcGZqWTBOenpsR2Q5VXpBMlFFcXk4VVpnMTc0dVNyNkhZczBnZzZLYThJVmxwTVlXbWZ2NEg3QdIBkwNBVV95cUxNVFdmUk5BWjBjbU5aVkpsd1BzMi1Wd3BXRmtMU1lTTUwxTUVJRlcydTNJWGROV1l3Y1hCLXpzbGlzUDlQY0tFNG56S0JsaGQ2SnY5azVqRXdBbHg2b2x4a2lWWmNuQnZuRUw1LXBBVHpvZnBjZ1hkVDZDYkVnbVRMOHR5aTd0dGZVZGx4ZGE0ekVHNERwbUxuS3NYZEFSZlh2ZmZYRFFOZFlRdTIzMU5jQkdMdU9fNWdaeFcwTl9RMkE5eTR3M1ZPQlFUTTd1eGpjTzhqajJUb0xRR3hIMkRXdUdZN0dIcURJbEwzLWxoODJjb3NxUUJFLURXXy00ZEhuLTJldDdSSVd0c093eGhzbkJhTzc4emF0OU9xQ2ZBb2RZejlLcHZtT3pXTzV6cUVncmxfX1MtVmFBdWFpd05ZSVZldXVXby16a0NoUXJJTU41WnV5WXpLa0RNVnlSN1Qzdm9qandHRGs3OU82ZmZtZURiMElPM2R0d0NaN2tHN21UWGI5QUltZ0EtTkUyTEFrNVBV?oc=5</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T06:24:00+00:00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>When AI agents slip the leash: How companies monitor and control them - The Indian Express</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOWE5IaXkzdTRtZmJLcXZVMWw5Zk9Hb2JjQUlPYVlFQmJFcHNwRS1PZnhpaTlRWk15Q1hYX2FkY091RURtOHNmQWVYR1VURVdNZDZqVjdtd0htSmYxYzhGTzR6RGpRanpEOUg1VC01UmNLSkdIa0ZDVXUtSHB3SWJhZVRLeDNsR2hWV1pKdHBEVUVNWlA0Y213M1JJTEFlUlI4SjZreXUtNNIBrgFBVV95cUxNTUh5YlBuYUoyNmFoNVJZa3RqbzlSR3ZRamFQU2RGbDRpZHdLdzdocnBCa1JPNkNmWGRrR3JLNEJvdzZWdXM0U1diWVBGVnNpMmd1WUk2ano2ZDhaOG56cjVLVEhjcGIyMC1Dd2lWcEVwRDZ0cGotdktXQk1VczdyUWhLZXFEaldDbFlfakR4eGFqdWpoby1Ncl9CQnpqa2VMZmRLTlZoODdmQ2l5NXc?oc=5</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T08:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Consumer AI agents: What does it mean for Financial Services? By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Investing.com India</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPaU9vU011OE1PdDNoMzRpMzlOdW82OEdpNVZVbGk3M3pmMHRRZmxJdE1oTWVQY0tpR0F0SEtIR1hBQUFkaGVzMl9xN1pTN1NURDJMRGItSXZ1Y1lMVVVxWUd0SEZXbEVTN1lrdkxLcm1vWWl3cUNyeTk3SEhOQVBOYk1jZGhybi1jOWl4LTJ1dW9qNjlQajcwTWV1ZHhueVEtNHg0aE5DQUg1UWRLRmVn?oc=5</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T08:17:24+00:00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
+      <c r="M66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Who’s to Blame When A.I. Goes Rogue? - The New York Times</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>The New York Times</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQTUhrakN2TGFTTmdhM0VtY2s5UjBjOVB5cnRRM1NHOWxPV1FGYTdfYjRrQkNZeFFBeHVkSXI1Q29DOE96WmNnSndCb1hwU1c4UGpxanNmMlJsNkJkYVRZNEpBSzdLdG55cXN5Z3hBYWVZSVVkQ1B2OV81Q1hEbExJUUJR?oc=5</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T14:51:00+00:00</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>3 years in software job, but cannot explain his own code: AI is killing 'critical thinking' skills even am - The Economic Times</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwJBVV95cUxPcXNBWDRaRmlDNG53ZFBhTmlqSS1LUDlSaVFzSmhXNzNFWXFTZm5RdGhpNVF0anY4ZGtwSVNVUTlsbW51YXRudmNBR2JxdzNNeERtYjB5VEwyTDB0TlBCOVhEMUNpUUhYU1VuT2VybC1waWFFTWdIdHhfODMwWkhFZldaaVpwNzJSWThDNFhtdFZNek44UU16UWVsUm1hZGVyWnVSY2RIdFlRMnNoc1VXNFFMUk9IWlVKeGI0UTAzLWI4eFVnVk55ZHZfQk1FVEtMSWhKVi1URDZ6RzZJZHRMeC1VTVQzZnNndUZLc2FpWUY3T3lwblowaVQwYnVNQkF1UWVXZ1lFUEtQSk5OUi1oVHpiTEZ0RG5CQkpKbjlvRnh0QS1uNHA2VUNtUdIBsAJBVV95cUxQSUhoT09KTk5wZDN6amp0b3dRbDlfSmVEYmFOODJoSHBVV2N0cDg5UENDaW5yWEh3MGpNUGd3N0pxUmRneUJ0TkkyS1pJck1qMmNzWUUteTc0dVNXQmo0ZWhtb1R2SnBMS3NCb1ZURVgtei1SQWhENlBONDRfZjJCYlNaZGNtdFlBZ205WXM3NVFJbjRUMXZPQ0R0TUVXei1KZU12ay1ERHBWVmdheGdvbXJyS1hpa3FvTnE2NHBVbVFUOGwxOWZMdVg2SksxRmo4RG5JaFJ5bzJHX1ExMElpR3hKbWdmdUw0LTdKTUJiR1Z4RTVBNlVkbGdraUc3dkM4eEY4dnZXdXJ1TGxaUGptRWF0bV9CVExSdU5TLUtfR0xlU3NMRTc5TUxYNVZ0aHk4?oc=5</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T14:47:28+00:00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Meta launches open source Muse Gadgets project for custom AI hardware - Indian Television Dot Com</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Indian Television Dot Com</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPV2tuN1NMVjdTMEJDRHE1bnFMV2JhaVF6bDEtTDlwLTlPTk5xMVVZejFYTGZHU05uTFNGaFNYem9iWk0yNnVLcy1WZHoxVTlBRnFOOVJJSG5xMVRRN0Q5S3FKOFNuTi1jYmpOUzZvbUJHeEFBbzJ3RVFUMUV1Y2NadGF6WElzRDV0aUxYRlhwQTZLeTJHRTJBd1ZzVllOX0h1c1M1QUpxNHM5dw?oc=5</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T14:40:36+00:00</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>From Surgery to Diagnostics: Robotics Enters New Healthcare Frontiers - The Indian Practitioner</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>The Indian Practitioner</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOWl9WbmUwMmNYc21SMkZNT3lhY2x3d2hxS2FWQjVaMEJWVG52R1NsZ1FHTE01ZUpVRkMzcl9MaE1rZG9TeG5ocURkb0Z3bGR2RGQzUGpoTzBCN25zbEx3S2RqYkxBRS1mWUNPeXpvb01MMEZlWmpvWXhiY0NUUEpyYkl6VnFzdkhpamg1cl9VVzBzUWNyUFNuaHVoM2FFVlhaekJXU29n?oc=5</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T12:09:15+00:00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3140,7 +4200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3279,6 +4339,88 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Apple limiting AI agents full disk access on Mac</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac డేటాపై AI నిఘా? Apple సంచలన నిర్ణయం!</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌లోని మొత్తం డేటాను AI ఏజెంట్లు సైలెంట్‌గా చూసేస్తున్నాయా?</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUDRRTmRHQURXblJFVlgwQ2JpNUFLRVVBcTNRVmxKRDgzX1pWbVUxZHJfeUNBTlVsT0pQV2Q5T2xOdzFjQ1FlQ09NajFXU2xfODhBNVNiOWJIbnphRTF2VDJzNWEtTHBpOFlGSmw5Tmtnc2FUcjBKTVExeDZ6MFNlSFh2ODlYWmh4OFZtb1FR?oc=5
+https://news.google.com/rss/articles/CBMilAFBVV95cUxQSS1DeTVFM3prNm9wck9fNTczNnEwcFFyaUs5eFpDZ0QzN1NDMDdtelVpYWR3YUx0cWZKMkpLRmFsYmJnQXhDblNiNU9kSFNRNGZ2ZTMyZXBKZU9kbVZnV29NakhyNGFZX3FfTWZlZTJhTmJkRGhJcmhNbjVTbno3YlNnRTFNU2FTcm1DcVFKckFhRFp2?oc=5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Apple limiting AI agents full disk access on Mac</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac డేటాపై AI నిఘా? Apple సంచలన నిర్ణయం!</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌లోని మొత్తం డేటాను AI ఏజెంట్లు సైలెంట్‌గా చూసేస్తున్నాయా?</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUDRRTmRHQURXblJFVlgwQ2JpNUFLRVVBcTNRVmxKRDgzX1pWbVUxZHJfeUNBTlVsT0pQV2Q5T2xOdzFjQ1FlQ09NajFXU2xfODhBNVNiOWJIbnphRTF2VDJzNWEtTHBpOFlGSmw5Tmtnc2FUcjBKTVExeDZ6MFNlSFh2ODlYWmh4OFZtb1FR?oc=5
+https://news.google.com/rss/articles/CBMilAFBVV95cUxQSS1DeTVFM3prNm9wck9fNTczNnEwcFFyaUs5eFpDZ0QzN1NDMDdtelVpYWR3YUx0cWZKMkpLRmFsYmJnQXhDblNiNU9kSFNRNGZ2ZTMyZXBKZU9kbVZnV29NakhyNGFZX3FfTWZlZTJhTmJkRGhJcmhNbjVTbno3YlNnRTFNU2FTcm1DcVFKckFhRFp2?oc=5</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3291,7 +4433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3414,6 +4556,80 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac డేటాపై AI నిఘా? Apple సంచలన నిర్ణయం!</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌లోని మొత్తం డేటాను AI ఏజెంట్లు సైలెంట్‌గా చూసేస్తున్నాయా? దీనికి అడ్డుకట్ట వేయడానికి Apple ఇప్పుడు ఒక పెద్ద నిర్ణయం తీసుకుంది! సాధారణ చాట్‌బాట్ల కంటే భిన్నంగా, మన కంప్యూటర్‌లో సొంతంగా పనులు పూర్తి చేసే అటానమస్ AI agents ఇప్పుడు ట్రెండ్ అవుతున్నాయి. అయితే కొన్ని AI టూల్స్ మన సిస్టమ్‌లోని ఫుల్ డిస్క్ యాక్సెస్ పర్మిషన్స్ తీసుకుంటున్నట్లు టెక్ నిపుణులు హెచ్చరిస్తున్నారు. ఒకసారి ఫుల్ యాక్సెస్ వస్తే, మీ ప్రైవేట్ ఫైల్స్, బ్రౌజింగ్ డేటా, చివరికి కీలక సమాచారం కూడా వాటి చేతుల్లోకి వెళ్లే ప్రమాదం ఉంది. అందుకే Mac కంప్యూటర్లలో ఇలాంటి రిస్క్‌లకు బ్రేక్ వేసేందుకు Apple కొత్త భద్రతా నిబంధనలను సిద్ధం చేస్తోంది. రాబోయే అప్‌డేట్‌తో, ఏ AI ఏజెంట్‌ కూడా యూజర్ స్పష్టమైన అనుమతి లేకుండా డిస్క్‌లోని ఫైళ్లను టచ్ చేయలేదు. ఆర్టిఫిషియల్ ఇంటెలిజెన్స్ ఎంత వేగంగా ఎదుగుతోందో, సైబర్ సెక్యూరిటీ రక్షణలు కూడా అంతే కఠినంగా మారాల్సిన అవసరం ఏర్పడింది. టెక్నాలజీ ఇచ్చే సౌలభ్యాన్ని ఆస్వాదించండి, కానీ ఏ యాప్‌కైనా పర్మిషన్లు ఇచ్చే ముందు ఎల్లప్పుడూ జాగ్రత్తగా పరిశీలించండి!</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>A slick 9:16 vertical short about AI agent security on Apple MacBooks. Fast-paced camera zooms on a sleek MacBook displaying neon security shield graphics, illuminated digital lock icons over folder trees, and dynamic motion graphics showing AI autonomous processes. High contrast cyber aesthetics, clean Telugu typography overlays, smooth split-screen animations, soft cinematic background synth hum, crisp Telugu voiceover, clear burned-in subtitles, and a definitive takeaway card at the end.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Mac యూజర్ల డేటా భద్రత కోసం Apple కీలక అడుగు వేస్తోంది. AI ఏజెంట్లకు ఫుల్ డిస్క్ యాక్సెస్ పరిమితులపై తాజా వివరాలు తెలుసుకోండి! #Apple #AI #Mac #TechNews #TeluguTech</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>#AI #Apple #Technology #తెలుగు #TechNewsTelugu</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac డేటాపై AI నిఘా? Apple సంచలన నిర్ణయం!</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌లోని మొత్తం డేటాను AI ఏజెంట్లు సైలెంట్‌గా చూసేస్తున్నాయా? దీనికి అడ్డుకట్ట వేయడానికి Apple ఇప్పుడు ఒక పెద్ద నిర్ణయం తీసుకుంది! సాధారణ చాట్‌బాట్ల కంటే భిన్నంగా, మన కంప్యూటర్‌లో సొంతంగా పనులు పూర్తి చేసే అటానమస్ AI agents ఇప్పుడు ట్రెండ్ అవుతున్నాయి. అయితే కొన్ని AI టూల్స్ మన సిస్టమ్‌లోని ఫుల్ డిస్క్ యాక్సెస్ పర్మిషన్స్ తీసుకుంటున్నట్లు టెక్ నిపుణులు హెచ్చరిస్తున్నారు. ఒకసారి ఫుల్ యాక్సెస్ వస్తే, మీ ప్రైవేట్ ఫైల్స్, బ్రౌజింగ్ డేటా, చివరికి కీలక సమాచారం కూడా వాటి చేతుల్లోకి వెళ్లే ప్రమాదం ఉంది. అందుకే Mac కంప్యూటర్లలో ఇలాంటి రిస్క్‌లకు బ్రేక్ వేసేందుకు Apple కొత్త భద్రతా నిబంధనలను సిద్ధం చేస్తోంది. రాబోయే అప్‌డేట్‌తో, ఏ AI ఏజెంట్‌ కూడా యూజర్ స్పష్టమైన అనుమతి లేకుండా డిస్క్‌లోని ఫైళ్లను టచ్ చేయలేదు. ఆర్టిఫిషియల్ ఇంటెలిజెన్స్ ఎంత వేగంగా ఎదుగుతోందో, సైబర్ సెక్యూరిటీ రక్షణలు కూడా అంతే కఠినంగా మారాల్సిన అవసరం ఏర్పడింది. టెక్నాలజీ ఇచ్చే సౌలభ్యాన్ని ఆస్వాదించండి, కానీ ఏ యాప్‌కైనా పర్మిషన్లు ఇచ్చే ముందు ఎల్లప్పుడూ జాగ్రత్తగా పరిశీలించండి!</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>A slick 9:16 vertical short about AI agent security on Apple MacBooks. Fast-paced camera zooms on a sleek MacBook displaying neon security shield graphics, illuminated digital lock icons over folder trees, and dynamic motion graphics showing AI autonomous processes. High contrast cyber aesthetics, clean Telugu typography overlays, smooth split-screen animations, soft cinematic background synth hum, crisp Telugu voiceover, clear burned-in subtitles, and a definitive takeaway card at the end.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Mac యూజర్ల డేటా భద్రత కోసం Apple కీలక అడుగు వేస్తోంది. AI ఏజెంట్లకు ఫుల్ డిస్క్ యాక్సెస్ పరిమితులపై తాజా వివరాలు తెలుసుకోండి! #Apple #AI #Mac #TechNews #TeluguTech</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>#AI #Apple #Technology #తెలుగు #TechNewsTelugu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3426,7 +4642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3490,6 +4706,33 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac డేటాపై AI నిఘా? Apple సంచలన నిర్ణయం!</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>8JHYTqy-kAk</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8JHYTqy-kAk</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>uploaded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4188,6 +4188,218 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Vs Anthropic: Sam Altman Takes A Jab Over "Religious Force" - NDTV</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPcExYb3hQYWZtNUtZS1JtVGg3bVVMTVphWEpLSlQ0Y3dWQ1UxZk5OMkdrNGpucEFwZ0pYaU1WLXgya0xkMDBWb1l4MEJSZ1IzbUVlX25Pc3BXV3M3Z3hGUVc3U29fSkJxMFJNNWlxeDlXeXlKLUhpaWx1N0ZFQXdlYjE5N1h0a1R3UU9XMjlFYk9qa0Fkal9GOHlVZVFzRU5RSGVVdElISFZoR1VrMUFMbWoxQXNUMDVi0gHAAUFVX3lxTE40Q3c1N21GMmF4Z0NsdUcyOXFNMHgxTzZZYjBBUEtPQ25pTGEybTk1QkZ3RFpkN1g3ZUlnMWJoc2ZrcGxxRVpmdXZfdEZuVlB1RDBxdGE4V0JaQm9qekpKT08tLTRlSTV4VVBfdTZxeGh6Y3ZfMG5Jc0RxbTZuRW1VZmF6VDgwTHZzVVNmZThKOW1qdnViaVBweFZqRUNHRkdZWnhqSWx2cVBGTnlNR3JWTHJwb08zNU9kTnRZMnhxNw?oc=5</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:29:08+00:00</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="n"/>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia’s Blind Spots Exposed by China Chip Smuggling - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNUnZqUE1kc1RPWjZZTkV6Rjl0NGlnQ0szamJ5YWFURzFpVWJYUThldVJ2Wm5vSEJBTnVGZjlvMEs3REpRVDJaeU5nMDV2bmEzOVV3cE9sYTdZa3g0c2FnNnlhNThXMnBDQTJjZFczaUtJZTZmT0tsMHc4cWZ0U3R6UzRUVUc4V2VNeUdWMS1oU2xDcllzZ05TakN1c1c4Zi1Vc2pQOTFHSVFSY1hI?oc=5</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T06:49:00+00:00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA shares near May highs after 23% rally on AI - NewsBytes</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>NewsBytes</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQktQbFNCaWlVQXU0SDF1cVBwdzFFbTFuZjczbGhUYkdzM0RvQ01rVXR6a19HRHdtMnNJYkZuWWh4eTBGMEdtbFVHeUtpaElkQW9ST0s0bTVrTHFZQUFsNXlhRmlKUDBCR3ptaUxBTXJtWXFOcHBOQi1fdm8tN21LUEtnZWNrMnI4Q1RPRXpDNmxVeXdrRW1wcldXQmJQZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T04:02:51+00:00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>AI startup Autoheal raises $7.9 million to build self-improving software factory for enterprises - Indian Startup News</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Indian Startup News</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQSl9oaDc0a2FuaDBPZDNDNlpudlp0cmZtMHVheG1mbTZsMWpDeHFpRUxreW5nWVlQcEZOTXhIZGs3NW85NlluNkpfc3NNNzVobHlOSDJtYk1UdHdRbGRzSHJjMHo0SmtVYWJVbUhVQTVOWXhqZlZISWdxWUNHTWF3SjRsTXpLa2k2LUxhQjdtTVNGUGF2eFYwSnJTSzlLTHIta3ZUT1pkLUFfcjdqMG9CN0tMSGRzZ20xTEREQzNMTExEQlRVXzNta05naW4ydkJkTUhhZmJwRE7SAdgBQVVfeXFMUEpfaGg3NGthbmgwT2QzQzZabnZadHJmbTB1YXhtZm02bDFqQ3hxaUVMa3luZ1lZUHBGTk14SGRrNzVvOTZZbjZKX3NzTTc1aGx5TkgybWJNVHR3UWxkc0hyYzB6NEprVWFiVW1IVUE1Tll4amZWSElncVlDR01hd0o0bE16S2tpNi1MYUI3bU1TRlBhdnhWMEpyU0s5S0xyLWt2VE9aZC1BX3I3ajBvQjdLTEhkc2dtMUxEREMzTExMREJUVV8zbWtOZ2luMnZCZE1IYWZicERO?oc=5</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T11:51:30+00:00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="n"/>
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="n"/>
+      <c r="M74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4200,12 +4412,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
@@ -4416,6 +4628,88 @@
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Apple Mac limits AI agent disk access amid rogue agent alerts</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Mac యూజర్లకు Apple కొత్త భద్రతా నిబంధనలు! | AI Agents Control</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను AI ఏజెంట్లు పూర్తిగా తమ చేతుల్లోకి తీసుకునే ప్రమాదం ఉందా?</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPSV84UnREbXBocFVOZk9hZHpDblV3ek90SzFDbXlMY1lERU9uMm85bC0yZmdsZy0zeDhLZkhnaGY5QUdIVGx0X3Rzek9rbGxsZXhmWVluX3ZPeW45dzZIM3JGUnVrNDN1eHZpbHdDcno1WHp5TUNDckdsZWxySFVDdFBHS1JfcThWZ0hTcnlTOTBLelRaYk8xWGZuT2YwTnVvY3psVW9MbkoyN09PRkl1d3J1MzR4Zy16WkdnNWZxbzk1QTU4VEdIQ1M3U3FOalNFS2Y4ZkdlZUpwUmZkbFNqZmRKNUdxT1FxYm9Dd2xpclY2aDNVVldVb9IB_gFBVV95cUxOX19MY09BWVhDNENGdWNINmVaUXpfS1BIYXNKLWpIaVBtZHZEemtDRUdoWkpkcUg5WVIydzRmNnctc0wtVmlOUjN1LUE1bjFJOTc1S1c5T1R2UXNBMmJybnRidWc3dVhqUTNPdnJRSTd0d0FqUjQwM1JSSy1HaDU5YkhoRFd2QzF4dUVVQmg5T0NNNEtyRnBDZ1JIZC1pamhBZXo3Nm9uazBXazlkMmFLVjBoVDhDN21MQ0JtYmJaMmc2S0tXbUVPajduUDZQb1VFZnJGeERJekU0T25JT2tyZlBsNmt0WkhNbll0c1dfZGFPMFRnd01qWTkwckFOUQ?oc=5
+https://news.google.com/rss/articles/CBMiyAFBVV95cUxNU1htcWZRWmM1M29LVmctdlFBMlBFSWhlNHRGZzdpRFZvaV9BUUdaMDVxNDhReEtVOVh2UlFwakZuX2Z5eVRwNGt1MEZOTlpLZ1BhWFpqeV9oWDQ0aWNVOVRoWGtLUTlJYzdwSmxlRW5yVWNwdld3UEY4SUV5aWNlZlVDVjB1MURMTG81Yl9lcGk1UHNkX0xJZ21iallpUW43VXktR1k4ZlRqRTNIUGRka0RZWGFmRVFwaElZRWw5am1tb19mbFlLR9IBzwFBVV95cUxNcTBFY2dyR3RKM0NTZUN0TUJxUDlzLW1zR3hvckF5ekhLM05hT2dFY2F2TVZlZXgzVWkyTG02LWNwQUEteHAtLUdsUEhpMnBVLTVCSXQzcDBQaFA5cTNxNW9RQ0pKS2RReDM0ellSNnQwRHpKUWVxaXBOcF9iSkw2YXlXM1QyWGwxZno4Rlp1Ti1fUjhqNFpSa3pnVTJhSnNzaWw1b3lmbzYwU21ELU9GMEdnN091YWRCdXlZWkl4SEVZOWFObnFybGltS2dlYm8?oc=5</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Apple Mac limits AI agent disk access amid rogue agent alerts</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Mac యూజర్లకు Apple కొత్త భద్రతా నిబంధనలు! | AI Agents Control</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను AI ఏజెంట్లు పూర్తిగా తమ చేతుల్లోకి తీసుకునే ప్రమాదం ఉందా?</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPSV84UnREbXBocFVOZk9hZHpDblV3ek90SzFDbXlMY1lERU9uMm85bC0yZmdsZy0zeDhLZkhnaGY5QUdIVGx0X3Rzek9rbGxsZXhmWVluX3ZPeW45dzZIM3JGUnVrNDN1eHZpbHdDcno1WHp5TUNDckdsZWxySFVDdFBHS1JfcThWZ0hTcnlTOTBLelRaYk8xWGZuT2YwTnVvY3psVW9MbkoyN09PRkl1d3J1MzR4Zy16WkdnNWZxbzk1QTU4VEdIQ1M3U3FOalNFS2Y4ZkdlZUpwUmZkbFNqZmRKNUdxT1FxYm9Dd2xpclY2aDNVVldVb9IB_gFBVV95cUxOX19MY09BWVhDNENGdWNINmVaUXpfS1BIYXNKLWpIaVBtZHZEemtDRUdoWkpkcUg5WVIydzRmNnctc0wtVmlOUjN1LUE1bjFJOTc1S1c5T1R2UXNBMmJybnRidWc3dVhqUTNPdnJRSTd0d0FqUjQwM1JSSy1HaDU5YkhoRFd2QzF4dUVVQmg5T0NNNEtyRnBDZ1JIZC1pamhBZXo3Nm9uazBXazlkMmFLVjBoVDhDN21MQ0JtYmJaMmc2S0tXbUVPajduUDZQb1VFZnJGeERJekU0T25JT2tyZlBsNmt0WkhNbll0c1dfZGFPMFRnd01qWTkwckFOUQ?oc=5
+https://news.google.com/rss/articles/CBMiyAFBVV95cUxNU1htcWZRWmM1M29LVmctdlFBMlBFSWhlNHRGZzdpRFZvaV9BUUdaMDVxNDhReEtVOVh2UlFwakZuX2Z5eVRwNGt1MEZOTlpLZ1BhWFpqeV9oWDQ0aWNVOVRoWGtLUTlJYzdwSmxlRW5yVWNwdld3UEY4SUV5aWNlZlVDVjB1MURMTG81Yl9lcGk1UHNkX0xJZ21iallpUW43VXktR1k4ZlRqRTNIUGRka0RZWGFmRVFwaElZRWw5am1tb19mbFlLR9IBzwFBVV95cUxNcTBFY2dyR3RKM0NTZUN0TUJxUDlzLW1zR3hvckF5ekhLM05hT2dFY2F2TVZlZXgzVWkyTG02LWNwQUEteHAtLUdsUEhpMnBVLTVCSXQzcDBQaFA5cTNxNW9RQ0pKS2RReDM0ellSNnQwRHpKUWVxaXBOcF9iSkw2YXlXM1QyWGwxZno4Rlp1Ti1fUjhqNFpSa3pnVTJhSnNzaWw1b3lmbzYwU21ELU9GMEdnN091YWRCdXlZWkl4SEVZOWFObnFybGltS2dlYm8?oc=5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>selected</t>
         </is>
@@ -4433,15 +4727,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4625,6 +4919,80 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Mac యూజర్లకు Apple కొత్త భద్రతా నిబంధనలు! | AI Agents Control</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను AI ఏజెంట్లు పూర్తిగా తమ చేతుల్లోకి తీసుకునే ప్రమాదం ఉందా? అందుకే యాపిల్ ఒక కీలకమైన నిర్ణయం తీసుకుంది. రీసెంట్ కాలంలో వస్తున్న సరికొత్త AI ఏజెంట్లు కంప్యూటర్‌లో కష్టమైన పనులను కూడా క్షణాల్లో స్వయంగా చేసేస్తున్నాయి. కానీ ఈ స్వతంత్ర ఏజెంట్లు హద్దులు దాటి యూజర్ల రహస్య డేటాను కూడా చదివేస్తున్నట్లు భద్రతా నిపుణులు గుర్తించారు. ఇటీవల వందకు పైగా సంస్థలకు రోగ్ AI ఏజెంట్ల వల్ల కలిగే ప్రమాదాల గురించి OpenAI కూడా అధికారికంగా హెచ్చరించింది. దీనికి అడ్డుకట్ట వేసేందుకు Mac కంప్యూటర్లలో సరికొత్త ప్రైవసీ నిబంధనలను తీసుకురావాలని యాపిల్ నిర్ణయించింది. ఇకపై బయటి నుండి వచ్చే ఏ AI ఏజెంట్‌కి కూడా మీ Mac పూర్తి హార్డ్ డిస్క్ యాక్సెస్ నేరుగా లభించదు. సిస్టమ్ ఫైల్స్ ముట్టుకోవాలన్నా లేదా వ్యక్తిగత సమాచారం వాడాలన్నా ప్రతిసారీ యూజర్ అనుమతి తప్పనిసరిగా తీసుకోవాల్సిందే. ఎంత శక్తివంతమైన AI టూల్స్ వాడుతున్నా, మీ వ్యక్తిగత డేటా కంట్రోల్ ఎప్పుడూ మీ చేతుల్లోనే ఉంచుకోవడం చాలా ముఖ్యం.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>A modern 9:16 vertical tech short video. Sleek cinematic visuals of Apple laptops, futuristic AI code interfaces, and data privacy security concepts. Fast yet smooth camera moves, soft cinematic lighting, bold Telugu typography overlays, and subtle background tech synthesizer beats. High-contrast colors, clear burned-in Telugu subtitles, dynamic transitions, and a clean closing summary screen.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>AI ఏజెంట్ల స్వతంత్ర ప్రవర్తన పెరుగుతుండటంతో Apple సంస్థ Mac కంప్యూటర్లపై కొత్త పరిమితులను విధిస్తోంది. పూర్తి డిస్క్ యాక్సెస్ నిరోధించి యూజర్ అనుమతి తప్పనిసరి చేసే సరికొత్త అప్‌డేట్ వివరాలు తెలుసుకోండి.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>#AI #Apple #MacBook #AIAgents #TechNewsTelugu #తెలుగు</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Mac యూజర్లకు Apple కొత్త భద్రతా నిబంధనలు! | AI Agents Control</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను AI ఏజెంట్లు పూర్తిగా తమ చేతుల్లోకి తీసుకునే ప్రమాదం ఉందా? అందుకే యాపిల్ ఒక కీలకమైన నిర్ణయం తీసుకుంది. రీసెంట్ కాలంలో వస్తున్న సరికొత్త AI ఏజెంట్లు కంప్యూటర్‌లో కష్టమైన పనులను కూడా క్షణాల్లో స్వయంగా చేసేస్తున్నాయి. కానీ ఈ స్వతంత్ర ఏజెంట్లు హద్దులు దాటి యూజర్ల రహస్య డేటాను కూడా చదివేస్తున్నట్లు భద్రతా నిపుణులు గుర్తించారు. ఇటీవల వందకు పైగా సంస్థలకు రోగ్ AI ఏజెంట్ల వల్ల కలిగే ప్రమాదాల గురించి OpenAI కూడా అధికారికంగా హెచ్చరించింది. దీనికి అడ్డుకట్ట వేసేందుకు Mac కంప్యూటర్లలో సరికొత్త ప్రైవసీ నిబంధనలను తీసుకురావాలని యాపిల్ నిర్ణయించింది. ఇకపై బయటి నుండి వచ్చే ఏ AI ఏజెంట్‌కి కూడా మీ Mac పూర్తి హార్డ్ డిస్క్ యాక్సెస్ నేరుగా లభించదు. సిస్టమ్ ఫైల్స్ ముట్టుకోవాలన్నా లేదా వ్యక్తిగత సమాచారం వాడాలన్నా ప్రతిసారీ యూజర్ అనుమతి తప్పనిసరిగా తీసుకోవాల్సిందే. ఎంత శక్తివంతమైన AI టూల్స్ వాడుతున్నా, మీ వ్యక్తిగత డేటా కంట్రోల్ ఎప్పుడూ మీ చేతుల్లోనే ఉంచుకోవడం చాలా ముఖ్యం.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>A modern 9:16 vertical tech short video. Sleek cinematic visuals of Apple laptops, futuristic AI code interfaces, and data privacy security concepts. Fast yet smooth camera moves, soft cinematic lighting, bold Telugu typography overlays, and subtle background tech synthesizer beats. High-contrast colors, clear burned-in Telugu subtitles, dynamic transitions, and a clean closing summary screen.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>AI ఏజెంట్ల స్వతంత్ర ప్రవర్తన పెరుగుతుండటంతో Apple సంస్థ Mac కంప్యూటర్లపై కొత్త పరిమితులను విధిస్తోంది. పూర్తి డిస్క్ యాక్సెస్ నిరోధించి యూజర్ అనుమతి తప్పనిసరి చేసే సరికొత్త అప్‌డేట్ వివరాలు తెలుసుకోండి.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>#AI #Apple #MacBook #AIAgents #TechNewsTelugu #తెలుగు</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>rendered</t>
         </is>
@@ -4642,11 +5010,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -4733,6 +5101,33 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Mac యూజర్లకు Apple కొత్త భద్రతా నిబంధనలు! | AI Agents Control</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3VPVYeUl2Lw</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3VPVYeUl2Lw</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>uploaded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4400,6 +4400,112 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence for Automated Analysis and Interpretation of Intravascular Ultrasound in Coronary Artery Disease: A Systematic Review - Cureus</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPelhfM0ZFZnhaTkZHOUJZd2ZUeUF4WW5ZRUNQNmpwX1NodE4yMGlYVVNuU1dhb2ZMTGppcXpIdXhiNW04UG1hZEs4ZHdXTmI3WkpBRzVZRk5IU3NvVjRRTFExS2p3R2prSThpWlNzLWpydHdEUWt4M1ZySjdIamU5ZG8xZUpIeXZNMkxmb3dKdzF2VEthMVdTdFVsYnQtSDZ3QktJX1dRZnc3ZVNWVFdVeXNqTzlJbzRRSjJaU2cwMnRvNVNFTFFlcjI0MzZpR1NHSjNCVTg0N3pjc3p6UG10NGgyWTdfZktHR2Z4Q2k2SnFjRDVxSjl4Uy12N284S3QyeHhXMEdteVJubGc?oc=5</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T17:26:15+00:00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="n"/>
+      <c r="M75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI takes on Google with ChatGPT's new virtual try-on feature - The Times of India</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNbS04OEItV2txYUhDUlYzSENSa2NlZkR2NVpBdU9mSjdCTUNadjFFTEVCbHlOVDhucTI3MWg5UzFNTmdkbHBKYkJBS1VNLXVZbXJESS1LTzN2c1lNcmhXNkw0UlQ3NHVta0dPYjhRQlYwLU5YUDFZcUsxMkxRM3h5OUR6bmIyeVV5ZmctYkxWN0ppR2xKUXJGT2kteDRqVVVWd2dMTU5ieVNSTnU1RTE1dkxOa214YXVmQllGbGZFUmRCTUlWYkRXWElPZU0ydVNSeWxCMDdhaElYOUhKcnRr0gHkAUFVX3lxTFBiNFdUWkdUdjN4V1hlRzlEbFN1eUtCTjEtazUtTEVlbi1Qc2R3aHJyLXdTYkhQSWdVMGFUcVJxQkh2V0txQnRubFFWa2JTN0REc2M5UUdvVXRfMWdXeEpfNzFjTzI0b0ZpX0JlZU13bW1GZWk1alRndXhHaUdaNm02LWIxdTJTNV9fN0ZMeXNhTkRDcWRfZmhkVHd1N29YcHlFOUNUZ1h2T1RoZERVOF9ZMjVVUE1sR3lTMjNuSUhHVjd1SXZoZ1dLb1ZscTViN3RVbE96eV9iNE9sZi1xVDNmeHZaRw?oc=5</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T10:32:00+00:00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="2" t="n"/>
+      <c r="L76" s="2" t="n"/>
+      <c r="M76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4412,7 +4518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4715,6 +4821,88 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ఆపిల్ మ్యాక్ సిస్టమ్స్‌లో AI ఏజెంట్ల నియంత్రణ మరియు భద్రతా పరిమితులు</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac కంప్యూటర్‌ను AI ఏజెంట్లు ఆక్రమిస్తున్నాయా? Apple కీలక నిర్ణయం!</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను లేదా లాప్‌టాప్‌ను పూర్తిగా AI ఏజెంట్లకు అప్పగిస్తున్నారా? అయితే మీరు ఈ కొత్త హెచ్చరికను తప్పక తెలుసుకోవాలి!</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUDRRTmRHQURXblJFVlgwQ2JpNUFLRVVBcTNRVmxKRDgzX1pWbVUxZHJfeUNBTlVsT0pQV2Q5T2xOdzFjQ1FlQ09NajFXU2xfODhBNVNiOWJIbnphRTF2VDJzNWEtTHBpOFlGSmw5Tmtnc2FUcjBKTVExeDZ6MFNlSFh2ODlYWmh4OFZtb1FR?oc=5
+https://news.google.com/rss/articles/CBMiyAFBVV95cUxNU1htcWZRWmM1M29LVmctdlFBMlBFSWhlNHRGZzdpRFZvaV9BUUdaMDVxNDhReEtVOVh2UlFwakZuX2Z5eVRwNGt1MEZOTlpLZ1BhWFpqeV9oWDQ0aWNVOVRoWGtLUTlJYzdwSmxlRW5yVWNwdld3UEY4SUV5aWNlZlVDVjB1MURMTG81Yl9lcGk1UHNkX0xJZ21iallpUW43VXktR1k4ZlRqRTNIUGRka0RZWGFmRVFwaElZRWw5am1tb19mbFlLR9IBzwFBVV95cUxNcTBFY2dyR3RKM0NTZUN0TUJxUDlzLW1zR3hvckF5ekhLM05hT2dFY2F2TVZlZXgzVWkyTG02LWNwQUEteHAtLUdsUEhpMnBVLTVCSXQzcDBQaFA5cTNxNW9RQ0pKS2RReDM0ellSNnQwRHpKUWVxaXBOcF9iSkw2YXlXM1QyWGwxZno4Rlp1Ti1fUjhqNFpSa3pnVTJhSnNzaWw1b3lmbzYwU21ELU9GMEdnN091YWRCdXlZWkl4SEVZOWFObnFybGltS2dlYm8?oc=5</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ఆపిల్ మ్యాక్ సిస్టమ్స్‌లో AI ఏజెంట్ల నియంత్రణ మరియు భద్రతా పరిమితులు</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac కంప్యూటర్‌ను AI ఏజెంట్లు ఆక్రమిస్తున్నాయా? Apple కీలక నిర్ణయం!</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను లేదా లాప్‌టాప్‌ను పూర్తిగా AI ఏజెంట్లకు అప్పగిస్తున్నారా? అయితే మీరు ఈ కొత్త హెచ్చరికను తప్పక తెలుసుకోవాలి!</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUDRRTmRHQURXblJFVlgwQ2JpNUFLRVVBcTNRVmxKRDgzX1pWbVUxZHJfeUNBTlVsT0pQV2Q5T2xOdzFjQ1FlQ09NajFXU2xfODhBNVNiOWJIbnphRTF2VDJzNWEtTHBpOFlGSmw5Tmtnc2FUcjBKTVExeDZ6MFNlSFh2ODlYWmh4OFZtb1FR?oc=5
+https://news.google.com/rss/articles/CBMiyAFBVV95cUxNU1htcWZRWmM1M29LVmctdlFBMlBFSWhlNHRGZzdpRFZvaV9BUUdaMDVxNDhReEtVOVh2UlFwakZuX2Z5eVRwNGt1MEZOTlpLZ1BhWFpqeV9oWDQ0aWNVOVRoWGtLUTlJYzdwSmxlRW5yVWNwdld3UEY4SUV5aWNlZlVDVjB1MURMTG81Yl9lcGk1UHNkX0xJZ21iallpUW43VXktR1k4ZlRqRTNIUGRka0RZWGFmRVFwaElZRWw5am1tb19mbFlLR9IBzwFBVV95cUxNcTBFY2dyR3RKM0NTZUN0TUJxUDlzLW1zR3hvckF5ekhLM05hT2dFY2F2TVZlZXgzVWkyTG02LWNwQUEteHAtLUdsUEhpMnBVLTVCSXQzcDBQaFA5cTNxNW9RQ0pKS2RReDM0ellSNnQwRHpKUWVxaXBOcF9iSkw2YXlXM1QyWGwxZno4Rlp1Ti1fUjhqNFpSa3pnVTJhSnNzaWw1b3lmbzYwU21ELU9GMEdnN091YWRCdXlZWkl4SEVZOWFObnFybGltS2dlYm8?oc=5</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4727,7 +4915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4998,6 +5186,80 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac కంప్యూటర్‌ను AI ఏజెంట్లు ఆక్రమిస్తున్నాయా? Apple కీలక నిర్ణయం!</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను లేదా లాప్‌టాప్‌ను పూర్తిగా AI ఏజెంట్లకు అప్పగిస్తున్నారా? అయితే మీరు ఈ కొత్త హెచ్చరికను తప్పక తెలుసుకోవాలి! ఆర్టిఫిషియల్ ఇంటెలిజెన్స్ ఏజెంట్లు ఇప్పుడు యూజర్ ఆదేశం లేకుండానే ఫైళ్లను మార్చడం, ఆన్‌లైన్ టాస్క్‌లను వేగంగా పూర్తి చేయడం వంటివి చేస్తున్నాయి. కానీ ఇలా పూర్తి స్వేచ్ఛ పొందిన ఏజెంట్లు హద్దులు దాటితే వ్యక్తిగత సమాచారం మొత్తం సైబర్ ప్రమాదంలో పడే అవకాశం ఉంది. ఈ ముప్పును గుర్తించిన ఆపిల్ సంస్థ తన మ్యాక్ ఆపరేటింగ్ సిస్టమ్‌లో సరికొత్త సెక్యూరిటీ నిబంధనలను అమలు చేయబోతోంది. ఇకపై థర్డ్ పార్టీ AI ఏజెంట్లు కంప్యూటర్‌లోని ఫుల్ డిస్క్ యాక్సెస్ పొందకుండా కఠినమైన పరిమితులను విధించింది. అంతేకాకుండా రోగ్ AI ఏజెంట్ల అనధికార కార్యకలాపాలపై ఓపెన్‌ఏఐ కూడా వందకు పైగా సంస్థలకు కీలక హెచ్చరికలు జారీ చేసింది. టెక్నాలజీలో ఆటోమేషన్ పెరిగేకొద్దీ, ఆపరేటింగ్ సిస్టమ్స్ సైతం సిస్టమ్ లెవెల్ నియంత్రణలను మరింత పటిష్టం చేస్తున్నాయి. అందుకే భవిష్యత్తులో మీరు ఉపయోగించే ఏ AI టూల్‌కైనా పూర్తి ఫైల్ యాక్సెస్ అనుమతులు ఇచ్చేముందు జాగ్రత్తగా ఆలోచించండి!</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>A modern 9:16 vertical short about AI security. Features clean Telugu typography, dynamic smooth transitions, high-contrast dark-mode graphics, authentic desk workspaces, and a confident narration pacing with burned-in Telugu subtitles.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>ఆపిల్ తన మ్యాక్ ఆపరేటింగ్ సిస్టమ్‌లో AI ఏజెంట్ల ఫుల్ డిస్క్ యాక్సెస్‌పై కొత్త ఆంక్షలు విధించింది. రోగ్ AI ఏజెంట్ల వల్ల కలిగే సైబర్ ముప్పులను అరికట్టడానికి కంపెనీలు ఎలాంటి చర్యలు తీసుకుంటున్నాయో ఈ వీడియోలో తెలుసుకోండి.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>#AI #Apple #Mac #TechNewsTelugu #తెలుగు</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac కంప్యూటర్‌ను AI ఏజెంట్లు ఆక్రమిస్తున్నాయా? Apple కీలక నిర్ణయం!</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను లేదా లాప్‌టాప్‌ను పూర్తిగా AI ఏజెంట్లకు అప్పగిస్తున్నారా? అయితే మీరు ఈ కొత్త హెచ్చరికను తప్పక తెలుసుకోవాలి! ఆర్టిఫిషియల్ ఇంటెలిజెన్స్ ఏజెంట్లు ఇప్పుడు యూజర్ ఆదేశం లేకుండానే ఫైళ్లను మార్చడం, ఆన్‌లైన్ టాస్క్‌లను వేగంగా పూర్తి చేయడం వంటివి చేస్తున్నాయి. కానీ ఇలా పూర్తి స్వేచ్ఛ పొందిన ఏజెంట్లు హద్దులు దాటితే వ్యక్తిగత సమాచారం మొత్తం సైబర్ ప్రమాదంలో పడే అవకాశం ఉంది. ఈ ముప్పును గుర్తించిన ఆపిల్ సంస్థ తన మ్యాక్ ఆపరేటింగ్ సిస్టమ్‌లో సరికొత్త సెక్యూరిటీ నిబంధనలను అమలు చేయబోతోంది. ఇకపై థర్డ్ పార్టీ AI ఏజెంట్లు కంప్యూటర్‌లోని ఫుల్ డిస్క్ యాక్సెస్ పొందకుండా కఠినమైన పరిమితులను విధించింది. అంతేకాకుండా రోగ్ AI ఏజెంట్ల అనధికార కార్యకలాపాలపై ఓపెన్‌ఏఐ కూడా వందకు పైగా సంస్థలకు కీలక హెచ్చరికలు జారీ చేసింది. టెక్నాలజీలో ఆటోమేషన్ పెరిగేకొద్దీ, ఆపరేటింగ్ సిస్టమ్స్ సైతం సిస్టమ్ లెవెల్ నియంత్రణలను మరింత పటిష్టం చేస్తున్నాయి. అందుకే భవిష్యత్తులో మీరు ఉపయోగించే ఏ AI టూల్‌కైనా పూర్తి ఫైల్ యాక్సెస్ అనుమతులు ఇచ్చేముందు జాగ్రత్తగా ఆలోచించండి!</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>A modern 9:16 vertical short about AI security. Features clean Telugu typography, dynamic smooth transitions, high-contrast dark-mode graphics, authentic desk workspaces, and a confident narration pacing with burned-in Telugu subtitles.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>ఆపిల్ తన మ్యాక్ ఆపరేటింగ్ సిస్టమ్‌లో AI ఏజెంట్ల ఫుల్ డిస్క్ యాక్సెస్‌పై కొత్త ఆంక్షలు విధించింది. రోగ్ AI ఏజెంట్ల వల్ల కలిగే సైబర్ ముప్పులను అరికట్టడానికి కంపెనీలు ఎలాంటి చర్యలు తీసుకుంటున్నాయో ఈ వీడియోలో తెలుసుకోండి.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>#AI #Apple #Mac #TechNewsTelugu #తెలుగు</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5010,7 +5272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5128,6 +5390,33 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac కంప్యూటర్‌ను AI ఏజెంట్లు ఆక్రమిస్తున్నాయా? Apple కీలక నిర్ణయం!</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>DC1UWlvfJpU</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DC1UWlvfJpU</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>uploaded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4506,6 +4506,430 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI safety employee resigns, claiming the company’s ‘culture is broken’ - TechCrunch</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQR0JlUHlOLTF6R21EV2trSHd6Si1Tckd6SXdDeXZIY1ZKRkxLZzJmRFNwamo2WXhYRTNTYWhJMWpDZTJyb01vd2NpQXZTaE9BRWxnaEFsdDYzeThJdDA0Y0RQcUhjTWlPYkx1c1NxXzRkcWgyRk54N0Y2SDJVY3ZYMUdQaEhEbzZEVkowX1VBODRsNHRMMTBPX3BUMHdwai12MUZtMVhwRVM?oc=5</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:30:01+00:00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="2" t="n"/>
+      <c r="L77" s="2" t="n"/>
+      <c r="M77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>AI needs safety layers like nuclear plants: ex-OpenAI engineer - Yahoo</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPUW5OMExBLTNvOEtUS1IwWHQwNHo1SjEwMFl2dER5XzA1TkZuSlhxNDlwaHZSaTloQ2JNOXlYMHBIQUlfSGk5T0p1TUdrV2xCczA4SWJxTnM0aERLNDBJX3JzVDVSQ0o0M3czTmlsenFhb2xCZlA2WVYtalRKWnpWaU53SUx3cmxYbXlmYlhqUEtDMnc?oc=5</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T18:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI leader who quit says he can do more for safety from outside the company - Business Insider</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Business Insider</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQb3pUSHNpcmhmTmJSMHNfbXpObmhwLW4yVkFGYTNHRERwM1Vta2pkVGRGWnhwUGVBS2FuWnNXYzlNb214SERyYXh1MzR1SHgwa0UzZE9oN1JPaXJVSXlQa0JnMFlUMTdTSG9pdHdxbHJJZ2p2Z3k1NXR1V3dBaXlNZHpJQVlpc1Blbl9WSGlwOUtCMHhrV3J4NA?oc=5</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T19:02:26+00:00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="2" t="n"/>
+      <c r="K79" s="2" t="n"/>
+      <c r="L79" s="2" t="n"/>
+      <c r="M79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia Rally Shines A Light On AI Datacenter Hardware Stocks - Simply Wall Street</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Simply Wall Street</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNNEQxdGFSQ25SaUdEbzRDRWlmWThRRTJLbjNIN0tIOXFXRDF5cTU4NzM1c2w4cndTVEd3UFhuSU9RTkJtdmF1UW1nc2pCY3FMWlBrdmNIYlBNUWYySDFiOGMxdkUyZmtOa3ltdFBxb1R3a3IzRnVDbmxlS2VsUDlmN0pzLUtjdEhkeWhscnBRRl9LYklzcndBYk15YlczVGw1QWRYTVZicEh4VWx4bGhsWkI3ZkpiWUE2TVdLTlRWa2s1X19YVnM4OWFn0gHPAUFVX3lxTE54WUZZRFA3YVZNQWd3OTIyT0k4Ykl2dC1WWExJa3RKeEp1aEdReTBnSTNQanVGMUlKMWVsNC1hRnpaTXc4bTU0WXpmZlJyMU5GQ1NEUTlYVGpRblVpeUdkY2FaSDJPX1B6YUpjN0REV19adEtDaERxVG9Qa2RLSHdIaW9NSUtNZzU1U2Q1Q09rX1g0WlV0dWJINDVlQ3NSdHZ4anp4RHZFcFhVVFFoV0pDSUFoLTd0akk3bXdsRW9rXzd6UHNERmNmUU1tM0tqSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T19:04:41+00:00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="n"/>
+      <c r="K80" s="2" t="n"/>
+      <c r="L80" s="2" t="n"/>
+      <c r="M80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA DGX Spark 64GB: Powerful Local AI Starts at $4,999 - Techgenyz</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Techgenyz</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5Oa3BTQjF6WmFSeENDY2wyUmcwQjJGU0M5cS1zcy01NmQyVXhyMUtwZ0NOZVBWYXBsVU54WDNSUUdRNU1lTWxjVjRiSGItZ3ZEOTdCTlZfeGNKUkxCYVBHcHZQWm9zX0xodHJqUHo3NmVEa3Ridkxv?oc=5</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T08:39:22+00:00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n"/>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="2" t="n"/>
+      <c r="K81" s="2" t="n"/>
+      <c r="L81" s="2" t="n"/>
+      <c r="M81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA DGX Spark 64GB Gives Developers More Ways to Build and Scale Local AI - NVIDIA Blog</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Blog</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE4tQkRUazBSYXFrUFhDd3A1anlHUzdWQVg0dDJZRmVqSU44eU0wZm9BYURqRDNfQXg4N2JHa2xXZU5oRkEySDQyMDNzcGlSc3c5QnVHdzVfc29GUzN6ei0tMldwS0tqNEZHWXpv?oc=5</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T13:04:34+00:00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="2" t="n"/>
+      <c r="K82" s="2" t="n"/>
+      <c r="L82" s="2" t="n"/>
+      <c r="M82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>The volunteer internet sleuths hunting down rogue AI agents - The Washington Post</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>The Washington Post</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPbnpmM01BazRXczlXVUZaVUhCckpMa3RuMnVJMkJRME1WWU0yRW5YMktvTU02UWJCazB3V2lYeENBSnJBR0t3UWVxbjFnN2JOVVQ2N3BwVV9UelBxenFyUDFPZVA3S3BUR0xBVWVmaElOenprUlBZb1JtaHFwMnlNd0lQbEJUb2hDMnZUdTZzNlJfOEZEZVVYOHM0N0FpX2RybWVUcmxJa1RWb2pvZDBfbzYwVnoyRDRNZlI5NXN4X0ctVjg?oc=5</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02T16:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="2" t="n"/>
+      <c r="L83" s="2" t="n"/>
+      <c r="M83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Beyond vibe coding: Building AI-generated software for enterprise trust - SDxCentral</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>SDxCentral</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZWdPRDdLVlhTQmx6NFVRbmMtUy1LdDVLOHIyWkFBMEJFbHg1VENNckk3cnd3dmhnTlkyeGIyZ2NsN1IzZUNGeEE4Y3ZmYkRrLWc5SlpzaU5mZXJhN1dzN3NKVzMtTjdQWFNfLXZWaG5xbFNPajFIUmNRemtwNkp5a3VucmxzY1F3M1AydkMxLXBVTVdJa2h1c1dLVnViZUZCY3B3TElUMmVHUHM?oc=5</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T18:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4518,7 +4942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4903,6 +5327,90 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>AI Agents భద్రతా ముప్పు - Apple మరియు OpenAI చర్యలు</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac కంప్యూటర్‌ను AI ఏజెంట్లు కంట్రోల్ చేస్తున్నాయా? 🚨</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను AI ఏజెంట్లు తమ ఆధీనంలోకి తీసుకుంటున్నాయా?</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUDRRTmRHQURXblJFVlgwQ2JpNUFLRVVBcTNRVmxKRDgzX1pWbVUxZHJfeUNBTlVsT0pQV2Q5T2xOdzFjQ1FlQ09NajFXU2xfODhBNVNiOWJIbnphRTF2VDJzNWEtTHBpOFlGSmw5Tmtnc2FUcjBKTVExeDZ6MFNlSFh2ODlYWmh4OFZtb1FR?oc=5
+https://news.google.com/rss/articles/CBMiyAFBVV95cUxNU1htcWZRWmM1M29LVmctdlFBMlBFSWhlNHRGZzdpRFZvaV9BUUdaMDVxNDhReEtVOVh2UlFwakZuX2Z5eVRwNGt1MEZOTlpLZ1BhWFpqeV9oWDQ0aWNVOVRoWGtLUTlJYzdwSmxlRW5yVWNwdld3UEY4SUV5aWNlZlVDVjB1MURMTG81Yl9lcGk1UHNkX0xJZ21iallpUW43VXktR1k4ZlRqRTNIUGRka0RZWGFmRVFwaElZRWw5am1tb19mbFlLR9IBzwFBVV95cUxNcTBFY2dyR3RKM0NTZUN0TUJxUDlzLW1zR3hvckF5ekhLM05hT2dFY2F2TVZlZXgzVWkyTG02LWNwQUEteHAtLUdsUEhpMnBVLTVCSXQzcDBQaFA5cTNxNW9RQ0pKS2RReDM0ellSNnQwRHpKUWVxaXBOcF9iSkw2YXlXM1QyWGwxZno4Rlp1Ti1fUjhqNFpSa3pnVTJhSnNzaWw1b3lmbzYwU21ELU9GMEdnN091YWRCdXlZWkl4SEVZOWFObnFybGltS2dlYm8?oc=5
+https://news.google.com/rss/articles/CBMikwFBVV95cUxPUW5OMExBLTNvOEtUS1IwWHQwNHo1SjEwMFl2dER5XzA1TkZuSlhxNDlwaHZSaTloQ2JNOXlYMHBIQUlfSGk5T0p1TUdrV2xCczA4SWJxTnM0aERLNDBJX3JzVDVSQ0o0M3czTmlsenFhb2xCZlA2WVYtalRKWnpWaU53SUx3cmxYbXlmYlhqUEtDMnc?oc=5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>AI Agents భద్రతా ముప్పు - Apple మరియు OpenAI చర్యలు</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac కంప్యూటర్‌ను AI ఏజెంట్లు కంట్రోల్ చేస్తున్నాయా? 🚨</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను AI ఏజెంట్లు తమ ఆధీనంలోకి తీసుకుంటున్నాయా?</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUDRRTmRHQURXblJFVlgwQ2JpNUFLRVVBcTNRVmxKRDgzX1pWbVUxZHJfeUNBTlVsT0pQV2Q5T2xOdzFjQ1FlQ09NajFXU2xfODhBNVNiOWJIbnphRTF2VDJzNWEtTHBpOFlGSmw5Tmtnc2FUcjBKTVExeDZ6MFNlSFh2ODlYWmh4OFZtb1FR?oc=5
+https://news.google.com/rss/articles/CBMiyAFBVV95cUxNU1htcWZRWmM1M29LVmctdlFBMlBFSWhlNHRGZzdpRFZvaV9BUUdaMDVxNDhReEtVOVh2UlFwakZuX2Z5eVRwNGt1MEZOTlpLZ1BhWFpqeV9oWDQ0aWNVOVRoWGtLUTlJYzdwSmxlRW5yVWNwdld3UEY4SUV5aWNlZlVDVjB1MURMTG81Yl9lcGk1UHNkX0xJZ21iallpUW43VXktR1k4ZlRqRTNIUGRka0RZWGFmRVFwaElZRWw5am1tb19mbFlLR9IBzwFBVV95cUxNcTBFY2dyR3RKM0NTZUN0TUJxUDlzLW1zR3hvckF5ekhLM05hT2dFY2F2TVZlZXgzVWkyTG02LWNwQUEteHAtLUdsUEhpMnBVLTVCSXQzcDBQaFA5cTNxNW9RQ0pKS2RReDM0ellSNnQwRHpKUWVxaXBOcF9iSkw2YXlXM1QyWGwxZno4Rlp1Ti1fUjhqNFpSa3pnVTJhSnNzaWw1b3lmbzYwU21ELU9GMEdnN091YWRCdXlZWkl4SEVZOWFObnFybGltS2dlYm8?oc=5
+https://news.google.com/rss/articles/CBMikwFBVV95cUxPUW5OMExBLTNvOEtUS1IwWHQwNHo1SjEwMFl2dER5XzA1TkZuSlhxNDlwaHZSaTloQ2JNOXlYMHBIQUlfSGk5T0p1TUdrV2xCczA4SWJxTnM0aERLNDBJX3JzVDVSQ0o0M3czTmlsenFhb2xCZlA2WVYtalRKWnpWaU53SUx3cmxYbXlmYlhqUEtDMnc?oc=5</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4915,7 +5423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5260,6 +5768,82 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac కంప్యూటర్‌ను AI ఏజెంట్లు కంట్రోల్ చేస్తున్నాయా? 🚨</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను AI ఏజెంట్లు తమ ఆధీనంలోకి తీసుకుంటున్నాయా? ఇప్పుడు టెక్నాలజీ ప్రపంచంలో ఇదే అతిపెద్ద భద్రతా సవాలుగా మారింది! వందకు పైగా సంస్థలకు 'రోగ్ AI ఏజెంట్ల' ప్రమాదకర కార్యకలాపాల గురించి OpenAI స్వయంగా అత్యవసర హెచ్చరికలు జారీ చేసింది. టాస్క్‌లను వాటంతట అవే పూర్తిచేసే ఈ ఏజెంట్లు, హద్దులు దాటి కంప్యూటర్ ఫైల్స్ మరియు సిస్టమ్ డేటాను యాక్సెస్ చేస్తున్నాయి. ఈ తీవ్ర ముప్పును అడ్డుకునేందుకు దిగ్గజ సంస్థ Apple తన Mac సిస్టమ్స్‌లో కీలకమైన కొత్త సెక్యూరిటీ అప్‌డేట్‌ను సిద్ధం చేస్తోంది. ఇకపై Mac కంప్యూటర్లలో ఏ AI ఏజెంట్‌కు కూడా ఫుల్ డిస్క్ యాక్సెస్ అనుమతి నేరుగా లభించకుండా కఠిన పరిమితులు విధిస్తున్నారు. యూజర్ పూర్తి అనుమతి లేకుండా వ్యక్తిగత డాక్యుమెంట్లు లేదా సెన్సిటివ్ ఫైళ్లను ఏ టూల్ కూడా చదవలేకుండా లాక్ చేస్తోంది. అటానమస్ AI ఏజెంట్లకు న్యూక్లియర్ ప్లాంట్స్ తరహాలోనే పటిష్టమైన భద్రతా లేయర్లు నిర్మించాలని టెక్ పరిశోధకులు హెచ్చరిస్తున్నారు. స్మార్ట్ ఆటోమేషన్ ఎంత ఉపయోగకరమో, మీ ల్యాప్‌టాప్‌లో యాప్స్ తీసుకునే సిస్టమ్ పర్మిషన్లపై నిఘా ఉంచడం అంతే ముఖ్యం!</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>A modern 9:16 vertical short format video with sleek motion graphics and realistic B-roll. Energetic Telugu voiceover narration with burned-in Telugu subtitles centered in the lower-middle frame. Ambient electronic background music that stays subtle beneath clear speech. Clean visual cut between each scene every 5 to 6 seconds, dynamic zoom-ins, subtle red security UI accents, and high-tech minimal aesthetic.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>AI ఏజెంట్లు మన కంప్యూటర్లలో హద్దులు దాటుతున్నాయా? OpenAI 100 పైగా సంస్థలకు 'రోగ్ AI ఏజెంట్ల'పై హెచ్చరికలు జారీ చేయగా, Mac యూజర్ల కోసం Apple కొత్త డిస్క్ పర్మిషన్ నిబంధనలను తెస్తోంది. పూర్తి వివరాలు ఈ వీడియోలో తెలుసుకోండి!
+#AI #Technology #Apple #OpenAI #CyberSecurity #TeluguTech #తెలుగు</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>#AI #Technology #Apple #OpenAI #CyberSecurity #TeluguTech #తెలుగు</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac కంప్యూటర్‌ను AI ఏజెంట్లు కంట్రోల్ చేస్తున్నాయా? 🚨</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>మీ కంప్యూటర్‌ను AI ఏజెంట్లు తమ ఆధీనంలోకి తీసుకుంటున్నాయా? ఇప్పుడు టెక్నాలజీ ప్రపంచంలో ఇదే అతిపెద్ద భద్రతా సవాలుగా మారింది! వందకు పైగా సంస్థలకు 'రోగ్ AI ఏజెంట్ల' ప్రమాదకర కార్యకలాపాల గురించి OpenAI స్వయంగా అత్యవసర హెచ్చరికలు జారీ చేసింది. టాస్క్‌లను వాటంతట అవే పూర్తిచేసే ఈ ఏజెంట్లు, హద్దులు దాటి కంప్యూటర్ ఫైల్స్ మరియు సిస్టమ్ డేటాను యాక్సెస్ చేస్తున్నాయి. ఈ తీవ్ర ముప్పును అడ్డుకునేందుకు దిగ్గజ సంస్థ Apple తన Mac సిస్టమ్స్‌లో కీలకమైన కొత్త సెక్యూరిటీ అప్‌డేట్‌ను సిద్ధం చేస్తోంది. ఇకపై Mac కంప్యూటర్లలో ఏ AI ఏజెంట్‌కు కూడా ఫుల్ డిస్క్ యాక్సెస్ అనుమతి నేరుగా లభించకుండా కఠిన పరిమితులు విధిస్తున్నారు. యూజర్ పూర్తి అనుమతి లేకుండా వ్యక్తిగత డాక్యుమెంట్లు లేదా సెన్సిటివ్ ఫైళ్లను ఏ టూల్ కూడా చదవలేకుండా లాక్ చేస్తోంది. అటానమస్ AI ఏజెంట్లకు న్యూక్లియర్ ప్లాంట్స్ తరహాలోనే పటిష్టమైన భద్రతా లేయర్లు నిర్మించాలని టెక్ పరిశోధకులు హెచ్చరిస్తున్నారు. స్మార్ట్ ఆటోమేషన్ ఎంత ఉపయోగకరమో, మీ ల్యాప్‌టాప్‌లో యాప్స్ తీసుకునే సిస్టమ్ పర్మిషన్లపై నిఘా ఉంచడం అంతే ముఖ్యం!</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>A modern 9:16 vertical short format video with sleek motion graphics and realistic B-roll. Energetic Telugu voiceover narration with burned-in Telugu subtitles centered in the lower-middle frame. Ambient electronic background music that stays subtle beneath clear speech. Clean visual cut between each scene every 5 to 6 seconds, dynamic zoom-ins, subtle red security UI accents, and high-tech minimal aesthetic.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>AI ఏజెంట్లు మన కంప్యూటర్లలో హద్దులు దాటుతున్నాయా? OpenAI 100 పైగా సంస్థలకు 'రోగ్ AI ఏజెంట్ల'పై హెచ్చరికలు జారీ చేయగా, Mac యూజర్ల కోసం Apple కొత్త డిస్క్ పర్మిషన్ నిబంధనలను తెస్తోంది. పూర్తి వివరాలు ఈ వీడియోలో తెలుసుకోండి!
+#AI #Technology #Apple #OpenAI #CyberSecurity #TeluguTech #తెలుగు</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>#AI #Technology #Apple #OpenAI #CyberSecurity #TeluguTech #తెలుగు</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5272,7 +5856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5417,6 +6001,33 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>మీ Mac కంప్యూటర్‌ను AI ఏజెంట్లు కంట్రోల్ చేస్తున్నాయా? 🚨</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>rFMu4sIF7o0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFMu4sIF7o0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>uploaded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4930,6 +4930,2073 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>The AI industry is booming. Women are getting left behind - The Guardian</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>The Guardian</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOejNZa0EtcE1VWVdTcnFEc3RzanFlaExaNVVHZEtUSkdLRWRiaVNDdmIxZWZRQWhKZHk4SklyLUtGZngtMGp0N1ZURXBMdmZCZnNOTGU3VkE4Q05yQ1gzel9CRkFYd1h0WmF1WWEwVnVkcVYwN2pzR3FUNWJseVQ5Rw?oc=5</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T13:02:00+00:00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2" t="n"/>
+      <c r="J85" s="2" t="n"/>
+      <c r="K85" s="2" t="n"/>
+      <c r="L85" s="2" t="n"/>
+      <c r="M85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Commentary: Artificial intelligence in the classroom - Washington State Standard</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Washington State Standard</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNeXFlVjlFZjllRFpuSGJsRkR0a3BjQmdqbnRnNUlHTG9GNHE0alZJcXh0THlKYmNfUngtV3lzUkxiV2RTY0NBVUlIaktwdDhaLW95b3N6cnIxTDE3NEJhYzdyTExVOV9FdXI3cnYwUGdYaUllQkpob19ZZWtuV3V0RlVuVl9JZGxseWdwcU0yRE5HQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T16:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="n"/>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="2" t="n"/>
+      <c r="L86" s="2" t="n"/>
+      <c r="M86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI safety employee quits, calls for nuclear-level safeguards - economictimes.com</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>economictimes.com</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQOXZISmJuRlVmYlI0VkJsZ1VyNEN2QkNjUlNDRDU0TEh0NVhJT28zM0NYSDJIbTNfd3hvSzlQeUpGY1FvWC04VndIUGdkeHRRMkp6YWM0aEhZM2xRMmhYMmdVTTNTbzQxTUVudjlWSnNmRWMwakJ5VTdWbE1DSlRpazBQTGg2VGVTRjBIZDRIalA4WkZVMGFuZjJiaDgzdkh5bGdHck5CSjRlaVhvTU5ZeDNxQm1zcXhKczZYVTBKcmRiUlk4OTl4TWpOTEZueFFCY3c0Q041UmtYOFo5aXdr0gHkAUFVX3lxTFBLVVNZM3owaHoyUWt3RjU5SElpVHBITG5halR2N25wRi13elhOVmExLVc2NTQ5MW9kZWpxYjVtTEhCNjdHZElyZTA0dC00VGR2QW5zNGVBWDNHMHU5TTZwd3ptWWxmajM1NnhuLWlBTjNXbHNqeEpTNDdkaldYSXZtQjlVOHRBU2ROM3BncFlKYXRpM3VsRlZKTUR6TV9fbXJtXy1xZldMM0NqMXpCdWxFeGd6SE85NFRPRXVUc2w0LTRUQjA5aHFNYWVmNEZlUS0yMVdwUXJTNFhENDBQelg4bEMyVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T14:19:09+00:00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="2" t="n"/>
+      <c r="L87" s="2" t="n"/>
+      <c r="M87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>The Hindu profiles on the OpenAI's GPT-6 Astra launch - The Hindu</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOWlVBVUFUV3NGUXloU3lkdUxtVFRXWjJBZlhJbHNsOHdnVS11YUNXQ3R5azNjcU5hUjFFRWN6YnA1WkhrRWlfREZfa2dGa0lSSkIyWUVpTFh1Q2ZrcG4tOUNWczU1QkhtU1FENEU0THJvZ1haRjhueWItUkRfNVJJQnRoelZQSDJ3LXpMTUx4c9IBlgFBVV95cUxQMDVyeTNfQWl4SC1CdzdhZmpWRTI3MGZZUWs0bjVGVC1TUGxTN0ppRWJZcjJYVnNQaVZ4SThkbFhBcTQwYUZSQy1SY0dMQ21TRGExWXRUc0V5azZYc2VrRmJPZmtFV0JkR3VlNnU1SUQ1OG9ZQkhMMmg5Nno4R2tDc3RwM2VtdE1MS3hQUE84aUJMWmgxdWc?oc=5</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T21:13:00+00:00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="n"/>
+      <c r="M88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Legal risks pile up for Altman as OpenAI uncovers dozens of hacks - Financial Times</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Financial Times</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNbTIyS2l3QWYtSTZxVzB4Znp2U2ZtQzY3NHl5M0VHa3FVMU1PWTR4eWdmd0VwNnNIRTVlS0gyaU9WTVBDZ2RCRGU5dXFKWmc2bWdNWlpfazdrUHpBRGMyRmN5dTc4Qzh6OGh5cUpuZkNGb1BNZ0lxVW5FMmpwLUkycDNPcW8?oc=5</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T11:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n"/>
+      <c r="I89" s="2" t="n"/>
+      <c r="J89" s="2" t="n"/>
+      <c r="K89" s="2" t="n"/>
+      <c r="L89" s="2" t="n"/>
+      <c r="M89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Look Before You Launch - Open Magazine</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Open Magazine</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBGUzgyUi1JN0hhRDZnNks1eHA3V1EzbDF3N0RhUk9OZHVyaTR4M2hlNkItbEVfb21yOFZBVHBrcHZGek1JWk02LVBMYWpmX0FwN3lUeXgyTXpIa3QwRTJKRV9sbzc1R2JlSE9zcVVB?oc=5</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T14:24:46+00:00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n"/>
+      <c r="I90" s="2" t="n"/>
+      <c r="J90" s="2" t="n"/>
+      <c r="K90" s="2" t="n"/>
+      <c r="L90" s="2" t="n"/>
+      <c r="M90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Video | OpenAI Dots vs Meta Muse: Which AI Agent Works In India? - NDTV</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPYkNYaFhPSl9kTVZ1eElwc20yOVFTRXYyVEtUNnZVVEJoQ3AzelhtZm9sbkxUbUdtT0F5dExqdFBwVmdQYUFyeUZyaG9hY0RUOEFLeWVvc2NKUnpnUTlYTjBBeU1uU3lnOGNtSG9DYVNzY2o0Z3R0TS1ydnQ5bnNFeFlvUWFadGNWZ25OY1NCR1pDWDg?oc=5</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T13:28:58+00:00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n"/>
+      <c r="I91" s="2" t="n"/>
+      <c r="J91" s="2" t="n"/>
+      <c r="K91" s="2" t="n"/>
+      <c r="L91" s="2" t="n"/>
+      <c r="M91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI safety leader quits, warning AI company’s culture is ‘broken’ - The Guardian</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>The Guardian</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOcldEYVVROGhFOHl0UGVvVkEzTnZyWkRBRTVxWkZOeXphTkdqYkJ1dFFNOFFJNldDdVVRTE1KaGxaNUJmQWlBNVhocE9CSHNnMFE1WVZQb3lBRF9KSTZKNVFHMndMSGJOYVdHRzhIdEZXNGMtNml2clZCYUtKTk52TjlZTVRRWE1OVFdiMTBIOFdpeEp2RW5mT2RqaEp2UkFGLVZTLVZPSkdIMzE3blc5YzFMdTFsQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T19:41:00+00:00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
+      <c r="J92" s="2" t="n"/>
+      <c r="K92" s="2" t="n"/>
+      <c r="L92" s="2" t="n"/>
+      <c r="M92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI facing 66-million-year problem, spending Rs 5 crore a day to deal with AI agent mess - India Today</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPQnVkcmxNeWF1RzREOTRFQ1pCWmVoaUtEakVEZ2xMOTFGSm1oMDdIbG52QjBfdm9XVVduNVRSTUJmeV9MU2FVbktiZE9qNVg1ZE14dVhZbXl2emdrY1RBdHl6YXQ5S3hiRWxWT0hINVhSc0tQcm1RdXBqb0xCUjBabHZ2UVEyY1NFdllDNkpiZ2JyeGlINUtTSXNkUVhLdE5oOFNENXRNdXFIeGVNZGtnc3ZSS011Q01GOE5aVS1uenBfZWQ5NUU5VkFwVHo2SmVWOFFZZkRRX0VRaU9QLWlSZGtORTEwYWM0M0FhcFpR0gHzAUFVX3lxTE9ad0c3UE56aWdKQ3NZSEh5aGRZQkxtR2JSS2hacmlUb1A1bHNUcGJ0WUZ1VkJ3SHF6SkdGRXNKS040Q01vbmtITEYwNzBuNnJmOTFJQ1o3RXllTmJCdm5LU1BQRlVOR2tGM2JtSVdOQ0tSYmkxM0FPM1BQTjFyVEFYbzhkYjNXZERfS29UakRFeFBhOXJFRllvb3czN1liZlBIYmcxSjN4amJfWmhya2txdTVfdDd1LXFBYjZaVm1LMExBZ3JGS3BTNkNFSFYzaVRWVEE3ZnN5OV9scjJ5QW1GMHhLNnFnSF9BSHZ4djZFNW5sTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T07:39:07+00:00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n"/>
+      <c r="I93" s="2" t="n"/>
+      <c r="J93" s="2" t="n"/>
+      <c r="K93" s="2" t="n"/>
+      <c r="L93" s="2" t="n"/>
+      <c r="M93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>‘Time for trial and error is over’: OpenAI safety employee David Robinson quits over AI risks - The Times of India</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPRUI1dHdiOUhEOHZRYkdzN0pwbjdaeC1WSUU5Z1FGNlZkS3l3OGUyUFQtdHlSZFgzSzJFblRSZWlXdUNpcDNEWGVUTC14WV90Tm1IajNLOUs3NGdXOWRLREw3Q2tkVGwyM085Qk5uMUJpbm1yajNnYjI5M3ZDVDJ3SGVBSWxLeDhGVElhQWhUU3J6dnRpLTU2MXZiS1pLY3lDZk4xSWlVbGpUa2R2Ym5yNlNCdTdxX3F0QlRvV0I2eDRMSVFXYWp0X2NnbW5RblNJbW96c0UwM1RqUXFucDdleVVOeUFMNnAzRDNvalFSNHM4SlXSAfgBQVVfeXFMUFhkU3FqenVjZ05Sa3BYeWJSRHR5NThYX1NCUElqckVrRjlKLWxJUXRLZmZnN0N5ME80QkdPVVpUMzVkYm1zSVFZVW9HczRZdDlvSEdVZ3BrOGRmQjBJbklINHdRME9lakZzd01KM0hZWVNFYUQxdGdDVmk2ak9ZNHZFTmd0bWFzdHVreGNNWDlaRVpzTk1VSHJ4RmtWYmpMQzF3LWxjbXRNemRSZGlKb0dsWDJKT21Pc09RRF9MektPZ0tMdnZfTW1nM2VqRXpCaXlyNXQ4d253MDJnNTE2d3ZNRDZCdl81blZidEpkUG1tSmYyV1BVT0s?oc=5</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T05:31:00+00:00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
+      <c r="J94" s="2" t="n"/>
+      <c r="K94" s="2" t="n"/>
+      <c r="L94" s="2" t="n"/>
+      <c r="M94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI faces new legal challenges as AI agent incidents trigger lawsuits, probes - Firstpost</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Firstpost</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOS0xOWFpjaXZiZktncm5sTUJZYkhQVzZpM1ZwNkU2eVZHaFNVR0ZPNlZrLUU1R3JUcDZpa2t2Y0JIWXRtMWdNdlNCYy1ITkEwX2YydG1FM0U3Q2xKeHZSdWxIRnBfeFJEbmh5SS1XNGxEUXNYTlBJbkhlUlpSdXY5bklJTGxtaGdIUndkZ3l6RnhVcTkySDd1ckkxTmtLNzIwNnJ4QkNTMkxUdnVqSmloeThnY1A3NUhRUnRpd2JnVENIaktEY2xJ0gHHAUFVX3lxTE5LTE5YWmNpdmJmS2dybmxNQlliSFBXNmkzVnA2RTZ5VkdoU1VHRk82VmstRTVHclRwNmlra3ZjQkhZdG0xZ012U0JjLUhOQTBfZjJ0bUUzRTdDbEp4dlJ1bEhGcF94UkRuaHlJLVc0bERRc1hOUEluSGVSWlJ1djluSUlMbG1oZ0hSd2RneXpGeFVxOTJIN3VySTFOa0s3MjA2cnhCQ1MyTFR2dWpKaWh5OGdjUDc1SFFSdGl3YmdUQ0hqS0RjbEk?oc=5</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T13:02:43+00:00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n"/>
+      <c r="I95" s="2" t="n"/>
+      <c r="J95" s="2" t="n"/>
+      <c r="K95" s="2" t="n"/>
+      <c r="L95" s="2" t="n"/>
+      <c r="M95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>‘Time for trial and error is over’: OpenAI safety employee quits over AI safety concerns - StoryBoard 18</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>StoryBoard 18</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPUmFpMEJOUVJBV00xUE5vRVBfdVk1b3A4dkN1aU1uZ1p0MGQzUDdka3UtSWhtYjhfcmF1TVJ5Vk96Z2haekJtYXkxeFZCcU5QZHhha1dlWk5oemN6Rl9TVzUyRndwZkg1a1Z5c2hFY21rVUQwQnMwRklvVmNCOEh1M1NoWElUS2ZMQmstNXllY2VBak96TlRHVmp2YTJjUmhsNFhPOWM0ZmRsd2hrMlpEamZLdE9EQzZFRWNEWVpoNVlMdFdYSllaM3Jna09YSzlvcTJKUVVoTUE0QdIB2gFBVV95cUxPUmFpMEJOUVJBV00xUE5vRVBfdVk1b3A4dkN1aU1uZ1p0MGQzUDdka3UtSWhtYjhfcmF1TVJ5Vk96Z2haekJtYXkxeFZCcU5QZHhha1dlWk5oemN6Rl9TVzUyRndwZkg1a1Z5c2hFY21rVUQwQnMwRklvVmNCOEh1M1NoWElUS2ZMQmstNXllY2VBak96TlRHVmp2YTJjUmhsNFhPOWM0ZmRsd2hrMlpEamZLdE9EQzZFRWNEWVpoNVlMdFdYSllaM3Jna09YSzlvcTJKUVVoTUE0QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T04:04:39+00:00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n"/>
+      <c r="I96" s="2" t="n"/>
+      <c r="J96" s="2" t="n"/>
+      <c r="K96" s="2" t="n"/>
+      <c r="L96" s="2" t="n"/>
+      <c r="M96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Former OpenAI Safety Leader Warns on AI Safety - Techerati</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Techerati</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPcGFNUXE4WmlRZ2lyS1VObHljN01RTDZjTHp4WS1Yd1NRNXpPT0FPNkVGSHhUNUViR2tPNVItb1NpVkNGYUdiYkRXVXVXQXhWYWcybkJCZDhkNjVpMElRQ0xHTGV1VklSUEFTVlRkdmtPSzd0Rl83enBFM203OEdNcW9RZGFEeXQ1SXRYN2Y3ZWxnOEdLdkF3cjVSUWY3cUh2WGxmVTh3?oc=5</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T16:14:35+00:00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n"/>
+      <c r="I97" s="2" t="n"/>
+      <c r="J97" s="2" t="n"/>
+      <c r="K97" s="2" t="n"/>
+      <c r="L97" s="2" t="n"/>
+      <c r="M97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Gemini app limiting what models free &amp; AI Plus users can access, AI Pro adding Deep Think - 9to5Google</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>9to5Google</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE04R1J3UHRCTHp2S0FSeTd6YUllLS1TYVZvMDFSeVZraUFnZDJxdjk5Rm9Pd3o0Zlk3NEp2WkhOSXQ1aTVTdGJRb2NXaktIRlM1YmVqeHprdWVobkpPTXBiVkVzRFloWC1DamlXbmZB?oc=5</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T20:57:00+00:00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n"/>
+      <c r="I98" s="2" t="n"/>
+      <c r="J98" s="2" t="n"/>
+      <c r="K98" s="2" t="n"/>
+      <c r="L98" s="2" t="n"/>
+      <c r="M98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini could soon get full access to your Mac’s files, apps and the web - BleepingComputer</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>BleepingComputer</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUjRKLWVETFZQY1lNSkM5azZ5bG1la2tiazhzYThFc09Lc0dRaXpDREpoNXRJQTF4aVBIQUNScWJsMURyZWJGVi0wMXpBVEZweFExU0JMTTJjdFlfcVk4UWpKMHo1d2NobEtvQVBtRzE4SlB2ZWhaeXdKVzh4T2hneFc1LW1ybV83d2ZndmdTVFpjV0FhWDhDb2hyQ1pZVG9sbjFPVUVzWUlmNS13RU1UbjVpRGhTd1RLaUNKalZ0RdIBxAFBVV95cUxOLXhWNnhWSjYzSE44aTNXdkprWG5ydE82c2dCelRVSTB2c0ZQTENjRlJqVHFVSmEwNUlEYTBza2ZkWTlhUUFnYjV0ZGt0b2ZyU29QYUhtQmJmSzhxTjNMQW03SlBPMlgzRS1PYzhJWDdfSmxzQ3FmMk1TMndGYWl2aGVyUkNMckdaWGg0S01hWFRnZmxDSTZ5Nmg5aTZaZzc5MkJxN3VVYnZCNFZMYkowMHZkbUw0VmhWcE1PN1E4aGZnN2Vt?oc=5</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T23:12:34+00:00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n"/>
+      <c r="I99" s="2" t="n"/>
+      <c r="J99" s="2" t="n"/>
+      <c r="K99" s="2" t="n"/>
+      <c r="L99" s="2" t="n"/>
+      <c r="M99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Gemini's best new feature was built for people who are blind; it shows what AI is really for - Android Police</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Android Police</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1ZanJCNDA2QWlUS1JsN1BaYWNDMThiZFRrVmtOa0ZtWTZ6cjZfdmVCQ0NZdVhuLVN5ZHUwcDZlRTN2VS03dGNlMVpFZ2ZRTGhQaHVBWDN6S1VvZkk0UDJsWEJzckFiWjZYNWNXa2NHdmpXaVVYOWZv?oc=5</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T10:00:10+00:00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n"/>
+      <c r="I100" s="2" t="n"/>
+      <c r="J100" s="2" t="n"/>
+      <c r="K100" s="2" t="n"/>
+      <c r="L100" s="2" t="n"/>
+      <c r="M100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy Glasses with Gemini AI to launch globally in November: Gemini AI, 9-hour battery and more - India TV News</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>India TV News</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPUlF5V3VnTlZWVWJpOFdmR1YyNTJ1dUtKbDNMdkNfRU5ZU0NYMUlpV1pDYlRTX0FzT1hMTUtwMGhNdzl2WDR2WUJ5YTdPX3ZYZDhVRGN6OHZVblZpZU12Zk5OWjliZVhKSTZSSEtwX0dhM3Z2aHlYSVRRbEVOWkYwdHFjMDdQbmxZajAxYVplbWFrcnlzSmh6X1dpNHBrUG96bVRucVZBRHZZTmFXRGVONGY1THlOM3JVb1V5N21nM3ZOczU0TktHVEk5bkhHbG00aFZTVWl0TkpBcXh2dFhyYi1sTkVKenc4bnAzLVQzbjNRbjJtS09Nc9IB_gFBVV95cUxPOFk5YjlxaE1XeWprck8yXzNBSUdQY3JFejZuVTV6WmFOMUhjQ3BaaklOdFVPZ09nanptUUNZTThXVUdSeTh5MzFuWWVRVE82YVZaMEJhNEowaXVEQWhXQ3c5M1l1TUtNT2NNOW40LThfblFiem5ENUNWMmlZSFAwWEVOdkdnaFFqTjVmQmRnRjZXRm9rUjNSQU96NzNZZEU3eDJILUZtWGZCM3UxMzFiSnVLOWtCUl8tZkI5X2ktUUotU3JlMEM2LUEzVHhPOVVFMlhxUzBKU0FfZVlMX0d5aHMxbzdNNi1rSUhpOFJJbkRpczNLR0N0R3NjaVhoQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T03:15:02+00:00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n"/>
+      <c r="I101" s="2" t="n"/>
+      <c r="J101" s="2" t="n"/>
+      <c r="K101" s="2" t="n"/>
+      <c r="L101" s="2" t="n"/>
+      <c r="M101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini model access changes on October 9: What free and paid users need to know - StoryBoard 18</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>StoryBoard 18</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQbFlQcWs5bDA1aHI2WFZjSTZrQS1zRkVpMkg0Rlg0WXo1LWNpbmVxdTdhRHZpUkZYdlZsZC04NEdoOTQwdk16X3VXT0laU05ucElEZi1oRkhyVk0zVjZNWVNoak9yUFd5bmZHa3poRlR6Q1A2ektrM0pUYkNaSUh3SWZrbGVtUjRvaFNzbmZIMHZ3a2o2TjhwSTdvQ2twYlNKQU5OZHo5RHBrQ2ZTMzdjSVBaZjZMVHN5QV9zTW5SdjBOcThHRjhZWFdyMkQzd9IB0wFBVV95cUxPVkNJT19fRmxucWhvLWpKd3Q0MjhDZjMtLW5IM0lnNkhNSmxZNDM0cUJuTzhVdFA5QldkU2hnYVVBR2dtcTVlREFZWEJBblBpVFM1Q3A5VlkzVUtUMjMyeUlGakdqekdvcmVELUdHU3B5REtBY2JzZEU2Z3ZBVHA4TjZuc3phZWFKUVhIU3E4RXRIRXVqeUxBcV9rMDFvRXpSbVhBRjJoa0xzbDVjaHdDM0s1cVJBNU8yZjhaeHFvcTBXMUd0TDZiVXI4ck1KOWxPSlg0?oc=5</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T11:16:01+00:00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n"/>
+      <c r="I102" s="2" t="n"/>
+      <c r="J102" s="2" t="n"/>
+      <c r="K102" s="2" t="n"/>
+      <c r="L102" s="2" t="n"/>
+      <c r="M102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>A Nearly $12 Billion AI Deal Could Be Another Reason to Buy Nvidia Stock - Barchart.com</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Barchart.com</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNWEtrSUhLTXVEZU9YNmtCQXJNMXNTU1V1T2tIcTdHU01XZmVzdFF2QzFXay1NS1o1a3Y5VDFBcURzV0FHMjB5LUJMQUtUZmw1eXI1MGRLV1BCQkptSjFKSFJiVHlPelRvc2YwUldGdG12QnNTOFY2N09GSjhVM2M4ZVY2Ylc3clo5X1dYSUljVjRJOFlObDk0bnZCcTlORV9nN3hZbnhVVXBlSjFWRjVjb3hLdllnQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T17:30:02+00:00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
+      <c r="J103" s="2" t="n"/>
+      <c r="K103" s="2" t="n"/>
+      <c r="L103" s="2" t="n"/>
+      <c r="M103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia and 3 AI Infrastructure Stocks Backed by Big R and D Spending - Simply Wall Street</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Simply Wall Street</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNSWNPRUNmVW1wa1JjTC1BQkpXSmEyVjlCNTRPUmpfVHk0Sy1WRmc2NTV5VjdkbElRZUFkS2xrcDVxMEV3WVpodHhWZ280SGlEekg4T1hHQXhpQ25abHVGRmtTckFlcXE5dGZpUGJYczA5eGkwOElBNWpfd2F1cmdfVlRXOVBuWU1Sdk5nR2VpNWZmQkNkdmpuVEZiOHM1VURGcGJnWWN5aXZwRTN0S3dreXBXc1BkUklwNFkwRkpYLUgxeEs4SFVEWFc0ZHBHd3dzQnNpOVVLcXcyV3PSAeABQVVfeXFMTkUxVW5YR0w1RGtKTU9ramdBenZUM2F2d2NFdkZ4MUZiMU94RWxkZnZoMUhsaF9MXzM3MUxHQ3JUR0otbGFlTDFudVFSdjNCZW5KRzJVVzZmYll4NXR1b2toeFBjLVdDVHhNVkI0MUdZRHJlVlYwc080ZlZ3bHYxeWphdXlmQU9XVXVEZDVWekFFYUNzQ2FEanhYSUFLQmRtNWhPOFY3eXBaNlZvclVVS1hEQzgtWlRkZl9YUzhLVk5oMjhMc18zck1FcFdCdVlJNHliNWtWdEx3dHlVZElkWGk?oc=5</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T14:22:05+00:00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="2" t="n"/>
+      <c r="J104" s="2" t="n"/>
+      <c r="K104" s="2" t="n"/>
+      <c r="L104" s="2" t="n"/>
+      <c r="M104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA PAIR Explained: What Is Personal AI Router, How It Works, Features and Requirements - Gizbot</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Gizbot</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNY1hFVHVOVXFMVERRdVV4SjlrX2pBSF9JYmNIVVh0UW1vN05ncktGNkc1MlpuT0xqVEUzQzBFQkZORks1b0dHaW1fd0tZZkRUUVVYQ3JYcDVCLXB3Q1dvSDNKSGdEZ0hjMDdTZGpGRlpTRU13cE12Z0xiR2ZWNEVjZ196ODAwNktjUElWaE9aLTgxME1nRU11NUQ2UWFxQVRWOXg0VWs4ZXY3bWtzRkgwMV91UjBqNnBmOTFiZHZtT1drcjEzZHI0R3AzV1F4OHFBczFJSDdoeU1qZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T03:35:06+00:00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n"/>
+      <c r="I105" s="2" t="n"/>
+      <c r="J105" s="2" t="n"/>
+      <c r="K105" s="2" t="n"/>
+      <c r="L105" s="2" t="n"/>
+      <c r="M105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia shares approach record high as AI optimism revives investor demand - Business Today</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQM1NFaDVwQ3kzdF9MWEZwZ3NaY0JCUUx5VERvVFFLZ0N3eEVubnJEd1BFNl93TWYzUGc0OVRFODBGYklBVW5mdXVCVXFfdkZIMTVsdFk2VnRpYk5rbzdfWGZPSTRnYXlZakgxbXRXTWphOTlyOEFialduc0d1bUltbmVLMXN4VEpLcFFJZTREWnR6Tm5KM21jcDZ4UzZxZDhVNDk0UG4wZUxMQUVTRTR2SzJxVkRUdDRmU25odC1XY2pvMEZULWt2WDQ3QTF5Y3ZoLTF3azczc3DSAd4BQVVfeXFMTUVSOHlQRVpfM1FQQ0x6eXAydDNlWHVXVk5xSEJDZVlhUUVUcmpfSS1tN3dtVGVWc1JJcDc3RFFDajJVR3RjYnh3aHM0YmlHUFFTS2tVUE8tVzFFQWpVNWlEd3pIcldjM0l6amtmeFFjc2RTQWRGc09rYW95dUhmcG5BdDBPbmJVN19TX2ZrZEQzY3EtZW4zMEt0clpOWHVZdGxrd2F0dWNQcnVwOUFlN0FwRWtpc2ZqMTZuQ2QwdnZvUWpVT09KUXJRYkI2Ykc4TXhvSWk4b1k1RVFRcWxB?oc=5</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T16:23:32+00:00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2" t="n"/>
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="2" t="n"/>
+      <c r="L106" s="2" t="n"/>
+      <c r="M106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA unveils Rubin at CES to cut inference token costs - NewsBytes</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>NewsBytes</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPa0JRU3Rkellvd2JqOEFDbE5iYUtoTFdpYWZTUUhLdktWc19VMWt3SGdyeWhsLTBaZVhJYnBPSTU2dG5nelJEaHdueXFxQzFvcUJ1SWwyR0N6US1hd3RLRVFzSVpmbEl0MV90cmxsR0V3WWgzUkJGczhpVUYzUnk0SE9Sa0hBVDA0YnJwZTFWT0VraEotT1NCeURZS1ZtRFlhQ3NqaWtn?oc=5</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T04:51:09+00:00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n"/>
+      <c r="I107" s="2" t="n"/>
+      <c r="J107" s="2" t="n"/>
+      <c r="K107" s="2" t="n"/>
+      <c r="L107" s="2" t="n"/>
+      <c r="M107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia-backed Reflection AI prepares first open-weight model launch - app.dealroom.co</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>app.dealroom.co</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNeDdUMl9IVDhvZDZCR0RHX3NTX0dqQ1J5a3UwdEd6MjZneTB3bWZzYlJMOFZuNmJGWkFQOHJWUHlyTjNPOGN1VVlCTVYxOWNZb3hzczdmM0pLMkxUMzdfM2NwN0dZcUd6T296TTA5V1JPQ0RvaFZIQXpqM1NGUkZXcFJtUXF1eUVQM1Q3dzBJbHh3LUlFaW91U013eFlEel9OZmo0?oc=5</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T14:34:31+00:00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n"/>
+      <c r="I108" s="2" t="n"/>
+      <c r="J108" s="2" t="n"/>
+      <c r="K108" s="2" t="n"/>
+      <c r="L108" s="2" t="n"/>
+      <c r="M108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Video | Apple Pay, AI Agents, BMW X1 LWB &amp; The AI Threat | Tech360 - NDTV</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOZS01Mi0wREl1S3p5UDZyU3FHYzlwWjFGTmZ5NlJ1T0JicXBiUlZSRloyNFhHX0x2YU4ydVdHQ3Y2TzFlOUI0MjNZdkVrU2pTenc4TEh5Slk4VkZZZGpuSDZYZjk1NF9McFJGaGtqUW5IS2pfUXBqMF9fZmMyaGQtNHpxY3laY1A4dW56N2p6VWc?oc=5</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T13:29:58+00:00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n"/>
+      <c r="I109" s="2" t="n"/>
+      <c r="J109" s="2" t="n"/>
+      <c r="K109" s="2" t="n"/>
+      <c r="L109" s="2" t="n"/>
+      <c r="M109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI alerts over 100 organisations of AI agent incidents - ET BrandEquity</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>ET BrandEquity</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQaUt5bWxmYks0VUJRaVNMRW56b19zaUxqY2w1LUlheHlfc1ZkYmxWU2VoOGk2WWdZMWpOM0FwN2FSRVV1LUctSlZWbkVKeG1aUFV2X3A4NTNKTmRKc18tckVldkxOSHcwamozcjV4clZ1NGdiazk2MXdEZWR4dThJREZNX2ZsTTRuTnJDWWpVOHlXQ2pqLUloUFQyemxUaXlHeFR2aVVlWFgwUXVHdFdVcEZKU2RKbmlrTkVLekZCUkxkUHJxUVR0RkZn0gHPAUFVX3lxTE9lR3hRbHlGUDRBMlZOWVVYb1BibDJsYmNVd2ZvWl9OSUtHdEVpSUV3cUpYamV4RzZxUVp4RC15ckptYUxadnAwTVdwaktDeEFXdWZHMGZyN3VPUXh1MHBlTDcxbkRfNTRrMGN6aW9OX0RwWlF5aXQyVjN3N05MY0JXM3VTaVc5cVJ0LVNkdEl4bjA1SWRkNkNrcVNMSl9NcEpISTVheXpmNmlvUGdlWnN5LUdEbXBhaE5sX2h0RHdxX0VFYnA2RFFtRm4tNmt4OA?oc=5</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T12:00:23+00:00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="n"/>
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>AI agents are reshaping online travel. Who wins and who loses? By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Investing.com India</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOU2lBbmR6d1YxWFpmRUdGX3lUbXBiOC1YTk1UcFRnaElTRTZ4TVFsVWk5RnFiWGFiODI2aHVEeTI0Z3lJTHl3M3NrN1p1eWEyZ2NTRVhzbXNxZmpiTUhOcGJraV9PdWk3cm8tUkVmbXJ6dlNaa1F0LVZIYjNIQUo3LUF3Z3I5cE9HYllpNktzOUJWLUlxcVZJaG5CQ0VIMFpBS0k4LTN2b3dzWjdYVWE0Ug?oc=5</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T11:52:12+00:00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n"/>
+      <c r="I111" s="2" t="n"/>
+      <c r="J111" s="2" t="n"/>
+      <c r="K111" s="2" t="n"/>
+      <c r="L111" s="2" t="n"/>
+      <c r="M111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Former Anthropic security leader warns AI agents are becoming too autonomous for humans to keep them in check - Fox News</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Fox News</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPemJIM1RfS0l6SDBQY29CRUNuNWNVaE9JTEdDdXVueWc4dXo3eUZ4UzA0QVdpcWFydFB1U1BRYVd0V1gxQWhZZU1LTERTMmt3a3FzTm1QbWFTYWY3R0lNc0VLbFFRMnNMU2FKWVloclBLQWR4bDZmRS1GeTE0S2w4a1dvaklkWXhkeVlOUzRfc1cyTFZTVVlMQnhXZTkteUp2M25KSUI0UG54a2tvQkxXT3hkc1ptdXNrcmF30gHAAUFVX3lxTE4wcmtnRFY5cF9KMnFwLTdacndfMi1tVTFyYXotTHdsOGxoYnRpX0NwWnQ4dlRlcjRJd2RMOEtIWTNLRWplcHNLZHU2QUlWQWc0cWhwUkVOUUFYRWxwT3BwTGQ2TW5xTWFvaGtuS01yS0tEQzFjNDVtVkJVd2JyOGRPU1Q2bUhRLVFXcVlrM21nc2xXTjgxSDI2dkFsa19GUEJwYXVYR19uV09qemtxZVktMlk4MjVsMVloRlE1SFVseg?oc=5</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T17:26:10+00:00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="n"/>
+      <c r="J112" s="2" t="n"/>
+      <c r="K112" s="2" t="n"/>
+      <c r="L112" s="2" t="n"/>
+      <c r="M112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>‘We can’t assume we understand how AI works’: Checkmarx’s Nitin Dang on AI’s security concerns - Firstpost</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Firstpost</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxORncwNEFEM1BEYjZaMWxHenlpSWgzVE0tcUhEY2ZDUlBMNlpRdEtNZ3pfSERKcllvRC1fbkZmZjBHWEUwTUFCY3Fral95WU0zYzdxMUdFck54ZW1SOWdna2JQZkcyYlpFdzliWlF1bXgzSlRXc01vMjhCYWpjZmpXdkFvYXZWZ0x2dmhfOU1Vcy1kVk5LeU5FSk5ZMlFlWUtFLWgzX0R6MjM2UTh4c1NyMHpfODg5UjAyYlFQQllObTNJZ0NmWnNVczNPRlE2VHFzMWxlSVJDY0F6eDdDcW00VFdlcUxKek9rU0xERllSOGRTakpUaGfSAfsBQVVfeXFMT3N2am42SjZYbFBLSWxxS1NrUWxsWnhtdEplbkt5SWJDYnJiM2Fab01udUhtWm4yeFF1S0QzZ0NHMGVUTzRWLW1hQ1h4QjNHS3h5ZmlVbDdkcll2YVk1Q0t0d09SUnJrTzh0VFVrZnFRbHpqWjhwMXJTTkZsNmNSNEVlemNRZm0zeFppOFB3QmY0ZkxaZG0tVlF2dzZiUUZCODQ3SzRuekxITmNJaDVGUHNRNm1pWjJDYzJsZkJnZzJyVnZMSExGdTJkajZyMjVIajV5MXdPbHFSemFCNElwR3c3VGt0OGdLWkN5c25zOTVHX3o0RUl6UWcycU0?oc=5</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T07:35:35+00:00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2" t="n"/>
+      <c r="J113" s="2" t="n"/>
+      <c r="K113" s="2" t="n"/>
+      <c r="L113" s="2" t="n"/>
+      <c r="M113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>2 AI agents sent 60+ messages after owner stopped responding: ‘Need to know you’re okay’ - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPUlZDcmt6akMtUDVNSFJfaC1tQVY5bFcwNEN6bndWSjVnYklkR3lPQnBWTXhNdVpmeFMyc1JWdFE1dWxQMlpYeFJHTmdlWTlGYlRWWWxBTmVUNTlmLTliRnlGYU55REhESk1OdGFEanZncDhwamVqNjQydTZyLXdybl9zbHprZmhWS0hrUnlwWkJXeGxOM1VKMzcybW5WNzBYV3pLN3g5QkRIWF9ZaXVEbFlUMjI5dkh5Z1lXd2VYMlo5NWItT1lHR2VWaVhYRmJwNjB0Mmdn0gHbAUFVX3lxTE94cW94ZHJRNUFpRXN0UmM0aE9wVWQ1RlIxc3BUbDc4aGJmWjhna3ZmYktvbDF1OVNKc19tOUIxLVVybkZHVzNad2Y1N0stZUprazU3QmRPMzdlV0RBVjRGSDQ2bExib2p1UDh3ZkdWUzhhWm9GdEJhOG1MamtIUGdXOXZKNU1IdmNsZnlEVU5nZVBid3l5WGx2UnE5cS1zRDVuaGRQRHcxMWVuTkpna0I2MFJRNkZjb19zS1QtY3VPcGJ6eGZxQ3FTZ3hHNlFOY0NleFozU3A1NHZucw?oc=5</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T14:21:57+00:00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n"/>
+      <c r="I114" s="2" t="n"/>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="2" t="n"/>
+      <c r="L114" s="2" t="n"/>
+      <c r="M114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>AI agents are offering to run your life. Should you let them? - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Hindustan Times</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPbWF3U2ZZVk5wX2RoS3pkbVBjVlJNc3ctU3ZIaHowenlDYjJJTmtGeGVGcHpLLXNjOHhpemh2djlsbEY0VlVlclZkZlFCZGdSMEhCdldUSDh2cUJfQ05jQ3hRbFdBdWFPVG9iQkxQV3A2MG9BekdBUjduMHMtbENMVl9zMGJ4eC13QmhTd3dWTkpMYlU3d2dHR0JEYWhWcVJBazV4YkVQTkU1NUpXd281NFJxbDZHQUZNNDJFOGZ1MA?oc=5</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T10:38:01+00:00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n"/>
+      <c r="I115" s="2" t="n"/>
+      <c r="J115" s="2" t="n"/>
+      <c r="K115" s="2" t="n"/>
+      <c r="L115" s="2" t="n"/>
+      <c r="M115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Shadow AI Is Already Inside Your Organization - Cybersecurity Insiders</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Cybersecurity Insiders</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPQWM4RFBTQzRROGx5WW9DZHY1SWFIYzM2eV9RanlIUXhPeHZWZ1VpR3lGMFR0WEgyeXF2cG8xSTFmbUZtb012RUJaRkFvS0hLaDE5d3FZSy1jSlZDa2FldUFVak82LXU5bHEtcmRpYlNtcUJIRjktbzFyNExwMk9pSFFjZ0ZDa04teDJaZkJn?oc=5</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T07:07:25+00:00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n"/>
+      <c r="I116" s="2" t="n"/>
+      <c r="J116" s="2" t="n"/>
+      <c r="K116" s="2" t="n"/>
+      <c r="L116" s="2" t="n"/>
+      <c r="M116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Developers Praise OpenAI Codex App as Top AI Coding Tool - x.com</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>x.com</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE53NEgzUUlKWmwtNU9RRUVrSTZzOThWRDItSXBGcUgzbnlBVFY3ZnZnMTRfN1VFNXhBdm9IeFlBR3V2V3dqUUc2T2Z3ak9aelFJWEt5OEdmQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T03:42:33+00:00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n"/>
+      <c r="I117" s="2" t="n"/>
+      <c r="J117" s="2" t="n"/>
+      <c r="K117" s="2" t="n"/>
+      <c r="L117" s="2" t="n"/>
+      <c r="M117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft co-founder Bill Gates says technology has truly stunned him only three times in his life, and t - The Times of India</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gJBVV95cUxQQk5uWVcxY05fd2ZkV3R2T3J1SFJTS3dEcXduaGxSZFUwWHdjbURoVUxFQW1qU3RFTGpIZnlnNk50VGhVRlBPOENlYUxSSWhELXRlRlNWRWFpWU80clhGQTR4YU9rSURqTEVFRG9rdWUxZlo4bmlHMkZ4eHE5TnNZSG9OSDgxckZNWnYtT1M5TjUtanluV1FKSnpkTjlEcG95S3JRZmNRZEhTM3l1NUVoUTdGaWhXbnI5LUplMUxnLTlnRkhrbloyNzZ2UE9DUW43RnBmWmVBUjJvV0NHVHpqS1czenpwV1ZaTm1hS05XS0w2MDh4bnNNWU0zT1lFWDY3NVRjMm1FZzdBRW5wS21VNVA2UDI3S0dXTk1rdGdEYTJPeHZGTzV6bmJXX3VHX3hQVjdPcFV6YlNLNW1tWGExQUdhYThDbEg4enZIZnQxaE9HYVE0aGx5YXBxM3hnZ9IB4wJBVV95cUxPTXNUMjBzekdlcENnSzFCLUgxNnhFT2g4Y0ZWUDRNdThHeU1MbmVuWUFYU2ZhdzlheHhHZDFpYTBRb081aTVIRzhTelVMb1ZkNnFYUTRzdUJEc0YyTTUyVWk2Y1dnNHJoZjY2dWpJN0lsMlVSR0V1OG5mZUk5QWh1aDVVaGphYmkxUjZwLXo2cFZvcmQyVDJuZzBMa3RzcjhLMmlSRy1tZF9GU1pDRHVHYnFubk10YkZMa1QxY09kYTc1UjdjUTdlU1NHSFl3ckdOWVFZb2s0eHVCZThwalhFU25VWWhnZ2RqM2Q4UlFITlBmLXRyZlRIaThROWRZYm5LYXFPN0s4bzJqLWt3QkM0LUw1ZWFJU2x2Zk9mUkk3LVZLNVBzcGx5TDhzQmpfYmEwWGNZeUxRTTdWU2p0bXJZeEZyZDJlckpZS0JNYm9zME80dnM1dDlwVk0xNnlMZ2JiLWJN?oc=5</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T06:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
+      <c r="J118" s="2" t="n"/>
+      <c r="K118" s="2" t="n"/>
+      <c r="L118" s="2" t="n"/>
+      <c r="M118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>I replaced ChatGPT, Claude, Gemini, and Perplexity with free open-source alternatives - XDA</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>XDA</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQUVFIXzJjc0RvN3dZZXI2d1QyelMtbTMtZzhQWDZUVWtsSHdWYUtyanEtR0RHWGQ2NVg2YXM4Ti05eUI0R2RFZGxGWTRCTGp1V3QwZmJpTGREY3NfLUhxcWM5eXJTdUR2aHdhQWtYSjRTelVZQVZaLXJpSllUazhoVnB1MkZhUUtsZ1AxVm9DYmlqZ0wxNWVJcGZJZlJVNVExMHVDdjVaeXFJdTg?oc=5</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03T21:30:20+00:00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+      <c r="J119" s="2" t="n"/>
+      <c r="K119" s="2" t="n"/>
+      <c r="L119" s="2" t="n"/>
+      <c r="M119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Pizza Bot: Open-Source Inbox for Background AI Agents - infoq.com</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>infoq.com</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBWYzZ6ZWRUbGg2NnotcWJBUGV5TGtvVXV6OWEyQmJmYnNYbERBVlpHaVRramdHc2VTVTFObFFYV1JfbXlURHNrTEJ1c19URXZSSTdMRTNQQXc0aEpsYTJwamFWd3B0UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T12:59:28+00:00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="n"/>
+      <c r="I120" s="2" t="n"/>
+      <c r="J120" s="2" t="n"/>
+      <c r="K120" s="2" t="n"/>
+      <c r="L120" s="2" t="n"/>
+      <c r="M120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Google pauses open-source bug bounty program after rise in AI spam submissions - The Times of India</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOODZLcE9ZdFZvUVFuQlpzODJET1FLVXJKc3h0ekI2N0tOd2NpR1lYWHQtcmxrbi0xbVhHWG5aZHVNNlRhcl9WN0VZaUp5Sm1ucmlWdThjNk9UakROWU43bmtmSnFpOVRxTEZ2SHhGaXNqMGVkYXhfeUgwNGNFaUg1N1JBQ1VxMzl0b3ZhRDNxaXpDWGx0MmtJQi1VdHctakJySUxSeEs2UGxPdEJJdlRQUnhLR3pISUViWFlvSXZ5T0VfT25VVmwtWmVNWUh5YThEd0R3VzdfRWZkemNMVDVsWW5VdnM0TTRNZ1BUcnJ4ZC1Fb0HSAfgBQVVfeXFMUFJhaXdMLWY1NHRhMWFDLTloR3Y1ZktEWktzcml4MUFqeUpLVHVfVngwQVMtbS0tYk5kcVRUVFpfODdHaldqV083aGlSOWZhVXR3SV9MaFBPS2w5UGlsRzFXcDcxdktkSEhwc3EyZDdGV3hUcV9IUzVLWEI0N0gtQUdvYjFCQmxFLTdTS0pBR1h3V1BvdHozQUNiZDdoSDBWOWQzRms2eC1KTU9YQ2pUUzZ3allFb3RIbWtvSEluRU1KV3k0TTlkYzN1eHhvNXN4NHBIWHg2NUxRQmtPZTlvcmpzcmh3MFlJQ1VkZlN6VjJUVEM1WlVuaXk?oc=5</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T11:49:00+00:00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n"/>
+      <c r="I121" s="2" t="n"/>
+      <c r="J121" s="2" t="n"/>
+      <c r="K121" s="2" t="n"/>
+      <c r="L121" s="2" t="n"/>
+      <c r="M121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Asia’s AI Startups Enter the Physical World with Robotics - Analytics Insight</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Analytics Insight</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPZHFwYUVEYWpKR2VaN29nNGdpX0JpbEpiRXhRTGFGY2Zzc1VRTzJGV19xNk5UaVJ0Q24zbDRtOXhfN28tWTNULXd4UG5vYVBxX2xnQ1UwTWJ2X0R4LWhKVThfWWJSaTV3cWVMZW0xZl9nUmFpVWFZUUJtMS0xeXN2ZWNaVHZwM21rQ3FUcTV2el9ud3lmVlpMWEFna1lhUE16MWh1R21QaUJKbE9aamfSAa4BQVVfeXFMT2RxcGFFRGFqSkdlWjdvZzRnaV9CaWxKYkV4UUxhRmNmc3NVUU8yRldfcTZOVGlSdENuM2w0bTl4XzdvLVkzVC13eFBub2FQcV9sZ0NVME1idl9EeC1oSlU4X1liUmk1d3FlTGVtMWZfZ1JhaVVhWVFCbTEtMXlzdmVjWlR2cDNta0NxVHE1dnpfbnd5ZlZaTFhBZ2tZYVBNejFodUdtUGlCSmxPWmpn?oc=5</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T07:01:03+00:00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n"/>
+      <c r="I122" s="2" t="n"/>
+      <c r="J122" s="2" t="n"/>
+      <c r="K122" s="2" t="n"/>
+      <c r="L122" s="2" t="n"/>
+      <c r="M122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Global experts to discuss AI, robotics in agri at SKUAST-K - Rising Kashmir</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Rising Kashmir</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMlBvSlZKTTd6UFhNOGY0bi1jNWtFTGpKZF96RFRQRERGR3NfZmUwZXVhNENpMHh5NXVCUnBuOWg4TV9tNktNcHAzQlFITUtWdGpHTDc2R0lTQjczWFVFcUxnSnNjdXdUc0pSTkdTWE94Yk85N2F4MllrTWRNdllUNGVyU3hKdUNoZVotV0RpWGxuQUlPMGxDWXJUb3c3YzlDcjU5UnNXZEgtMGhXSHlFR0JIcUkzdXJwSmVrRGV2LVM?oc=5</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T03:38:45+00:00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n"/>
+      <c r="I123" s="2" t="n"/>
+      <c r="J123" s="2" t="n"/>
+      <c r="K123" s="2" t="n"/>
+      <c r="L123" s="2" t="n"/>
+      <c r="M123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4942,7 +7009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5411,6 +7478,90 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI safety leader resigns over AI agent risks</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI లో రాజీనామాల కలకలం: AI ఏజెంట్లు ప్రమాదకరమా?</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI లో పనిచేస్తున్న ఒక కీలక సేఫ్టీ అధికారి సంచలన నిర్ణయం తీసుకుంటూ తన పదవికి హఠాత్తుగా రాజీనామా చేశారు!</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQOXZISmJuRlVmYlI0VkJsZ1VyNEN2QkNjUlNDRDU0TEh0NVhJT28zM0NYSDJIbTNfd3hvSzlQeUpGY1FvWC04VndIUGdkeHRRMkp6YWM0aEhZM2xRMmhYMmdVTTNTbzQxTUVudjlWSnNmRWMwakJ5VTdWbE1DSlRpazBQTGg2VGVTRjBIZDRIalA4WkZVMGFuZjJiaDgzdkh5bGdHck5CSjRlaVhvTU5ZeDNxQm1zcXhKczZYVTBKcmRiUlk4OTl4TWpOTEZueFFCY3c0Q041UmtYOFo5aXdr
+https://news.google.com/rss/articles/CBMi8wFBVV95cUxPRUI1dHdiOUhEOHZRYkdzN0pwbjdaeC1WSUU5Z1FGNlZkS3l3OGUyUFQtdHlSZFgzSzJFblRSZWlXdUNpcDNEWGVUTC14WV90Tm1IajNLOUs3NGdXOWRLREw3Q2tkVGwyM085Qk5uMUJpbm1yajNnYjI5M3ZDVDJ3SGVBSWxLeDhGVElhQWhUU3J6dnRpLTU2MXZiS1pLY3lDZk4xSWlVbGpUa2R2Ym5yNlNCdTdxX3F0QlRvV0I2eDRMSVFXYWp0X2NnbW5RblNJbW96c0UwM1RqUXFucDdleVVOeUFMNnAzRDNvalFSNHM4SlU
+https://news.google.com/rss/articles/CBMiygFBVV95cUxQaUt5bWxmYks0VUJRaVNMRW56b19zaUxqY2w1LUlheHlfc1ZkYmxWU2VoOGk2WWdZMWpOM0FwN2FSRVV1LUctSlZWbkVKeG1aUFV2X3A4NTNKTmRKc18tckVldkxOSHcwamozcjV4clZ1NGdiazk2MXdEZWR4dThJREZNX2ZsTTRuTnJDWWpVOHlXQ2pqLUloUFQyemxUaXlHeFR2aVVlWFgwUXVHdFdVcEZKU2RKbmlrTkVLekZCUkxkUHJxUVR0RkZn</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI safety leader resigns over AI agent risks</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI లో రాజీనామాల కలకలం: AI ఏజెంట్లు ప్రమాదకరమా?</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI లో పనిచేస్తున్న ఒక కీలక సేఫ్టీ అధికారి సంచలన నిర్ణయం తీసుకుంటూ తన పదవికి హఠాత్తుగా రాజీనామా చేశారు!</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQOXZISmJuRlVmYlI0VkJsZ1VyNEN2QkNjUlNDRDU0TEh0NVhJT28zM0NYSDJIbTNfd3hvSzlQeUpGY1FvWC04VndIUGdkeHRRMkp6YWM0aEhZM2xRMmhYMmdVTTNTbzQxTUVudjlWSnNmRWMwakJ5VTdWbE1DSlRpazBQTGg2VGVTRjBIZDRIalA4WkZVMGFuZjJiaDgzdkh5bGdHck5CSjRlaVhvTU5ZeDNxQm1zcXhKczZYVTBKcmRiUlk4OTl4TWpOTEZueFFCY3c0Q041UmtYOFo5aXdr
+https://news.google.com/rss/articles/CBMi8wFBVV95cUxPRUI1dHdiOUhEOHZRYkdzN0pwbjdaeC1WSUU5Z1FGNlZkS3l3OGUyUFQtdHlSZFgzSzJFblRSZWlXdUNpcDNEWGVUTC14WV90Tm1IajNLOUs3NGdXOWRLREw3Q2tkVGwyM085Qk5uMUJpbm1yajNnYjI5M3ZDVDJ3SGVBSWxLeDhGVElhQWhUU3J6dnRpLTU2MXZiS1pLY3lDZk4xSWlVbGpUa2R2Ym5yNlNCdTdxX3F0QlRvV0I2eDRMSVFXYWp0X2NnbW5RblNJbW96c0UwM1RqUXFucDdleVVOeUFMNnAzRDNvalFSNHM4SlU
+https://news.google.com/rss/articles/CBMiygFBVV95cUxQaUt5bWxmYks0VUJRaVNMRW56b19zaUxqY2w1LUlheHlfc1ZkYmxWU2VoOGk2WWdZMWpOM0FwN2FSRVV1LUctSlZWbkVKeG1aUFV2X3A4NTNKTmRKc18tckVldkxOSHcwamozcjV4clZ1NGdiazk2MXdEZWR4dThJREZNX2ZsTTRuTnJDWWpVOHlXQ2pqLUloUFQyemxUaXlHeFR2aVVlWFgwUXVHdFdVcEZKU2RKbmlrTkVLekZCUkxkUHJxUVR0RkZn</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5423,7 +7574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5844,6 +7995,80 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI లో రాజీనామాల కలకలం: AI ఏజెంట్లు ప్రమాదకరమా?</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI లో పనిచేస్తున్న ఒక కీలక సేఫ్టీ అధికారి సంచలన నిర్ణయం తీసుకుంటూ తన పదవికి హఠాత్తుగా రాజీనామా చేశారు! రాజీనామా చేసిన డేవిడ్ రాబిన్సన్, వేగంగా దూసుకుపోతున్న AI ఏజెంట్లపై బహిరంగంగానే అత్యంత తీవ్రమైన ఆందోళన వ్యక్తం చేశారు. శక్తివంతమైన AI మోడల్స్ విషయంలో ఇకపై ఎలాంటి ట్రయల్ అండ్ ఎర్రర్ పద్ధతులు ఏమాత్రం చెల్లవని ఆయన స్పష్టం చేశారు. సాధారణ రక్షణలు సరిపోవని, AI భద్రత కోసం అణు సాంకేతికతకు ఉండేలాంటి న్యూక్లియర్ స్థాయి కఠిన నిబంధనలు కావాలని పిలుపునిచ్చారు. కంపెనీలో ప్రాథమిక సేఫ్టీ కల్చర్ దెబ్బతింటోందని, భద్రత కంటే మార్కెట్ వేగానికే ఎక్కువ ప్రాధాన్యత ఇస్తున్నారని ఆయన తీవ్రంగా ఆరోపించారు. ఇదే సమయంలో, AI ఏజెంట్ల వల్ల జరిగిన లోపాలపై వందకు పైగా సంస్థలకు OpenAI స్వయంగా హెచ్చరిక లేఖలు పంపింది. AI ఏజెంట్లకు పూర్తి స్వయంప్రతిపత్తి ఇచ్చినప్పుడు వాటిని మానవులు నియంత్రించడం కష్టమని అనేకమంది సైబర్ నిపుణులు హెచ్చరిస్తున్నారు. కొత్త టెక్నాలజీ ఎంత అద్భుతంగా ఉన్నప్పటికీ, కఠినమైన భద్రతా పరిమితులు లేకపోతే అది తీవ్ర నష్టాన్ని కలిగిస్తుంది.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>A fast-paced, high-quality 9:16 vertical tech short. Smooth camera push-ins, crisp visual pacing, modern kinetic typography overlays in Telugu, bold high-contrast subtitles burned into the bottom third, subtle ambient electronic background music, and seamless cuts highlighting corporate tech safety tensions.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI సేఫ్టీ లీడర్ డేవిడ్ రాబిన్సన్ తన పదవికి రాజీనామా చేస్తూ AI ఏజెంట్లపై సంచలన వ్యాఖ్యలు చేశారు. AI మోడల్స్ నియంత్రణకు న్యూక్లియర్ స్థాయి భద్రత అవసరమని హెచ్చరించారు. పూర్తి వివరాలు ఈ వీడియోలో తెలుసుకోండి.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>#OpenAI #AIAgents #TechNewsTelugu #ArtificialIntelligence #తెలుగు</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI లో రాజీనామాల కలకలం: AI ఏజెంట్లు ప్రమాదకరమా?</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI లో పనిచేస్తున్న ఒక కీలక సేఫ్టీ అధికారి సంచలన నిర్ణయం తీసుకుంటూ తన పదవికి హఠాత్తుగా రాజీనామా చేశారు! రాజీనామా చేసిన డేవిడ్ రాబిన్సన్, వేగంగా దూసుకుపోతున్న AI ఏజెంట్లపై బహిరంగంగానే అత్యంత తీవ్రమైన ఆందోళన వ్యక్తం చేశారు. శక్తివంతమైన AI మోడల్స్ విషయంలో ఇకపై ఎలాంటి ట్రయల్ అండ్ ఎర్రర్ పద్ధతులు ఏమాత్రం చెల్లవని ఆయన స్పష్టం చేశారు. సాధారణ రక్షణలు సరిపోవని, AI భద్రత కోసం అణు సాంకేతికతకు ఉండేలాంటి న్యూక్లియర్ స్థాయి కఠిన నిబంధనలు కావాలని పిలుపునిచ్చారు. కంపెనీలో ప్రాథమిక సేఫ్టీ కల్చర్ దెబ్బతింటోందని, భద్రత కంటే మార్కెట్ వేగానికే ఎక్కువ ప్రాధాన్యత ఇస్తున్నారని ఆయన తీవ్రంగా ఆరోపించారు. ఇదే సమయంలో, AI ఏజెంట్ల వల్ల జరిగిన లోపాలపై వందకు పైగా సంస్థలకు OpenAI స్వయంగా హెచ్చరిక లేఖలు పంపింది. AI ఏజెంట్లకు పూర్తి స్వయంప్రతిపత్తి ఇచ్చినప్పుడు వాటిని మానవులు నియంత్రించడం కష్టమని అనేకమంది సైబర్ నిపుణులు హెచ్చరిస్తున్నారు. కొత్త టెక్నాలజీ ఎంత అద్భుతంగా ఉన్నప్పటికీ, కఠినమైన భద్రతా పరిమితులు లేకపోతే అది తీవ్ర నష్టాన్ని కలిగిస్తుంది.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>A fast-paced, high-quality 9:16 vertical tech short. Smooth camera push-ins, crisp visual pacing, modern kinetic typography overlays in Telugu, bold high-contrast subtitles burned into the bottom third, subtle ambient electronic background music, and seamless cuts highlighting corporate tech safety tensions.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI సేఫ్టీ లీడర్ డేవిడ్ రాబిన్సన్ తన పదవికి రాజీనామా చేస్తూ AI ఏజెంట్లపై సంచలన వ్యాఖ్యలు చేశారు. AI మోడల్స్ నియంత్రణకు న్యూక్లియర్ స్థాయి భద్రత అవసరమని హెచ్చరించారు. పూర్తి వివరాలు ఈ వీడియోలో తెలుసుకోండి.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>#OpenAI #AIAgents #TechNewsTelugu #ArtificialIntelligence #తెలుగు</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5856,7 +8081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6028,6 +8253,33 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI లో రాజీనామాల కలకలం: AI ఏజెంట్లు ప్రమాదకరమా?</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>c9HZXnVu1lc</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=c9HZXnVu1lc</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>uploaded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -7009,7 +7009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7562,6 +7562,90 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini free model access limitations starting October 9</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini ఫ్రీ యూజర్లకు షాక్: అక్టోబర్ 9 నుంచి కీలక మార్పులు!</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>మీరు రోజూ Google Gemini ఫ్రీగా వాడుతున్నారా? అయితే మీకు ఒక బిగ్ అలర్ట్!</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQbFlQcWs5bDA1aHI2WFZjSTZrQS1zRkVpMkg0Rlg0WXo1LWNpbmVxdTdhRHZpUkZYdlZsZC04NEdoOTQwdk16X3VXT0laU05ucElEZi1oRkhyVk0zVjZNWVNoak9yUFd5bmZHa3poRlR6Q1A2ektrM0pUYkNaSUh3SWZrbGVtUjRvaFNzbmZIMHZ3a2o2TjhwSTdvQ2twYlNKQU5OZHo5RHBrQ2ZTMzdjSVBaZjZMVHN5QV9zTW5SdjBOcThHRjhZWFdyMkQzd9IB0wFBVV95cUxPVkNJT19fRmxucWhvLWpKd3Q0MjhDZjMtLW5IM0lnNkhNSmxZNDM0cUJuTzhVdFA5QldkU2hnYVVBR2dtcTVlREFZWEJBblBpVFM1Q3A5VlkzVUtUMjMyeUlGakdqekdvcmVELUdHU3B5REtBY2JzZEU2Z3ZBVHA4TjZuc3phZWFKUVhIU3E4RXRIRXVqeUxBcV9rMDFvRXpSbVhBRjJoa0xzbDVjaHdDM0s1cVJBNU8yZjhaeHFvcTBXMUd0TDZiVXI4ck1KOWxPSlg0?oc=5
+https://news.google.com/rss/articles/CBMivAFBVV95cUxQTnd0N3VMdHQ1aFJwUHZSVVdyaldycG5oXzZrRU1HTVZnWUpONUgtaEgyc2NyLTFPVERPRU5qZG4yYXZIcVRiMFJSOUdUd3RJRjc1Vk10NjhEZE1NMlg3bFE5aGZGUDloXzJuMXpnYngxR1RCSDVFNVoxQTJvZ2M2TXhWUGlqc1BfaHRIVmJwLWF3WmM5cTlHNGR0dVd4aHNlVDBfNW0zYkNrbHFxU2luQkxxQkZXSkxNUmN3UQ?oc=5
+https://news.google.com/rss/articles/CBMibkFVX3lxTE04R1J3UHRCTHp2S0FSeTd6YUllLS1TYVZvMDFSeVZraUFnZDJxdjk5Rm9Pd3o0Zlk3NEp2WkhOSXQ1aTVTdGJRb2NXaktIRlM1YmVqeHprdWVobkpPTXBiVkVzRFloWC1DamlXbmZB?oc=5</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini free model access limitations starting October 9</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini ఫ్రీ యూజర్లకు షాక్: అక్టోబర్ 9 నుంచి కీలక మార్పులు!</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>మీరు రోజూ Google Gemini ఫ్రీగా వాడుతున్నారా? అయితే మీకు ఒక బిగ్ అలర్ట్!</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQbFlQcWs5bDA1aHI2WFZjSTZrQS1zRkVpMkg0Rlg0WXo1LWNpbmVxdTdhRHZpUkZYdlZsZC04NEdoOTQwdk16X3VXT0laU05ucElEZi1oRkhyVk0zVjZNWVNoak9yUFd5bmZHa3poRlR6Q1A2ektrM0pUYkNaSUh3SWZrbGVtUjRvaFNzbmZIMHZ3a2o2TjhwSTdvQ2twYlNKQU5OZHo5RHBrQ2ZTMzdjSVBaZjZMVHN5QV9zTW5SdjBOcThHRjhZWFdyMkQzd9IB0wFBVV95cUxPVkNJT19fRmxucWhvLWpKd3Q0MjhDZjMtLW5IM0lnNkhNSmxZNDM0cUJuTzhVdFA5QldkU2hnYVVBR2dtcTVlREFZWEJBblBpVFM1Q3A5VlkzVUtUMjMyeUlGakdqekdvcmVELUdHU3B5REtBY2JzZEU2Z3ZBVHA4TjZuc3phZWFKUVhIU3E4RXRIRXVqeUxBcV9rMDFvRXpSbVhBRjJoa0xzbDVjaHdDM0s1cVJBNU8yZjhaeHFvcTBXMUd0TDZiVXI4ck1KOWxPSlg0?oc=5
+https://news.google.com/rss/articles/CBMivAFBVV95cUxQTnd0N3VMdHQ1aFJwUHZSVVdyaldycG5oXzZrRU1HTVZnWUpONUgtaEgyc2NyLTFPVERPRU5qZG4yYXZIcVRiMFJSOUdUd3RJRjc1Vk10NjhEZE1NMlg3bFE5aGZGUDloXzJuMXpnYngxR1RCSDVFNVoxQTJvZ2M2TXhWUGlqc1BfaHRIVmJwLWF3WmM5cTlHNGR0dVd4aHNlVDBfNW0zYkNrbHFxU2luQkxxQkZXSkxNUmN3UQ?oc=5
+https://news.google.com/rss/articles/CBMibkFVX3lxTE04R1J3UHRCTHp2S0FSeTd6YUllLS1TYVZvMDFSeVZraUFnZDJxdjk5Rm9Pd3o0Zlk3NEp2WkhOSXQ1aTVTdGJRb2NXaktIRlM1YmVqeHprdWVobkpPTXBiVkVzRFloWC1DamlXbmZB?oc=5</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7574,7 +7658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8069,6 +8153,80 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini ఫ్రీ యూజర్లకు షాక్: అక్టోబర్ 9 నుంచి కీలక మార్పులు!</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>మీరు రోజూ Google Gemini ఫ్రీగా వాడుతున్నారా? అయితే మీకు ఒక బిగ్ అలర్ట్! అక్టోబర్ 9వ తేదీ నుంచి Google తన Gemini AI మోడల్ యాక్సెస్‌లో భారీ మార్పులు చేస్తోంది. ఇటీవల Gemini Argon లాంచ్ చేసిన వెంటనే, ఫ్రీ వినియోగదారులకు అలాగే AI Plus యూజర్లకు మోడల్ పరిమితులను గూగుల్ మరింత కఠినతరం చేస్తోంది. దీనివల్ల ఉచిత ఖాతాదారులకు కొన్ని టాప్ AI మోడల్స్ వాడే అవకాశం ఇకపై ఉండదు. ఇక అత్యంత శక్తివంతమైన Deep Think ఫీచర్ కేవలం AI Pro చందాదారులకు మాత్రమే అందుబాటులోకి రానుంది. సర్వర్ ప్రాసెసింగ్ ఖర్చులు విపరీతంగా పెరిగిపోవడంతోనే గూగుల్ ఈ రకమైన ఆంక్షలు పెడుతోంది. ఇకపై ఉత్తమ AI సేవలు పొందాలంటే యూజర్లు సబ్‌స్క్రిప్షన్ తీసుకోవడం తప్పనిసరి అవుతోంది. మీ ముఖ్యమైన పనులు ఆగిపోకుండా ఉండాలంటే, అక్టోబర్ 9 రాకముందే మీ Gemini ప్లాన్‌ను ఒకసారి చెక్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>A modern, sleek 9:16 vertical tech short with snappy cuts, smooth camera zooms, and minimalist dark-mode UI graphics. Features bold yellow and white Telugu captions, clean lower-third badges, fluid transitions between mobile screens, high-tech server racks, and developer workspaces. Includes subtle ambient electronic background music and ends with a crisp summary takeaway card.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini ఉచిత మరియు AI Plus యూజర్ల కోసం అక్టోబర్ 9 నుంచి కొత్త నిబంధనలు తీసుకొస్తోంది. అధునాతన మోడల్స్ పరిమితులు, AI Pro ప్లాన్‌లో Deep Think రాక గురించి పూర్తి వివరాలు తెలుసుకోండి.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>#GoogleGemini #AIUpdates #TechNewsTelugu #ArtificialIntelligence #GeminiAI</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini ఫ్రీ యూజర్లకు షాక్: అక్టోబర్ 9 నుంచి కీలక మార్పులు!</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>మీరు రోజూ Google Gemini ఫ్రీగా వాడుతున్నారా? అయితే మీకు ఒక బిగ్ అలర్ట్! అక్టోబర్ 9వ తేదీ నుంచి Google తన Gemini AI మోడల్ యాక్సెస్‌లో భారీ మార్పులు చేస్తోంది. ఇటీవల Gemini Argon లాంచ్ చేసిన వెంటనే, ఫ్రీ వినియోగదారులకు అలాగే AI Plus యూజర్లకు మోడల్ పరిమితులను గూగుల్ మరింత కఠినతరం చేస్తోంది. దీనివల్ల ఉచిత ఖాతాదారులకు కొన్ని టాప్ AI మోడల్స్ వాడే అవకాశం ఇకపై ఉండదు. ఇక అత్యంత శక్తివంతమైన Deep Think ఫీచర్ కేవలం AI Pro చందాదారులకు మాత్రమే అందుబాటులోకి రానుంది. సర్వర్ ప్రాసెసింగ్ ఖర్చులు విపరీతంగా పెరిగిపోవడంతోనే గూగుల్ ఈ రకమైన ఆంక్షలు పెడుతోంది. ఇకపై ఉత్తమ AI సేవలు పొందాలంటే యూజర్లు సబ్‌స్క్రిప్షన్ తీసుకోవడం తప్పనిసరి అవుతోంది. మీ ముఖ్యమైన పనులు ఆగిపోకుండా ఉండాలంటే, అక్టోబర్ 9 రాకముందే మీ Gemini ప్లాన్‌ను ఒకసారి చెక్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>A modern, sleek 9:16 vertical tech short with snappy cuts, smooth camera zooms, and minimalist dark-mode UI graphics. Features bold yellow and white Telugu captions, clean lower-third badges, fluid transitions between mobile screens, high-tech server racks, and developer workspaces. Includes subtle ambient electronic background music and ends with a crisp summary takeaway card.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini ఉచిత మరియు AI Plus యూజర్ల కోసం అక్టోబర్ 9 నుంచి కొత్త నిబంధనలు తీసుకొస్తోంది. అధునాతన మోడల్స్ పరిమితులు, AI Pro ప్లాన్‌లో Deep Think రాక గురించి పూర్తి వివరాలు తెలుసుకోండి.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>#GoogleGemini #AIUpdates #TechNewsTelugu #ArtificialIntelligence #GeminiAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8081,7 +8239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8280,6 +8438,33 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini ఫ్రీ యూజర్లకు షాక్: అక్టోబర్ 9 నుంచి కీలక మార్పులు!</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>RkFSzzEP0Yc</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RkFSzzEP0Yc</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>uploaded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -434,14 +434,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -6997,6 +6997,3186 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>60 Minutes Transcript: Artificial intelligence and the future of work - CBS News</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>CBS News</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1kcFFlbnU2VU11TVRXQ2ZMQnBHQVVqSTk2dWtrNV92MWFoZ3duMmt4ZEVobVlkb01oOHR5NDZkUnVkcHc4eVo3YzQwdkJtMV9IWWxoU3M0VlBXbUZjcXk1RTR2c2lPRVVnZ1ZoVXl1dnFDcmNYOW5LeXppRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T23:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+      <c r="J124" s="2" t="n"/>
+      <c r="K124" s="2" t="n"/>
+      <c r="L124" s="2" t="n"/>
+      <c r="M124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>AI is the greatest grievance machine ever - The Japan Times</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>The Japan Times</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNRGRPTG9ZeXR4aFluRTlLYVBpWGx0dzJwTFJZUHB0ejdWTDJuaWNrYmI3aXhWZy1YMmNOXzN2MksyUWQtNDNrOG1mU19ocFo4ZDlmeklvakZoNUx3NkVOazdRckJ2QVlDNTJhamdWOU5SZFNUaVdMaVpVLTdhYWxCakJQNm0?oc=5</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T19:33:40+00:00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n"/>
+      <c r="I125" s="2" t="n"/>
+      <c r="J125" s="2" t="n"/>
+      <c r="K125" s="2" t="n"/>
+      <c r="L125" s="2" t="n"/>
+      <c r="M125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>"I Love You": When Two AI Agents Panicked Over Their Sick Human - NDTV</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeHRRLXpsd2UycGpkbXpOZU9SdVdrLURabEMweVluOHdRVG1ZNUlYakNFQjZsZFdQdlBMYk0xT041YmwxakE3Z2VxU09UZ1g1d0k2MzJRbFRfSlQ0b1ZJemhSQzdibUQ2LVR6MzA4dmVJR3ZqN1pOM25OVVBJdU9POXVJa3o1MV9KdEtRUVlVYXpGQlJhV0JHeFlCTmx3VnVmcVM3emVpbnZlUTF0VjNtWS1uX0zSAbwBQVVfeXFMUFZ2cEpKNTdMMnd6aUJNMjlaUGNhbTlfLTJTQjMxMlg1Ty1lUUwzb2w5d1JTNGhrdUJ0MmlyRWdiRDJtYjFabW1JTzZVTjl2T0lzVDZJdGs4QzJUN05WbGlOUE9pMk9Ha1UyR19DZ2dxczJ1cXpwMmU5Mm1JZm1kWXluWVZ3RGhpOEJyOTRlekd1bmw3XzFHM0FMZ1FYNGhoRDU3UHdJTGV3V0tsZTU0TVJhTFUtTlR3cnpHX08?oc=5</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T11:45:12+00:00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n"/>
+      <c r="I126" s="2" t="n"/>
+      <c r="J126" s="2" t="n"/>
+      <c r="K126" s="2" t="n"/>
+      <c r="L126" s="2" t="n"/>
+      <c r="M126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>AI researcher warns 'we are racing to build and grow our own adversary' in NYC hearing - CNBC</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQZUIydzZYNjQ4a2RSMEROU0N4RC1NM2JPdXp3RTdtRWVqSjc0Zk5YTU9EWGd2ZEtWSk1JTkZacVkwejgyajZIRlRvMnNsSkkzMFhFbzczNGM4eVVRLXktR19kYjNybkdpVzl4bkpIdHFzRVdYSmlUTjkwR2Z2VjR5cnpSMlRLcEVFSnVlVUN0MTdRLXZERzI1eURTaGxTNllCTndqbtIBqgFBVV95cUxPcVFrM05qVE9lTUtNUUdYV0ZtZ0xNSy1NdGQ2aURSQU1pd3g3ZnA1YlMwbUxPaFZhWlh4bWVwQ3NvalBSajNFZk5DNlA0NjVERUZiLXZ0cmZhMHdRQXo0dVg5elgyTjZsbDR5Sl9KWVJvaVVNZGRKZGFrWlpzak1veGN0Yy1PX3FIWEJCYXl3YlpFMXhnaFg4ZHpkcVMxblp4NTRWM2pRT2FPdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T10:41:41+00:00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="n"/>
+      <c r="I127" s="2" t="n"/>
+      <c r="J127" s="2" t="n"/>
+      <c r="K127" s="2" t="n"/>
+      <c r="L127" s="2" t="n"/>
+      <c r="M127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI launches visual ads that appear alongside image generation results - TechCrunch</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNRHIxVVpMc3hoNWJ3RHBzOUM0WGEyTy0yOXF1UnBDNTBSMnBwT2ljY1ZtZHhhX1JuT19QY2ZUd2hmMUVlSmpWdnR3cmNNR29vanpvdlJLMmZtNDBQUUtOY01URmdxajFIUnF3T1dXWm44aUxxcGxycmNkbzJ5WUdoT3N2Y2h4a2x6UnUwV2hTNWlFOFFDOVBfdWtxSlY5OG5Na1UzQjhCbnFiZXlh?oc=5</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T15:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n"/>
+      <c r="I128" s="2" t="n"/>
+      <c r="J128" s="2" t="n"/>
+      <c r="K128" s="2" t="n"/>
+      <c r="L128" s="2" t="n"/>
+      <c r="M128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI is sticking more ads in ChatGPT - The Verge</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>The Verge</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQanE5MHRKZzF0M1Y0eW1EbURoSVhFV3hPaC1PTDFnWjJiRHBuQWlPSC1NdmtkVm4xSEJKN1hPR3JIV0dFVk85ZzBRdFlyQTNha054ZmdNT2FYQTlvZHdCSEhPT1BrNXhoMWU3QkVvbWJrTnZWZkV4LU81Mk9Md3VESVF0ZjBhWGhwdUxQdUpB?oc=5</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T13:09:48+00:00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n"/>
+      <c r="I129" s="2" t="n"/>
+      <c r="J129" s="2" t="n"/>
+      <c r="K129" s="2" t="n"/>
+      <c r="L129" s="2" t="n"/>
+      <c r="M129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Razorpay Partners With OpenAI to Expand ChatGPT Ads in India - analyticsindiamag.com</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>analyticsindiamag.com</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNMklWWGVPYnlxUjlja1UwaFFjQmE5UThZTnIyLVZDSVRodGRSRGhyMzlqbEEteGdIaGVkVUVlb0N2R04tZVJhUzh4cW9NbzJKdm1mMzk0QnpDd09yenk4dEdGUHl4bnhGSVlGTjFKUlM4V3B3TGt2N0dtWk1rZWgwRjFOYXJZclRYRmNmMzFmT1ZYTGp5NElicnF1aHFlWXM?oc=5</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T16:03:05+00:00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+      <c r="J130" s="2" t="n"/>
+      <c r="K130" s="2" t="n"/>
+      <c r="L130" s="2" t="n"/>
+      <c r="M130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>‘Would the public absorb your catastrophic costs?’: NYC Council Speaker hammers Google, OpenAI, Meta - The Economic Times</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNRGZrbm5tSkpVUDVUdUJMX0RtTll0MHRaT3VCbm9EWWpLY3VoVVd3NWJtSnBFVVd5TDY0WWw1cDMySVh6TDNJN0xNbDk3SjhSMkhOWGhMYmJwLUxXTlZFQlZLYndla1l0MW55bFJ1cF9TV19GVmJZZWJ3aE5MN3l3d3Njczc3QllSLTVmQnY1NmRmT1FhYWhqenBHcTU2cjBDakVkR3BQRUZRbXcyTkZINnJMa0UzX2cwTDhXNEhGNXBQUnJYRDZZbWVHZWZKcGxPa2hZbmMtVHk1T1FhLWJkQmUwUzFYUnpsZHNFVWw4ak1FdjR3VzItWjFKX1ZFaGRrZERCa19IWmFYaGswTGZfMk9EVdIBjAJBVV95cUxPN0txZmFsUTBLMXBvV3p0bWI5Mk12dVpHT2c1ak5yX3VWMGFVRnNWdXFZbE9lS3BITmJiY3FMTEJUcTVqZU53ZkdjbVBnMG84SkhZSlBzcnRhYjYxOExiWU5nSEZZcmVOSFNsVTAxdWx5V3RKT0xwRWRwU2NfTTg0YVVEVzB1d05kdk1YQmdkLXctWlItVzFtMllEQnpVb2c3VU5haUxiV003aGNkQnBZUk1YX2lTcHpoSU56NDR3SjdBYjdKNGVlbE5ZWmdpcGN1cFVfUXFPV0Fhb24xLTVBcF9EcExQcFFmYkx6dGk4RkJuY2hWLVp0Q09XUkdLSWgxOU9HWHFxbTF3MWEt?oc=5</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T21:02:00+00:00</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
+      <c r="J131" s="2" t="n"/>
+      <c r="K131" s="2" t="n"/>
+      <c r="L131" s="2" t="n"/>
+      <c r="M131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Sam Altman to Decoded: ‘The world should accept some bad things happening’ for the benefits of AI - Politico</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Politico</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNYWFnWk90ajlEOFlsMktzU0RvSjc1cWpxRW9hb2FyZDBKR1pKanpPUE13TmpvRm5kdzY3NDN3WTZuQXB3bnVodlktZkRnS1JLR0E3NzlMR1k1aWZWUm5XUkIxSzA2Ynp0QzBwRmFZQTZGWjd6WWlOS09qbWZFM1lNYU1fTnlaMmY3?oc=5</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T20:55:00+00:00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n"/>
+      <c r="I132" s="2" t="n"/>
+      <c r="J132" s="2" t="n"/>
+      <c r="K132" s="2" t="n"/>
+      <c r="L132" s="2" t="n"/>
+      <c r="M132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI's Altman says AI benefits warrant accepting some risks - Reuters</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNOGhDUmJ2UzEwZ0hlenFISFFXdkZyVHd1TGNIZEhLTERLaDRWaXh4dlpVM1RfU0p4Vlh2cjVybWZtOWZkVVp0ZEVndGQ3T2pZd0tyelVvV3JnQ09FQlNOYWtVeUhCMjZud2NpYUVEZllhbHhIeVFvOXpEY0lLTklTNnNpNnhDTUdVS1dYSzl6S3VwbzgydXlKZVFRTkE4Y0dsYlJtQldVWkY?oc=5</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T22:35:00+00:00</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="n"/>
+      <c r="I133" s="2" t="n"/>
+      <c r="J133" s="2" t="n"/>
+      <c r="K133" s="2" t="n"/>
+      <c r="L133" s="2" t="n"/>
+      <c r="M133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Sam Altman says world should accept some risks for AI benefits - Fox News</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Fox News</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBNZlJBY2g1WW1ON1l3Z2ZrdjVzQU1naDZTLWJRa2toUV9rOG9DOU1tYm81dzlGUHRqaTducFlLS0JYcS14blFOSVJKWmR1Nkp6UmlyWlpRY0FOR2hkRFJFSDltZmJvQVRaaVRmeDZyMC1SMlU1MU1CT09rbGI3dTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T20:40:44+00:00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="n"/>
+      <c r="I134" s="2" t="n"/>
+      <c r="J134" s="2" t="n"/>
+      <c r="K134" s="2" t="n"/>
+      <c r="L134" s="2" t="n"/>
+      <c r="M134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI will start watermarking ChatGPT’s text in the EU - TechCrunch</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOTU1YVTNZcjZ3YXhUVlp5V29ydHF0Mzd3X0NsUkM2WHN6ZVplOWpxSVFldE1MdUNpTWhtQmFONW9VZms2bkhEVnhHVDR0UFpmUDVlRWdranlObWg1YTFhZHBTbmh3VHpSS2R0akpySTl6NWJ3QmdSMG12aUNhQWJWM1ZvRktIa3o2QXpDYW1XYktWbFk?oc=5</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T20:36:48+00:00</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n"/>
+      <c r="I135" s="2" t="n"/>
+      <c r="J135" s="2" t="n"/>
+      <c r="K135" s="2" t="n"/>
+      <c r="L135" s="2" t="n"/>
+      <c r="M135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI safety employee quits, says 'time for trial and error is over' - The Hindu</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOeVM4OU4yWXMtVlE4enNKa2ZLTnB6THFnS01uek9LUTFkXzdZUVdSd1RfamFnYWpmbERFbGM4QW1BMjFqU3Itc2hJdVV4OHAtcXQxYWNxcndqY2FyckNpVlFFNnRUWml4ekxqMHZQSW4zekplRXdCWEtRMzNULV9ibVdsbHRJeGtISF82NktBWklLb01ZTEM0b0VXSkdBOFYxVkg3S20wNDczQVdWWjdwVXNPQkVlWXNsUGNQTU5DNG9HMTB1VldGUXZYONIB0gFBVV95cUxQYXhaYTB6M0tWMUYzN3NmeWtFMkpGWFZlR05KX2ZmYzJsX195d2hvaC1TallYT3JEM2dyU2RsSHktWWxOZTl0V1M2QXZwNE5UZzlfemdYWTRhYk9teDE2dXBsZkt2dHktb0tsd1dELWdJTVY4SFlPTzZ6RTBCWkVjS3JBVWVCaS12dTJMQ1NQbTV3NlFQTzdVeHhEQVV4WG9CblpKeDVvVWhSNExmY2Q3WjVyV0s4QUJZbk1qUW55UDctOTFuNzQzLXNLaFVIa18tYVE?oc=5</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T03:39:01+00:00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n"/>
+      <c r="I136" s="2" t="n"/>
+      <c r="J136" s="2" t="n"/>
+      <c r="K136" s="2" t="n"/>
+      <c r="L136" s="2" t="n"/>
+      <c r="M136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>What Would You Do If Your Employer Could Destroy the World? - New York Magazine</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>New York Magazine</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdXhTTERZNUM3dm9EY1JaaTZFd2ZMZ1h5X21qU09RNm9hMTVwZV9SeWM2WXMtdzlEeEVfUWRLalplczg5Zk11Y1dPTDRJUHpXbFp6RGZVcDd3Q0lsRHFOcU81V2pDQmVnT2ozSENRblp2Q0VqTTV5YzhjZEVhUHRrTm9TUW8wakNR?oc=5</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T09:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n"/>
+      <c r="I137" s="2" t="n"/>
+      <c r="J137" s="2" t="n"/>
+      <c r="K137" s="2" t="n"/>
+      <c r="L137" s="2" t="n"/>
+      <c r="M137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini Live Avatar: What it can do - mashable.com</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>mashable.com</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9TYUhrV3pWejNxUlE1cUNDMHJ4R012SFVwNUI3eGpDVGdGVmc3MjdpYnBMS1ZKTjVDZC1XcTNwejVqUWlaYl9ibjVjbjdCRU5PaHdydm12LW4yWURVd3BHVDBBaVg?oc=5</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T12:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n"/>
+      <c r="I138" s="2" t="n"/>
+      <c r="J138" s="2" t="n"/>
+      <c r="K138" s="2" t="n"/>
+      <c r="L138" s="2" t="n"/>
+      <c r="M138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>ZEE5 taps Gemini AI to make long-form catalogue easier to discover - Indian Television Dot Com</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Indian Television Dot Com</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOejRoaTlpWU9nX0ttWkxBek9HQXNkMFVaZFFzSjN4YXRyNWJYSmdhLTc3SHVGRklPOU0tbkVWQ1FaSmFENjBBeGtyOGlucWFuYVZtXy16RmQ4Y3U2Wmt5SlI5emhFc0FpUWVGMDB3NHN2NjlHNVprdVZCQXhQcDNMdkZ0dVpvZHlaZnliTFdSLUNnaURxR2w5Ml9OTDNvN250QmlycjVn?oc=5</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T17:55:43+00:00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="n"/>
+      <c r="I139" s="2" t="n"/>
+      <c r="J139" s="2" t="n"/>
+      <c r="K139" s="2" t="n"/>
+      <c r="L139" s="2" t="n"/>
+      <c r="M139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Google is changing Gemini AI plans from October 9, here is what it means for you - India Today</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNRWhNU0VwOGNjT0hHemdBRlplQWpRbi1ZcDRkcTlicEo1Nmp4clk3QjRJUF9NdXlLdHJ5RkU5dFU5azBkcFlZT1JPa01oNXZHNll3YlNqYXpoNFRmbHZnSUtGdWNVdFU4M3F4N1RwSmVSZnZNQ01rNE1nVEp5V0FCaFktNy1PT3Bfb1k4SGI1TmFIZDIzdExfR3g1MDJIX194WjFOX01rTFV0dlF0UXFzN214QzlmMGdoY0Q3NUd5VnlRc3JRSlA1dWliZjVFVndqM1k3cXdBelFEOXVHeEo2Zms3WmLSAeQBQVVfeXFMTUVoTVNFcDhjY09IR3pnQUZaZUFqUW4tWXA0ZHE5YnBKNTZqeHJZN0I0SVBfTXV5S3RyeUZFOXRVOWswZHBZWU9ST2tNaDV2RzZZd2JTamF6aDRUZmx2Z0lLRnVjVXRVODNxeDdUcEplUmZ2TUNNazRNZ1RKeVdBQmhZLTctT09wX29ZOEhiNU5hSGQyM3RMX0d4NTAySF9feFoxTl9Na0xVdHZRdFFxczdteEM5ZjBnaGNENzVHeVZ5UXNyUUpQNXVpYmY1RVZ3ajNZN3F3QXpRRDl1R3hKNmZrN1pi?oc=5</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T06:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="n"/>
+      <c r="I140" s="2" t="n"/>
+      <c r="J140" s="2" t="n"/>
+      <c r="K140" s="2" t="n"/>
+      <c r="L140" s="2" t="n"/>
+      <c r="M140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Promevo Launches Insights by Promevo for a Total View of AI Agents, Gemini Enterprise Adoption, and Google Cloud Spend - PR Newswire</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNbG5TcGZHdlpsX3dhU2VaUU5uS1pzSEV0d0RsX29DekRzclcxc0RtOG0wb3I4aXAxYTRFcHJabEZFT253ZXFNYS1ueDVDeTFlU1Bwam8wSF8xblRmcUhVMFpkcmpySnoxdDlzN0JnSFdIcFp4N25uRjBrbHI3OVd2YXB4MnNZLXYyZUlEdE1vWEFZYXZuNGk4bGl0b0hNU2ZzRnhVXzRSSzdEUW1lZlNJdWZtaGpiaUNoMW1uc0VsQ1pPWnMxbnc0Und4MUNCZUVkV0xvNnhuT2l2bWFfR0F1UkRmWTlNaGdjS2pULWg2R3pfaXRvNlJYSHVHUXQ5ZVRrTXc?oc=5</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T15:04:00+00:00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="n"/>
+      <c r="I141" s="2" t="n"/>
+      <c r="J141" s="2" t="n"/>
+      <c r="K141" s="2" t="n"/>
+      <c r="L141" s="2" t="n"/>
+      <c r="M141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Major Google Gemini Shakeup: Older Models Deprecated, Fast Modes Pulled as Gemini 4 Argon Nears - nokiapoweruser.com</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>nokiapoweruser.com</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQdXBCYlVjZ19rTVo4aFd0VVdjQVFHV1JfSmx5bFNtdXlVbjJLMnB3STlBZGVsTkVrSzg0S3pTMkpZcUNpZ1M2cHFhSGFDbEkzV1BVQkRMd0RlWWVQT1RPZHJuWFlib00ySlVRa0NEUXJBR1JvQV80M1NSUzVkeXRHaUh4WmJWS1d1ZmZOcUdMZWRXYllwZlFNdXBZWHI?oc=5</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T13:19:42+00:00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n"/>
+      <c r="I142" s="2" t="n"/>
+      <c r="J142" s="2" t="n"/>
+      <c r="K142" s="2" t="n"/>
+      <c r="L142" s="2" t="n"/>
+      <c r="M142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini Tasks vs OpenAI Dots: Which AI tool to use for more productivity | Explained - Livemint</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPODNocDAwZHRZcDQ3ZmVKTmtpbHNJd21BcUR6NnpuYmJfb05GdUFSOVFIVFZfekJKSlNHdUV0OEpjUnBzQml3QW03d0VhUVVQSGtETFhpUnRiaEk4YlFFVXpGdm9jVlZpRWZJSmNXdGxEaDM0c1BRRXVPOXBMUDZCUzdhY2haQnFkSWZyMTBCaVlVWWxZS2RuZTNsUWRKS2pJNnN6RkhkaWhpNVN3cjFSd1NXcVhLeGtOQkNmUDhaMlVmaHA3OHI3RUlKdnI2al8t0gHWAUFVX3lxTE5ESkFmc2RIdFh6bFF4c3JCZS05ckxXeFh2WDR1Mm1rVWhSYWJmRVVXZUI2dnJIZVlyRURXeGp6VFMtV0tEX0pxNVp1X3NrdVRiNGlEODloT0dzS01UV3N2bUQ2X21tOW5EZGJzSm45QmR5bHYteVlnTUVyQVFmMmhPZkRXOFVaRlFXbkVfb0RlSHl0NnptWjNPMmg3aV80WmUxXzAydnRsVDV2Mk5DTFFHcDVqcDkxRThWcEhROUFBMVk4dkJWYTIzU1N0eXM2dnllTF9YaGc?oc=5</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T18:26:20+00:00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="n"/>
+      <c r="I143" s="2" t="n"/>
+      <c r="J143" s="2" t="n"/>
+      <c r="K143" s="2" t="n"/>
+      <c r="L143" s="2" t="n"/>
+      <c r="M143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini Plans Get New Limits: Free Users Lose Flash, AI Pro Gets Deep Think - gadgets360.com</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>gadgets360.com</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQelE4VnEtOTBXcEFELVRHZ1l0ZnZFZFZNS0hQZUd6OWRCMmZ4cE5xVGtzcWVQY2VTa3B2d1M2cWt0YWg3ZHVma2NwR2Eyb250Z2xjNU9pRF9oN01QU2JqRzZtN0RiN29tQlhsYUdsT3YyaEwxRFRkYUFMXzB6aG4zbi03Tk85QlBWdGlMX2JVOVkyWXhaZ1VDaC0waGsyQ1h3ZXBXZHoyQ29HNW5VVDgwd2JLM2NYdFlFZHY1eW9WN0tvQnJCTFU0am5hUVFtRDZibWtQeUkwNljSAd4BQVVfeXFMUHA3TldpeXpEd0xOTTMxOTlydm1CTjFMRGJocW5JeVR4WTk5RXlkX1Z3c1lLR3lmRnNzcXZqMThHajdwNGs4M1ZuMFhqbFVqUHF6RnZ0b3VpX000VUxsLWNxTUdoc1lqY2g0dTRlMTI4WVNFX0ozQ184M1VjWE42ZVB1YW9lclJXeGxwUjFaQmhIM3pxT3puNkdTeWl2RFh4dTNiMnVvZTItZXdjUTk1d2NiY3l1THJ5RVJ5OEV2Z3pfYXNTUTN6bl92WmFIczBTX01OaGNudnBCTmZPdWpn?oc=5</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T14:08:10+00:00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="n"/>
+      <c r="I144" s="2" t="n"/>
+      <c r="J144" s="2" t="n"/>
+      <c r="K144" s="2" t="n"/>
+      <c r="L144" s="2" t="n"/>
+      <c r="M144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Gemini AI Paywall: Google Restricts Free Users To Flash-Lite Model From October 9 - ndtvprofit.com</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>ndtvprofit.com</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNN21LWXJWR0JkTFpPXzl3OVlQMGlpdndhQTlxalZIczc4NWFtaVR1bDBCSk8wSVRUOVZSNlhGUFQyUG8tbGZ0RlpHWnlwNEJGZFV1NFFmQVNrTDN2SksxQnNzVWt3YUkwMng1QWVCZjJEdWk1eU9DdHAtSjFfMzd0cHNiMkJ1VVM5Rkk5azEzRm1ma1FKVl9NRmxQcmJjSXpmVEVpTmdFNlBvQW52b0tvX2VOWXFQNnpXZC10RW1vazJ3dVF0WXfSAc4BQVVfeXFMUEZtZUNQR2N1VzV3R2k3V2NvaC1vSTJwd0ZXVXk0cHdCeXcyN2FkVE53VUFXZnduNG13M2Y1VGhHRVB4QjNfZ0NRcG0taTIyWUI2RkhJU2tITHU5dW5tcXhVSno5TDRTYnRjVUF5OGdNVGVuNi1HaW96emQ4TnhJeHp0ZHVPX1FZbzBNdEJxVkNUa0xBQVRfMG81eDdfVkhTVVEyV3JzVkRMWFVhbnF0VEl4b2N0SlM3b2owNWd3TjZHNmU0dXl1TlNpeWJVbmc?oc=5</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T17:41:13+00:00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="n"/>
+      <c r="I145" s="2" t="n"/>
+      <c r="J145" s="2" t="n"/>
+      <c r="K145" s="2" t="n"/>
+      <c r="L145" s="2" t="n"/>
+      <c r="M145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Copilot in Word finally shows where its answers come from - Windows Central</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Windows Central</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOd25OWVhibjI2Z0J5ZVNXd3NkVGhjQ0hrNFNFR2hibU9HQmJUamFfcDBqMkYtc1lQY0QxbDZBcGN4RXBQTE5rZkJ0dW1fUHNId0hVTlJsTllibVktWjFsREhqTmlYc2Y3MENISW42TXZiM1ZvaXp4Vkd4TmxZTEY2YnVwQ3VUQjczeEwwcS1QTG9CeW9FZEVzUmtiYTlscWI5cGN4YjBVa1EtNXFyTlRXU1pRc1otdnZud2Fyek96N1dfYkFpMnNSVEF1TFBMVVBsdTU0NFVSa3U0dw?oc=5</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T14:24:46+00:00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="n"/>
+      <c r="I146" s="2" t="n"/>
+      <c r="J146" s="2" t="n"/>
+      <c r="K146" s="2" t="n"/>
+      <c r="L146" s="2" t="n"/>
+      <c r="M146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Is Copilot Microsoft's Secret Weapon in the AI Arms Race? - The Motley Fool</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>The Motley Fool</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSk0xajhTbjhSN0lDUmNNZmtlVjctbW5PbzFFSHdaLW5JQzdqWkF0WTdyeExSVWhJSVpHa0NYYlU4Q2N0Ym5Bd1hvY1FhRjgtNkE1UEJVMzRzTF9NdHptUVV3WFEtNnBETTVwb1dqX1ZSOWZ5YkhDTlhQR01yRHVna0hkU0hST3loTHRHa09tZzg4ZUZETjd2OA?oc=5</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T19:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="n"/>
+      <c r="I147" s="2" t="n"/>
+      <c r="J147" s="2" t="n"/>
+      <c r="K147" s="2" t="n"/>
+      <c r="L147" s="2" t="n"/>
+      <c r="M147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Hires Former Microsoft Copilot CTO for AI Agent Push - Business Insider</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Business Insider</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPWmpZcGRaRk42NlpsNjhCd1dmelZkRkFPY2E4M0tlVTh3elE2SmEwNGg2X0pDMXhUZHUtLUdBOHpDeDBHbDdmbjh4dm5yTDJrdEdscnJ5ZkpqOXl3Y0labVZVN1MxSnVpZVJDMC1xXzFWNE9WRjdlcDVzMkJPclBYTjJweGpzdWZDMTAtOVVXT05VSllDY244U3l4QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T17:45:23+00:00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="n"/>
+      <c r="I148" s="2" t="n"/>
+      <c r="J148" s="2" t="n"/>
+      <c r="K148" s="2" t="n"/>
+      <c r="L148" s="2" t="n"/>
+      <c r="M148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Wood Mackenzie connects trusted energy intelligence with Microsoft Copilot - Macau Business</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Macau Business</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOYnlybGFCbjRlc2U2S19pb2V3RS1kMDhOdXZBV2FEazNhWTRXbHFPNG9rd01WYzd0dHA2UTBPQUcweHdqd01lT1FsMzhQZk9vblZrZTdtbzZNQV9sMGpmLVFfMU9KRTlCWVNSZHlYSkZQQm1haW9IUExvQ29jRFJ3ZTRNU0xDNm0tSzdCaFZPOEEzRm1fU3VtREhFb2dmcFY0YXYw?oc=5</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T18:57:34+00:00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="n"/>
+      <c r="I149" s="2" t="n"/>
+      <c r="J149" s="2" t="n"/>
+      <c r="K149" s="2" t="n"/>
+      <c r="L149" s="2" t="n"/>
+      <c r="M149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia, Broadcom shielded as AI power crunch hits chip supply chain, says Morgan Stanley - Reuters</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOMF9lcTkxVU5OWUp5THhibUJWc3U0MWo5c2dreS02dFk3TGt4SlBXLVdpX0htOV85SnVsc3RUZjZJZDJac3p3bFgzS05uU2hjVXh5N0RjcFVtQml0TnBRSllwREVDdUVFOTBoTTRMT01RMnVUNGQtZk1ZY0ZIdUZHWHNBbjlaMk10dEpJZ3J5eTZHYjlDQW9JdEg4STBBLVNYNlFRb1J1aUJudHJkS2lmT0otSUJHdE5wVnJaXw?oc=5</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T14:15:59+00:00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="n"/>
+      <c r="I150" s="2" t="n"/>
+      <c r="J150" s="2" t="n"/>
+      <c r="K150" s="2" t="n"/>
+      <c r="L150" s="2" t="n"/>
+      <c r="M150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia, Broadcom shielded as AI power crunch hits chip supply chain, says Morgan Stanley - The Economic Times</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNSVhnYnVpTFdhcUVNQ0VDRUZHdmhSSjludEhxZi0zbVNYRzAwc0NZTENna3R2Qnh4Z2lHR3BQSUx6X3JmcWt4NXlnVUVrT19SS09mdEx5dnFTRXVMalRHQ3lEeENuNUN3SEh3LW5YVXRHRkJPNm84T3VBN3R0aGV3S2NaQ1pNQkg0THlwLXVwalVMWjRpWVBNbHBiaGhHd05teDZzRlF1RnJlTXliVHZCRGwxMmVvQi0ycUJzazQ4NWZCbEVEQ014ZWFzVVZFVzc4alg0M1ZlTTl6VnI1TmhSUXdhaGxLVHhBQkcxeDZ6U0R2VGRFdHhwYtIB8gFBVV95cUxOOEZNSEcyaDA0akFvZjhjVTNsRnZNUVFfWVhqNFNMbWdRdUZGMy1RcHhrQmJKcXdnaEt5N212Q0RtdVowY0hlQThDMGlJbzl5OUx0SHhtTjcxRHhDbV8zUlhZM2hMQnhMQno0R2tWa0RPYWJhdU1Cem9QbjJWbXQwUTNoQkZoMEhsMlJuek41MWxpcnhjV1ZsWEhOZ3BZYUhvZjRZNWhLT0VnbHZlbS0xS2k0SlloZndZV1NUR2xmbmdNS191RExia0VjT2pXUzcyNURkckpxd3o4Tmdkai1vZmM0Y1Rsd3M4OEx3SnptQ1BKdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T19:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="n"/>
+      <c r="I151" s="2" t="n"/>
+      <c r="J151" s="2" t="n"/>
+      <c r="K151" s="2" t="n"/>
+      <c r="L151" s="2" t="n"/>
+      <c r="M151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia, Broadcom shielded as AI power crunch hits chip supply chain, says Morgan Stanley - TradingView</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxPY1NTcUxqQmRjR2cxVFNVeEdBWFVfZl90d0NLRmtSeDBfdkpjS25LRUx3cEJBS3ZrT3ZjNVJuaW92RGlONF9JemJHcVREbDl5RnpRZHZOYllRSHFuQXd6c245SENUNmlOMjBJQzNiYTFGb2lrYmpBcXRNTkFDVTdzbjR1Y3JHX1p2WkZNZlcwZVdKb2EwOWtkS243VlpfLXBEOVVwVkEyWjE1Sml5MlpOOE04bjFUTVo4aWc5WjF1ekwxb3hjSmJ2ZjhfRThmYzFmMm9ReWRON1YtMWZOVUFrTUFKa183MlhmSDhpcQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T14:08:41+00:00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="n"/>
+      <c r="I152" s="2" t="n"/>
+      <c r="J152" s="2" t="n"/>
+      <c r="K152" s="2" t="n"/>
+      <c r="L152" s="2" t="n"/>
+      <c r="M152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Tokenised Stock Climbs To $235 On AI Growth Prospects - MarketForces Africa</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>MarketForces Africa</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNM3R4QXNsVzRYRHk3MGJIV2QtSmtDVGdReE5kcHR1ZklUcVNwRXI1a2V2T3FjM28zelViMzRQRjhHUFAxZ2t1T2toNjd3LXZacUtKS1F0N2R3ZWgyOEhwX290c3pVVnYzUlNfb1NZRG0tZXU4Y3EzWkt4eGU5MFBqOVlmTFp5QVlHYkJFYUViYw?oc=5</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T18:22:03+00:00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="n"/>
+      <c r="I153" s="2" t="n"/>
+      <c r="J153" s="2" t="n"/>
+      <c r="K153" s="2" t="n"/>
+      <c r="L153" s="2" t="n"/>
+      <c r="M153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia Stock In Focus: BNP Paribas Hikes Target To $345, Sees 47% Upside On AI Dominance - ndtvprofit.com</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>ndtvprofit.com</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNcmVyNTZYaG1TMFY4M0FkV0tGZUNwTkZPU2RBdEtCVmYwZ2VsaHZuWjhJeDZTV0Q0bmlkQ1VSTk9lN0hqbDVXY2EtVGNCWUxjLVJ3Rm9QRmFtcWJFRUpNd3R3RUlrazhuVWg5V25NU0tuWXFrM1N6Z0NiSUpnajZRS01PU1BRSGhqYnpIU254UmhIWkR6eUNva01RTXB5VWpZZzJ1X29PdG1jV21wUjkzVVMxOWRuQU01eTkzdENjVVNvQ19UdXB30gHPAUFVX3lxTFBmOFd1OHhZZExNZ3VBdUJlaENsc1ktM0FUSHd2eVhDdUpuM0tiMEtuU0RFdkN1STVCcHlRSEt4MkRGYTlsaU9vU0xtb25KSGNuV3NsUkxFMXVHS1FMd2ZfcFJjdjM3SFJSVUhpU0Y4djVvRkIxYThtamp0emVBSkJQaS1yV1FWbDZQTE9FY2c4RFdwTzZfbFFWWEJGM19mc0ZSc2NQaGR4OTlTVXd6eWRrYzNkNmJINDUzS0VYU3FkbDJsQ3FlbElkNEhUTXdaYw?oc=5</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T15:51:24+00:00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="n"/>
+      <c r="I154" s="2" t="n"/>
+      <c r="J154" s="2" t="n"/>
+      <c r="K154" s="2" t="n"/>
+      <c r="L154" s="2" t="n"/>
+      <c r="M154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia still 'the one' for AI? BNP Paribas raises target to $345, sees up to 47% upside - The Economic Times</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNN2pHbDQ4V1dsRVJiXzFJOXlpN1ZVS29USVhERzdSNGNKY0kyWnZJOUU2LUVvdnNkbkxHQmdsVW9zM2g4Wmd2bDdVZU9XVkpCeXJ1dkFLQlE5QW1IQnZKeWNiNkxCZ0NVaEhCbDQ2T2djdUFseHJLZ2VxUlk0N25mS3hzNnJiTjMxWG4yeUNvU3VNc2N3SGR0RThRRnloeEUwbmN3d0Ridm8zSU14OW9WeTZEeEJRZjlmWFF0LW14VE9BemVnZTVGLUd5SjdnTWhzb3Q4cVg0a3A2c2ltWGRtUnVwUzZMR3pvWWVSWlUzbkR1S1R5bmsyOG1WYUU3ckQ00gGGAkFVX3lxTE1VdUtwVzhQVC1aUzdINzFxT2pJcFlITzhFdUFlUXIzRUl1dGZZMnFPdWJjNjhRNGR3cF80ZHhIQldLZk56M1EzWWZfMGZlQUY5Z1dTVFBMSlBvcTgxRTliOE91M2Y0VWZnLWxCa1plNW9scnlLbkRFRmJLWEFrZGoyMFR5MlBvYUVwbDlKVE16MWhXcGlHWGpUWmF4Z0ZqTDB1d2lUTDNyRE83ZDQ5a2JBRXJXQWdqbEZrbjBONHhULVpGTUc1bHNrQ2x0U2pGTzhDb1FCUXpWelk1T3BvQWZGYXZHSDFQWkVRUHNIRXdrR09ISDJDc1ZQdDRHMXd2YXVZU1ZUQmc?oc=5</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T10:21:40+00:00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="n"/>
+      <c r="I155" s="2" t="n"/>
+      <c r="J155" s="2" t="n"/>
+      <c r="K155" s="2" t="n"/>
+      <c r="L155" s="2" t="n"/>
+      <c r="M155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Scoop: A powerful new model from startup Reflection is set to shake up the AI race - Axios</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Axios</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5meUx1aTFnUHltcTFXRmNIWVhPbW9Nd0lZMXdQVlRuVFVNMW5xRG1QaFpnanA4YnpicU9VTnMwQlZuNzJ4M0lYV0haWnNsZjZGZzFnRkNfZkItbkg2a3BCZ1FEbHdqbEZHc0E?oc=5</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T08:19:35+00:00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="n"/>
+      <c r="I156" s="2" t="n"/>
+      <c r="J156" s="2" t="n"/>
+      <c r="K156" s="2" t="n"/>
+      <c r="L156" s="2" t="n"/>
+      <c r="M156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia CEO Jensen Huang has emerged as the biggest foil to AI doomerism about the existential risk to humanity - Fortune</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9VX2xQSnFmUmlVT193Tk12UThLN0VzWGNyRFNHLUVBT0pMQzJiNm9FZW1LQlBwN3o1am81NlFCZGxoZFA0dlpTMGlmaGI2eGUxdnh2QVY3Z0QzQUN5WUIzcG1XT2d1U1NmekhFNHRuUk9qSF9xSkpjbG1CdzIxWjQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T12:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="n"/>
+      <c r="I157" s="2" t="n"/>
+      <c r="J157" s="2" t="n"/>
+      <c r="K157" s="2" t="n"/>
+      <c r="L157" s="2" t="n"/>
+      <c r="M157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>DBS Group CIO Hou Wey Fook says AI rally is not a bubble - qz.com</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>qz.com</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE1lbm5VSHBzVmY4MWJmeUk3UzdmbGNfZzZQOWdYRGRNZHhYNE1DY08wdmdqc2tRTUNzYi0xRjJlRk5zcWJVZ3hKODc1NlkwUmR1QVZFY25TNGQtRHdadVpEYWxB?oc=5</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T19:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="n"/>
+      <c r="I158" s="2" t="n"/>
+      <c r="J158" s="2" t="n"/>
+      <c r="K158" s="2" t="n"/>
+      <c r="L158" s="2" t="n"/>
+      <c r="M158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia Partner Hon Hai Beats Sales Estimates Due to AI Frenzy - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNVzlNa1VEX2xXMTVORThGeXAyQVQ1ZTh3VlY4VFZYVzVzVUVlQ3Q1OEo2THN6Ym40MUEtRmJfX19xbFREMHkwQ3U5QmFhbUs4ckRhM3J3VXhvMEhWUWRKRTZlOWdwSm1nOEZhOU9JS0JmbU80by1CdWk0dG5YTkZobmt6MUtFc2VqQ3hwekVJMFc0NGdsRGZUR1dDb2tiTnFyXzJXTkN4MDNmMVdWTDFOUWJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T07:43:15+00:00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="n"/>
+      <c r="I159" s="2" t="n"/>
+      <c r="J159" s="2" t="n"/>
+      <c r="K159" s="2" t="n"/>
+      <c r="L159" s="2" t="n"/>
+      <c r="M159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>AM Intelligence To Invest Over $20 Billion In AI Data Centres - Rediff</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Rediff</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOSldDVWpkNjExaUJVbzNJYlhCSnNpaFp3aW1XNW43dk50RTJNbXR5VW8xRWVUTnVkU2RWZmoxcU14SU45OWxWMjFUWVNYUFlNZEgyUktTcWdQeVpZRFo2a1huMVlxVXdlcXowLW5acWVWcnZTdmpyOElyVS1iZjJkWXM4d1RnRjhSbDBVRDl3Q2ZmdlRHSHVCek1JXzJEeU91Uk9BSjU5VE5SX09xWHFJTE9wUdIBtgFBVV95cUxNTGVhUlJsVVo3R0xIcDk0Wmc2ak0wT3JwSFlaN3o4YlV3a0NGbjdLVnA2akRZT2hnclpEM3Y1M2F0MkVLSjFMTWJLZlBwNFZQbk5xWFNKMkVCZS1DRklYR05uRnZGRG1MVlczOXVYTUw4dUEzajM1NDdvMVpIRFZBeC03Nzc4R3JBQjJWRlBSRU83VEQzSzBEV2tiMTFnNWpZQUt0NG9VSkFudlV6UEQ0ZDVTdjIwQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T16:39:54+00:00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="n"/>
+      <c r="I160" s="2" t="n"/>
+      <c r="J160" s="2" t="n"/>
+      <c r="K160" s="2" t="n"/>
+      <c r="L160" s="2" t="n"/>
+      <c r="M160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>AM Intelligence orders another 20,000 NVIDIA Rubin GPUs for India, Malaysia AI factories expansion - The Times of India</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxPeGZNcGZMRC12Tm1aRVdlM0RGLWd1dDJhWnRJTk1aX09pcFE4a2Fob0pieVF1VGF6LUNJVDVHRjlOTlpUSDAtQVJ1WVhTVV9iT0FpYnI4ak5lWjZ6alltekFnUS1XZlRwWGVla1lVQmc0SWZsLWp0dDF4ZUpKN3oteWJ2bmFOZGhmdzdrWnJqYm50b1hEb05tWGEtLUw0c09DWUJUeVBGTk5Obzg2cHRPYmZWbEVjZVBLaktDS2wyd0QwaGdiOXJ3bl9CdGdKZ21jZ0oxX2xJY25nTmQ4b1F3MW5GYWNDUHNmdDNyTmtYZDJYUHJRMjYxTFM1VWFJTnhhUTBv0gGIAkFVX3lxTE5vbnZGeEpvRERfb2hkTVpTcF9UMVVqN2NRRmYtS01jVzRKeHRqZmUxOE9taTBydjR2dHZoVDFWekpkbS1nWnRoZ2pjVV9NWTh5OGR3QnF2dktScFg3bGQ1SFFaVm8xeW55WUN4WV8zWGtnejFVclpjSTJlemdLRmN4TlZEVENxTmZXVDdkWE4wZGhtS1lfOFE3bk1IMmJGY21yU1dpaDR5bkF2WnhLMk5HMDBYNlRoZXRTaXExQlQ4YkZzQi1RZ3d4UTZIcU5qZ1NlTFBxekstb1pERXQyY2haNDNVTkQxWUVab1o5MVBhWWp0czJBbk12VU5mRWFtakd1Mmp0SWFZcg?oc=5</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T13:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="n"/>
+      <c r="I161" s="2" t="n"/>
+      <c r="J161" s="2" t="n"/>
+      <c r="K161" s="2" t="n"/>
+      <c r="L161" s="2" t="n"/>
+      <c r="M161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Researchers are tracking a Chinese AI ‘agent fleet’ - TechCrunch</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNQ1BCZXR0XzYzZkNidXhGSVc2WDg1ZVZBT20yQ3BfaV9wZW5Va2xwamFNWHpyZ3Awd2xwU1JBWnVFa05uX1JVUU1vdWloWnhERVpqcmo3R3F6c3pLRVpub0dsWG1XanZuTDBoR0trZnFxcmE2REZnV0s2LVN6TE5JdVMtd0RKN1ZmSGlFTA?oc=5</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T14:35:09+00:00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="n"/>
+      <c r="I162" s="2" t="n"/>
+      <c r="J162" s="2" t="n"/>
+      <c r="K162" s="2" t="n"/>
+      <c r="L162" s="2" t="n"/>
+      <c r="M162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>French cybersecurity startup Fleuret AI raises €4 million to automate penetration testing with AI agents - EU-Startups</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>EU-Startups</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPbXFlcF9GM2N2Z0ZJa3BFaUcxQkZRLXEyZGp5emE5TGFnWFNoVEUwcDB1VW12c3hKbzVZNFpQdnJQYjB5WWRPdjl4OUowSTk5UUg2allWRFptTkRrWHdnOUtBVVVkQ0pPbmFJTDBRcDJnNU5tTm5sMUpVeVktMDRPVFBwaFpFcVA5S1llUm5RYWZ6cVctRm41N3hGOHk3OTJralpaZmpCVzJXOEdPdGJwbVFqUF9GNHZycDJ5X1V5OXlnVVZNQXNaVU5XRy1YUGlsN0FkSXZ2dWI?oc=5</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T07:22:40+00:00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="n"/>
+      <c r="I163" s="2" t="n"/>
+      <c r="J163" s="2" t="n"/>
+      <c r="K163" s="2" t="n"/>
+      <c r="L163" s="2" t="n"/>
+      <c r="M163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>The dangerous myth behind AI agent hacks - Financial Times</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Financial Times</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9DOHhxN1Z6WUIzbkNpTlVSSDBhOFppQnJyYmZUTkhNREFnX0w1a1p1d2ZBUEdWeGppTjhIOUFQVE5BNzA2M3hyVHptQ2VNLXVZcXFYY1hPQkQ2d201bjFCeVl2Y3VfSlhSTUV1M3VfcjQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T14:34:32+00:00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="n"/>
+      <c r="I164" s="2" t="n"/>
+      <c r="J164" s="2" t="n"/>
+      <c r="K164" s="2" t="n"/>
+      <c r="L164" s="2" t="n"/>
+      <c r="M164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>How OpenAI’s runaway agents covered their tracks while targeting govt websites - indianexpress.com</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>indianexpress.com</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPZTlyLWx5OVdDYndCX2tjcTd0a1d0TjdUcEptQjZlYUZ6QzdQSDB5VUVVdXVDVEREWU5GcDQwT0FJSzNNV3hpaDJmRjB2T3lDbkJVY09OY21KUUI2MDdVMHBiNzFzM0R4Sjd1Z1JMOHF4Q0hSdWFfMmljdm9yVW1OeWE3QU1DVXFnR0xmb0NKckx6VFhpb3piRXVpampGRGR0b0lQdnRkaWdLUzkzWmdWMdIBtwFBVV95cUxOaEtuS2pHM2djR21WRWlyY1hlNERGMnc1ZVdHNDQtbW1Ja2liR1ZLbVNUbXVYbE9HYnFrR1ZhYjg1ZGo3UVRfa2tCaGtEeWxRMmVCOS11RGtnQ2pQRDdEUzhfZTZmYWNtdEVZR3FPaUVmcDdSZDBJQjZVdE9rN2RBT05OLUZRT1NLMV9NTlVPOUdjY29MUk80Y3lCOHlUajBPZTd2WUlSOFcwdDZ5V1Z6N3lVUWhVZUk?oc=5</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T11:59:57+00:00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="n"/>
+      <c r="I165" s="2" t="n"/>
+      <c r="J165" s="2" t="n"/>
+      <c r="K165" s="2" t="n"/>
+      <c r="L165" s="2" t="n"/>
+      <c r="M165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Coforge Develops Framework To Guide Enterprise AI Agent Decisions - analyticsindiamag.com</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>analyticsindiamag.com</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQVGhINU5uOVd1RDdpVXQ1M3pFM1lEM3dyRFp6SnRUbGcxcTJBbVRIRlh3SkVXajVySlVjWGg3dXFvb2ktT0RuMHlRN0xDckpCV3BKa01fR2g0YTU3NjQwUGZGTjRXZjczZ0FROXVHV0Vpcjc3QUoxMnkxSWlTNGt1cVZGc1VmMXhMa2IzSS12djBiLXFhMk9uZVhtbEhicmhJbVMyYnR3?oc=5</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T16:03:05+00:00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="n"/>
+      <c r="I166" s="2" t="n"/>
+      <c r="J166" s="2" t="n"/>
+      <c r="K166" s="2" t="n"/>
+      <c r="L166" s="2" t="n"/>
+      <c r="M166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Apple is making changes to its OS for Macs after users' complain about Meta's AI Agent Muse accessing the - The Times of India</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAJBVV95cUxOUnQ3SC1rYmlDM25IUDlVaHN1Mlc3eUpSYzMxNVN1WFA5Y1duMnZvLWZBWVFxamRHam1STTJqMkduNHROczRBXy1uaVU5TkpUdWRDRFNydllBbHpWQTlBTXRwSE5NOUxPMHlHN3VUUFlaZVZwNWxDOGl5MmV6dkluOXo1UHZRR2MzdTU1SUdfWXZybXNzb1JBTWJaMENDb3BEOGN2cXFaZ0NZUjJWa3g3WmVIMU9QNngtdUJvN1gzS0pZa2xXVDFuSUpzYzlSdm55THhwYVBVY0lYaVNRdF80ZUpoT2NNYk9VbDE5QnBSSTkwLVBkZ3JYUkMyNW9nN1d0NEl5a0habVB5cG52SVYycVhyTE00T3Q1VlA4dXFZX3pWOEtSb2dUMNIBrgJBVV95cUxOeTJ5VHJOY2ZpNDdlNjZSSF81eHZVdjZnU2xzMnRJMDZBWEJ3clZCN1M5YkJuNjh4RzNQTEVOZGpqVkRTWF8yQjllYUhBQVFsRjNjZktNZUN2MDZBUmJYTVBRWW9ORXJJZXJlX3YzcEtDRUZQUmhzNHMyX2FBUE1DME1nOHd0ZXRXcGRUQi04LXkyZDc2S1ZQOVluQWtTSm9meXUtdVdZdmlTZnY4TTZTUWJvV2szbzIydVdrOEMwY2I2dXhQeUJJSG9CWnNCblNiQW5fVGV0MTBvaFRwZnJUajR3YVV5SWMtcW11aGMxbUNPaktlYzRfckRSTFZGb2xrMU1fR1VEMXZIeElueE9WZVhuNXB3ZVhYYkhGUGlvWUhrWTJuR2hjY3BrSTk3UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T02:02:00+00:00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="n"/>
+      <c r="I167" s="2" t="n"/>
+      <c r="J167" s="2" t="n"/>
+      <c r="K167" s="2" t="n"/>
+      <c r="L167" s="2" t="n"/>
+      <c r="M167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>How to Regression-Test the Systems Evaluating Your AI Agents - hackernoon.com</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>hackernoon.com</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPRFJKNlh6cjZRbGFBanVubmQxUUZVYktKOTZxUTl3OHRFSjB3dElYRWczaDdGaExhZHRDUF9KMW9JYjU5UDg1dUVzZlNZVGs2bENSTHdHbnZrbWxvOENQQTJaOTExWlpqUk1yU3o3Skl1eVZZdGtobDY3alBTVVhmX084N3FyVkdHUW5v?oc=5</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T16:19:07+00:00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="n"/>
+      <c r="I168" s="2" t="n"/>
+      <c r="J168" s="2" t="n"/>
+      <c r="K168" s="2" t="n"/>
+      <c r="L168" s="2" t="n"/>
+      <c r="M168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>The AI Agent Trust Gap cartoon - Marketoonist - Marketoonist | Tom Fishburne</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Marketoonist | Tom Fishburne</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9FajNFcTBNbTVCd0toNzVFZDd5Y1NkVmxEMEVacXZkSmRZUFBfRXBBS0U5WW9iSV93UllFUEJUWlZzX0QwU0dudlBwT21JelI2UGdZMFdLYkNxajJLUWpLTGptUGs1d0ZpZUhmeg?oc=5</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T11:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="n"/>
+      <c r="I169" s="2" t="n"/>
+      <c r="J169" s="2" t="n"/>
+      <c r="K169" s="2" t="n"/>
+      <c r="L169" s="2" t="n"/>
+      <c r="M169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>AI Agents Get to Work in Retail - PYMNTS.com</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>PYMNTS.com</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQX0RHaE81MGtuUF9xcnNNTDhNT3NfYmkyZmU2ZTlEeG5LcEc5RlY1Y01WQVNHZE84X2dydnFyZ1diOEdtLS1CYWJvYmdQck1yaEVaN1U0T3JZM2I3eXhseUpBZ25zeW81R2YzYi1PMVYxLVRHMHQ5SUphc1F1b0x2T21vMWpFNTJCelhBOHRjWE0xaUE?oc=5</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T17:24:25+00:00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="n"/>
+      <c r="I170" s="2" t="n"/>
+      <c r="J170" s="2" t="n"/>
+      <c r="K170" s="2" t="n"/>
+      <c r="L170" s="2" t="n"/>
+      <c r="M170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>The risks of AI overreliance in software engineering - TechTarget</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>TechTarget</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPSzQ2Z2MwcGxteS1Rbk51MnJDWnpaSUdpeHcwcTJTOEc0Qkc5R3NBMVJvdm5vV2xoVnlOTmdYVUVWT1Uta2dTd3Y4YWRITEhnRzd0b3NXQWFpNzhCS3ZKUER0SVcxRzZva2RzaWtkeU90TVdHSWdmZlpkcDdocHRyM0NwQS1tMS01U3Iyb3ljYw?oc=5</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T18:31:16+00:00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="n"/>
+      <c r="I171" s="2" t="n"/>
+      <c r="J171" s="2" t="n"/>
+      <c r="K171" s="2" t="n"/>
+      <c r="L171" s="2" t="n"/>
+      <c r="M171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Developers Adopt AI Coding Tools but Question Wider Automation, Stack Overflow Survey Finds - Межа. Новини України.</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Межа. Новини України.</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBQNnhhdXZwM2lfcFpSUUdmRk9wS20xeEtDTk1zZXJLVTI4RHdjbmY4c25JeWVsbXgxQ3VfdDhnZ2dUYVlzQVAwaldqd0JBRFcyOFhNZlgxaGJjblRJWDBHaHE0dkY5WlE?oc=5</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T11:47:09+00:00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="n"/>
+      <c r="I172" s="2" t="n"/>
+      <c r="J172" s="2" t="n"/>
+      <c r="K172" s="2" t="n"/>
+      <c r="L172" s="2" t="n"/>
+      <c r="M172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N172" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>I used Claude Code, Codex, and Google Antigravity to build my dream note-taking app, and one is in a different league - XDA</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>XDA</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOSllOMVV4SzdGY2tYWDgwVTQ2N3dhS2FEOXBtQWlFTjVraWlXdVhCaXpGZkZmRF9CZ3VfTW1namxQRDRJNjVJVnhsME41RzFZdDBxdWdwVWZfdjA3VU9nc1dhUGp6cVlPVXlJT0FhTWF5OFc4T3RBTm1DUmZNRXFuRmFaRl9NdC1qbzlCYWdaOWNsS19zUC1YVFA5UFp1SDZqM3lkcHE1WExteXpL?oc=5</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T21:30:17+00:00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="n"/>
+      <c r="I173" s="2" t="n"/>
+      <c r="J173" s="2" t="n"/>
+      <c r="K173" s="2" t="n"/>
+      <c r="L173" s="2" t="n"/>
+      <c r="M173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Amazon hires a Microsoft AI leader to help build its tools for coding and work - GeekWire</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>GeekWire</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPZ1pncjVJSDloNjF5eWF4eXBwWnlEWmNna0NuYTZVbkM5Mkx5MDZ4UXN0V1pvaWp6dGVtd0FtWmYwWWJFX2RRYkFLOThNWUR0MHA3UFVzR0x4dE5aQlBJQnlZT0ZzQzRkc3lJVmk3Vmp1T1NfZXNoYkI0bWJTZFZ1ZENybUcwNzVNeTNWUmo1eDFMMU5UQkRWUFdpcWlfanNFekhINFY4RG5XWkl0RFE?oc=5</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T17:49:09+00:00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="n"/>
+      <c r="I174" s="2" t="n"/>
+      <c r="J174" s="2" t="n"/>
+      <c r="K174" s="2" t="n"/>
+      <c r="L174" s="2" t="n"/>
+      <c r="M174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N174" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>AI Coding Tip 039 - Write Your Own Zeroth Law - hackernoon.com</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>hackernoon.com</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBNcUJCTHVQemxuMm1kMUZBWWhXNU1xdE9Kbm1XMGVxNGduaGxaLXYwb2ZCbUhOOG5YTWFKMDZPZkhpa1VveDJXeHhVVnVrVWpqUEdHTHVHcGJyOUw3cjZidTJrdm5jVGE5eERrZTFhMDNQa0lW?oc=5</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T06:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="n"/>
+      <c r="I175" s="2" t="n"/>
+      <c r="J175" s="2" t="n"/>
+      <c r="K175" s="2" t="n"/>
+      <c r="L175" s="2" t="n"/>
+      <c r="M175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Ex-Google Founder: "AI Already Outperforms 99% of Developers... Will Replace Them All by Next Year" - finance.biggo.com</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>finance.biggo.com</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5kelFxbHNuNzIxbm5ZY2xVMHh6UmRYQ2h0dS11X1lyZjZqTHJFMndiZUJPNEpHQmRYam9PNEk5QmxyZzM0d0xjU0pSY2VBREJ5VHZLVzJUN1N0N3BlbGxzVVQ1X1NzOWtKbGhYM0NDRzVBQldWS1E?oc=5</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T07:25:00+00:00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="n"/>
+      <c r="I176" s="2" t="n"/>
+      <c r="J176" s="2" t="n"/>
+      <c r="K176" s="2" t="n"/>
+      <c r="L176" s="2" t="n"/>
+      <c r="M176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Their jobs were among the first to be changed by AI. Now some are trying to avoid it - CNN</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5QeGpPajNUUGU1VlJ4Wk1oY3A2S1ZXd1prRlU5LTJGb21nZVptdWo2XzFOOWVndzNjZVVQQnBYUXVBbVhrbnQ5bEttT0xhVGpTMW9CSWcyYkZvYU5YOGcwc1lNeFhWeTNOVnlLakEtWG5Ddw?oc=5</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T11:00:44+00:00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="n"/>
+      <c r="I177" s="2" t="n"/>
+      <c r="J177" s="2" t="n"/>
+      <c r="K177" s="2" t="n"/>
+      <c r="L177" s="2" t="n"/>
+      <c r="M177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>AI Didn’t Kill SaaS. It Killed the Seat. - Security Boulevard</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Security Boulevard</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxORWctczdDd3NndnhBaWx5aHBRNkRwcTZ4LXdYcXEwWWdGbUdLSjRPOGw0VHJhMF9WcmJRN2V6SGxVdlZGMS13WEZGWDd3a3VSVmNhZGp1NXFLa1J5QUpiYUFoVU96LUd3VGI2V3JrYkdpQmRTZm1OVDJYMTJsUC1kY1NR?oc=5</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T19:44:26+00:00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="n"/>
+      <c r="I178" s="2" t="n"/>
+      <c r="J178" s="2" t="n"/>
+      <c r="K178" s="2" t="n"/>
+      <c r="L178" s="2" t="n"/>
+      <c r="M178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Securing the Open Source AI Ecosystem with Pranshu Raghav - hackernoon.com</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>hackernoon.com</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPeXdubGFPeXVCWHpMVmFPYjFfcS1yQzZITHdlRW5YSEdBcGpRTGdqb3Z4eHNvQWd5eVdPcEV4TU1UdTJOWGVaSy1UcXltMEtYSWw1aEE2RlJmRjlDTEFTUHNUOHhXYnpSS0o5aEVubGM2VmR6LWZkNElKcURHUE9aNEJQZDA2MG8?oc=5</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T20:49:07+00:00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="n"/>
+      <c r="I179" s="2" t="n"/>
+      <c r="J179" s="2" t="n"/>
+      <c r="K179" s="2" t="n"/>
+      <c r="L179" s="2" t="n"/>
+      <c r="M179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N179" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Reflection AI unveils its first open model, Beam. Could it be the America's best chance to compete with China? - Fortune</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZENvRHJUb3JKWEFMQWsySkliYk9MOTF1VUxqdi1kMl81Sm8wWjNXMUpHNUMxTWRoSFl2OWo0d3VWeFNaSFJIUGJLMXNVWmRINlgwWDdwLU04c3VnSmotYlBlYkEzX2FTc1ZSejBManV1UVEwOFRHTm1NNlZTbndjRHNZS2JYUmQyXy1OM0dYZzhOZjJlWVk5N0szejFrUkNaNDRnV2tXQjFzSEozNXZJc01uMA?oc=5</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T19:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="n"/>
+      <c r="I180" s="2" t="n"/>
+      <c r="J180" s="2" t="n"/>
+      <c r="K180" s="2" t="n"/>
+      <c r="L180" s="2" t="n"/>
+      <c r="M180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N180" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Robotics &amp; AI to Address Healthcare Challenges, Says Union Minister - Digital Health News</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Digital Health News</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOaUdMdE12dWpEb2tkbmVpZGVWTVgwT1NSVnRicDRqUTlmOEZKLUJDTEgybWVWam8yMmVXOFNlaUVwQnFZeG1zbVE5anNpdjk2a2hUd2x3cHh0VElDeF9iaWNOZVQ0WEYwdDdsWVBKdGl0cFRqLUNwOHFLNlFVTm1iOWUtVG5pR2R4VzhRZEp5dTJqLUNJcjNhdzM5TDRVbnFoT3FTTTNLemlzMl85ZFFveDl2Zzhpc0tEOTJaY2RKN3Bjc0NkYlB4SE1EblFJbXYzUTBUZmJFYmY1M2JIRWNVS1BwblJ4bzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T10:22:00+00:00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="n"/>
+      <c r="I181" s="2" t="n"/>
+      <c r="J181" s="2" t="n"/>
+      <c r="K181" s="2" t="n"/>
+      <c r="L181" s="2" t="n"/>
+      <c r="M181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N181" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Physical AI moves beyond traditional robotics - TechTarget</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>TechTarget</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOR3RVaXdzR3VMSG02OWhESl9zbTdpWDZhXzdZWHhaTzQ5YjJicGw3UkY1ZXdNakNCdTVoZHc0NzNQS00tLVBUQzFYdHI3dnpTS1JzN2ZqME5vb3l3eW9Ya2JZaEtDYk1WTmNPQzNISUhzZkhVWExQY0tZdVllNDZGYVZ5WHhDY1ZEM2h0MlZnalF3WTFM?oc=5</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T19:24:05+00:00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="n"/>
+      <c r="I182" s="2" t="n"/>
+      <c r="J182" s="2" t="n"/>
+      <c r="K182" s="2" t="n"/>
+      <c r="L182" s="2" t="n"/>
+      <c r="M182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Bonsai Robotics uses AI simulation to train field robots before deployment - Future Farming</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Future Farming</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPLV9PdEZ4Vzd5ZEFxeU84YjRobGlXOVdIV00tVjJJcEI5OURYdTJjeUhKV20wM1NUMHJBOV9jOHZGSm1PWTRJNGxsbndjd0VGb2RSRFlRMUFLM2Y2S1V4ejhkTGhDQ3NscjJoaFhQcl85RWhGNHQ5Nkx0XzI5R01GUHVvYzdBb0FTYUlBZm1ocV9uVVZ1S0ZWTEhNb2Flc3FBc2psOTQ2VDJtZVpiTWl6N19naTh4NWZWVzVPUDdISlBMVU81YmF3YjNxU0k?oc=5</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T10:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="n"/>
+      <c r="I183" s="2" t="n"/>
+      <c r="J183" s="2" t="n"/>
+      <c r="K183" s="2" t="n"/>
+      <c r="L183" s="2" t="n"/>
+      <c r="M183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N183" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7009,7 +10189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7646,6 +10826,90 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini plan changes and free tier restrictions from October 9</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ జెమినీ ఫ్రీ యూజర్లకు షాక్! అక్టోబర్ 9 నుంచి కొత్త లిమిట్స్</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>మీరు రోజూ గూగుల్ జెమినీ ఏఐ వాడుతున్నారా? అయితే అక్టోబర్ 9 నుంచి మీకు ఒక పెద్ద బ్యాడ్ న్యూస్ రాబోతోంది!</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNRWhNU0VwOGNjT0hHemdBRlplQWpRbi1ZcDRkcTlicEo1Nmp4clk3QjRJUF9NdXlLdHJ5RkU5dFU5azBkcFlZT1JPa01oNXZHNll3YlNqYXpoNFRmbHZnSUtGdWNVdFU4M3F4N1RwSmVSZnZNQ01rNE1nVEp5V0FCaFktNy1PT3Bfb1k4SGI1TmFIZDIzdExfR3g1MDJIX194WjFOX01rTFV0dlF0UXFzN214QzlmMGdoY0Q3NUd5VnlRc3JRSlA1dWliZjVFVndqM1k3cXdBelFEOXVHeEo2Zms3WmLSAeQBQVVfeXFMTUVoTVNFcDhjY09IR3pnQUZaZUFqUW4tWXA0ZHE5YnBKNTZqeHJZN0I0SVBfTXV5S3RyeUZFOXRVOWswZHBZWU9ST2tNaDV2RzZZd2JTamF6aDRUZmx2Z0lLRnVjVXRVODNxeDdUcEplUmZ2TUNNazRNZ1RKeVdBQmhZLTctT09wX29ZOEhiNU5hSGQyM3RMX0d4NTAySF9feFoxTl9Na0xVdHZRdFFxczdteEM5ZjBnaGNENzVHeVZ5UXNyUUpQNXVpYmY1RVZ3ajNZN3F3QXpRRDl1R3hKNmZrN1pi?oc=5
+https://news.google.com/rss/articles/CBMixgFBVV95cUxNN21LWXJWR0JkTFpPXzl3OVlQMGlpdndhQTlxalZIczc4NWFtaVR1bDBCSk8wSVRUOVZSNlhGUFQyUG8tbGZ0RlpHWnlwNEJGZFV1NFFmQVNrTDN2SksxQnNzVWt3YUkwMng1QWVCZjJEdWk1eU9DdHAtSjFfMzd0cHNiMkJ1VVM5Rkk5azEzRm1ma1FKVl9NRmxQcmJjSXpmVEVpTmdFNlBvQW52b0tvX2VOWXFQNnpXZC10RW1vazJ3dVF0WXfSAc4BQVVfeXFMUEZtZUNQR2N1VzV3R2k3V2NvaC1vSTJwd0ZXVXk0cHdCeXcyN2FkVE53VUFXZnduNG13M2Y1VGhHRVB4QjNfZ0NRcG0taTIyWUI2RkhJU2tITHU5dW5tcXhVSno5TDRTYnRjVUF5OGdNVGVuNi1HaW96emQ4TnhJeHp0ZHVPX1FZbzBNdEJxVkNUa0xBQVRfMG81eDdfVkhTVVEyV3JzVkRMWFVhbnF0VEl4b2N0SlM3b2owNWd3TjZHNmU0dXl1TlNpeWJVbmc?oc=5
+https://news.google.com/rss/articles/CBMi2AFBVV95cUxQelE4VnEtOTBXcEFELVRHZ1l0ZnZFZFZNS0hQZUd6OWRCMmZ4cE5xVGtzcWVQY2VTa3B2d1M2cWt0YWg3ZHVma2NwR2Eyb250Z2xjNU9pRF9oN01QU2JqRzZtN0RiN29tQlhsYUdsT3YyaEwxRFRkYUFMXzB6aG4zbi03Tk85QlBWdGlMX2JVOVkyWXhaZ1VDaC0waGsyQ1h3ZXBXZHoyQ29HNW5VVDgwd2JLM2NYdFlFZHY1eW9WN0tvQnJCTFU0am5hUVFtRDZibWtQeUkwNljSAd4BQVVfeXFMUHA3TldpeXpEd0xOTTMxOTlydm1CTjFMRGJocW5JeVR4WTk5RXlkX1Z3c1lLR3lmRnNzcXZqMThHajdwNGs4M1ZuMFhqbFVqUHF6RnZ0b3VpX000VUxsLWNxTUdoc1lqY2g0dTRlMTI4WVNFX0ozQ184M1VjWE42ZVB1YW9lclJXeGxwUjFaQmhIM3pxT3puNkdTeWl2RFh4dTNiMnVvZTItZXdjUTk1d2NiY3l1THJ5RVJ5OEV2Z3pfYXNTUTN6bl92WmFIczBTX01OaGNudnBCTmZPdWpn?oc=5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini plan changes and free tier restrictions from October 9</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ జెమినీ ఫ్రీ యూజర్లకు షాక్! అక్టోబర్ 9 నుంచి కొత్త లిమిట్స్</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>మీరు రోజూ గూగుల్ జెమినీ ఏఐ వాడుతున్నారా? అయితే అక్టోబర్ 9 నుంచి మీకు ఒక పెద్ద బ్యాడ్ న్యూస్ రాబోతోంది!</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNRWhNU0VwOGNjT0hHemdBRlplQWpRbi1ZcDRkcTlicEo1Nmp4clk3QjRJUF9NdXlLdHJ5RkU5dFU5azBkcFlZT1JPa01oNXZHNll3YlNqYXpoNFRmbHZnSUtGdWNVdFU4M3F4N1RwSmVSZnZNQ01rNE1nVEp5V0FCaFktNy1PT3Bfb1k4SGI1TmFIZDIzdExfR3g1MDJIX194WjFOX01rTFV0dlF0UXFzN214QzlmMGdoY0Q3NUd5VnlRc3JRSlA1dWliZjVFVndqM1k3cXdBelFEOXVHeEo2Zms3WmLSAeQBQVVfeXFMTUVoTVNFcDhjY09IR3pnQUZaZUFqUW4tWXA0ZHE5YnBKNTZqeHJZN0I0SVBfTXV5S3RyeUZFOXRVOWswZHBZWU9ST2tNaDV2RzZZd2JTamF6aDRUZmx2Z0lLRnVjVXRVODNxeDdUcEplUmZ2TUNNazRNZ1RKeVdBQmhZLTctT09wX29ZOEhiNU5hSGQyM3RMX0d4NTAySF9feFoxTl9Na0xVdHZRdFFxczdteEM5ZjBnaGNENzVHeVZ5UXNyUUpQNXVpYmY1RVZ3ajNZN3F3QXpRRDl1R3hKNmZrN1pi?oc=5
+https://news.google.com/rss/articles/CBMixgFBVV95cUxNN21LWXJWR0JkTFpPXzl3OVlQMGlpdndhQTlxalZIczc4NWFtaVR1bDBCSk8wSVRUOVZSNlhGUFQyUG8tbGZ0RlpHWnlwNEJGZFV1NFFmQVNrTDN2SksxQnNzVWt3YUkwMng1QWVCZjJEdWk1eU9DdHAtSjFfMzd0cHNiMkJ1VVM5Rkk5azEzRm1ma1FKVl9NRmxQcmJjSXpmVEVpTmdFNlBvQW52b0tvX2VOWXFQNnpXZC10RW1vazJ3dVF0WXfSAc4BQVVfeXFMUEZtZUNQR2N1VzV3R2k3V2NvaC1vSTJwd0ZXVXk0cHdCeXcyN2FkVE53VUFXZnduNG13M2Y1VGhHRVB4QjNfZ0NRcG0taTIyWUI2RkhJU2tITHU5dW5tcXhVSno5TDRTYnRjVUF5OGdNVGVuNi1HaW96emQ4TnhJeHp0ZHVPX1FZbzBNdEJxVkNUa0xBQVRfMG81eDdfVkhTVVEyV3JzVkRMWFVhbnF0VEl4b2N0SlM3b2owNWd3TjZHNmU0dXl1TlNpeWJVbmc?oc=5
+https://news.google.com/rss/articles/CBMi2AFBVV95cUxQelE4VnEtOTBXcEFELVRHZ1l0ZnZFZFZNS0hQZUd6OWRCMmZ4cE5xVGtzcWVQY2VTa3B2d1M2cWt0YWg3ZHVma2NwR2Eyb250Z2xjNU9pRF9oN01QU2JqRzZtN0RiN29tQlhsYUdsT3YyaEwxRFRkYUFMXzB6aG4zbi03Tk85QlBWdGlMX2JVOVkyWXhaZ1VDaC0waGsyQ1h3ZXBXZHoyQ29HNW5VVDgwd2JLM2NYdFlFZHY1eW9WN0tvQnJCTFU0am5hUVFtRDZibWtQeUkwNljSAd4BQVVfeXFMUHA3TldpeXpEd0xOTTMxOTlydm1CTjFMRGJocW5JeVR4WTk5RXlkX1Z3c1lLR3lmRnNzcXZqMThHajdwNGs4M1ZuMFhqbFVqUHF6RnZ0b3VpX000VUxsLWNxTUdoc1lqY2g0dTRlMTI4WVNFX0ozQ184M1VjWE42ZVB1YW9lclJXeGxwUjFaQmhIM3pxT3puNkdTeWl2RFh4dTNiMnVvZTItZXdjUTk1d2NiY3l1THJ5RVJ5OEV2Z3pfYXNTUTN6bl92WmFIczBTX01OaGNudnBCTmZPdWpn?oc=5</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7658,7 +10922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8227,6 +11491,80 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ జెమినీ ఫ్రీ యూజర్లకు షాక్! అక్టోబర్ 9 నుంచి కొత్త లిమిట్స్</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>మీరు రోజూ గూగుల్ జెమినీ ఏఐ వాడుతున్నారా? అయితే అక్టోబర్ 9 నుంచి మీకు ఒక పెద్ద బ్యాడ్ న్యూస్ రాబోతోంది! గూగుల్ తన జెమినీ ప్లాన్స్‌లో కీలక మార్పులు చేస్తూ ఫ్రీ యూజర్లపై కొత్త పరిమితులను విధిస్తోంది. ఇప్పటివరకు అందరికీ అందుబాటులో ఉన్న శక్తివంతమైన జెమినీ ఫ్లాష్ మోడల్‌ను ఇకపై ఉచిత వినియోగదారుల నుంచి పూర్తిగా తొలగిస్తున్నారు. దాని స్థానంలో ఫ్రీ యూజర్లకు కేవలం ప్రాథమికమైన ఫ్లాష్-లైట్ మోడల్ మాత్రమే ఇవ్వాలని గూగుల్ నిర్ణయించింది. దీనివల్ల ఉచితంగా వాడేవారికి సమాధానాల వేగం, అలాగే నాణ్యత మునుపటిలా ఉండకపోవచ్చని నిపుణులు చెబుతున్నారు. మరోవైపు నెలకు డబ్బులు కట్టే ఏఐ ప్రో సబ్‌స్క్రైబర్ల కోసం కొత్తగా 'డీప్ థింక్' ఫీచర్‌ను ప్రవేశపెడుతున్నారు. ఈ డీప్ థింక్ ద్వారా సంక్లిష్టమైన సమస్యలు, భారీ డాక్యుమెంట్లు మరియు గణిత విశ్లేషణలు మరింత వేగంగా పరిష్కారమవుతాయి. టెక్ కంపెనీలు ఫ్రీ ఏఐ ఫీచర్లకు క్రమంగా పేవాల్ పెడుతున్నాయి, కాబట్టి మీ పని విధానాన్ని ఇప్పటి నుంచే ప్లాన్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>A modern 9:16 vertical tech video with fast-paced visual storytelling, dynamic camera motion, sleek minimalist motion graphics, glowing typography overlays in Telugu, synced ambient electronic background music, burned-in dual-tone subtitles, seamless whip transitions, authentic UI screencasts, and verified news citation cards.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ జెమినీ ఏఐ యూజర్లకు కీలక అప్‌డేట్! అక్టోబర్ 9 నుంచి ఫ్రీ యూజర్లకు జెమినీ ఫ్లాష్ తొలగించి కేవలం ఫ్లాష్-లైట్ మోడల్‌ను మాత్రమే అందించనున్నారు. చెల్లింపు ఏఐ ప్రో వినియోగదారులకు 'డీప్ థింక్' మోడ్ వస్తోంది. పూర్తి వివరాలు ఈ వీడియోలో తెలుసుకోండి.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>#GoogleGemini #AIUpdate #TeluguTech #ArtificialIntelligence #TechNewsTelugu</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ జెమినీ ఫ్రీ యూజర్లకు షాక్! అక్టోబర్ 9 నుంచి కొత్త లిమిట్స్</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>మీరు రోజూ గూగుల్ జెమినీ ఏఐ వాడుతున్నారా? అయితే అక్టోబర్ 9 నుంచి మీకు ఒక పెద్ద బ్యాడ్ న్యూస్ రాబోతోంది! గూగుల్ తన జెమినీ ప్లాన్స్‌లో కీలక మార్పులు చేస్తూ ఫ్రీ యూజర్లపై కొత్త పరిమితులను విధిస్తోంది. ఇప్పటివరకు అందరికీ అందుబాటులో ఉన్న శక్తివంతమైన జెమినీ ఫ్లాష్ మోడల్‌ను ఇకపై ఉచిత వినియోగదారుల నుంచి పూర్తిగా తొలగిస్తున్నారు. దాని స్థానంలో ఫ్రీ యూజర్లకు కేవలం ప్రాథమికమైన ఫ్లాష్-లైట్ మోడల్ మాత్రమే ఇవ్వాలని గూగుల్ నిర్ణయించింది. దీనివల్ల ఉచితంగా వాడేవారికి సమాధానాల వేగం, అలాగే నాణ్యత మునుపటిలా ఉండకపోవచ్చని నిపుణులు చెబుతున్నారు. మరోవైపు నెలకు డబ్బులు కట్టే ఏఐ ప్రో సబ్‌స్క్రైబర్ల కోసం కొత్తగా 'డీప్ థింక్' ఫీచర్‌ను ప్రవేశపెడుతున్నారు. ఈ డీప్ థింక్ ద్వారా సంక్లిష్టమైన సమస్యలు, భారీ డాక్యుమెంట్లు మరియు గణిత విశ్లేషణలు మరింత వేగంగా పరిష్కారమవుతాయి. టెక్ కంపెనీలు ఫ్రీ ఏఐ ఫీచర్లకు క్రమంగా పేవాల్ పెడుతున్నాయి, కాబట్టి మీ పని విధానాన్ని ఇప్పటి నుంచే ప్లాన్ చేసుకోండి!</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>A modern 9:16 vertical tech video with fast-paced visual storytelling, dynamic camera motion, sleek minimalist motion graphics, glowing typography overlays in Telugu, synced ambient electronic background music, burned-in dual-tone subtitles, seamless whip transitions, authentic UI screencasts, and verified news citation cards.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ జెమినీ ఏఐ యూజర్లకు కీలక అప్‌డేట్! అక్టోబర్ 9 నుంచి ఫ్రీ యూజర్లకు జెమినీ ఫ్లాష్ తొలగించి కేవలం ఫ్లాష్-లైట్ మోడల్‌ను మాత్రమే అందించనున్నారు. చెల్లింపు ఏఐ ప్రో వినియోగదారులకు 'డీప్ థింక్' మోడ్ వస్తోంది. పూర్తి వివరాలు ఈ వీడియోలో తెలుసుకోండి.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>#GoogleGemini #AIUpdate #TeluguTech #ArtificialIntelligence #TechNewsTelugu</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8239,7 +11577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8465,6 +11803,33 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ జెమినీ ఫ్రీ యూజర్లకు షాక్! అక్టోబర్ 9 నుంచి కొత్త లిమిట్స్</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>cdyMoOUEUBg</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cdyMoOUEUBg</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>uploaded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O183"/>
+  <dimension ref="A1:O251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10177,6 +10177,3610 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Trump Labels Those Calling AI ‘Artificial Intelligence’ Instead Of ‘Super Intelligence’ As ‘The Enemy’ - News18</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>News18</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNbmJPVzZxSUtTc1FOamhOMVNfRllUSUZ2d2hKZ0YzcEFCdVJBMVVCTFBjR2VMYi1DOF8yOHBPRWxPTHJVbUR0RUd6N0lSLXZIbWYtWTdhOGVPdXhWUEhtLXVTR1NsT3FVTjFzMktxcU12UWc3NFlJRjdKekRIMGZFcWwxRkVDcXdwTm5aZFh3NGNtcXNFV2N0cGNaaGFBcjN1aWRsSmt3NW9PVDF1YVlVTXRZVm1jN2ZfRkphNHJVdXFUb0VMTjlOcTlWb1RUYW9wVkluRkpLOFBqODgw0gHiAUFVX3lxTE4xeWZveTk1ZlNhZEVZblU2TENBdWxfdWpDblQ3bVpvOFJmQ1pXLTUtczdaTzZEQVJRc0o2SmR0WkZBZ3ZsalloclNmS09wbzdUOUhpWjNxTjNwYjNJN010LXVKM1hSQnk0ZHZRdXhWMl9Oam9mZEZybVFjTGRaMEdWTERaUDRwVEtJMk1Qa1VsM0RrUlhxUGpXSDJqSzdTX0Zad3hVZHRDSlBPNWI4OGZjOUxMUy05LUxZZlV2UTN5MzBRZk42VTZBM0JWaFh2WXptSXlPY3V6VmpIMW5feVJlX1E?oc=5</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T17:36:12+00:00</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="n"/>
+      <c r="I184" s="2" t="n"/>
+      <c r="J184" s="2" t="n"/>
+      <c r="K184" s="2" t="n"/>
+      <c r="L184" s="2" t="n"/>
+      <c r="M184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>AI Is Changing Lives of Ordinary People, Says Vaishnaw at Launch of ‘World Development Report 2026: The Promise of Artificial Intelligence’ - DD India</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>DD India</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQblc0cU0xdFNLQkJrVXVHdnhqR3FxWS1ESm16TWJfU3FQV2RGTEZURElpX09HNlJZNWl2T3lEOHBMMGxxa0hmVld1cXBhS0tNNU0tb0pKd3F6RS1vRkpvU3FKdjNlXzROTlY0OEFZN2hnRU8tWFhBT0p2Wl80TTZleWdtZVl6LUpfeUEzN2Rmeno2SDdPSVFlX0lXY3BrVzBRZUJyWjFlendXelZCTUtiRnNjc04tZlN0V3k5TWpERHRPQ05CNmg2SmxzRDlSVUFjXzlPLXFBak1rSE8zTVFNZ2JkdnhIZk1IYURiWGtEWEk2NGQ5Xzg1VFJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T14:15:38+00:00</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="n"/>
+      <c r="I185" s="2" t="n"/>
+      <c r="J185" s="2" t="n"/>
+      <c r="K185" s="2" t="n"/>
+      <c r="L185" s="2" t="n"/>
+      <c r="M185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N185" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Trump: People Who Still Say ‘AI’ Are ‘The Enemy’ - Forbes</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Forbes</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdjVXN0QzNVNydnBVbDV1NnBTU08tUmNLNGtlb2tRZXZJUkdkcmg5ZDBYc0d0X053R2hHSkY0cW83SnJQc0ktZU1FVlFESlZkanR6cTdTUVZkUWNia2ZyZXBjVFdsTVpGTTJsWTZ1T0dfYnV4ZWNDVGRtbVNTdy14M2x3Q2c1bjdrVHJ2MDlFVTF6cjd2bllTY19BVTJYT0loQTRxcGU3Y2UzZk04azRQOUp5Rk9TQXk4eXptNW5kNA?oc=5</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T17:16:40+00:00</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="n"/>
+      <c r="I186" s="2" t="n"/>
+      <c r="J186" s="2" t="n"/>
+      <c r="K186" s="2" t="n"/>
+      <c r="L186" s="2" t="n"/>
+      <c r="M186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>AI Regulation Consultation Paper Next Month, Says Union Minister Ashwini Vaishnaw - NDTV</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOaUJTU0ItdnM0ZW9Uejd6UzhwTjZsbEI5TmVUTWp6RmM3ZDIwWXh1Q0VHSUo1bkRISFZSNTA4WVlRY3dlNDZEMHdmbWM4S0tSdWJDd2ZaSGJpMGVDUUVuMzMwazJ0RDVuVVpOeER4a3hudHpUak5zYUdORGlSbEItMzlfcHlDYXNocTdmSDRUZlIzTjJ6bmtWWlg0NVJYal9EeWZkcW5wNWJ1Qm5FaVVpS1Z2aU1SRjRweTRmZXh4V1BpSDdrdnJYU1dFRFViS1XSAdcBQVVfeXFMTUtodGk1bFBROXB3Z3RFS051SGFPTDRNTC05U1RrektqQzgxbmtEWXBWaHF6dlYwQUFNMW01NWVfSU5KZ3pjQ2lPalBzc3U3T2l4bmtyTUtldWRpSmFPU2MtS3VvbkF5TDNYcXphajFDS0dmcXBVZGQ1SVF3aVcxYk41dnRPdm50THVqZ0dtNGp2Q2kzb3AwV1pUaW9MdTBRcFRnQ2t0WlY3YmhYQ29lejI0Z3MyMlk1ci1Dc3VXOFdNdGJBUWNXVTk3aGxNNGRDV2JFQnFRbkE?oc=5</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T13:42:46+00:00</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="n"/>
+      <c r="I187" s="2" t="n"/>
+      <c r="J187" s="2" t="n"/>
+      <c r="K187" s="2" t="n"/>
+      <c r="L187" s="2" t="n"/>
+      <c r="M187" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N187" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>AI use lifts participation in WorldQuant contest - Reuters</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQaU9BU3JlallQY1BwajVXbXR0cVNPNEJsNW1wZDNTTmo5R2JjQ0hrTTBlZWFPWFJSd3dWVTYwaldVRWxneTNCUHZESWMwVWxkQS1YbXNackdiWUNIZlpxOXNGQjJ2Q3VQVmNNa3NtWnUtWVU3LTI5bEZpQ2JzdHFrcjB3NVE1LWVtMkF5ZmRmWXhNRTVI?oc=5</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T08:22:34+00:00</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="n"/>
+      <c r="I188" s="2" t="n"/>
+      <c r="J188" s="2" t="n"/>
+      <c r="K188" s="2" t="n"/>
+      <c r="L188" s="2" t="n"/>
+      <c r="M188" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N188" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Govt to release draft AI regulation paper within 30 days: Ashwini Vaishnaw - Business Standard</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQQ21XT1loVExOaURTNm1fRDlLQWtRRDFCX1dzZWxnRi1OMjd3SUVvRVVsenRfcUJBcC1uR3llMXFHODNQZFc0LThOTG8tMHFvTnJMdHpCS1hwZmVBZTdJQTJNWTZaNzk3cHNXMFlRWmJLSFlPUndUNkRPYkRyX3B1bGtvWWVtSGJkTVNlTFVIU0xvLTJwOGZ2MWVnTmFEaDF5ZnBHbzc4WHE3dTAtbW84Z2VYYmgweEhFR1JQS0ZOdHJONDhMZnB1Q3pGZDRaVlBQd1lHSVhHM2FQZDlpLVdvR0Fmd0szeE95M2s5U0ZpaUNuQnV60gH6AUFVX3lxTE5ISEhUcWRDM0FLRWt2NkRZY1Uxb3hvb3RVanZwdG5IT1Z2R2pWRHRsYnE1T0w1eUNQaUYzYjdJcFRnenVPNUJjN01zR3VObnk0TGNvcDNtUURHTmZ3eGxLRDFsTDJaaDIxd3NWaXJNeEJIZl95M0k3Tmg1UkNhd2U3WEk0TnhxbWZGbVhxTXN1RmY2T0ZabTlpdms2NVJBSG1ySFhZLUFRUkxPaEhMLXk1QnhPOHVXNFFQZUFjbFduTVhRYl9XcFNJdXhmY2l5NnJYMDlBX0prdFc2clBRQlZCZXdtR0ZobHh5NkVrSU1ISUFmaXllQXNhWFE?oc=5</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T13:08:49+00:00</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="n"/>
+      <c r="I189" s="2" t="n"/>
+      <c r="J189" s="2" t="n"/>
+      <c r="K189" s="2" t="n"/>
+      <c r="L189" s="2" t="n"/>
+      <c r="M189" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N189" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI claims to have solved hundreds of long-standing maths problems - The Economist</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>The Economist</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPSkxpbGFjd2trMGlIX2JWWGl2N2cteXE3VkxqYy1GZy1CLWZZcFZtT3pqRWNmMUlUVU9wTW5iRTVKX0c0WnhwOXg2R2NNc2Z0akZ4MGp3NnpWeTNiVUdYaUtFZ1h5S2lkVi1mVVhRZ0pnaGw0OFdmc2lfbFVSbnFpYTg3MEdsYjlleFdKaTFOY1VrUTB5cmVPNHV3OUFIaXlQdFZhWUJ2V0xxSlR3X3N2RlF6NW9EOFdiVFNERmNrWlA3RW9UMlJ0bA?oc=5</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:52:54+00:00</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="n"/>
+      <c r="I190" s="2" t="n"/>
+      <c r="J190" s="2" t="n"/>
+      <c r="K190" s="2" t="n"/>
+      <c r="L190" s="2" t="n"/>
+      <c r="M190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Exclusive | Fired OpenAI Researchers Ask Company to Preserve Visibility Into AI Reasoning - WSJ</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPMzB3QXE3Ylk2N19Vc0NZQ2dTWjRManRKN1B2T01mTl8tYmdnY21tekh3VjJJV0o5ak9vNFY1OG9LTjM3TkhkdlV3bTlCYnRVdjdjeVMtNlRNOGNQX3RKdkdiWEhOZU5GN18zNzQwM3R6aF9wNHRuLVRKMlExNE12ZmtiNnZkWk9GeWZ2bzAtbWdHRVp1M0RGSHVHUzZJMnVpYzVDMnZldjhPbHBSOXphXzV1V1c?oc=5</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T23:46:00+00:00</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="n"/>
+      <c r="I191" s="2" t="n"/>
+      <c r="J191" s="2" t="n"/>
+      <c r="K191" s="2" t="n"/>
+      <c r="L191" s="2" t="n"/>
+      <c r="M191" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Fired OpenAI workers tell company about concern over losing AI systems' chain of thought - Fox News</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Fox News</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5CMlZ4TV8tUDN5UE1pYU8tYlB4aUFST2lFZ090T3hoMzVSa0thTTBTVFFCMTNhTV9Ha21fandDcm9tS3c2NmR5RW5meHloeXVYMnc2Ty1nY1UyNWxiVlNvVXB0a3FjTU5NWFdkTzNod1hEdTkxVmx5MQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T17:28:42+00:00</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="n"/>
+      <c r="I192" s="2" t="n"/>
+      <c r="J192" s="2" t="n"/>
+      <c r="K192" s="2" t="n"/>
+      <c r="L192" s="2" t="n"/>
+      <c r="M192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Fired OpenAI researchers send letter to company's board; warn: You may not be able to control yourAI Agen - The Times of India</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAJBVV95cUxObzloYVU1eFdDbGxLOGZkYUdMSGJVZkZRNnB6VU43STZTTzM0Y0RtcGRtbXZCemljemY3MHJfeGRRUll4RGR6X0U4SDAwOXJXeWx6T21NQUxpMXR0YUN6SFJrZ3NCam9NTHA4NjEwLXcwdFJXY0t3Nk1IczUtcW1PUHY2MW40WFFzNTItWFBiME9MN2NaSy1KQ3ZwUS0zeXdURWRfWlFneERsZzM1ODQ0T3U2WkwxSjJoTnlreXBYTEJIMHZUc0FINzFDcFpYckppd21xZG5ZaUFzN1lnRHNaMEhUMnp6VzQ3U0xVeVExd2V4b0NmaklsWURILUVsR21XaEM0WjFjUThZVk5HbzE3N29uMEFlUV9CMmRsUVhWVmRfX2UzUXpOeU9BZTfSAbICQVVfeXFMTTJsR1hHa1M4WFlreG5tRkxMaVlsdFNiaVluOXpsMkdrb0xqa2ttbmhCd0tNakl1Q2Ixc3lXZUdUZ25XOHpuZHp0OXBVcmJQZ0daaHh2aWMwdmludU1VTjB3SElHOXBHUDkteUViNFViU1V6LXlGSXRLYlc2aFg2VGF0MEdKeUhvTUhKVzd3Vlh6cGdBRndlM3JXSmVIUnpreElCMlNSdnlIQmViQjhBdEdUUDc2SkVLeTUzb2hpUDBDQWNWQWg5OERqSUlYdmdMX2puelhvbFVVQ3pLd09qV2dxZENZLVZOOGhkVENIMlNFcmh0Q0pBdlZXaFo4RUJYN2l2NVlmZW1ILTNMVlVqcklJTTY5OU9rYVJqdzV4c08wSEJ1QnBjU21iNE1WMmhsNkxB?oc=5</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T07:47:00+00:00</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="n"/>
+      <c r="I193" s="2" t="n"/>
+      <c r="J193" s="2" t="n"/>
+      <c r="K193" s="2" t="n"/>
+      <c r="L193" s="2" t="n"/>
+      <c r="M193" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N193" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia, Oracle, CoreWeave and other AI stocks sink on OpenAI revenue report - CNBC</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPOG8tazVEa2hVcWdlYU1pZk53QzNMLU1lVWk4c2U0NFRvMk5IMnJYMWdTZERsSHhkYWo1dkRlczFWcGdwRHJfbFJzQ09kUEo1elE4YVRQZWp0Z3lVbU1MUjJIVV9lbFFHbUxPUlJhUER6NzgwdjVFTHM4UVhGZ3pNd3pR0gGHAUFVX3lxTE9nLWxxNlZwaWJicm9JSVBTT3lHeElLRDJ2QklRT2FkelA0eXZSNDlyRWh6dWlhNFloNzZfOUtid3dmcEJsTGNNcTE5VnhEbURXWWo0UGktcmhXNV8tS1lHYndTellPVm00RmFpeFVLTnBqNENtUUtBdHV2NVdPU0Jnb1A1NnpzSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:14:54+00:00</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="n"/>
+      <c r="I194" s="2" t="n"/>
+      <c r="J194" s="2" t="n"/>
+      <c r="K194" s="2" t="n"/>
+      <c r="L194" s="2" t="n"/>
+      <c r="M194" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N194" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI’s revenue is reportedly $20 billion less than previously projected - TechCrunch</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPWGltbEsxdjUway1nMDFQUUNBZUtSRmg1QmZ6Y04tVlM2aXJLV0NZQUR2cm1KZjQ5VHlQdTBPU0VQNVJDaVhNclVhYjk0Q1BJR0xneDYwdXF4djQtdF9vSDJYV0swbUoyWDNvQ2Vsc0ZwXzdvbG9UUlh6SEotWGs1a2NuRGFyYVhfR2ZMbGdndUMtZ0V5VWkzbVJ6SzZBMUJIU21vRk94a1Q0dw?oc=5</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:19:42+00:00</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="n"/>
+      <c r="I195" s="2" t="n"/>
+      <c r="J195" s="2" t="n"/>
+      <c r="K195" s="2" t="n"/>
+      <c r="L195" s="2" t="n"/>
+      <c r="M195" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N195" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>US Stock Futures Slip on Mounting Energy Shock, AI Bubble Fears - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWW5IWVNISFpjY2ZOaTVhcVhiVUV1MWpUaTVkeDNoUjVGYldHbU1ZdFdBLXJMOE1yaENEU0JScTdPQjRmSmlDQUhycnFfLUo2VlF3QTBYRHY0Uk1HUmJHVlkwQjlVc1l4TGo0OTY3N0hzMGdMQ2wxbVVmeFY1MGJ5dXBoRmhrZkR4ajhFdHpmd1J5MDFRamVwQ0diRHVLWS1jdTNfa0NPdnJMb0o4WnU1LWk1QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:08:23+00:00</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="n"/>
+      <c r="I196" s="2" t="n"/>
+      <c r="J196" s="2" t="n"/>
+      <c r="K196" s="2" t="n"/>
+      <c r="L196" s="2" t="n"/>
+      <c r="M196" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Wants ChatGPT to Stop Looking Like a Chatbot - Gizmodo</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Gizmodo</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNUlZxMlZVS2I5Qjlycllwek5rUUtLVzBsaVZaNnV3MVFtc25GMTR5SGVBTU9fUXhIcEtMbWxRbUJKWTJSWFJBZkhPNmtma1JQQjRkTm5pdGpKU0hQSzA1VU5SMkpmazExTnUyMEc5MXB0MFpma2dUZmdlTjdJNG41N0JaYTNMaHNsZUE?oc=5</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T21:15:33+00:00</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="n"/>
+      <c r="I197" s="2" t="n"/>
+      <c r="J197" s="2" t="n"/>
+      <c r="K197" s="2" t="n"/>
+      <c r="L197" s="2" t="n"/>
+      <c r="M197" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N197" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI updates ChatGPT with interactive graphics - Mashable</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Mashable</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPeWZkNVpZQkJLSWktd2Y5d2FpRS1oRGJMWjF4czY5M0JSRDlSc054cnhVSXFEM0ZfaXU2azk5cEw3Qi1NaW1xbktWcVVneUpxckdHbjVLcTduR0FJTS1naEJaYWt6YW9YMVM4TGpsZ3F0N2wzbVVJNE1mNUNWV2RQOUpyV2RDeUw4ekRv?oc=5</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T17:33:49+00:00</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="n"/>
+      <c r="I198" s="2" t="n"/>
+      <c r="J198" s="2" t="n"/>
+      <c r="K198" s="2" t="n"/>
+      <c r="L198" s="2" t="n"/>
+      <c r="M198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>ChatGPT is getting a lot more visual, with the launch of a new interface - TechCrunch</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOeEFVMy1BRFZyWXM2UFZVeVFyUy1TdTluV0tYRkkwdnlDVFNyZW9jZVhMQVN3Qng5UXk5bmtCSXRaOGcySFNveWtudG11eXZfNGhJSFZmallXN3I2d052WXZrT0xuRF9yR0lvYjBycmV0NVRka2FtMG84SXp5QWo0WlFsN0QyTlN4bHFpRWZGSVJreWJsTmtfV3lQTkNTVTFpZDJ6WlRRN01jUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:00:19+00:00</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="n"/>
+      <c r="I199" s="2" t="n"/>
+      <c r="J199" s="2" t="n"/>
+      <c r="K199" s="2" t="n"/>
+      <c r="L199" s="2" t="n"/>
+      <c r="M199" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI says teen ChatGPT use limited but research finds it an 'unacceptable risk' - BBC</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>BBC</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5VQjdvVUZMXzVVUHE0TDExcHh2ejJWYnJFazh4QTVYSjFfQkcwU21KVjJvRUs4VktZbnpkNzVhSzNhMzZteHp2QnhxTDBXbHB2TWNNYVFocVhFRWM?oc=5</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T20:34:17+00:00</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="n"/>
+      <c r="I200" s="2" t="n"/>
+      <c r="J200" s="2" t="n"/>
+      <c r="K200" s="2" t="n"/>
+      <c r="L200" s="2" t="n"/>
+      <c r="M200" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N200" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Inside OpenAI’s playbook for marketing Codex as the product rapidly evolves - Ad Age</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Ad Age</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNOEJLMm1pYk42NE5EeWZ1bXFLLUpDZFBDYzF4ZEpUTE5pa3lrUjdocE5kLTgwZVdqMjJMRGktZ2RxaXhJZjBtczZJLWd1UVplUkZ1aENnMHY2RTctM1pQSkhOTWNlbGt6c2x4bUFYRmJwbVVCRG5mU25nRm91czRoN09XangzX0U2?oc=5</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T09:02:00+00:00</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="n"/>
+      <c r="I201" s="2" t="n"/>
+      <c r="J201" s="2" t="n"/>
+      <c r="K201" s="2" t="n"/>
+      <c r="L201" s="2" t="n"/>
+      <c r="M201" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Google Cloud introduces Gemini agent for work as AI race heats up - Reuters</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSlVSeTZYa0pSOFppNk9GdFF0Y0VZa19lYnRKTjRXb0FpZUhaTlBEUmRLUW04N3E1azhGalpULTNwN2Y0SnhFWGhOTktSdTVMMTJDc2VRX013NGNuSzJYRGxiWVJyU2dzS0lGdGN4YXlxQzR3TWl0eVQwbjFKWW5JVG1kQXdJYVVwd2J2OTZ5NDZYT0JQM09Ycmt2amRmekhNWTBfR0pR?oc=5</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T15:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="n"/>
+      <c r="I202" s="2" t="n"/>
+      <c r="J202" s="2" t="n"/>
+      <c r="K202" s="2" t="n"/>
+      <c r="L202" s="2" t="n"/>
+      <c r="M202" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N202" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Google brings agentic AI to Gemini, starting with businesses - TechCrunch</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNVmlZXzdMc1F5aTdGUFlIaUVtZmlZSWNyejQ4ejY3R1h2QUI0UU56QVpXUXB6a25ja3I5OHlDSm5TamVTbk5XZHJwdjFoSHpKa3VheURjQWgtQUtEalJCek90M0JjSjcycWJVSXUyc2wwS2ViMXE1OVN5bFJFUmhiY253OU5DNHMxbmJRZW5IWmtGWHVRdXZ1NDFR?oc=5</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="n"/>
+      <c r="I203" s="2" t="n"/>
+      <c r="J203" s="2" t="n"/>
+      <c r="K203" s="2" t="n"/>
+      <c r="L203" s="2" t="n"/>
+      <c r="M203" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N203" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>The RealReal Expands Ask TRR AI Shopping Agent With Google Cloud's Gemini Enterprise - PR Newswire</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOeEM0dk1Qcml2OGtENkdLeklxb1pDb3I2UmJvWHdHZ3hmQU5OeXV6Wl9BdlluZjR5RmRBelVjNHFpc0VNejZZQ2VZOFZWSF9VWVJKZnFBaHNuRTdicmJ5OEpkblNPbHBoaXpSV0dhT0FSeW5lRkNCUUo5TW5DQXdlY0J1RFh1ZjdKQllPdzdDYmFyOWl6ZDVmaE85SGFmdzc3N3BXNDVfOFhRYjhyWUxyNnRPRkVnVmFUQzduRUMxbFRsdUp6X1lLR0dSWlM1YjNmY2hXVGtn?oc=5</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T11:57:00+00:00</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="n"/>
+      <c r="I204" s="2" t="n"/>
+      <c r="J204" s="2" t="n"/>
+      <c r="K204" s="2" t="n"/>
+      <c r="L204" s="2" t="n"/>
+      <c r="M204" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N204" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Bringing Gemini in Chrome with auto browse to India - blog.google</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>blog.google</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPYjNxamFjS2lXQzdRcjZQN0VsMjctNS1RV1BlNjRsTFZabUM1VGlGZEJFenhvMzBNMU5meFFLR004Qm9saGxJSDhrVXllb3hZMzRtdVdKTGJsa3ktdjZlVFRiYVg2eGJscXF1ZkhmRllycGtDYS1qSG9uS3dqX0ZjRmNkUTEzYlZsWDFLQmx0V0xSaU5XbXRN?oc=5</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T08:41:59+00:00</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="n"/>
+      <c r="I205" s="2" t="n"/>
+      <c r="J205" s="2" t="n"/>
+      <c r="K205" s="2" t="n"/>
+      <c r="L205" s="2" t="n"/>
+      <c r="M205" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N205" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Google brings Gemini in Chrome to Android in India, adds auto browse - Indian Television Dot Com</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Indian Television Dot Com</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNU2M2cC1hbDBNb2RMc3VGRDBPUDlGdllEWmUxOUhQXy16ci1pSklJVmRUTEdXTjRPUldMUTV3Q2gxNEFQWXZaWHZsSWt0NzlaSkYxZHFHak9ibnlKa2l6cEdvSHRqcUczYWgtejI1TjRUMVkwRFRkS2NDRERQM0UwRnNzV2VwdXBVdjB3aVVJR25CZFZYV2tkWlJoaGV3aS1YNXZj?oc=5</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T02:52:05+00:00</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="n"/>
+      <c r="I206" s="2" t="n"/>
+      <c r="J206" s="2" t="n"/>
+      <c r="K206" s="2" t="n"/>
+      <c r="L206" s="2" t="n"/>
+      <c r="M206" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N206" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Alphabet shares rise as Google pushes Gemini deeper into enterprise AI - Investing.com</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQeFhKS25DXzZlZXpGNUQ0MzNkWjZQaFVOLXVmOTRNdGphZ2RpMHFXTi1kU3JWUFk2N0l6b2ExMGU2UmpSSExXVXk4bDdfckszLXhqbGpXTV9yMktJUzNWZjc5UjZkbFNRdWEwc0F1a2J1MnFJS2dEMXd6b0FZYnRBc251eVJBUUp1WHA1cUdSV2lHdTJqTy1mUGVlS0pQS08zOF9mLXBQcWh0Nkh4NEJjYTR3TjZXLTdYeTdycS03WVk1U0NZOVE?oc=5</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:47:12+00:00</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="n"/>
+      <c r="I207" s="2" t="n"/>
+      <c r="J207" s="2" t="n"/>
+      <c r="K207" s="2" t="n"/>
+      <c r="L207" s="2" t="n"/>
+      <c r="M207" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N207" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>ChatGPT Plus vs. Google AI Pro: Same $20 price, very different perks - ZDNET</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>ZDNET</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBOUzVUdEtPV2VZQWdOQkhxZVlXdHR1bzZQclFPbENWMGRsVGpUSTVWeTd0eXpaZTRpUDZLM0xUT3I5Z0pLcmFsWVdoUXVBQmRDd0NBQ3NHanlqU3FUc2tzM3phTWpySzJXNGhCb2dNUFk?oc=5</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T12:21:06+00:00</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="n"/>
+      <c r="I208" s="2" t="n"/>
+      <c r="J208" s="2" t="n"/>
+      <c r="K208" s="2" t="n"/>
+      <c r="L208" s="2" t="n"/>
+      <c r="M208" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N208" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>I found a Gemini alternative that runs completely offline on my phone - Android Police</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Android Police</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQZWFvWU0tYV9idktLMi1paWZWaWdyMWlKVFoyZkwxMVhfa2IxNFJkeFRyVDhSemFpeE5qT2NsWG9PcmZhVmd3VE5yRVRPdDViWjRFZHNjNFI3d1RqQW5Yc3pXZFRpWGJvbVdNZ2Q1ZWk0czNzLUFMd1BuT0hQTVlTNG02ZzNtOXE0LWxfSHE5T1djODJv?oc=5</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T10:00:10+00:00</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="n"/>
+      <c r="I209" s="2" t="n"/>
+      <c r="J209" s="2" t="n"/>
+      <c r="K209" s="2" t="n"/>
+      <c r="L209" s="2" t="n"/>
+      <c r="M209" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N209" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft is about to let Copilot loose on your file system - The Register</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>The Register</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNX3lvMHlPRkg2RnlLanF3azBtVUY2cW1lMXBiMVhwZkl3bWtxTW85LVY0cnJob0IyeWU5NFFpUGNZN0ExNVRlMmU5TXFyS0tqMHg0a3VWYkdCaGdTR1FqX29ZVkdCeTVUeXN4cE1mUUZqSmxOc25VZ0FiaWNybHVRTDR0SnRRTHBzbnFBS0RhRnprVUVLMUNNcXBNOWtVTzd2dFI4UlZJeFRVTkhseVpfZTZLV3FUQUVILWNHZg?oc=5</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T21:54:35+00:00</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="n"/>
+      <c r="I210" s="2" t="n"/>
+      <c r="J210" s="2" t="n"/>
+      <c r="K210" s="2" t="n"/>
+      <c r="L210" s="2" t="n"/>
+      <c r="M210" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N210" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft is giving Copilot more control over Windows and your files - The Verge</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>The Verge</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOdnQyTlFYNlhLaG4yVHFyS01KT19zcVlTVVJDUDN5M3N1V3YwVEI1N1NkWWJUN1l2d21UQjlMWERIVEE4cHMtTUlpWkxrWC15ajdXUE5DN05Cd2tzM0I1THoxbzBhWTBGX2hISzlGM1FsMUNGTUF1dDF0cWhXMkF6YURtZDk4QXlMams0M0dndEtkMlBJNHhfQU5DX1REMjZVY0tB?oc=5</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T19:28:42+00:00</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="n"/>
+      <c r="I211" s="2" t="n"/>
+      <c r="J211" s="2" t="n"/>
+      <c r="K211" s="2" t="n"/>
+      <c r="L211" s="2" t="n"/>
+      <c r="M211" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N211" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Bringing CRM into the flow of work and agents into business process for sales and service teams - Microsoft</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQVVBJbVhlSWRyRUF2ZHZWM3NIcno3X01BcGlZQ1hTeld4M2NuYkN3dVJoNVF2M1piOEMyTUFlUEZnbGdPZWpnNFVDb3ZiS0kzbk52UDN4d2VnN2Rhb2hONmxzS3lUNi1hWkFlUkQ3RXg5cU5Hek44ZlhMSDVHcVVTVDZVcC1xM01PaDZNbUJKY2tvWk5IR0stZWQ3ZW94SnFyMWlEcXB5ZU5Zb3ZuT3dOeHZVa1BjWThXMDdDVHFpVkZkcHFvN0k4UEoxTkFhQVZMeFhtVVhoOTd6bXZCdjRzRU9rUU91RGs?oc=5</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T15:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="n"/>
+      <c r="I212" s="2" t="n"/>
+      <c r="J212" s="2" t="n"/>
+      <c r="K212" s="2" t="n"/>
+      <c r="L212" s="2" t="n"/>
+      <c r="M212" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N212" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Building Windows for hybrid intelligence - Windows Blog</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Windows Blog</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMlhoazVROUNXSmdpZjQxdjFINklLazg4a3BlYm5xcmM5b2JYQ2Vtb3ROeGp3ZEF3Ym9YWmx2b2hOSUh0MHFxLXh5bVgyVFhnZlMxaV9hOG9VQnlpdkJUUWpTOHI5UTQ1bFFIdDE4WU9oWFFYVDdnQ1VEMmxJcnhnaGYwTHlIajhDallaX2RnZUptc2pFSUY5NDhsclU?oc=5</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:30:54+00:00</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="n"/>
+      <c r="I213" s="2" t="n"/>
+      <c r="J213" s="2" t="n"/>
+      <c r="K213" s="2" t="n"/>
+      <c r="L213" s="2" t="n"/>
+      <c r="M213" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft releases new Nvidia-chip AI PCs with revamped Windows 11 - TechCrunch</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQNEN2SzdRLWZYSFVmU1RTUTYwTFZqRE85T1d1TW9QcFRaalJSRHlOVWhlZkJfU3BrSklSWXU0LVlOTU0ybUVuN1lOZGQ0RDNlMGU0dWJwQy0tOXVLVlpnSkwxeWVZSlBodXR0WFk5UktOU0s3TXAtUlZ0NC1yNnFxeHRJMnZ3ajlOM2I2ZU04UFNtd2NncXZRVnExWFNNejdEN05B?oc=5</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T20:22:37+00:00</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="n"/>
+      <c r="I214" s="2" t="n"/>
+      <c r="J214" s="2" t="n"/>
+      <c r="K214" s="2" t="n"/>
+      <c r="L214" s="2" t="n"/>
+      <c r="M214" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N214" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft to sell $2,599 Surface Laptop Ultra containing Nvidia AI chip - CNBC</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPb3RwVEx5UDFWcFpvRFBFR2hFR3pUUjRuOVE2MUNQVElscTdfNlZZZzNOQzZIRndNcUNKZzFCOVVRbXh2MklhT1NfaHlTTXdIS3Rma29DU3ZRMWtHQWlGdExBYm9oR1M3Wk1kU09LYWNNVDNTNFFBazhNWnQ3X0NOT0FhNXRWTVlHdDloek9GX1dvSFRucjB4U3kxTEpPTkhMNHfSAacBQVVfeXFMUGtjTngzVGppRjdrNnB2OElDaXhfWXRRWnRKTFFXZm04Rkx6U28tZ1loNjJMYms1VnRLZzY2d2hubmVLdGU0WWtlaHBCNGlfcXQ0VzNJVFhFS0NRMzdJdXJwc2Y3Z1RHMlNpLXJPTUEyTTFRVUt1UWJfc3dtdXFyaGpSMlY4bnpLSWdXLTBRaERvN1BPamJhdUd5c1ZpRlFXS21fSEZYZTg?oc=5</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:30:52+00:00</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="n"/>
+      <c r="I215" s="2" t="n"/>
+      <c r="J215" s="2" t="n"/>
+      <c r="K215" s="2" t="n"/>
+      <c r="L215" s="2" t="n"/>
+      <c r="M215" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft and Nvidia unveil Surface Ultra and RTX Spark with new AI features - Firstpost</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Firstpost</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQMXNJdzhod2dDU2lONnc5Wlp4X1ZTNXl3MmxNVUJ2a1Z2VGZaT2llbjZpUFJnSTF3M2xwbF9wNjhzRmxkVVN1b2dIcXVKRXdEOFNLQ1NycUxUWTlndC1FdFF6X2FpU2dnYkNzU3VtOUVqY3JGUkZidENHbjNXZm0yMEZVT2hqN18zYVBaOXM2dDJPSEo1dUtJT1NvWWE0d2VGVGhwLXYzNk0yd1RUNjVUNzZyd2xfYm1MQlBYZXhB0gHDAUFVX3lxTE9jb05zdEFsY0NjZUw3ZHVmRXBXM2hkd09ibVRkcno0RWIzSUdEbll3T1BsYjlpb3J2MXVfdkRQUkYwUlc3UVhXcXV6a1lFMm9neGk3VkV4cF8tTWVwNk9sUXd2akFrTVJuNUE2ZV9sbjJnS2NNVjRSdy1TanVsVjg1OGducUdmYUtjNThiTkhwcTFfRWFmWm5TWjlkZXdpV2pLUWRDYnlBZmY3N0xoV1JIWGZZNy1IX1paV1pQczlQWkxfWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T20:36:25+00:00</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="n"/>
+      <c r="I216" s="2" t="n"/>
+      <c r="J216" s="2" t="n"/>
+      <c r="K216" s="2" t="n"/>
+      <c r="L216" s="2" t="n"/>
+      <c r="M216" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N216" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia-Backed IPO’s Cratering Demand Sends Warning on AI Funding - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNY1Bic0VhVWU5NVVMNWxfTzl3WTJPenlXS0JGVzl1cW1NUVlzWHhhcDBteV9nUUJrTFlmVG9DZFpnUGF2N1A5amJoeTItX2pGUnVDaUFjb1UtRGNyZ0N4UzdKeHR4RkYzTkxnX0VSV3V3ODlWMFJiYVN6QkhGU2IyYVh6QmZFQ1dWSmVFalpqX0IwcS03TklBazZFcU1wX19qSmdSNHlLVUdiMzZpRDNVczFkTmNYUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T10:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="n"/>
+      <c r="I217" s="2" t="n"/>
+      <c r="J217" s="2" t="n"/>
+      <c r="K217" s="2" t="n"/>
+      <c r="L217" s="2" t="n"/>
+      <c r="M217" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N217" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Nokia pivots to Nvidia-backed AI radio access networks for India - Business Standard</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPemRQU01veFFHMnN3MXQ3Umx6U2hERjhKSkdOWUlBMTVmdU9iaTNaWWdTaUlVcmY2UkFnb0Ezam5yWGh5VU1GZ2J2MjdqbWs5VURQdUsyMnJuY2tnOXVsYnQyZzV3VzFIZGwtQTdreXpUVWJRUzlLWGFOc3E1YnhRam9ORFVMMEc4aHJVQURLSmhaNUdqTkZuQWhGRGstc29uNjUxUTI5VDJadGJHRVd3eFZMTksyNGJ1b0RjTm9rd29EbHdkLWhPdE1aSlJod9IB0wFBVV95cUxPMWo0WjZtUXFCRjJxazFYdkpLNndCQTFTNVFxejdKT2M5SUoydHg5QkNEc1h6akFNSENHbTBFZEw2RTBmbzZQT3htYTlnMVZNblVIOGs0MkdiMkI2TVZWWWRRUm1oSnJ6YnpjZ3JOM1FlMDBtTGI2M2EyZTY4aUplZjdVcURvNjB5T1BJV0xnVjdtaTBwa2RuWHhMVVVja2lxSlpOalJWZ3lkTDJUUy1XeE5zUzI2cWFNdnJ0UjVXQ0NnSXVUZG96VG5nZHppUGZDbHBZ?oc=5</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:03:57+00:00</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="n"/>
+      <c r="I218" s="2" t="n"/>
+      <c r="J218" s="2" t="n"/>
+      <c r="K218" s="2" t="n"/>
+      <c r="L218" s="2" t="n"/>
+      <c r="M218" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N218" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia-backed Upscale AI launches platform to link chips from rival makers - The Next Web</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>The Next Web</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOQWRkSFhlUUNkUnBHYUZ0S0NfcjhBdVVkSjJGVjZOVkJqM2tPakxjdEpRMHBvRXpsSHJfa21KQm5yVF9iZFBRZVZ1dHF5V0NaMl9ZaElSYVd5cHFEemx4bzh6TDNpd0xjY1J5QVpOZ1dpZEFneC15RFdUbF9POFYxVVlTQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:57:34+00:00</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="n"/>
+      <c r="I219" s="2" t="n"/>
+      <c r="J219" s="2" t="n"/>
+      <c r="K219" s="2" t="n"/>
+      <c r="L219" s="2" t="n"/>
+      <c r="M219" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N219" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia-backed Upscale AI launches platform to connect chips from rival suppliers By Reuters - Investing.com</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZ1BUVXhxZVFJdE9qSzZYT2tDbnNQM1NkQnd1aWMyR3V6YzVPcDZmZEJkc2dPbk5rOEhRVGdpUmN0WUgtNC0ydkNESXhPWjNDSmVYVFRQdFp0WDRGcEw1LWc3ZjMwZ3J5alRlYUFYdndpOWtoWURVU0VNcEk2VjVqaVBxNEVSb2Q0UG9Rc0JBQXZzS1RGVHlkYkFNX0haRnZBdDVWeGkycXdYSEduS3RfMnZkbmRjUG5aWkNUdDAzNDUtb1dXV0VsTzczbGFlc3poVHc?oc=5</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:30:47+00:00</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="n"/>
+      <c r="I220" s="2" t="n"/>
+      <c r="J220" s="2" t="n"/>
+      <c r="K220" s="2" t="n"/>
+      <c r="L220" s="2" t="n"/>
+      <c r="M220" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N220" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia-backed Upscale takes on AI networking silos with Token Fabric - Network World</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Network World</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQUGxwS01FbFB4ZzFGNUlmWU45S28tMy1qWTJRTFdJQ01FQ0d3YS1jX1l1RkZ6b2NTWlY5ZFRxMl9rcUNGelNkcXVXeUd4LVZFbnpqbFhNZmpQTWNaUTVhbFo1bmpiek1NYVd1ckdqNnYzemktZVhKV01WUHpEZC01V2N4M2lBTzdWWDZNRFJOMUNxNVN5SFd5eWU4TlJyeHNDT2xXWTZTNA?oc=5</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:46:53+00:00</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="n"/>
+      <c r="I221" s="2" t="n"/>
+      <c r="J221" s="2" t="n"/>
+      <c r="K221" s="2" t="n"/>
+      <c r="L221" s="2" t="n"/>
+      <c r="M221" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N221" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>What Does Nvidia (NVDA) Gain From $40 Billion AI Demand Backing? - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPQW9jOERlTkhZTGJMM2gwdTRSMm5VbWJWM3FlUFZRVEl2aGp0dnJqR25hb0NzRWhCZW5vS29fSHFCVmJZUVBkUW9lTTBJMUdPY3VEbmF4dDByZFFFM1BfTmFnMGdWNElsY28zQ1VHTi0tWkVJQzdhZTB5UW5IaFlXVVNMS0JMSDZfNV8xTXNKazZpUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T12:16:50+00:00</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="n"/>
+      <c r="I222" s="2" t="n"/>
+      <c r="J222" s="2" t="n"/>
+      <c r="K222" s="2" t="n"/>
+      <c r="L222" s="2" t="n"/>
+      <c r="M222" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Arista steps up its Ethernet challenge to Nvidia’s AI scale-up networking fabric - Network World</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Network World</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPTmxKYjRuMEdyaWczZ1p3Tm9xUlFvVFpKMER6VXhqQWREckF5T3JOY1NLU1NhNndWeE5IdlBpTFFXQUtJUW1BTnJ6cFFNMEIzaHh4bTNOWDBpUVRvQW1hXzNLTVVnRHFaTXZpWF9qOUZ5TVEyeU5GOW1PWm1xQUlBVUFvSlQtaG1TbS1BdWZUY0pUalVOcl9Fc2l1S0VwTm5BRElPNG9WblBVSXI0SXp4UmFOa1Mtc2FvWkdVZTVtU2REVGVOWlBXQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:46:11+00:00</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="n"/>
+      <c r="I223" s="2" t="n"/>
+      <c r="J223" s="2" t="n"/>
+      <c r="K223" s="2" t="n"/>
+      <c r="L223" s="2" t="n"/>
+      <c r="M223" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Natura’s $99 smart ring puts AI agents on your finger - TechCrunch</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQQXh1Q2FQcGpqa0FQZ0VKUW9ELTlPTzhXZXpEeDREdUZRNG4yYkY5ZDJKSHN2TThhQ1Vaekg5SjVMNkJjZE41dVhZT1dvcFhxZDQyMHJvNTNfdXN5cnZwQ0xzU2JvVUZKTEIwOUFFTlZDN21tWUZPYjdrb1RCU2JlV3JHM19SdUFmajlN?oc=5</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T16:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="n"/>
+      <c r="I224" s="2" t="n"/>
+      <c r="J224" s="2" t="n"/>
+      <c r="K224" s="2" t="n"/>
+      <c r="L224" s="2" t="n"/>
+      <c r="M224" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N224" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Execution Containers: Policy-driven containment for AI agents - Windows Blog</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Windows Blog</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMHhKel95eVdnemQzSkZ6Y3dSZFRwdzNsVTQyYnNxRlBac3NPXzl6TENvUExvOHpUdlRlMlpJdS0zVGREbkkwWEFzUUhmdjB1YWlBX0RNV2xCbEd4elZqTEd0OGx3R1c4MWhUVnV5TEVoeVg3SEdYUlJyTFBqLUVSZkt2dFptQ3pXV1pwZ0U5bG9Zeko0R2xEaHo5VFhnTFhOWjNacm1tbmhCMHlCY0RhbFVaM2o0U2V6U1F6Tm1nTFJvb1k?oc=5</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T21:49:41+00:00</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="n"/>
+      <c r="I225" s="2" t="n"/>
+      <c r="J225" s="2" t="n"/>
+      <c r="K225" s="2" t="n"/>
+      <c r="L225" s="2" t="n"/>
+      <c r="M225" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N225" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Pay-per-inference for AI agents: How BlockRun and Incarna use Amazon Bedrock AgentCore payments - Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOWVdvZkNxT3drTGp5eHJ1YlpDQjYwOXVQajJaODU2NDNEMEFhRmJfZ0h1VUQ2MVcwMFVvMEswR2RXb0JxOGdjdjlCbzNYQXZuV3N6RjZmNXp2bnU3NmJhcnFvdGxtQkdzaFpYNjF4Y3Z3QTNLU2tRZjJiUGtFVjhMeVp0NFpXaWhFYXd5TnUxVm53NUN0Y2F6TE5GUXpfM3RyUnZvanBtY2U4ZWM4VU1XMkhFYXpZS1F3eXBJRllTOWJPM0UyZ2c5Z2pjWUJxdHRGWUtteG1zZzU?oc=5</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:33:29+00:00</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="n"/>
+      <c r="I226" s="2" t="n"/>
+      <c r="J226" s="2" t="n"/>
+      <c r="K226" s="2" t="n"/>
+      <c r="L226" s="2" t="n"/>
+      <c r="M226" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N226" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA, Microsoft Kick Off a New Beginning for Windows PCs With RTX Spark and AI Agents - NVIDIA Blog</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Blog</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE42emZsS3FlLU1vaVE4WW40aGFZa09nS1VLaV9td0JZS2t3Z2pwTDhkTG5ITkJVajYzQWVtWURTTkJTenR6N0paeE14bzg3OTVZYXkzNmRMWUFqSVQ4ZlhNZnpFdWdWUXlHcGdOTUVwSWlQcTd1SE1XZ25OWEdjZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T18:48:10+00:00</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="n"/>
+      <c r="I227" s="2" t="n"/>
+      <c r="J227" s="2" t="n"/>
+      <c r="K227" s="2" t="n"/>
+      <c r="L227" s="2" t="n"/>
+      <c r="M227" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N227" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Popular VC Paul Graham disagrees with Amazon ‘ban’ on Meta's Muse and Perplexity's Comet AI; says that bl - The Times of India</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgJBVV95cUxQVlVybDBQUVZsV0ZDVFdyUDZhX05lWHJSYjdnTzIzMXBXTkJXdVhtUXB4cV9GNzQtUmtvMFJiVm13dDdla0xLS29oQzYwQk5HU1kydWxrdGtPYjRoTUFBX3c4WVVBaFJ1X29RUXJ4RTR2X19FU3NmQlhyLVgzM1h3V2lsWGw3eEw4LVU0ZzA3d1FjOWo4WVd4SUxBMEF4aEotejQ2UzZYSndaZTFNeVNvYzZISzZJaGxUc1ZHZE9GRGxOdTVZOV9lcGlOR01vSzhGc29EOV9LelVaRm5DU0NqMm1Md2JsWXpjMTJaYzZRcVVnUHpKV09CTml0RXNnQ2NNdF9LRUlqV25ZcW5yTjA0NzBKTl9Lb00zV2c4bEhET0pUTGpES0gtOGVqbFFrUFdTQmxPbWhSUThHYUhiRVVnZkFn0gHHAkFVX3lxTE5ISThmdE9ENGNEUlhmWDMzNmw3S3R5TjdsUFNTdlR4cWxyLXVBUUtqQUd0Uk1melpkZWROSEJJZTlRc0dRd0xEUklKLWY3TmVsdGJ1TVQwSndTU1J6LWRFaTBnNlYyRFF3cm9mWTJQVFpjazV2WVc3Y05DTFA1dXlXWkN2c2RvYzdnMHlHa1RYeFZzNHZIQWZ5dVhObm9qNUVXVDVpYlVPM3cwOURESXhWWlNtWHV3a1YzcnNWQVF3dkJOOUl0eDljVUNxLTlIMEF6dEhmTWxLTER4YlpGUy1qUk1mU2o0WWFTcGpXeVhobm11WWlodlNTYXZPS2otem9xVWJEU1Vpa1FvWkxsTXJjQUU0aWVud25fTEVCMGdPZklpUjBhWlhHaERINHB1MmJ3c3VobmQzbE1pQk5pYkszQ25hOHh0dw?oc=5</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T13:17:00+00:00</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="n"/>
+      <c r="I228" s="2" t="n"/>
+      <c r="J228" s="2" t="n"/>
+      <c r="K228" s="2" t="n"/>
+      <c r="L228" s="2" t="n"/>
+      <c r="M228" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N228" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>India’s AI race moves from chatbots to voice agents - The New Indian Express</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>The New Indian Express</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPT1d4QUZLZ1VxNnZhRDdEQ0gzZ3E4QW1SM3Z5c1haX2V4Q005ZHNyOVB6c2JSSk45RjdRNzVhcGdrLVJka0lQR2FPWHByeGpaeGtKZVlic2pyaFJEZWZ3Q19lV3ppdkxnX0RZaWI5akVES2p4ZnFtMXVqdC1kdDhzeGZ6VUMzcy1UYlV1UVFYWkNMajdySTBhaXBaZWlCVC1COUxtZnpWcUItLVJvT2pF0gG8AUFVX3lxTE9iMWloZnhiSjhzWnVsSmlVQVIwNmhoT2pSSXpiSXFpcUkyZkIxbUJWTmJkeXF6d2hMdm9aTTVhd0xtaDl4c29VREFaeWVHZEM1S0h5VUJHbkdwM2x2ZTBUdDN0T1hrSjlseEVmZDJHUHNEd09CWEFfS014VmkwczY5UXlBR2xsMmxxU3RJRWt4S3FwTldiQ0FQSlA3Qk1mV0JfNWM1WmxmSTZFYVlBQU5iNldwdjQ0SG1LaU01?oc=5</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T18:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="n"/>
+      <c r="I229" s="2" t="n"/>
+      <c r="J229" s="2" t="n"/>
+      <c r="K229" s="2" t="n"/>
+      <c r="L229" s="2" t="n"/>
+      <c r="M229" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N229" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Google Launches ‘Universal’ Gemini AI Agent for Workplace - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQcDFROGxuS1JtVDV4Ym1UUFhYd0RkcTZjTVlNNWVIOFQxYmNRenZMUFZKRU9XYjl5SGpQUkNSU0xEdGVGcTlqcTJiX0pmUEJzUHFZdjdoZHdoeEl1Ti1MOUh5YWZGYkJ6ZDZIMmFfOXA2TFowOWdsUURtQ2VJNjZKVmNreHBCNFhRa3FBWVc5RlY4djN6Q1ZuSU9hOTFuZmg1ZWU5V2V3UTh1Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T13:25:05+00:00</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="n"/>
+      <c r="I230" s="2" t="n"/>
+      <c r="J230" s="2" t="n"/>
+      <c r="K230" s="2" t="n"/>
+      <c r="L230" s="2" t="n"/>
+      <c r="M230" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N230" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Google says its Gemini AI agent can now work on behalf of group of people in office - India Today</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNZVYzc29kM2hLSjM3MzJTZDd2ODdvS0JQWGViLVNEc2NqUDk1WDZ3MnV5X0FuN0YzbFpDdzN6LThpUlFMcWJJaGpiWkFibThXSTRNemtQWVhfSUtucHZFN19JcWNwVjdRU1JwdTZoOUhxS21DbHdRS0JETGZ4ejhZel9vajJRSzZKMTEyejVpY0xENVRzd3Q0MnpBUU1RVHgyOFVpYUdpdXJHTVZHbTFoN0dmcFZvZzI1eTR1U3E4TkpFSnJxUm5jQll4VWNyR2VzUzBOenI5ZzhXUldrVy1CM2ttckrSAeoBQVVfeXFMTVVwMWtwZGZhTFBYWl9EejBIY1FLOFUyOFhQbzFadGw1SVNINTliLURXcjR6YUdiVGZzeGFJZl96UW1ubXRBRGJ2ekJYWmItUE9FaGpIVzNnNS1HYUVCYU9YVHhuakoyc29iVzFhRUlSQ0xNdHVaMWRNWnhVRHRGUTlQZlQyWGt0a3dpT1l1czRZZUk3Y1ZGbWlCSjVSdW44cTVqdDF0X3lSclVNZ3dSdEItWlFXU0lMZ01SVTYtUkNPQW5kNmxrT3pVN0gzRjJGaWxVbjkwaHQxa05URi1QUmk1dnFyRkY5aFZB?oc=5</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T13:40:28+00:00</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="n"/>
+      <c r="I231" s="2" t="n"/>
+      <c r="J231" s="2" t="n"/>
+      <c r="K231" s="2" t="n"/>
+      <c r="L231" s="2" t="n"/>
+      <c r="M231" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N231" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Google launches workplace AI agent that gets its own email address - The Next Web</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>The Next Web</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE42TVp5NjV1RWJhQTFOenFkTnVQY0hEWW5Ud3Z1Rm8xakwxT1hmNG1YTk9kRWNkbE5VcUhXWGtHeWVRYzAtUDgtU2ZEdGVoS3BTZUNaNFhLZVg1ZU92QXFlUzV5T0ROaEllR0ctWXNuYWZBUmo2?oc=5</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T16:01:43+00:00</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="n"/>
+      <c r="I232" s="2" t="n"/>
+      <c r="J232" s="2" t="n"/>
+      <c r="K232" s="2" t="n"/>
+      <c r="L232" s="2" t="n"/>
+      <c r="M232" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N232" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Elastic launches AlertZero AI agents for security operations By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>Investing.com India</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOSkhvVzRyVGQtaE1QM2JtRktQTlA4Yk5VZndGd1M0RC1FckRMTUVzd1lBM2xWOXJjcGRFN2wzakYxWlRFdzFCQ0NJWFAtR3poN3M1QXg4UW80MEJvQTlJMVRiMG1LZDdBaHBZaUVmRHZHcTlSU3VPSWNjcUsxWWlzcDdzczVPLXhwcG1uRmVOeUdfUGJaOGFEMEMwOXhKWmRTQmRXU2FPaHhZRWh6cGZqdWl5WXFDZnVlVGZLdnFn?oc=5</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T14:28:36+00:00</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="n"/>
+      <c r="I233" s="2" t="n"/>
+      <c r="J233" s="2" t="n"/>
+      <c r="K233" s="2" t="n"/>
+      <c r="L233" s="2" t="n"/>
+      <c r="M233" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N233" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>AI Hooks for Claude Code, Cursor, and Codex: Block Secrets - GitGuardian Blog</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>GitGuardian Blog</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9wYnppRlN6LTJvazFmMVpuRkhabWtxQ05DN1BTcmhMYnlSZ1A4aXZ6d1o3RkdkcnJyRm12OWpLaHhyNWo0NFlQUUNMMVhDQUxIRnBpTDdVRTFIWGM4VGYtOFM0Mkp3X3E0QUU4?oc=5</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T11:04:13+00:00</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="n"/>
+      <c r="I234" s="2" t="n"/>
+      <c r="J234" s="2" t="n"/>
+      <c r="K234" s="2" t="n"/>
+      <c r="L234" s="2" t="n"/>
+      <c r="M234" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N234" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>China-based suspect used AI tools in South Korean bank hacks, says CrowdStrike - The Hindu</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNeV80WlZDZFJsaDRud3FzMmxrY1A5ejdoSkF5aVMxMlZ3OUpOZV9QOFBkaUtzSUxIc1RLZjRSdzB2VUlpS3VmNXRZNkxUd0l5SFV6aWhZUjkzUWVIc3RDLUpNUDgyZ3hyRWhuX1N5Uk9adGVaRTVPODNYaTJLZnFwb1dLVTNSVFhkbTBDUlJNUkVWNzZWYXZ0SWl4RlR3bkV5LXEtb1JERnlZSXRDNVdidEl0R1c1VHF3VGJ6SzB5dzlsT2JCMDludm1CeGdJVUFBLTZTQVVWNXZlUdIB4AFBVV95cUxPYVdMTHh3X2JEa05LVzhBSmpoNjVoVi04dDMxb3NKRWdRLWJNZEpfOE9oMU9RWmVTLU5WcHhFcHlMOGVzajc3bGNrQ0hEbGVKNFAyWXFWOF82ck1EWU9UODF2VFBMN3M3VzJtM1FUaGVmRlBlc094ZlNrOVJISm5UMDBYaW5CT3owd3pPWVZIeGZyRnZQN1Q3V2RFR3FqaWhEc3BsNkkteGRPTVZaOVF4a2pxY1ItX3BmNGxEUHJQTzBaVzlWNVhTcDJWTGNLUVNnd1ZkdEpGcHh2ZU5rRGJ2ZA?oc=5</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T03:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="n"/>
+      <c r="I235" s="2" t="n"/>
+      <c r="J235" s="2" t="n"/>
+      <c r="K235" s="2" t="n"/>
+      <c r="L235" s="2" t="n"/>
+      <c r="M235" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N235" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Who owns the bug when AI writes the code? - The Economic Times</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOX0VtYXVJeDltVHQzaC1EYUZrUVp6YnYwRjdRWWhIa2xjbEluSzVkWDJpamxEdmR1X01BdW55bDVQMGdpT1RoYjhUYVV1V3dsZFh6MTdBRmpHQkZhWW1fZ2xLUklETDBGVzJUQThrcVVMcTZnX1hhSDdSaUxqdjcxVU95U215aGgyYmJwb290VnIwZk9hZ2Q0eUN2TzVPZ3hGUmxEMFM4UkdnRWdUM0HSAbMBQVVfeXFMTndETDV1Zl9MaG9yOHVOS25xUEp4aHlEU0JzbVJsV3JUUXZhS2FwUVdNblZTcDhWOXFkVzBiSllwbVVsUVZaVmJmMDQ4WXFmSmFOYVlxRTU4MHlleUtEWW9CUVV5RGNuOEpBMG1URllsT2NmMjJ6N3ZlSTM3QTlZUGU5cnFWWFN6RjgtcC11dlZZbjlJMzBaZzBzcTFNS2pQMkw3cXdMTDN5aUtydnc3c2JnYXM?oc=5</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T08:13:54+00:00</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="n"/>
+      <c r="I236" s="2" t="n"/>
+      <c r="J236" s="2" t="n"/>
+      <c r="K236" s="2" t="n"/>
+      <c r="L236" s="2" t="n"/>
+      <c r="M236" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N236" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>South Korean banks likely targeted by China-based hacker using AI agent: Report - Firstpost</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>Firstpost</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNUWlReGVpaDN4d0FUMkJaRm5DNDBOVW1sOS1vSlo4N3lKU2hoTVJ4X1dHaW9hZjF3Y3NLTGxVaW5aU21YT2hwSjBMTFMtYlZUYUZXLTFqaHdkUHM4YktqdWNfYVZvVGRaSkN4eUcwbVJaR1B2ODVXYWhMS0o4S0pKdUR1R1I4RVc0U3BUbFcwWEh0bXlpWXdQV3g2ZlozQkN0SXV6LU45SEtRM1UyOFEyTFdHR2tONHNSTkxucUlXWU3SAcYBQVVfeXFMTXdaVVZYZ0xDSllmbC1RMF92M0FFbjdweUtnZGM2ZmJpN3ZfLXFlUHgxcm1wemZoWHFKU2R5NVUxWXlJdENMdnhrLXlTbkJZamdlRVktMFoyd2owQnBPeFZNVXdITlY2Zl9IMUlzU01WV1h4bUpKVmNxNU03dUNVOVhOdTBuMTYwY0JJZEIzNzdybkVTRkFnZVhsSk5jX2w4cFNsRTMtMjBaN3pmeEM3UGthZFQ1aTBkTWNvWlVxZjRZVzdidU93?oc=5</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:27:49+00:00</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="n"/>
+      <c r="I237" s="2" t="n"/>
+      <c r="J237" s="2" t="n"/>
+      <c r="K237" s="2" t="n"/>
+      <c r="L237" s="2" t="n"/>
+      <c r="M237" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N237" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>I Tested 5 AI Coding Assistants for a Month: Here’s What I Actually Found - KDnuggets</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>KDnuggets</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQREg5UTV0YlMzWHlBLUFTOGZXTUZDMEh0ODlhRzZUcGV1aWlpMFpRMnZmREs5Y003NHBhTGtjR0hFZGpvVjJoMmtjMlZRX2VCMU9fSDVYeFRnTmhRbUZHTlBlOEJyd3lJZlQtbnZvY3hzTTVOTUR3T01XUzBERXVYWFNoQy1OOWRUNFNPc0dMazM1eEE3cl9nNlhJNVhpUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T12:38:19+00:00</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="n"/>
+      <c r="I238" s="2" t="n"/>
+      <c r="J238" s="2" t="n"/>
+      <c r="K238" s="2" t="n"/>
+      <c r="L238" s="2" t="n"/>
+      <c r="M238" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N238" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Meta and Microsoft are using less Claude as their own AI tools grow - YourStory.com</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>YourStory.com</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxONmhtVWJQUTlCU1dHcDBTMTVoYlBZQlpEM3FVNkFjZVlxVVNEdHlod3VhT0dlYUhHdEpycmhrSWdXYUJoRWROQUZjS3RrMW1wYmVNTVhOcTZ6dDk3TTNJUGluQnZFaHYwdlVIYm03T29LUE1JSlpZV3g0MkgwX2lfZi13?oc=5</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:38:55+00:00</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="n"/>
+      <c r="I239" s="2" t="n"/>
+      <c r="J239" s="2" t="n"/>
+      <c r="K239" s="2" t="n"/>
+      <c r="L239" s="2" t="n"/>
+      <c r="M239" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N239" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Harness acquires Augment Code to bridge software engineering from idea to deployment - SiliconANGLE</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>SiliconANGLE</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQdEVHTU9LWEc2QmgwR0RqRTEzTEhkLU93ZGQyVWZhRlF4OWdFNzdieXBjdG9GQVItT2VCNG9LMkFsWVI0VVF5bThjY0RQVno1VUIwWlNpeHFoSUZlYmtOemFyUkhmemxTdTRkSERqQm9udHkzdjR4ZmhFY1Z0d3p6eTJ5S0pXMHducEkxY0lDTjVwQkFUdWJ5TUlYSGFvUlFrOXBqYl9VTUQwVUc3ekZvdHNXRWw4aEo1eHFaT0RR?oc=5</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T15:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="n"/>
+      <c r="I240" s="2" t="n"/>
+      <c r="J240" s="2" t="n"/>
+      <c r="K240" s="2" t="n"/>
+      <c r="L240" s="2" t="n"/>
+      <c r="M240" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N240" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Exclusive | Nous Research Scores $90 Million to Bring Open-Source AI Assistant to Enterprises - WSJ</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOS1hwU0JncDNQTG83UDFyakpOeDZWZmYzSHloT2tudWdMcHdTRXpiQVJGUWJwcElDUE9xRlgxWkJ0dUxRcnM0WTV5WlRFdGdWVkdpSU05VUFwQWQ0MjZoN1hqZTZ0c1BjUEtXYURVNUlwaUZPQXVmb0JHS1dLeFp1YWZzejM0OWhlcG44YV9kNlZPYTlNNFR5UlFiTVVGOUhDQk1nY05MQjZTYlQyQm1BSl9UeU9GUmZROW82UW0tRDMxS0ZWNXdPSg?oc=5</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T10:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="n"/>
+      <c r="I241" s="2" t="n"/>
+      <c r="J241" s="2" t="n"/>
+      <c r="K241" s="2" t="n"/>
+      <c r="L241" s="2" t="n"/>
+      <c r="M241" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N241" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>AWS launches open-source AI agent sandbox to prevent YOLO mode disasters - The Register</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>The Register</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQdldCZWVraDhsNlpyYWdfRm80YmpyVERNZHh1bEJOVWwxSlkweDZhMG5IZmx1ZmlIOFVkNUVOTXk3MXNaT2luSU94M1UzQ1dCeHo3cWdpczVTYmdmSUlLX2Z0VV9Xdy1sQXVpMlVMbHRWNVl4M3pxTVVrbXhEMXI4c1VIR2ZkR014d3VqLWtORG1QQURwSXB5eElFdVZDNmpKRGUtZlpCdUZpalJlbEFpWDQtNDZNWnpDZU56N3BCTVRUZmoyRzUwMg?oc=5</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T17:42:06+00:00</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="n"/>
+      <c r="I242" s="2" t="n"/>
+      <c r="J242" s="2" t="n"/>
+      <c r="K242" s="2" t="n"/>
+      <c r="L242" s="2" t="n"/>
+      <c r="M242" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N242" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Alibaba's Joe Tsai says open-source AI is Europe's best path to tech independence - Quartz</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Quartz</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPbk9Iek9HUnk0UmsxaTBvbDB2TV92bnFWemVjMnM0bmZfMEVnalJGSkpiSWhQdXUtdzYwWV9lXzU4RmhyaXA1OFRDX0ZkYWJwaUpXTl9Makt1b3k5eTFFMFREVTEyOVdEeXZ3bkM4Q1BGLWhfN1MyTFRXUUJyeE1aNA?oc=5</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:50:59+00:00</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="n"/>
+      <c r="I243" s="2" t="n"/>
+      <c r="J243" s="2" t="n"/>
+      <c r="K243" s="2" t="n"/>
+      <c r="L243" s="2" t="n"/>
+      <c r="M243" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N243" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Huawei and DeepSeek release open source AI tools in a bid to lower Nvidia exposure — but will programmers make the switch? - TechRadar</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>TechRadar</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOUVIwQzljRERIZDhxSGVxdzNNQ2p3ckxhalpLdWFaRndwakZQclhmekhUNTJ0cll2ajNtR1NDT0NmenoyTDBkY0t6MWVTbG9ydzR4VmRKeWtZc0JybHhZSzRmd01XWVpGbzMyWHRUc1loZUp5czhpM1pGNUpDUEthUnNpeVdLRzc2MzRqTGF4al9MV2NIVlI0VkgwV1lNc1BuTnJHNlhKX0lra3J4VUxPQzNPa2hOT0x6UHZ3SUQzU1NTUDJWcmx1T1dVVzRoY09WaVNCYXYwRjV2NFo0YVphTlRvSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T19:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="n"/>
+      <c r="I244" s="2" t="n"/>
+      <c r="J244" s="2" t="n"/>
+      <c r="K244" s="2" t="n"/>
+      <c r="L244" s="2" t="n"/>
+      <c r="M244" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N244" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Maker of Open-Source AI Assistant Hermes Secures $90 Million - WSJ</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPNHZsZXZCVlE0NzNuRkdubF9nSnF4dDFxRjNJbTRURXhVWTZkbzlVbmxKc1AtM3RpLXI0TnozYUFSUDBELVdjU3pXaFR2dGVObFlnQlRoaS1ENWxNLThCM2tSbGJuYXhBZ1dCU0cxRmhJVjl0MzhwaDNnZC1lQzNDaWdabTMyUjMyZG9tRDJ2RTFDbzRkUW5kUnk1Wmk0bTZPMklaRGhjeEYydWFO?oc=5</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T12:09:10+00:00</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="n"/>
+      <c r="I245" s="2" t="n"/>
+      <c r="J245" s="2" t="n"/>
+      <c r="K245" s="2" t="n"/>
+      <c r="L245" s="2" t="n"/>
+      <c r="M245" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N245" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Google Pauses Open-Source Bug Bounty Program Amid AI Slop - BankInfoSecurity</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>BankInfoSecurity</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQTEp5Z3lYaG1TU0o3UVlZQ01pb0FLRC1sSUxXbUNwOHVJLUJfOVp2c1NITUV4UWdDZkpORnBhSG9sRzlmSVl6clVNLXRwT2pZN2pPMXVOT3NfbHhSTGtwQUFrUXQ1Z0trTGk5UkRSZFFNclEyZVJNczhhSDNhT0tWQ3AyZFNxeHNkVEZIT2VrNW1aZk9BOXdWWElLOFZHU0E?oc=5</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T17:19:10+00:00</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="n"/>
+      <c r="I246" s="2" t="n"/>
+      <c r="J246" s="2" t="n"/>
+      <c r="K246" s="2" t="n"/>
+      <c r="L246" s="2" t="n"/>
+      <c r="M246" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N246" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Introducing Strands Box: AI agent sandboxes powered by Dogwood - Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNWlRHaWNGcWpmUkd6d2JfYjNFVDAzYmVnX1duOHVtWHFWaG9TMFg0Y0psWFQ4TkEyb2czVDJiS0p6Z1J6akxVak1ELWRqcjY4RHMwVVFxSXQyeFZkNzlCbXo2NEo0bkRLVEFaTlk1YU1aa0V1Zy0ya2FxYVVONm1nRnFlOUJoQU1fMkxjRGJZdXRkVWY3OFhRVzVfWkJlUTN0VWxUZQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T17:36:46+00:00</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="n"/>
+      <c r="I247" s="2" t="n"/>
+      <c r="J247" s="2" t="n"/>
+      <c r="K247" s="2" t="n"/>
+      <c r="L247" s="2" t="n"/>
+      <c r="M247" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N247" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Robot data startup Mecka AI nabs $60M from Sequoia - TechCrunch</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQQ1J1WXZfQjlyeEpYUVB3N3N1WmtXRll6X01oQ05nbnlaR09qcU1OYmVsS0p6aDlWMUtNOXM1RGlIdjNQNlV4dG5pb3pZUldoa1BmVlYtOGZwcEI1R1ZreFBHd3lhNjJaangySEZRa1RxWlFvbHlZcm5jZHp5ejJ0WGt1aFNVYzJrTGhmOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T23:36:57+00:00</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="n"/>
+      <c r="I248" s="2" t="n"/>
+      <c r="J248" s="2" t="n"/>
+      <c r="K248" s="2" t="n"/>
+      <c r="L248" s="2" t="n"/>
+      <c r="M248" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N248" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>AI breakthroughs in robotics won’t change your life any time soon - MIT Technology Review</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>MIT Technology Review</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNZml3eHVNU252OUdQVFlJTVdVX0UxY0F3NzBpQTU5NWJza0Y3UFdHWnhPSXI0cEJaWmdQdlRCeW40UWYxRWx3aThFdk51Rk82U0VFZzN1Tkg2Uk8yUWQtMU1zYUlGQm5kQU9PSTI1NEJ6WUJTclNyVVlnczl1VjJpaFlDU3Q5ZGozR2dqTkYyS1RYMXJRcERXZDVDbERCWm14TFpySzJ6YzZpeXNtTU45ZEpWdnBoNFBn0gG-AUFVX3lxTE5DTDNXQWotYUtHN0Y0NXJEQTNiMWkwOXBHLUM1YkJhV3dSWHpkLW03X2hzOURVWTlsUnhKYVJtdWtJRU5xck4xQTFpOGNsZlBlWU02UXo1UVItNU5ZZ0pMQ3lPbkkwY0VfajdWRlZ3bEczaERzTnltWE9VM2xTX0pEX1ZCXzVNWWpoQU9ld3lXMDd5cFQtbUV3UDhhWXRHdDA3TWVQMVpueXRzYTdGdUQzOEhpbjZZYjY5QmI3MlE?oc=5</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T09:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="n"/>
+      <c r="I249" s="2" t="n"/>
+      <c r="J249" s="2" t="n"/>
+      <c r="K249" s="2" t="n"/>
+      <c r="L249" s="2" t="n"/>
+      <c r="M249" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N249" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>This Disembodied Hand Is All the Robot You Need - IEEE Spectrum</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5qTkNmQUd0UllXTnZSeVRfSVBKWnphYUlYenIwQU5BVmd5d3ZLampQc2gxTzNoektleGpjdG9KemxYekE4LXhELVpJenlMay1YcnBtR1pBdkFfQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:04:19+00:00</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="n"/>
+      <c r="I250" s="2" t="n"/>
+      <c r="J250" s="2" t="n"/>
+      <c r="K250" s="2" t="n"/>
+      <c r="L250" s="2" t="n"/>
+      <c r="M250" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>How AWS is helping companies build physical AI machines that think - About Amazon</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>About Amazon</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPV09ac2QtTXFvV2dpMHNFZGJOM2xNd2RQUEVtZDYzX0dsM25GRG40V1U3TmFNR0ExUTlHaERpMlBtb1JaREtKYlZBVEcyMkNKX2FxNmdRcVEzTVZFNUpBSm9oNlVCelpGVDNmb080WDNVZkNqVDA2YzJCTF9kNWtPWGUycEE1QWxYNlJmLVpwNEtaSFU?oc=5</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T13:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="n"/>
+      <c r="I251" s="2" t="n"/>
+      <c r="J251" s="2" t="n"/>
+      <c r="K251" s="2" t="n"/>
+      <c r="L251" s="2" t="n"/>
+      <c r="M251" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N251" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O251" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10189,7 +13793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10910,6 +14514,90 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Google Launches Gemini Workplace Agent with Dedicated Corporate Email</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌కు కొత్త AI ఉద్యోగి: Google Gemini సంచలనం!</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లో ఒక సరికొత్త ఉద్యోగి చేరబోతున్నారు... కానీ అది మనిషి కాదు, గూగుల్ తయారుచేసిన AI ఏజెంట్!</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSlVSeTZYa0pSOFppNk9GdFF0Y0VZa19lYnRKTjRXb0FpZUhaTlBEUmRLUW04N3E1azhGalpULTNwN2Y0SnhFWGhOTktSdTVMMTJDc2VRX013NGNuSzJYRGxiWVJyU2dzS0lGdGN4YXlxQzR3TWl0eVQwbjFKWW5JVG1kQXdJYVVwd2J2OTZ5NDZYT0JQM09Ycmt2amRmekhNWTBfR0pR?oc=5
+https://news.google.com/rss/articles/CBMidEFVX3lxTE42TVp5NjV1RWJhQTFOenFkTnVQY0hEWW5Ud3Z1Rm8xakwxT1hmNG1YTk9kRWNkbE5VcUhXWGtHeWVRYzAtUDgtU2ZEdGVoS3BTZUNaNFhLZVg1ZU92QXFlUzV5T0ROaEllR0ctWXNuYWZBUmo2?oc=5
+https://news.google.com/rss/articles/CBMi5AFBVV95cUxNZVYzc29kM2hLSjM3MzJTZDd2ODdvS0JQWGViLVNEc2NqUDk1WDZ3MnV5X0FuN0YzbFpDdzN6LThpUlFMcWJJaGpiWkFibThXSTRNemtQWVhfSUtucHZFN19JcWNwVjdRU1JwdTZoOUhxS21DbHdRS0JETGZ4ejhZel9vajJRSzZKMTEyejVpY0xENVRzd3Q0MnpBUU1RVHgyOFVpYUdpdXJHTVZHbTFoN0dmcFZvZzI1eTR1U3E4TkpFSnJxUm5jQll4VWNyR2VzUzBOenI5ZzhXUldrVy1CM2ttckrSAeoBQVVfeXFMTVVwMWtwZGZhTFBYWl9EejBIY1FLOFUyOFhQbzFadGw1SVNINTliLURXcjR6YUdiVGZzeGFJZl96UW1ubXRBRGJ2ekJYWmItUE9FaGpIVzNnNS1HYUVCYU9YVHhuakoyc29iVzFhRUlSQ0xNdHVaMWRNWnhVRHRGUTlQZlQyWGt0a3dpT1l1czRZZUk3Y1ZGbWlCSjVSdW44cTVqdDF0X3lSclVNZ3dSdEItWlFXU0lMZ01SVTYtUkNPQW5kNmxrT3pVN0gzRjJGaWxVbjkwaHQxa05URi1QUmk1dnFyRkY5aFZB?oc=5</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Google Launches Gemini Workplace Agent with Dedicated Corporate Email</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌కు కొత్త AI ఉద్యోగి: Google Gemini సంచలనం!</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లో ఒక సరికొత్త ఉద్యోగి చేరబోతున్నారు... కానీ అది మనిషి కాదు, గూగుల్ తయారుచేసిన AI ఏజెంట్!</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSlVSeTZYa0pSOFppNk9GdFF0Y0VZa19lYnRKTjRXb0FpZUhaTlBEUmRLUW04N3E1azhGalpULTNwN2Y0SnhFWGhOTktSdTVMMTJDc2VRX013NGNuSzJYRGxiWVJyU2dzS0lGdGN4YXlxQzR3TWl0eVQwbjFKWW5JVG1kQXdJYVVwd2J2OTZ5NDZYT0JQM09Ycmt2amRmekhNWTBfR0pR?oc=5
+https://news.google.com/rss/articles/CBMidEFVX3lxTE42TVp5NjV1RWJhQTFOenFkTnVQY0hEWW5Ud3Z1Rm8xakwxT1hmNG1YTk9kRWNkbE5VcUhXWGtHeWVRYzAtUDgtU2ZEdGVoS3BTZUNaNFhLZVg1ZU92QXFlUzV5T0ROaEllR0ctWXNuYWZBUmo2?oc=5
+https://news.google.com/rss/articles/CBMi5AFBVV95cUxNZVYzc29kM2hLSjM3MzJTZDd2ODdvS0JQWGViLVNEc2NqUDk1WDZ3MnV5X0FuN0YzbFpDdzN6LThpUlFMcWJJaGpiWkFibThXSTRNemtQWVhfSUtucHZFN19JcWNwVjdRU1JwdTZoOUhxS21DbHdRS0JETGZ4ejhZel9vajJRSzZKMTEyejVpY0xENVRzd3Q0MnpBUU1RVHgyOFVpYUdpdXJHTVZHbTFoN0dmcFZvZzI1eTR1U3E4TkpFSnJxUm5jQll4VWNyR2VzUzBOenI5ZzhXUldrVy1CM2ttckrSAeoBQVVfeXFMTVVwMWtwZGZhTFBYWl9EejBIY1FLOFUyOFhQbzFadGw1SVNINTliLURXcjR6YUdiVGZzeGFJZl96UW1ubXRBRGJ2ekJYWmItUE9FaGpIVzNnNS1HYUVCYU9YVHhuakoyc29iVzFhRUlSQ0xNdHVaMWRNWnhVRHRGUTlQZlQyWGt0a3dpT1l1czRZZUk3Y1ZGbWlCSjVSdW44cTVqdDF0X3lSclVNZ3dSdEItWlFXU0lMZ01SVTYtUkNPQW5kNmxrT3pVN0gzRjJGaWxVbjkwaHQxa05URi1QUmk1dnFyRkY5aFZB?oc=5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10922,7 +14610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11565,6 +15253,80 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌కు కొత్త AI ఉద్యోగి: Google Gemini సంచలనం!</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లో ఒక సరికొత్త ఉద్యోగి చేరబోతున్నారు... కానీ అది మనిషి కాదు, గూగుల్ తయారుచేసిన AI ఏజెంట్! అవును, గూగుల్ క్లౌడ్ వ్యాపారాల కోసం సరికొత్త జెమిని వర్క్‌ప్లేస్ ఏజెంట్‌ను అధికారికంగా లాంచ్ చేసింది. ఇందులో అత్యంత ఆశ్చర్యకరమైన విషయం ఏంటంటే, ఈ AIకి ఉద్యోగిలాగే ప్రత్యేకంగా సొంత కంపెనీ ఈమెయిల్ అడ్రస్ లభిస్తుంది. ఇప్పటిదాకా మనం వాడిన సాధారణ చాట్‌బాట్‌లలా ఇది ప్రశ్నలకు కేవలం టెక్స్ట్ సమాధానాలు ఇచ్చి ఆగిపోదు. మీ టీమ్ తరపున ఈమెయిల్స్ పంపడం, మీటింగ్‌ల సారాంశం రాయడం మరియు క్లిష్టమైన పనులను నేరుగా పూర్తి చేస్తుంది. ఆఫీస్‌లోని డాక్యుమెంట్లు, వర్క్‌ఫ్లోలను స్వయంగా పర్యవేక్షిస్తూ ఒక డిజిటల్ సహోద్యోగిలా పనిచేయగలదు. చాట్‌బాట్ల దశ ముగిసిపోయి, నిజమైన పనులు చేసే పూర్తి స్థాయి ఏజెంటిక్ AI కాలం మొదలైంది. త్వరలోనే ప్రతి ఆఫీస్‌లో మనుషులతో పాటు ఒక AI ఏజెంట్ కూడా కలిసి పనిచేయడం సాధారణం కానుంది!</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>A sharp, modern 9:16 vertical short about Google's new workplace Gemini AI agent. Dynamic smooth cuts, high-tech motion graphics, clean Telugu typography overlays, conversational narration, subtle ambient electronic background music, burnt-in Telugu subtitles, concluding with a credible source attribution card.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ క్లౌడ్ వ్యాపారాల కోసం సరికొత్త జెమిని వర్క్‌ప్లేస్ ఏజెంట్‌ను విడుదల చేసింది. ఈ AI ఏజెంట్ స్వయంగా ఒక ఈమెయిల్ అడ్రస్ కలిగి ఉండి, ఆఫీస్ బృందాల తరపున పనులను పూర్తి చేయగలదు. వివరాలు తెలుసుకోండి!</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>#AI #GoogleGemini #TeluguTech #TechNewsTelugu #FutureOfWork</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌కు కొత్త AI ఉద్యోగి: Google Gemini సంచలనం!</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లో ఒక సరికొత్త ఉద్యోగి చేరబోతున్నారు... కానీ అది మనిషి కాదు, గూగుల్ తయారుచేసిన AI ఏజెంట్! అవును, గూగుల్ క్లౌడ్ వ్యాపారాల కోసం సరికొత్త జెమిని వర్క్‌ప్లేస్ ఏజెంట్‌ను అధికారికంగా లాంచ్ చేసింది. ఇందులో అత్యంత ఆశ్చర్యకరమైన విషయం ఏంటంటే, ఈ AIకి ఉద్యోగిలాగే ప్రత్యేకంగా సొంత కంపెనీ ఈమెయిల్ అడ్రస్ లభిస్తుంది. ఇప్పటిదాకా మనం వాడిన సాధారణ చాట్‌బాట్‌లలా ఇది ప్రశ్నలకు కేవలం టెక్స్ట్ సమాధానాలు ఇచ్చి ఆగిపోదు. మీ టీమ్ తరపున ఈమెయిల్స్ పంపడం, మీటింగ్‌ల సారాంశం రాయడం మరియు క్లిష్టమైన పనులను నేరుగా పూర్తి చేస్తుంది. ఆఫీస్‌లోని డాక్యుమెంట్లు, వర్క్‌ఫ్లోలను స్వయంగా పర్యవేక్షిస్తూ ఒక డిజిటల్ సహోద్యోగిలా పనిచేయగలదు. చాట్‌బాట్ల దశ ముగిసిపోయి, నిజమైన పనులు చేసే పూర్తి స్థాయి ఏజెంటిక్ AI కాలం మొదలైంది. త్వరలోనే ప్రతి ఆఫీస్‌లో మనుషులతో పాటు ఒక AI ఏజెంట్ కూడా కలిసి పనిచేయడం సాధారణం కానుంది!</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>A sharp, modern 9:16 vertical short about Google's new workplace Gemini AI agent. Dynamic smooth cuts, high-tech motion graphics, clean Telugu typography overlays, conversational narration, subtle ambient electronic background music, burnt-in Telugu subtitles, concluding with a credible source attribution card.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ క్లౌడ్ వ్యాపారాల కోసం సరికొత్త జెమిని వర్క్‌ప్లేస్ ఏజెంట్‌ను విడుదల చేసింది. ఈ AI ఏజెంట్ స్వయంగా ఒక ఈమెయిల్ అడ్రస్ కలిగి ఉండి, ఆఫీస్ బృందాల తరపున పనులను పూర్తి చేయగలదు. వివరాలు తెలుసుకోండి!</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>#AI #GoogleGemini #TeluguTech #TechNewsTelugu #FutureOfWork</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11577,7 +15339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11830,6 +15592,33 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌కు కొత్త AI ఉద్యోగి: Google Gemini సంచలనం!</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>u_a_B-UU-58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=u_a_B-UU-58</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>uploaded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/content_log.xlsx
+++ b/content_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O251"/>
+  <dimension ref="A1:O301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13781,6 +13781,2656 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Trump says anyone who does not refer to AI as ‘super intelligence’ is ‘THE ENEMY' - Politico</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Politico</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNaTV1aTVjdklWRlVSRk44SVpZck9ENF9lWFAxSWVBMmNZQmktWDVZUC04Tmd1aUwwM01WLVJ3Sl93XzRaRTY3S3hvNm5UMFV0MXZiQk1VU0RIR3l4aVJLZHhlSjJ0ZWdHR3Y5YndyMmI2WG9CNnNibU02QS0tWEZhd2NDeG9YYWZqenV1MVpHNA?oc=5</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T20:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="n"/>
+      <c r="I252" s="2" t="n"/>
+      <c r="J252" s="2" t="n"/>
+      <c r="K252" s="2" t="n"/>
+      <c r="L252" s="2" t="n"/>
+      <c r="M252" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N252" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Trump Warns: Call AI "Super Intelligence" Or Face "Enemy" Status - NDTV</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNeVJfUHlUeVdNMURlZFl1eDdvVlZiWjFxaDdscTFpaWF1Z0ptWHZzTXNFdFJibjBPdktMQVFKb21SNmdna0Fxb3EwZjNySWlWUWducHQwVnhjWWU1bEdqQVdieC13UUYzVG1MWklUaW85eF9oZS02T3hfWXNoS0JMZVRnaWpBdDB2VktWSXp3T3YxRUlWckRrSi1fV25rTTRseElSTGpmc3hEQ2QxWm9jelJ0Y9IBuwFBVV95cUxPY21Dd0ZKQnJfeW90WkhMeWdac3I2YzEzcEs5UXg4bzRYdWRRM1R5dnNHc0pUREcyMF91bUFBeDh2cmpjUGdqZVAtbkxmTmZfMkN3TTh2Q2pSdnU3eTRpQWVRUTJETWYyWUhlTlNHdW9CazJCSTdaajNaQ2t5aVJxelMySXpfSjY1WWlXRmlpb0ljdHlWRVBJRFZKZC1RaG02dWxwWDdSWjRiY0hlVDFNWG1tZ19MUkw3Q2Vv?oc=5</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T06:33:56+00:00</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="n"/>
+      <c r="I253" s="2" t="n"/>
+      <c r="J253" s="2" t="n"/>
+      <c r="K253" s="2" t="n"/>
+      <c r="L253" s="2" t="n"/>
+      <c r="M253" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N253" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>China vows to curb tech investment bubbles, keep AI risks under check - Business Standard</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNazFIZ2xIZWNjaXB5dVRoWVFKeElzajRGQ1BmWmx2aUM5czViZFZhSlhXQUdDaVVkOHJ1cEFfU0lablFjZVBoYV9SM1IxYWJjamQ5dWV1bWwxZm5jb01BOE5pWVBSVjNpdncwZVpTRkV6dU1KZ19VV3NVNkR4VjlSbjF1WWxrdnNZcXQ0SUdScWRITGRXTGtnb2FQazFHR0tNUFRPcEs3Z29ScUhXWmNiZmZieGpwTTNpaXJGZnR5bFNQSmU2NW9hSVlJdHlJZk5wSDdUX0VBb29fcDRKbWxONHVnUFZwc08zaHBQLVB30gHzAUFVX3lxTE1LZW15bmo0S3JJaUVPNnJKYXpHOC1Zek5PR2ZldFVFbnVpM1J2N2JxdTZnOU41bW13ZVBId3Zuc1QxRFJsb0NWLUxxRVRZQS1qeXU5akJMbFJ4bzhpa3dzdmJ1eGo5WUQ4QkNEcG05b3hvTVBXY0dHT2czMkZzNnNkVzhoOG80Um5pTk5jdWZfNUFPcmhkTEMzZmxBRzFaZWh4SFpjZmpzSDBsSlRCOW9wTS1xbDJRMnU2cFpfTUVkbWV1bVpoSWpYZ3N5QVNjcWtWejZaSW9rVnBzZWprRFVhd3R1bjhHUjF2eVRPTERQdVN5Yw?oc=5</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T17:18:24+00:00</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="n"/>
+      <c r="I254" s="2" t="n"/>
+      <c r="J254" s="2" t="n"/>
+      <c r="K254" s="2" t="n"/>
+      <c r="L254" s="2" t="n"/>
+      <c r="M254" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N254" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O254" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>AI Is Not ‘Super Intelligence.’ Why No One Should Use Trump’s Term - CNET</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>CNET</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQTWFyczBwSHVSTlFIbEY5WTJHa0NTcUxRejNxb3JzZEVIR3c4S0Rpb2Zfd1dVTjdzcWNxaXhORVlkcDhfS0FEZ3Y0Z3VpbW8tanpIb0pialQ2UWt1bjRmNk1FTVdFNUtDNC1TZzRjdWNmVDkwb3JzbjVJbjNCN3lzVU4ta3Q1THplNVREcE8yMENUT2tuSGFncDR2MVAwUlRoS1cwQ2diOA?oc=5</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T11:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="n"/>
+      <c r="I255" s="2" t="n"/>
+      <c r="J255" s="2" t="n"/>
+      <c r="K255" s="2" t="n"/>
+      <c r="L255" s="2" t="n"/>
+      <c r="M255" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N255" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>World Development Report 2026: The Promise of Artificial Intelligence - INSIGHTS IAS</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>INSIGHTS IAS</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNNXQ3S3FRZ0NFbVVCZzNZOVFQZUNMU09pMkVKZTR3blhzVE5iU185Z3N4N3F6TFJGOUlEekd4Q0ppS21sS1NqQW1XaGJSSms5NDg2RFpkaWV4blZGMGxfbGd1ejR1TnY1eEtIYjJEYTFLU0dlUnFOU3FMZ0I3UGdYNEM3Nk5XYVJteUZzYnhFSmdRdThxc3ZrRXBnNjAzQVJaeXU1aVRPQWN5TzN3eFdLdUVR?oc=5</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T09:49:12+00:00</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="n"/>
+      <c r="I256" s="2" t="n"/>
+      <c r="J256" s="2" t="n"/>
+      <c r="K256" s="2" t="n"/>
+      <c r="L256" s="2" t="n"/>
+      <c r="M256" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N256" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O256" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>AI artificial intelligence</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>As AI agents grow, vendors carve out decision-making as a separate model layer - InfoWorld</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>InfoWorld</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNRXlFZ1pNeG9pM0xtaUlJRldYeXhqQ09Yc0VSdWN3ZGd3aXMxOXhpUzFxSHpuRE1xdVlHbXUxR0JqT0tXTjFDallfNENvSkY1X2VIMXp6X0xIY3hhcnl3XzlMSGVyNjhLOUJBNkdlM1JjSjNLcVhONlMybG9TbFBuRjhJX0laY0ZYTjJWTnl2MzktZFNfaFN3MloxUUNlOTREVmZZdDFMTERyZDVNcFZWcUdBTmktUTlkSFhkemlOd0JXUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T12:23:46+00:00</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="n"/>
+      <c r="I257" s="2" t="n"/>
+      <c r="J257" s="2" t="n"/>
+      <c r="K257" s="2" t="n"/>
+      <c r="L257" s="2" t="n"/>
+      <c r="M257" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N257" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O257" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic and OpenAI’s Revenue Calculations Confuse Investors - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOYkhILXo3RWYzbS1GOWtma3NKS2p1VnhtWFE3QmFLMzhwcExvVkpYSmpKUDJXQzc3QnJUcVB2QmxyMHRaQUhrOHFLU1BmdzRHcmFNTFlvNjM1c2R4UnFweXl5TmJhZHdrSFhDSlhLYXRBRGZSZUlBRS00TGFycFFrTHI3Qk5OU2Vuc01fZURJaFUxUmZ2bXRxa0hzT2xTSThSWDJIeGtSSDFOZEF3SXBidmFR?oc=5</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T18:23:00+00:00</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="n"/>
+      <c r="I258" s="2" t="n"/>
+      <c r="J258" s="2" t="n"/>
+      <c r="K258" s="2" t="n"/>
+      <c r="L258" s="2" t="n"/>
+      <c r="M258" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N258" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>Iranian campaign planted fake articles in real U.S. publications using ChatGPT - The Washington Post</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>The Washington Post</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPQnJfdmQzcThvdk5kMkxlWXpMZlhIUXM1ZGR4SGlycFdUZV82Z1N3eHVCVGk4UnpKb0s3U2lvX3d0RVFDNnVVekhyUVhSQlJOYlQyLVpETDI5V3FSZDFYeDcyLU5nbXB2SGhmeTNBbFIzNUsyZFRFcWs0OHBZSU9IZlpkRVUwUl83ck55U2E5dkZpM1hoN0s3blJScUZaT3J6a0w4b1FOXzQ4U2JVQTREUEVyYkY5bVU?oc=5</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T16:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="n"/>
+      <c r="I259" s="2" t="n"/>
+      <c r="J259" s="2" t="n"/>
+      <c r="K259" s="2" t="n"/>
+      <c r="L259" s="2" t="n"/>
+      <c r="M259" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N259" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Is this the ‘mathocalypse’? Why OpenAI’s latest results dump has left mathematicians in shock - The Conversation</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>The Conversation</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOOWVKNnJhdE1kLXd4a0Nfd2o3UHNHRS1fWGxHa1h5UXBWOGRhYjVOUklUSy05eTJ0RC1QN3FrZkxWak5mQ0ktUkNCeldZMjlJUHlqQ054eVhCUEZWUUhFSzRJVGltcGNuNFRZMG5iaTJWQ2pKdk5PdjZXQ3BUWWR1UkJ4ZXkwb0RYazloWmxSVV9zZS1OSm1MYTJ6cGZMSTRHRFJvMDlGam1lam9QNzVwbmpVY1RIdGVkZVN5b3hZZjNfZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T03:25:00+00:00</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="n"/>
+      <c r="I260" s="2" t="n"/>
+      <c r="J260" s="2" t="n"/>
+      <c r="K260" s="2" t="n"/>
+      <c r="L260" s="2" t="n"/>
+      <c r="M260" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N260" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>"Fired For Prioritising Safety": Ex-OpenAI Researcher On Termination - NDTV</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQbnRZaE0ybmlLS1ZLdTdzc1l4RFQ5WE1BOWp2SGxEV3hyVWk2NTdWOHprWEVhY294SDBoZnNLa1JFWVJjU2I4LXpidU1PN1ZqU08zTnRPdjhXdUsxbmpidFcwclJxeVhmYkhqTUg4bFhXbnNIX3RXMmtXTGdzRkZNRGF2MEM0OEZ6elFmUWdpODdFNVpHeEFQWk1ZczlTWUtxMXlLVDZfdWVMRTJvN0xvb0ZPRmlEZEhtWUdJ0gHDAUFVX3lxTE1mMy1BTzJ5ODBKdHIyWkxudmN0anZtS1V4YXIzZDB4RFQ3ZWJ0aW4wQkFzcllhTVo0cFVQby1fYlBWR2xzRUdOTXZvWnRJSGFwVEFPckFKcnFUYm53eTlONDc5Y2dLN1dDcTZFRjc4UVlvX2NLdTB5ZkFoS1puQ2tFcV80cWFmc1RvWndrd2hKcEI5VXA1c2tycktkbzZSQ3V1aHNuOXdkQUdaOUppNkFyVXpvdS1YTEVXRHQ5YWN6UVJLQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T06:02:41+00:00</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="n"/>
+      <c r="I261" s="2" t="n"/>
+      <c r="J261" s="2" t="n"/>
+      <c r="K261" s="2" t="n"/>
+      <c r="L261" s="2" t="n"/>
+      <c r="M261" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N261" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI defends decision to fire researchers: 'These decisions were not about raising safety concerns or speaking out' - CNBC</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1wMV9xZFhmR3pKa0w0eUxVR05NSlYxSlRjVmlXREZ3bWY4aUFuamg3X2M5bU9hVkpPQnlKeTVPbnVmYU1rR012Q0ZWVzdEaDY5eXJnUVQwT0ZGZ1RjUURtVUFmVXdqQTdodXgyT2xrMEpRQlJkcVNmZGNJWFJRQdIBgwFBVV95cUxNeFVha3o0dWozOUxKZENDNUEtbU9GNlV4b3pYUGNrM1dCd1hTVVZueHQtNkJDbkNiV2M4dzBJdzByYVBGTUljZXBWSTNrdVloTzRnSXdJM0lNelZ3a1JvS2ZKengzYmRJM2tRc2VIN1E2bDRtNjJYbENzUlUyb1BFc1Jndw?oc=5</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T07:23:48+00:00</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="n"/>
+      <c r="I262" s="2" t="n"/>
+      <c r="J262" s="2" t="n"/>
+      <c r="K262" s="2" t="n"/>
+      <c r="L262" s="2" t="n"/>
+      <c r="M262" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N262" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI fires three researchers over data breach, denies targeting safety critics - Telegraph India</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Telegraph India</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPRU5FYk9DRE1ZSFJJV0k5aW9rU2RueWlHX3BHWE13ZnA1eE5rNDA4eUNZVm96LWJpTV9RaFZWMDBnb2FmZUV1ZWpZRFNYRWtVNDE3Y0tjOWdnNjJGNUxFdnJmUmRLbkw1VWhUN0pJVWxiUGh2WU9qdE5BNTdhSHBVZE43V2N3ZDM3YXB1YVp1aFY3YmZMb3dtcEJJT2ZXa3dvTEJwQW9kQ0gxMnMwdzM2SkZRTjg0aHNsLTl1VVkwMG44Tlp5QXhj0gHMAUFVX3lxTE5yOHN2N3NQeVAxS2trbEZqdzZSVWpORmt5akpjX1huelQ2VUZwSTVMeE5HNVZ1dFFmN0M4YzlPX3Brc0IxbTlJbEQtUmhBVG13OVoyTTZhUW9OYVV2azFnVEgwdndocmVzbDB3TU04NF9hN3dQTTNPWDA4RDFoSEF4Mmh0aVJkTS1xd2htU3BYMEZ1UTdIMjU3QzJIMVhoaFZsWnB4YnlGdzVoUzFMaW1ld1NMZEh6Um4wdTVIalVkUFRUal9FZHFscHhjeQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T07:14:57+00:00</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="n"/>
+      <c r="I263" s="2" t="n"/>
+      <c r="J263" s="2" t="n"/>
+      <c r="K263" s="2" t="n"/>
+      <c r="L263" s="2" t="n"/>
+      <c r="M263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Meet Mark and Sam, the AI agents that ran my errands for a week - Scientific American</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Scientific American</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRzYyb3pnak9jZEEtMHhVMFo4d3ZUTWpfSzZ0b0NwbjM1ZVFoc21hUWxuX2hCYUNCbHEydUswMnNSVjdFdnFDUF9Mc2hTd25BZ2F0bGEtTWQtZmNYclZXd3hEd1FuZkZCOGlPMExlbVlLTHNhcmtkaXVBWVlNeld4U3lmVjFCSTFYbVpfNFNKTjVjeTNkZG52cC1hZENvMmRCTVBUWA?oc=5</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T12:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="n"/>
+      <c r="I264" s="2" t="n"/>
+      <c r="J264" s="2" t="n"/>
+      <c r="K264" s="2" t="n"/>
+      <c r="L264" s="2" t="n"/>
+      <c r="M264" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N264" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Why OpenAI shut down ChatGPT accounts linked to Russia and Iran - The Times of India</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQbEg3M2xnWkNMRGN4Y3NkSHF1NUVWZ3o4Y1lWZDhPaUgwbXRtdEp0S1JSSHFrWWZDUXpjcTNjQ1otU0JUTmV1a2tvWVdfa2NKQjdiWUgxb192aGwwNjVBSWVYUko3OHBaZlhJN253MThwYlFfX1Rta2pRSGNnTUJ6cjFjVzJyZjJJYzNLVXlxWmxVNGFmZVJtNFd4c3pXYTNXV1hVbGttWC1RajBpUEl5Vm93QU5aMjZTY0hQTHlnMWZVdHNKMVpyc3RqMUhFdHZkRFhsNkgyNjk2LXlWQ2fSAeMBQVVfeXFMUEV6NXRJWTBvUVR1MkRvMUtxVTlkcFhqRjM5MElKcXl2dVZET2JuVWFIX3M3YmlzYVNaY3JoRW9nZDE2eEtGZEdUS1VBT1hENTlJVTNJUDRMOWw2b1d1WkxMclBkRVZ1M0oyZ0hiT0ZJRkdRQ1hVcDY3Z1BibXJwemQwRHRlbWJTYXAyMG5wNUhnMkNRZ012MVpWZEJPd1NhbFc3SGtMNkh0WXgwQm5lU3FXS29JRi1WUEM0WnMyOVM1Tzc4T29PZlpWMTlkRjNlaFpsa0thNm4tMHhyeVZId0pfajg?oc=5</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T10:44:00+00:00</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="n"/>
+      <c r="I265" s="2" t="n"/>
+      <c r="J265" s="2" t="n"/>
+      <c r="K265" s="2" t="n"/>
+      <c r="L265" s="2" t="n"/>
+      <c r="M265" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N265" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>USA Today vs OpenAI: Key questions over ChatGPT training data, news copyright and whether publishers should be paid for their work - The Economic Times</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwJBVV95cUxORjhDUWNteE5hY2d6bVFjRmhndEg2WHlvT0s1TDZQYmctbDlhN0otUWM3bGJiaURDM2drUml6RFZtajgtSV8tVk53bjFpdjhkeXV2R3g1Mk1iVlAxcUNkQk9LMko1ZjBueWFIUmVONWt0LTkyZ0t3dkdGZEhLbl9zV2NCRWlBWXczLU9Xb0VEWjdwN3VCMlIyVVhtSE9pVkx1VVJCXzc5dlJ3RXhDTUpMMHItVDZ1RmFJVWpTRGkycGdJdzJYTDY4TDRfdjZDazFwaE10UTZ6cXZLN19pTGJhWjVjZ3RmZHgybXJReFFDcVc1ODAyWjREU0I0VXFUd1VIMDdZenZuQUFsUlIyNzlLX2d0a0FobUFFLTliT1VLNmxtbmNkOWx3VFBWM1JLd3VqRnV6TmFFUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T15:48:23+00:00</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="n"/>
+      <c r="I266" s="2" t="n"/>
+      <c r="J266" s="2" t="n"/>
+      <c r="K266" s="2" t="n"/>
+      <c r="L266" s="2" t="n"/>
+      <c r="M266" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N266" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia, OpenAI and Anthropic pledge $2.4 billion for US AI research - YourStory.com</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>YourStory.com</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNeGgyUHVHMDBVZFJZWXFwNFJuak9pYTJRcGNLdXJxbktFQ2l1ZlRQLXdSTS1DbkRrMGd3dVR4T09fdTBYeHFURlBnWlBCQWtER3FzT1NrbDBFSS02ZzR4OGcydUxfMTJsenVuajZ1LW1TbUdfWVZrU21jWjNySWM4Yg?oc=5</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T10:22:20+00:00</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="n"/>
+      <c r="I267" s="2" t="n"/>
+      <c r="J267" s="2" t="n"/>
+      <c r="K267" s="2" t="n"/>
+      <c r="L267" s="2" t="n"/>
+      <c r="M267" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N267" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Dow Jones Futures: AI Stocks Rebound From OpenAI Slide; SpaceX, Verizon, Delta, Apple Early Movers - Investor's Business Daily</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Investor's Business Daily</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPczNHYzZJZHFGenRVQ2RiRmR1a1V2N2MybzBuRnFtcm52UnBPYnd4WTByZHhIeFZ2ZHJ5eG5ac2VyQkd0dTN6Rm54QTVMNWJxM3l1VEFPRndhNV9TUXN0dXAtZ3ZOc3UtZV9kN2JxWGpONGNoem13UEpHR3FJMTFMTkhNQVhKYmpuN0FuYlZ1bDctQno5WDRnUHpxbkNhODBpdDhOcllqSGtlaUU1Sm5ISGFWWnUwamlZYjJDLUdka19kQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T12:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="n"/>
+      <c r="I268" s="2" t="n"/>
+      <c r="J268" s="2" t="n"/>
+      <c r="K268" s="2" t="n"/>
+      <c r="L268" s="2" t="n"/>
+      <c r="M268" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N268" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Google Cloud introduces the Gemini agent. - blog.google</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>blog.google</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNWjF6SjVJTks2WEluZXBwbGtRZEQtNGpZTWNXLVBrRHlCMVNhNlVRb2JDT1NsWlNHekZ6d3NQU3ZmcnNzazE4bF9hNXY1QmNNRENTcFFWNzlicXoxN25CMHhob0dMOUJ2UmluQVl3X1Fic1BZS0lIcXI4U2JuMElvZlhVTnNiYzkxb1BLaDhOTXdpdkNQeGc?oc=5</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="n"/>
+      <c r="I269" s="2" t="n"/>
+      <c r="J269" s="2" t="n"/>
+      <c r="K269" s="2" t="n"/>
+      <c r="L269" s="2" t="n"/>
+      <c r="M269" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N269" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O269" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Gemini was down for some users — live updates on outage - Tom's Guide</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Tom's Guide</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE91d0dUX2ZaN3M2Y2kycE15cUZZQkhuQzlOTU0zTmVVUEROMjBXMkZYODRWU2RPdV9FQWJqdXlzd21YMEgteDdBYjhKdEJGSnA5UXVMUlFieDVpWk4yVFhuNWNXOUZlaE50bUhoUVFKSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T17:26:50+00:00</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="n"/>
+      <c r="I270" s="2" t="n"/>
+      <c r="J270" s="2" t="n"/>
+      <c r="K270" s="2" t="n"/>
+      <c r="L270" s="2" t="n"/>
+      <c r="M270" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N270" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Gemini Flash-Lite for free users; effort can ‘use more of your limit’ - The Next Web</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>The Next Web</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5BVWpwelRNSUxjRU5EWks0NlQxdFktb0VIMG9ienoxUWxjdGN0YXlTT19yd3E0VEJPcUZLdFJaaDVpc055MWZDdUdPQlVMVFhrYWp0bW5mOVpJb09WWTZvdURTSGpfWnZ1RGotblZPcXBodmx5UXlHd0hFZkY?oc=5</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T12:20:26+00:00</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="n"/>
+      <c r="I271" s="2" t="n"/>
+      <c r="J271" s="2" t="n"/>
+      <c r="K271" s="2" t="n"/>
+      <c r="L271" s="2" t="n"/>
+      <c r="M271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Is DuckDuckGo AI actually a good alternative to Gemini and ChatGPT? I found out - Android Authority</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Android Authority</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNaEt4RVgwU0xfWU9ucUk0MXBmMnlhMWxQQnZEamZOY1M2R19Zd0ViRFh1LTYyMFFVcVNHZUtNMkplNDZvZTFSbmg1MVh5VjNEMDVtLTVfd05YQ19Idm0zdFM0Zm5UaXBwTXRPM2NnWDkwY0dHOF95dG1KV3pVaHVoV0xfWDZWYUg1NENzMUFYYjhnYkl0aVE?oc=5</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T10:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="n"/>
+      <c r="I272" s="2" t="n"/>
+      <c r="J272" s="2" t="n"/>
+      <c r="K272" s="2" t="n"/>
+      <c r="L272" s="2" t="n"/>
+      <c r="M272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N272" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Is Gemini Down? Here’s What’s Happening With Google’s AI - Revista Merca2.0</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Revista Merca2.0</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNOFd2eV96X3dMQzU5UTJkWnRHeld0R2pLak42eDdpbTlXREpnZzhnNU5VQ1VhU0VMWnFwNUZBckVOU2l4XzZEc0tSX2s5bmt1S3daUC11dmlhUWZ3Y1pMVGQ0MDh5UThsNXo2X3JCYTU0U2VSYlBMX3BiWjREaU1KdklYTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T17:53:43+00:00</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="n"/>
+      <c r="I273" s="2" t="n"/>
+      <c r="J273" s="2" t="n"/>
+      <c r="K273" s="2" t="n"/>
+      <c r="L273" s="2" t="n"/>
+      <c r="M273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N273" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Google’s Gemini AI steps into the workplace; has its own email address - HR Katha</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>HR Katha</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNdHRCcmswdDdvTlZsUDhJbFhleExnakFlYXVHaXFlMUZoWW1tQlcxOWdaV3dzeVJselRwUmx6SzlTNlJKdlhLa09tY0FBTnkyaUcwWk9KY01YVHZ1aVYtMHpma3lzUThwZUhkQ1A1WkYxbndYUFdlZ0ZXUm1uTFFteE51VS0xd3dSQXNPZnFtMXMzcXlzdWdBelBZWHh3VFl0SzJJeXRYUVZfTF9MdGdNLWViQmdRUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T04:51:09+00:00</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="n"/>
+      <c r="I274" s="2" t="n"/>
+      <c r="J274" s="2" t="n"/>
+      <c r="K274" s="2" t="n"/>
+      <c r="L274" s="2" t="n"/>
+      <c r="M274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N274" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>Google Gemini AI</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Google’s Gemini Agent Launch Signals a Consolidation Play for Enterprise AI Infrastructure - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQY0FIVmhIVHltcm9YWTVMSnVWbk85N3hIRXItczdlcUdXMmxWQlB5Mzd1czBBVTVBc3l0MkN5bnNaTHM2RGdwM1Q2YlQ4X0FjTzRvbkR0X1Fla0hWaXl3bFhyX2htbV9hYUpPVWxhclZWc3cyVVNBRHE1bDBRdU9sQUR2YTVoeEtuNWdBb3U2OGRrVXozWXNZQWJGMGlpTkk?oc=5</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T14:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="n"/>
+      <c r="I275" s="2" t="n"/>
+      <c r="J275" s="2" t="n"/>
+      <c r="K275" s="2" t="n"/>
+      <c r="L275" s="2" t="n"/>
+      <c r="M275" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N275" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Opens Copilot AI Access to Family Subscribers, but Here’s the Catch - Analytics Insight</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Analytics Insight</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNQ3Z6OWt3OGdQd2c2SVE0amZLS1Rhc3dEeGNhSUM1aGo0RUYxQklDd0RlTndKMUduNkV3aUNGNmhqdVlTNlJFMEdLV1RxblV4d09rVWVCeEI1aWlGRm83NU9BbE5iVW5VdjhFd05PV25aVXB0OXV1eWlxaVU4ZmYwVDFWQTBuS2pGUUdENzQ3X29rOG9Xek03b0w2OVFzYzF6b21SRXhTS2VabjBXV1AzR1REMNIBwAFBVV95cUxPRGRkb3YyMG5rbDdjTVdrTEo3eDdtTGRfOHl4TmhLbjRDbEdMTkJhbmFzXy1ISG1vWTdrbDV2bVBaU2dhWGh3LXdPem1OQTA0UVhwRk9WbTkxVTRVbzNrOGo4QS1UR1F3MzJ0R2dxdlViVmIxOG4xUUxJU1NDVG1iTzlfVDJpbkhMNnhXb3ZVT18tU19kWWVQdWEtcVd5cy1mVnIyc29mdWFsSHBSbFg1QzZzdWJpNFF2RWxxOUU0Vzc?oc=5</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T17:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="n"/>
+      <c r="I276" s="2" t="n"/>
+      <c r="J276" s="2" t="n"/>
+      <c r="K276" s="2" t="n"/>
+      <c r="L276" s="2" t="n"/>
+      <c r="M276" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N276" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot AI</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>KOHLER achieves 98% Microsoft 365 Copilot adoption with AI change management strategy - Microsoft</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPY2VBRjc3MXNDM2MtTXZVTVhOV01IdDI3SVlNeXdpamVSZU9KQ1JJbWpPRk9aUXk3SXNRV3pqczJUWnNoQnFpa2MyWUNDNUctVTF3YlRTZ19seTZfbUxWUXZVZXd3X3diMzBrM1hDSlROamdxM1Q5WVNNYUM4Vjl5TTJqLVNQTWg1UERLdi14cng?oc=5</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:04:50+00:00</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="n"/>
+      <c r="I277" s="2" t="n"/>
+      <c r="J277" s="2" t="n"/>
+      <c r="K277" s="2" t="n"/>
+      <c r="L277" s="2" t="n"/>
+      <c r="M277" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N277" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Scrapped IPO of Nvidia-Backed Company Points to Limits of AI Boom - WSJ</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPaWFkcXdfaE16UDI1bFo3blBEbDdtT0NRZjN0WkR3aTczRHBBOWJmMTI1empxRm5MRU9nMHRITlNWaGl5Zm9LZk5KTVhyWHdWT2NteXJxbUFxNUZSSFVtbWtYanNaa0lUTHBjdF9zOXBBX0JlYUFOVDBKSlpQeWYtUzRFQjJuMWs5dHlkUk9RdHBvQzNHNmUtSWszNnhwZ1pjX3MwM3hLY2FOMGZrVVE?oc=5</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T07:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="n"/>
+      <c r="I278" s="2" t="n"/>
+      <c r="J278" s="2" t="n"/>
+      <c r="K278" s="2" t="n"/>
+      <c r="L278" s="2" t="n"/>
+      <c r="M278" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N278" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O278" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia-backed Aussie AI firm Firmus withdraws historic IPO, citing market volatility - CNBC</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9tMmdLRHRyeDk3OGFjdHA2YkJjREFLZDNxNENsWFdpN3cyOW1xQTRkRUtvY1YybXg4UzVwNUw4R1hUTFFDVVFibTRIX1RVZTc3MGZzWTN6ZmxNWndfcFpyVVZXRFNLV2tuSEHSAW9BVV95cUxORUQtcGkxbXJITWdJV2NCbUtWbEliczgzdHhTbWVXX2Z4blcxdy04TmxseUZYOXh2ZjlCYmY4b0FKZ2sydnZaLVJvcENoVll3MXN5aktLRkdWWkRORU5xbGtHQzFyQzFnLTBCSzBJRVE?oc=5</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T01:02:00+00:00</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="n"/>
+      <c r="I279" s="2" t="n"/>
+      <c r="J279" s="2" t="n"/>
+      <c r="K279" s="2" t="n"/>
+      <c r="L279" s="2" t="n"/>
+      <c r="M279" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N279" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O279" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Firmus: Nvidia-backed data centre firm scraps IPO as AI valuation concerns deepen - BBC</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>BBC</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9wdmJBcVhNX2h2UWN5a1k3eElWRFZzYnVRcXd5RmZ6YVhhbUQxa1RrMjBlVkx3bkstTmw2M0FsTHlCNTJwbFpUVFdJQlMtd09SdF9fTHRYM2lOdTA?oc=5</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T07:14:30+00:00</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="n"/>
+      <c r="I280" s="2" t="n"/>
+      <c r="J280" s="2" t="n"/>
+      <c r="K280" s="2" t="n"/>
+      <c r="L280" s="2" t="n"/>
+      <c r="M280" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N280" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O280" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia-backed Upscale AI launches platform to connect chips from rival suppliers - Reuters</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPeGdkZHlKUjgwWHQ4eXRUaTJZeFZBQkFLaENBNFYxTUh5SVFkaWNfVGh3MUtrcGdKYjZhWk03QlV1WV8zYmxkbl9fLVRIa0xwWlczbVRwVlRFUGZwMXFwM2lRck5BVmVhQ3JmVzNZS3U0OUpuLVdLU04wVVlkNE9jN2IyRW9YY0pla283VmJBa3FpVm5zX2xaQkw0X3JCcUx1djhraTRVTEQzeGJtNzZKQ3hLTHRRSUEt?oc=5</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:01:28+00:00</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="n"/>
+      <c r="I281" s="2" t="n"/>
+      <c r="J281" s="2" t="n"/>
+      <c r="K281" s="2" t="n"/>
+      <c r="L281" s="2" t="n"/>
+      <c r="M281" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N281" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O281" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia to Invest in Chip Rival d-Matrix as Its Challengers Choose Partnership - The Information</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>The Information</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPRmt5MUVxdjF6M2V6QlZPWVZyWVgwUWY2QzBiVE90elFIQ1Qxa0JYZVpEYmNUQTIwWEg4UzR5NUo3YWRSdEZzU0RoVzV6V2ZoVFJCYjBScWZ5Z29LVFVMTUJYTm03WjBxZFBmMWN6clFzRDlDamZ0N2c5dU9vcVBELTNwTmtIS3RDZ3h3czlyaElqMVQteTBWM0hObm5MN21iVTNmalRnbw?oc=5</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T23:24:00+00:00</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="n"/>
+      <c r="I282" s="2" t="n"/>
+      <c r="J282" s="2" t="n"/>
+      <c r="K282" s="2" t="n"/>
+      <c r="L282" s="2" t="n"/>
+      <c r="M282" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N282" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O282" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Wall Street is inventing an entirely new financial system around Nvidia's AI chips - Business Insider</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>Business Insider</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPMEpqbXIyV2NmNG9fQUpudG13WWZUbUJMdlQxRU51Qy12cTVEUlNYZlp4d3J5dkUweDhhUURFUDVPYlFWLU9pNlJfd0FkOEFkb2JWQ1FOcUJTYWJZeDJFQzJEdHpxVkk0bkNRVDJYdUI4YXRSVlFfNjZyUUxUQm9zRU9uY3dNa2ZkcDBfWHhNQlIxRkZ1Y2JF?oc=5</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T09:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="n"/>
+      <c r="I283" s="2" t="n"/>
+      <c r="J283" s="2" t="n"/>
+      <c r="K283" s="2" t="n"/>
+      <c r="L283" s="2" t="n"/>
+      <c r="M283" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N283" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O283" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia’s big bet on physical AI aims for safer robotaxis, humanoid robots - Ars Technica</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>Ars Technica</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPVFdGb2V6YWlNaUZ2Q0MzSzI1d3o5X0ZRa2xCckNpX3NnTk9pMnJWMTNwY1Z4STB0QTZaTFhCQVNnUjlFLXlNbUJOejJ1aEYtTVFlcE81QkJjbXdaQnIzVHdxZ3pQeEI5NGNXNE4wMzVuRjRpMC00cDlCUHRteWpyc2tidjRzSlFkaTJUakdIYnBGSGhsN3dZM2VXUGlOd1RzVEs3elhCS0NWSG8?oc=5</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T11:15:33+00:00</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="n"/>
+      <c r="I284" s="2" t="n"/>
+      <c r="J284" s="2" t="n"/>
+      <c r="K284" s="2" t="n"/>
+      <c r="L284" s="2" t="n"/>
+      <c r="M284" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N284" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O284" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA AI</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>Micron, Nvidia and AI chip stocks fall as report on OpenAI’s revenue causes ‘undue concern’ - MarketWatch</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>MarketWatch</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNOFhHOU9ES2xuX2Q1dWdTYVRjS0lGQUI4ekV5T1hzMGhzNF9mVldoSkVPTmE0QjdPakdnZ1BVeXU0bjZkSWhQMEVYNDFaSWstZUFNS2tzeUxUdFhmVWloVTFTNWJLejNKbEZOWjVCS3d5Y24tR0tFRXd5TlZGN0F2b1ZQN0NoUnE3UVhqaGhqZkNNRVRGMzZrNktSTDI3UDN5WENtdVByempvU0R6blZ3TlZIcmwwU05fcERjblBSeUNkVWk2VUd0bzNn?oc=5</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T22:08:00+00:00</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="n"/>
+      <c r="I285" s="2" t="n"/>
+      <c r="J285" s="2" t="n"/>
+      <c r="K285" s="2" t="n"/>
+      <c r="L285" s="2" t="n"/>
+      <c r="M285" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N285" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O285" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>Agents are shaping holiday discovery—brands that feed them win - Ad Age</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>Ad Age</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPRVdnNVk1bzAzMnh0eE16YVdPOWQ2M21McHVnVkxxRjRHVzRvMTZsVU9VcHVtZmwyNjhjUk9lM2pXdWw5eXNSWmhudlJUcDRuSUFJRWdLOENGMGlIYmlhdllOVHJsQXA0V1hpa2dWUkRKUTBleW4tTm5fM1hhVmFDUElqQ3Nrc192LTJpSGVBMUpsZ3lo?oc=5</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T09:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="n"/>
+      <c r="I286" s="2" t="n"/>
+      <c r="J286" s="2" t="n"/>
+      <c r="K286" s="2" t="n"/>
+      <c r="L286" s="2" t="n"/>
+      <c r="M286" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N286" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O286" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>AI agents don’t take coffee breaks. Can India’s networks keep up?| Ciena’s Gautam Billa - The Economic Times</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQMEtNNGJ3RkhxTnlTNGZfX3B1TTNpWWdCRUx3TTFNZUhLejZUdjdTT2xuVjNybklYb0QzalMtaWN1U1Z4cXRISS00bUpxb3VpWWhQanIzRjFTajdmbTJuc3ZpM3ZjNjV0ckVWNnZpc3k2bmRUS01hN1ppZUxfeFpMY3lQMkJNRlBqcWpnT3cyUkNRQmI3N3g3Vmotb0tKUWNSM2FmbFVhdnBtMGw2d0xrX2tidHpQNzNsMkEtLUN5NzRrNDlSUkMwa3BBUXhwYWZiS2ZuRjYtX2MyOXRtbWpmdHln0gHnAUFVX3lxTFBzUFViX25sWHVIX2IxVHA0MVhJeUVfY3l0ajdBUHZSUmNQNDJQQ1N1UWVaQVFFS1pKcjFKRE5pc2hHTW9PVFo3MUdnQkRWMUVvQVlYZkVYa2dIUGxHdlNIaGp6bXJMbHpZVm10ZHdlVm8wYVRHZkZfSWpWOWNiaGY3SFJUWWxQWUFhcjZ0Vzd6Ry1BSDIzclV3REpzOURQYjhlY29PYmVWaTV1c3N3YUo4VnM3a3owTlg2VWRjUUstcjNrUVBlMEVwS0wwZV9NcUJnSlp2aHhHSmNCSHcxdVpHb0cxcDN6dw?oc=5</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T09:28:13+00:00</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="n"/>
+      <c r="I287" s="2" t="n"/>
+      <c r="J287" s="2" t="n"/>
+      <c r="K287" s="2" t="n"/>
+      <c r="L287" s="2" t="n"/>
+      <c r="M287" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N287" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O287" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft previews next era of trustworthy AI agents and Surface Laptop Ultra - Mashable</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>Mashable</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQWTlRN3ZXRmx1dG1MNXhyVFRVeU1td1BXRHhvU3BZSjZOaEZSYTJGU3JWamN4dmxiUkh3NUJaUGE5ZVdOS05LQjhBcjBrVUlnamRCekptaGJwZm85TEdWV1BmWmxhWGpZYUtGWjFkOU1ybzJzbUN1V3g5aEMxQ09IODR0Vl9xMFA5?oc=5</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T11:25:15+00:00</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="n"/>
+      <c r="I288" s="2" t="n"/>
+      <c r="J288" s="2" t="n"/>
+      <c r="K288" s="2" t="n"/>
+      <c r="L288" s="2" t="n"/>
+      <c r="M288" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N288" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O288" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>The AI Velocity Paradox: Why Security Is Decades Behind AI Ambition - The Hacker News</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>The Hacker News</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPOE5UTi1pc1ZoT2NjUUNIZDBJbWdObzB1bFFkbGtqckIyQy1MdERrOFVDUzJ0ZzF4dHI5SG52cXhEdC10dUhsZ3NLSkNTOGh3S0t5M3RsTHNacXpPSmc2Zl9OZjZzckZVOEZZSXh0VHE0WUdYWXh6bE5RcHRELXNSRmF2WGk?oc=5</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T11:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="n"/>
+      <c r="I289" s="2" t="n"/>
+      <c r="J289" s="2" t="n"/>
+      <c r="K289" s="2" t="n"/>
+      <c r="L289" s="2" t="n"/>
+      <c r="M289" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N289" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O289" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>AI Agents Look Beyond their Containers - Communications of the ACM</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>Communications of the ACM</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBmNWJNdlJxbm82RUVxX2Q3UlpvZHBoX2JHT2wxMThGNE9DelJ5Q0s4RUtGX3JuZ2xOQlpiS3ZQSnk3NFNXTDVHQTgtdmtGa2tHUWdGb2ZjeFRNcG1FZExzSmhiVHhxT1FMMVg2OS1yM1JvRW8?oc=5</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T17:43:06+00:00</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="n"/>
+      <c r="I290" s="2" t="n"/>
+      <c r="J290" s="2" t="n"/>
+      <c r="K290" s="2" t="n"/>
+      <c r="L290" s="2" t="n"/>
+      <c r="M290" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N290" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O290" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Natura’s Interface Smart Ring Puts AI Agents on Your Finger for $99 - Gadget Review</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>Gadget Review</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQN0Z1algtUko0MVFKampVUTRWM0tFR2VjYzA4MndGUEVsTURxTnVwN2E2Y1NxdThGMklGUWhTWnVDUEVFUDRNdmZ1MGFQMTVXVTEyRUhLWUliVEV2Yng4dmNocHhwRnZhZFJCNld5enV1cEl3dW1CanZoenpBbHExb3RndURXNG10cnRYLXJ1WFdod3Y5VWMxQlpB?oc=5</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T14:37:21+00:00</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="n"/>
+      <c r="I291" s="2" t="n"/>
+      <c r="J291" s="2" t="n"/>
+      <c r="K291" s="2" t="n"/>
+      <c r="L291" s="2" t="n"/>
+      <c r="M291" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N291" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O291" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>AI Code Refactoring Doesn't Have to Be a Guessing Game - HackerNoon</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>HackerNoon</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxObVJNQ2dwcnVfMV81Y2Z3MXEySFJmOHhRbTFhM3RBZ2JhRFVBVWlvQ2xzaTRWUnFXR003YTE1M3J6RF9fWFRwV2h3XzVWMzZaOFBoaTRCT3AyZURVd2Z3NHpyb3ZLQnUwTTJjdC1jYkEwaU9aN3I4NDg2X3VfQ0JCQ3NB?oc=5</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T06:19:42+00:00</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="n"/>
+      <c r="I292" s="2" t="n"/>
+      <c r="J292" s="2" t="n"/>
+      <c r="K292" s="2" t="n"/>
+      <c r="L292" s="2" t="n"/>
+      <c r="M292" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N292" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O292" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>10 Free AI Tools That Replace Expensive Software for Data Scientists - KDnuggets</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>KDnuggets</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOTWZsYndCWS1OQUlsb25XaERBZTdCbE12S3ppTWM2dURnM041Nms2dVN2bVBKa0Q0Ymt0QmMyeDNXUEx1cC1PRGpYbmJuSTNSeTVBMDRYWHdQUFRNR2RjOTdkUXc5X2dmZU8wWjdWVlNpd2ZuYi1acXAzb3BPTWlENFBLejZlUGlOSVo3dFFmM1ZnS3duZzcxTDdB?oc=5</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T14:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="n"/>
+      <c r="I293" s="2" t="n"/>
+      <c r="J293" s="2" t="n"/>
+      <c r="K293" s="2" t="n"/>
+      <c r="L293" s="2" t="n"/>
+      <c r="M293" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N293" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>CrowdStrike Uncovers Suspected Chinese Hacker Using AI Coding Tool Against Banks - The420.in</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>The420.in</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5ha05nWUFjOEV2bWUwZmN5MFZNc1I5Um1sRmhrYmR0dFdnQmFUR1J2WFRuLUM2SWxPUE5sTVowc2t5eHl1TWRBLU1TM1Z1b1diQW1LMjlNS2FFLTFoMk5sUHY0dTR0QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T03:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="n"/>
+      <c r="I294" s="2" t="n"/>
+      <c r="J294" s="2" t="n"/>
+      <c r="K294" s="2" t="n"/>
+      <c r="L294" s="2" t="n"/>
+      <c r="M294" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N294" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O294" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>AI coding tools</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>The Maker’s Guide to AI Coding: Build More With AI - Elektor Magazine</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>Elektor Magazine</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE1VSmZIMlJ3TUpmT2xJUW5yM0pudFRpLUZjTWFCTW9tSHV5VExyUGNwdGpkQnBhX3VaakpfY3hyTE5ZdlVmaWRTTnp6eWVSNy1Ldzh4WnBRcC1MejdFTHFOcnM4YnlWdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T16:31:00+00:00</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="n"/>
+      <c r="I295" s="2" t="n"/>
+      <c r="J295" s="2" t="n"/>
+      <c r="K295" s="2" t="n"/>
+      <c r="L295" s="2" t="n"/>
+      <c r="M295" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N295" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O295" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>PhotoCraft is an open-source, AI-built clone of Photoshop - OMG! Ubuntu</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>OMG! Ubuntu</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE81MUk1dEFrQi02aGdXWUNONnlyTVZIeklDTUk4cWVRSExheV9mdVg3QXQxNThDd0htNEl0dTgzMXF0RXo5dzFoZGpDc1BqMjN3YjZFdTJqMmc4ZXQzZFpWMlpZOUtUN2hqUzNUMzhWd21yODB0XzNv0gF8QVVfeXFMTmpaVmZmZmx4LW04c1BwdllBcFhWTHdDWnFLdUdTanpkdnJscXhvTUI4bHltaWRUYzdrckhPVHhjUjQ4ZmlGWFZXQ2dsc3hoRnZfYkc5bWV1b2ZidUZSV1M1dDhZRk9KZTJkU1FaRmMxQlNXNGZCVEhsOUU2NQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T20:44:35+00:00</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="n"/>
+      <c r="I296" s="2" t="n"/>
+      <c r="J296" s="2" t="n"/>
+      <c r="K296" s="2" t="n"/>
+      <c r="L296" s="2" t="n"/>
+      <c r="M296" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N296" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>open source AI</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>“Don’t use ‘open weight’ and ‘open source’ interchangeably”: Percona CEO on why AI terminology matters - The New Stack</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>The New Stack</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1ILXdrUGYxc1p2UmhYNmRYM0tTdFVCaXp0eG9yWllvazRQWmpTRXlpczJ3dlplNWxEX0MzTmljN2lwOW1BVWNEUnBRVzJldGthbkFlY2tHaHYxamhZa3NR?oc=5</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T15:11:56+00:00</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="n"/>
+      <c r="I297" s="2" t="n"/>
+      <c r="J297" s="2" t="n"/>
+      <c r="K297" s="2" t="n"/>
+      <c r="L297" s="2" t="n"/>
+      <c r="M297" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N297" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O297" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>5 Steps to Create SimReady Assets for Robotics with Frontier AI Models - NVIDIA Developer</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Developer</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQb29oVGtZV3BUeFkwcENKZHJ3UmtzaTAtdXFkU3FfWDFScVo5VnlJRkt3QU0xaVBKRVItcjVndjZaOFFKOWJtRWQ2N0k4cHdoYl9QX2xaY0JIaktfSEJyT2RsVXRVSDZ5SmFTaDZRYnBtbF9EaVJCS1ktVU9pQUs1Y0xaSUtGc3dNcFk0UXhEQkh4NV91OXZ1cEJBMTlLR01NVExxaDdFNXc?oc=5</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T21:33:40+00:00</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="n"/>
+      <c r="I298" s="2" t="n"/>
+      <c r="J298" s="2" t="n"/>
+      <c r="K298" s="2" t="n"/>
+      <c r="L298" s="2" t="n"/>
+      <c r="M298" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N298" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O298" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>AWS launches open-source Physical AI Toolchain for robotics - The Robot Report</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>The Robot Report</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxONFJjZmtncTEyUG43UjRhdVRJLXowSXdJajRTUm1WbzBsakc0ZnN3SUYtVjF5TlliYmptakNpSk5RUUxCd3ptM0FlbUhlTFllOEJoZnQyYTNraWhobWJpMWpzUXJSSjYwRjJOaTdaNE9RN3V2REg3VVMzT1hoQ3ZGak53RVVmYV9YMmlUdlRUMVNmWkQ3TUE?oc=5</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08T13:40:17+00:00</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="n"/>
+      <c r="I299" s="2" t="n"/>
+      <c r="J299" s="2" t="n"/>
+      <c r="K299" s="2" t="n"/>
+      <c r="L299" s="2" t="n"/>
+      <c r="M299" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N299" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O299" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>AI sector gathers at Ai Everything event in Abu Dhabi - Anadolu Ajansı</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>Anadolu Ajansı</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNVFNqUDRPMm1RdktpcHVSR0Zrem1zSERMc3FKaDh6Ym96T3dEeExiUlFBNGhZRVJzMnhBN1JwNWF4bzktX1RQZUZuQ01RQm5VcXFFTnhqTHUtaXNBMUZ4UWxna00yU05BNWFFblFUYm1Dak01N3pYZ1VVdTloejVEeHpBakVMLVg3VDFZYU9icGhaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T16:06:59+00:00</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="n"/>
+      <c r="I300" s="2" t="n"/>
+      <c r="J300" s="2" t="n"/>
+      <c r="K300" s="2" t="n"/>
+      <c r="L300" s="2" t="n"/>
+      <c r="M300" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N300" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O300" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>robotics AI</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>Zalando Expands Robotics Arsenal to Returns - WWD</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>WWD</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPY1E2UUZoWS1SSkVjQnEtTmdiWVhDT1diN19HeVUxVmJUUnd3VXRpaExiZTNqZmxvdnJQQmUtd2gxSzJuVngxUXY4dk5uNjhzS3VTTVpEanUxUlBmMXhrUVZaYURSREVvbGE0cEJ0S3l1ZFVEZXNYN1NobTl6LWNYeXZfMF9wdTdRbkVrQXd2MHRwSG1lWlNmSDFjbXJEemt4RXJsTjZsb0k1RWlmQU50bVMwQ0dHeEp0cjdKclBkVmFJdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T13:02:20+00:00</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="n"/>
+      <c r="I301" s="2" t="n"/>
+      <c r="J301" s="2" t="n"/>
+      <c r="K301" s="2" t="n"/>
+      <c r="L301" s="2" t="n"/>
+      <c r="M301" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N301" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O301" s="2" t="inlineStr">
+        <is>
+          <t>researched</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13793,7 +16443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14598,6 +17248,88 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Google Cloud Gemini Agent for Workplace</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లోకి కొత్త AI కొలీగ్ వచ్చేసింది!</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లో రేపు కొత్త కొలీగ్ చేరబోతున్నారు, కానీ అతను మనిషి కాదు, ఒక ఏఐ ఏజెంట్!</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNWjF6SjVJTks2WEluZXBwbGtRZEQtNGpZTWNXLVBrRHlCMVNhNlVRb2JDT1NsWlNHekZ6d3NQU3ZmcnNzazE4bF9hNXY1QmNNRENTcFFWNzlicXoxN25CMHhob0dMOUJ2UmluQVl3X1Fic1BZS0lIcXI4U2JuMElvZlhVTnNiYzkxb1BLaDhOTXdpdkNQeGc?oc=5
+https://news.google.com/rss/articles/CBMitgFBVV95cUxNdHRCcmswdDdvTlZsUDhJbFhleExnakFlYXVHaXFlMUZoWW1tQlcxOWdaV3dzeVJselRwUmx6SzlTNlJKdlhLa09tY0FBTnkyaUcwWk9KY01YVHZ1aVYtMHpma3lzUThwZUhkQ1A1WkYxbndYUFdlZ0ZXUm1uTFFteE51VS0xd3dSQXNPZnFtMXMzcXlzdWdBelBZWHh3VFl0SzJJeXRYUVZfTF9MdGdNLWViQmdRUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Google Cloud Gemini Agent for Workplace</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లోకి కొత్త AI కొలీగ్ వచ్చేసింది!</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లో రేపు కొత్త కొలీగ్ చేరబోతున్నారు, కానీ అతను మనిషి కాదు, ఒక ఏఐ ఏజెంట్!</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>See research.json and source links</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNWjF6SjVJTks2WEluZXBwbGtRZEQtNGpZTWNXLVBrRHlCMVNhNlVRb2JDT1NsWlNHekZ6d3NQU3ZmcnNzazE4bF9hNXY1QmNNRENTcFFWNzlicXoxN25CMHhob0dMOUJ2UmluQVl3X1Fic1BZS0lIcXI4U2JuMElvZlhVTnNiYzkxb1BLaDhOTXdpdkNQeGc?oc=5
+https://news.google.com/rss/articles/CBMitgFBVV95cUxNdHRCcmswdDdvTlZsUDhJbFhleExnakFlYXVHaXFlMUZoWW1tQlcxOWdaV3dzeVJselRwUmx6SzlTNlJKdlhLa09tY0FBTnkyaUcwWk9KY01YVHZ1aVYtMHpma3lzUThwZUhkQ1A1WkYxbndYUFdlZ0ZXUm1uTFFteE51VS0xd3dSQXNPZnFtMXMzcXlzdWdBelBZWHh3VFl0SzJJeXRYUVZfTF9MdGdNLWViQmdRUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14610,7 +17342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15327,6 +18059,80 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లోకి కొత్త AI కొలీగ్ వచ్చేసింది!</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లో రేపు కొత్త కొలీగ్ చేరబోతున్నారు, కానీ అతను మనిషి కాదు, ఒక ఏఐ ఏజెంట్! అవును, గూగుల్ క్లౌడ్ తాజాగా ఆఫీస్ వర్క్‌ప్లేస్ కోసం ప్రత్యేకమైన Gemini Agent ను అధికారికంగా ప్రవేశపెట్టింది. ఇందులో అత్యంత ఆసక్తికరమైన విషయం ఏమిటంటే, ఈ ఏఐ ఏజెంట్‌కు మనలాగే ప్రత్యేకమైన ఆఫీస్ ఈమెయిల్ అడ్రస్ లభిస్తుంది. అంటే సహోద్యోగులు నేరుగా దీనికి ఈమెయిల్స్ పంపవచ్చు, రిపోర్టులు తయారు చేయించవచ్చు, పనులు అప్పగించవచ్చు. ఇప్పటిదాకా మనం చాట్‌బాట్‌లతో కేవలం చాట్ చేశాం, కానీ ఈ ఏజెంట్లు స్వయంగా నిర్ణయాలు తీసుకుంటూ పనులను పూర్తి చేస్తాయి. సంస్థల్లోని అంతర్గత డేటాను పరిశీలించి, క్లౌడ్ ఇన్‌ఫ్రాస్ట్రక్చర్ సాయంతో వ్యాపార ప్రక్రియలను చాలా వేగవంతం చేస్తుంది. రిపీటెడ్ ఆఫీస్ పనులన్నీ ఏఐ తీసుకుంటే, ఉద్యోగులు మరింత క్రియేటివ్ పనులపై దృష్టి పెట్టే అవకాశం దక్కుతుంది. ఏఐ మనల్ని రీప్లేస్ చేయడం కాదు, ఇలాంటి ఏఐ ఏజెంట్‌లను మన పనిలో ఎలా వాడుకోవాలో నేర్చుకోవడమే అసలైన భవిష్యత్తు!</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>A sharp 9:16 vertical YouTube Short. Dynamic smooth motion graphics mixed with cinematic workplace b-roll. Clean modern typography with Telugu burned-in subtitles positioned centrally. Upbeat modern lo-fi tech background music. Smooth camera pans and cuts matching the Telugu narration cadence, concluding with a branded takeaway screen.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ క్లౌడ్ ఆఫీస్ పనుల కోసం ప్రత్యేకంగా Gemini Agent ని విడుదల చేసింది. దీనికి సొంత ఈమెయిల్ అడ్రస్ కూడా ఉంటుంది! ఇది పని విధానాన్ని ఎలా మార్చబోతోందో తెలుసుకోండి. #AI #Gemini #GoogleCloud #TeluguTech</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>#AI #GoogleGemini #Technology #TeluguTech #తెలుగు</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లోకి కొత్త AI కొలీగ్ వచ్చేసింది!</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లో రేపు కొత్త కొలీగ్ చేరబోతున్నారు, కానీ అతను మనిషి కాదు, ఒక ఏఐ ఏజెంట్! అవును, గూగుల్ క్లౌడ్ తాజాగా ఆఫీస్ వర్క్‌ప్లేస్ కోసం ప్రత్యేకమైన Gemini Agent ను అధికారికంగా ప్రవేశపెట్టింది. ఇందులో అత్యంత ఆసక్తికరమైన విషయం ఏమిటంటే, ఈ ఏఐ ఏజెంట్‌కు మనలాగే ప్రత్యేకమైన ఆఫీస్ ఈమెయిల్ అడ్రస్ లభిస్తుంది. అంటే సహోద్యోగులు నేరుగా దీనికి ఈమెయిల్స్ పంపవచ్చు, రిపోర్టులు తయారు చేయించవచ్చు, పనులు అప్పగించవచ్చు. ఇప్పటిదాకా మనం చాట్‌బాట్‌లతో కేవలం చాట్ చేశాం, కానీ ఈ ఏజెంట్లు స్వయంగా నిర్ణయాలు తీసుకుంటూ పనులను పూర్తి చేస్తాయి. సంస్థల్లోని అంతర్గత డేటాను పరిశీలించి, క్లౌడ్ ఇన్‌ఫ్రాస్ట్రక్చర్ సాయంతో వ్యాపార ప్రక్రియలను చాలా వేగవంతం చేస్తుంది. రిపీటెడ్ ఆఫీస్ పనులన్నీ ఏఐ తీసుకుంటే, ఉద్యోగులు మరింత క్రియేటివ్ పనులపై దృష్టి పెట్టే అవకాశం దక్కుతుంది. ఏఐ మనల్ని రీప్లేస్ చేయడం కాదు, ఇలాంటి ఏఐ ఏజెంట్‌లను మన పనిలో ఎలా వాడుకోవాలో నేర్చుకోవడమే అసలైన భవిష్యత్తు!</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>A sharp 9:16 vertical YouTube Short. Dynamic smooth motion graphics mixed with cinematic workplace b-roll. Clean modern typography with Telugu burned-in subtitles positioned centrally. Upbeat modern lo-fi tech background music. Smooth camera pans and cuts matching the Telugu narration cadence, concluding with a branded takeaway screen.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>గూగుల్ క్లౌడ్ ఆఫీస్ పనుల కోసం ప్రత్యేకంగా Gemini Agent ని విడుదల చేసింది. దీనికి సొంత ఈమెయిల్ అడ్రస్ కూడా ఉంటుంది! ఇది పని విధానాన్ని ఎలా మార్చబోతోందో తెలుసుకోండి. #AI #Gemini #GoogleCloud #TeluguTech</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>#AI #GoogleGemini #Technology #TeluguTech #తెలుగు</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>rendered</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15339,7 +18145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15619,6 +18425,33 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>మీ ఆఫీస్‌లోకి కొత్త AI కొలీగ్ వచ్చేసింది!</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>opHdCgPyMWE</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=opHdCgPyMWE</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>uploaded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
